--- a/Dados/table_PROD_RS_1_aux.xlsx
+++ b/Dados/table_PROD_RS_1_aux.xlsx
@@ -35826,37 +35826,37 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Atividades imobiliárias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Outras atividades de serviços</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Comércio</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Transporte, armazenagem e correio</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Informação e comunicação</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Atividades financeiras, de seguros e serviços relacionados</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -35900,25 +35900,25 @@
         <v>43199401906.9819</v>
       </c>
       <c r="H2">
+        <v>15316593214.1339</v>
+      </c>
+      <c r="I2">
+        <v>4703160222.37389</v>
+      </c>
+      <c r="J2">
+        <v>2519849282.60328</v>
+      </c>
+      <c r="K2">
+        <v>7976394529.13378</v>
+      </c>
+      <c r="L2">
         <v>9538258941.28175</v>
       </c>
-      <c r="I2">
+      <c r="M2">
         <v>21637904319.2024</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <v>20610812519.6039</v>
-      </c>
-      <c r="K2">
-        <v>15316593214.1339</v>
-      </c>
-      <c r="L2">
-        <v>4703160222.37389</v>
-      </c>
-      <c r="M2">
-        <v>2519849282.60328</v>
-      </c>
-      <c r="N2">
-        <v>7976394529.13378</v>
       </c>
       <c r="O2">
         <v>81717538568.4857</v>
@@ -35955,25 +35955,25 @@
         <v>42263627587.7646</v>
       </c>
       <c r="H3">
+        <v>15694304105.9122</v>
+      </c>
+      <c r="I3">
+        <v>4701872693.85616</v>
+      </c>
+      <c r="J3">
+        <v>2605987716.95201</v>
+      </c>
+      <c r="K3">
+        <v>8096203216.95811</v>
+      </c>
+      <c r="L3">
         <v>9663803596.20792</v>
       </c>
-      <c r="I3">
+      <c r="M3">
         <v>21729200146.9817</v>
       </c>
-      <c r="J3">
+      <c r="N3">
         <v>20692251495.1667</v>
-      </c>
-      <c r="K3">
-        <v>15694304105.9122</v>
-      </c>
-      <c r="L3">
-        <v>4701872693.85616</v>
-      </c>
-      <c r="M3">
-        <v>2605987716.95201</v>
-      </c>
-      <c r="N3">
-        <v>8096203216.95811</v>
       </c>
       <c r="O3">
         <v>82688402442.9198</v>
@@ -36010,25 +36010,25 @@
         <v>42594941683.1918</v>
       </c>
       <c r="H4">
+        <v>15970384104.7076</v>
+      </c>
+      <c r="I4">
+        <v>4683614115.20828</v>
+      </c>
+      <c r="J4">
+        <v>2678797983.11668</v>
+      </c>
+      <c r="K4">
+        <v>8222341265.81326</v>
+      </c>
+      <c r="L4">
         <v>9799492661.20715</v>
       </c>
-      <c r="I4">
+      <c r="M4">
         <v>21885014176.843</v>
       </c>
-      <c r="J4">
+      <c r="N4">
         <v>20591612529.2767</v>
-      </c>
-      <c r="K4">
-        <v>15970384104.7076</v>
-      </c>
-      <c r="L4">
-        <v>4683614115.20828</v>
-      </c>
-      <c r="M4">
-        <v>2678797983.11668</v>
-      </c>
-      <c r="N4">
-        <v>8222341265.81326</v>
       </c>
       <c r="O4">
         <v>83486833277.067</v>
@@ -36065,25 +36065,25 @@
         <v>43742892429.1802</v>
       </c>
       <c r="H5">
+        <v>16083281687.6211</v>
+      </c>
+      <c r="I5">
+        <v>4743760546.40374</v>
+      </c>
+      <c r="J5">
+        <v>2716316790.78848</v>
+      </c>
+      <c r="K5">
+        <v>8332972389.75673</v>
+      </c>
+      <c r="L5">
         <v>9936937720.831921</v>
       </c>
-      <c r="I5">
+      <c r="M5">
         <v>22225720498.311</v>
       </c>
-      <c r="J5">
+      <c r="N5">
         <v>20569950400.929</v>
-      </c>
-      <c r="K5">
-        <v>16083281687.6211</v>
-      </c>
-      <c r="L5">
-        <v>4743760546.40374</v>
-      </c>
-      <c r="M5">
-        <v>2716316790.78848</v>
-      </c>
-      <c r="N5">
-        <v>8332972389.75673</v>
       </c>
       <c r="O5">
         <v>84355144841.46021</v>
@@ -36120,25 +36120,25 @@
         <v>44041702617.7666</v>
       </c>
       <c r="H6">
+        <v>16387820029.2169</v>
+      </c>
+      <c r="I6">
+        <v>4864241973.82787</v>
+      </c>
+      <c r="J6">
+        <v>2591164844.95821</v>
+      </c>
+      <c r="K6">
+        <v>8377876120.92691</v>
+      </c>
+      <c r="L6">
         <v>10083478908.2877</v>
       </c>
-      <c r="I6">
+      <c r="M6">
         <v>21925994422.0421</v>
       </c>
-      <c r="J6">
+      <c r="N6">
         <v>21115775371.6448</v>
-      </c>
-      <c r="K6">
-        <v>16387820029.2169</v>
-      </c>
-      <c r="L6">
-        <v>4864241973.82787</v>
-      </c>
-      <c r="M6">
-        <v>2591164844.95821</v>
-      </c>
-      <c r="N6">
-        <v>8377876120.92691</v>
       </c>
       <c r="O6">
         <v>84559182940.2363</v>
@@ -36175,25 +36175,25 @@
         <v>47170978869.2244</v>
       </c>
       <c r="H7">
+        <v>16805804395.0588</v>
+      </c>
+      <c r="I7">
+        <v>5040203110.7631</v>
+      </c>
+      <c r="J7">
+        <v>2633531938.38284</v>
+      </c>
+      <c r="K7">
+        <v>8708037702.83519</v>
+      </c>
+      <c r="L7">
         <v>10203437825.2783</v>
       </c>
-      <c r="I7">
+      <c r="M7">
         <v>22069911492.6956</v>
       </c>
-      <c r="J7">
+      <c r="N7">
         <v>21118232099.3516</v>
-      </c>
-      <c r="K7">
-        <v>16805804395.0588</v>
-      </c>
-      <c r="L7">
-        <v>5040203110.7631</v>
-      </c>
-      <c r="M7">
-        <v>2633531938.38284</v>
-      </c>
-      <c r="N7">
-        <v>8708037702.83519</v>
       </c>
       <c r="O7">
         <v>86322009362.7247</v>
@@ -36230,25 +36230,25 @@
         <v>47195638923.3109</v>
       </c>
       <c r="H8">
+        <v>16973453608.9339</v>
+      </c>
+      <c r="I8">
+        <v>5110916391.24264</v>
+      </c>
+      <c r="J8">
+        <v>2624723450.62496</v>
+      </c>
+      <c r="K8">
+        <v>8836472667.92844</v>
+      </c>
+      <c r="L8">
         <v>10285327578.4554</v>
       </c>
-      <c r="I8">
+      <c r="M8">
         <v>22522720233.5737</v>
       </c>
-      <c r="J8">
+      <c r="N8">
         <v>21185969288.3836</v>
-      </c>
-      <c r="K8">
-        <v>16973453608.9339</v>
-      </c>
-      <c r="L8">
-        <v>5110916391.24264</v>
-      </c>
-      <c r="M8">
-        <v>2624723450.62496</v>
-      </c>
-      <c r="N8">
-        <v>8836472667.92844</v>
       </c>
       <c r="O8">
         <v>87231047587.7065</v>
@@ -36285,25 +36285,25 @@
         <v>45884369181.811</v>
       </c>
       <c r="H9">
+        <v>17224984907.5322</v>
+      </c>
+      <c r="I9">
+        <v>5124882243.63813</v>
+      </c>
+      <c r="J9">
+        <v>2658820598.51952</v>
+      </c>
+      <c r="K9">
+        <v>8674423271.441561</v>
+      </c>
+      <c r="L9">
         <v>10329693826.9641</v>
       </c>
-      <c r="I9">
+      <c r="M9">
         <v>22698761992.1064</v>
       </c>
-      <c r="J9">
+      <c r="N9">
         <v>21245738731.8264</v>
-      </c>
-      <c r="K9">
-        <v>17224984907.5322</v>
-      </c>
-      <c r="L9">
-        <v>5124882243.63813</v>
-      </c>
-      <c r="M9">
-        <v>2658820598.51952</v>
-      </c>
-      <c r="N9">
-        <v>8674423271.441561</v>
       </c>
       <c r="O9">
         <v>87764964734.4601</v>
@@ -36340,25 +36340,25 @@
         <v>45436731149.1208</v>
       </c>
       <c r="H10">
+        <v>17518180131.6082</v>
+      </c>
+      <c r="I10">
+        <v>5044076305.82777</v>
+      </c>
+      <c r="J10">
+        <v>2692172521.42857</v>
+      </c>
+      <c r="K10">
+        <v>8885828074.704149</v>
+      </c>
+      <c r="L10">
         <v>10334050783.582</v>
       </c>
-      <c r="I10">
+      <c r="M10">
         <v>22902954799.4512</v>
       </c>
-      <c r="J10">
+      <c r="N10">
         <v>21135013987.3901</v>
-      </c>
-      <c r="K10">
-        <v>17518180131.6082</v>
-      </c>
-      <c r="L10">
-        <v>5044076305.82777</v>
-      </c>
-      <c r="M10">
-        <v>2692172521.42857</v>
-      </c>
-      <c r="N10">
-        <v>8885828074.704149</v>
       </c>
       <c r="O10">
         <v>88079832330.6297</v>
@@ -36395,25 +36395,25 @@
         <v>44081212039.163</v>
       </c>
       <c r="H11">
+        <v>16927931275.9169</v>
+      </c>
+      <c r="I11">
+        <v>5019103915.06112</v>
+      </c>
+      <c r="J11">
+        <v>2721507718.75588</v>
+      </c>
+      <c r="K11">
+        <v>8736297919.255131</v>
+      </c>
+      <c r="L11">
         <v>10325543416.3758</v>
       </c>
-      <c r="I11">
+      <c r="M11">
         <v>23001585041.3092</v>
       </c>
-      <c r="J11">
+      <c r="N11">
         <v>21067194719.9714</v>
-      </c>
-      <c r="K11">
-        <v>16927931275.9169</v>
-      </c>
-      <c r="L11">
-        <v>5019103915.06112</v>
-      </c>
-      <c r="M11">
-        <v>2721507718.75588</v>
-      </c>
-      <c r="N11">
-        <v>8736297919.255131</v>
       </c>
       <c r="O11">
         <v>87363305976.5291</v>
@@ -36450,25 +36450,25 @@
         <v>44003317616.1232</v>
       </c>
       <c r="H12">
+        <v>17298946752.7678</v>
+      </c>
+      <c r="I12">
+        <v>4984164658.46456</v>
+      </c>
+      <c r="J12">
+        <v>2744793465.95978</v>
+      </c>
+      <c r="K12">
+        <v>8674600793.55636</v>
+      </c>
+      <c r="L12">
         <v>10310366619.7596</v>
       </c>
-      <c r="I12">
+      <c r="M12">
         <v>22993589956.0241</v>
       </c>
-      <c r="J12">
+      <c r="N12">
         <v>21040936909.1485</v>
-      </c>
-      <c r="K12">
-        <v>17298946752.7678</v>
-      </c>
-      <c r="L12">
-        <v>4984164658.46456</v>
-      </c>
-      <c r="M12">
-        <v>2744793465.95978</v>
-      </c>
-      <c r="N12">
-        <v>8674600793.55636</v>
       </c>
       <c r="O12">
         <v>87855950403.1554</v>
@@ -36505,25 +36505,25 @@
         <v>43321143780.7336</v>
       </c>
       <c r="H13">
+        <v>17252406531.1063</v>
+      </c>
+      <c r="I13">
+        <v>4929043858.77935</v>
+      </c>
+      <c r="J13">
+        <v>2728902613.50618</v>
+      </c>
+      <c r="K13">
+        <v>8623560747.638309</v>
+      </c>
+      <c r="L13">
         <v>10282945159.6187</v>
       </c>
-      <c r="I13">
+      <c r="M13">
         <v>22990907072.8069</v>
       </c>
-      <c r="J13">
+      <c r="N13">
         <v>20981303779.9297</v>
-      </c>
-      <c r="K13">
-        <v>17252406531.1063</v>
-      </c>
-      <c r="L13">
-        <v>4929043858.77935</v>
-      </c>
-      <c r="M13">
-        <v>2728902613.50618</v>
-      </c>
-      <c r="N13">
-        <v>8623560747.638309</v>
       </c>
       <c r="O13">
         <v>87525292417.5704</v>
@@ -36560,25 +36560,25 @@
         <v>40947432874.4171</v>
       </c>
       <c r="H14">
+        <v>16454130317.3393</v>
+      </c>
+      <c r="I14">
+        <v>4935503450.24764</v>
+      </c>
+      <c r="J14">
+        <v>2674966419.92549</v>
+      </c>
+      <c r="K14">
+        <v>8633077354.236589</v>
+      </c>
+      <c r="L14">
         <v>10239726954.334</v>
       </c>
-      <c r="I14">
+      <c r="M14">
         <v>22749254267.8258</v>
       </c>
-      <c r="J14">
+      <c r="N14">
         <v>21193601558.4642</v>
-      </c>
-      <c r="K14">
-        <v>16454130317.3393</v>
-      </c>
-      <c r="L14">
-        <v>4935503450.24764</v>
-      </c>
-      <c r="M14">
-        <v>2674966419.92549</v>
-      </c>
-      <c r="N14">
-        <v>8633077354.236589</v>
       </c>
       <c r="O14">
         <v>86334106576.853</v>
@@ -36615,25 +36615,25 @@
         <v>39961182978.3699</v>
       </c>
       <c r="H15">
+        <v>15857383322.6256</v>
+      </c>
+      <c r="I15">
+        <v>4720009984.45291</v>
+      </c>
+      <c r="J15">
+        <v>2613806563.94995</v>
+      </c>
+      <c r="K15">
+        <v>8480833670.96434</v>
+      </c>
+      <c r="L15">
         <v>10213768122.7248</v>
       </c>
-      <c r="I15">
+      <c r="M15">
         <v>22487256964.8625</v>
       </c>
-      <c r="J15">
+      <c r="N15">
         <v>20933105450.6365</v>
-      </c>
-      <c r="K15">
-        <v>15857383322.6256</v>
-      </c>
-      <c r="L15">
-        <v>4720009984.45291</v>
-      </c>
-      <c r="M15">
-        <v>2613806563.94995</v>
-      </c>
-      <c r="N15">
-        <v>8480833670.96434</v>
       </c>
       <c r="O15">
         <v>84863213800.65559</v>
@@ -36670,25 +36670,25 @@
         <v>39060205375.7791</v>
       </c>
       <c r="H16">
+        <v>15242666048.3559</v>
+      </c>
+      <c r="I16">
+        <v>4682514904.95143</v>
+      </c>
+      <c r="J16">
+        <v>2563687343.96314</v>
+      </c>
+      <c r="K16">
+        <v>8403529565.45538</v>
+      </c>
+      <c r="L16">
         <v>10203906309.5677</v>
       </c>
-      <c r="I16">
+      <c r="M16">
         <v>21935375517.1847</v>
       </c>
-      <c r="J16">
+      <c r="N16">
         <v>20927780865.095</v>
-      </c>
-      <c r="K16">
-        <v>15242666048.3559</v>
-      </c>
-      <c r="L16">
-        <v>4682514904.95143</v>
-      </c>
-      <c r="M16">
-        <v>2563687343.96314</v>
-      </c>
-      <c r="N16">
-        <v>8403529565.45538</v>
       </c>
       <c r="O16">
         <v>83484425857.6707</v>
@@ -36725,25 +36725,25 @@
         <v>37855778454.1207</v>
       </c>
       <c r="H17">
+        <v>14981958691.3252</v>
+      </c>
+      <c r="I17">
+        <v>4577156171.61499</v>
+      </c>
+      <c r="J17">
+        <v>2511047148.70201</v>
+      </c>
+      <c r="K17">
+        <v>8441966083.97593</v>
+      </c>
+      <c r="L17">
         <v>10221109874.5979</v>
       </c>
-      <c r="I17">
+      <c r="M17">
         <v>22133021968.9496</v>
       </c>
-      <c r="J17">
+      <c r="N17">
         <v>20857190476.263</v>
-      </c>
-      <c r="K17">
-        <v>14981958691.3252</v>
-      </c>
-      <c r="L17">
-        <v>4577156171.61499</v>
-      </c>
-      <c r="M17">
-        <v>2511047148.70201</v>
-      </c>
-      <c r="N17">
-        <v>8441966083.97593</v>
       </c>
       <c r="O17">
         <v>83103033042.6239</v>
@@ -36780,25 +36780,25 @@
         <v>38544560473.5281</v>
       </c>
       <c r="H18">
+        <v>14992480424.0613</v>
+      </c>
+      <c r="I18">
+        <v>4489791043.59869</v>
+      </c>
+      <c r="J18">
+        <v>2507920804.89544</v>
+      </c>
+      <c r="K18">
+        <v>8317155538.27416</v>
+      </c>
+      <c r="L18">
         <v>10257993138.4741</v>
       </c>
-      <c r="I18">
+      <c r="M18">
         <v>22298182521.3335</v>
       </c>
-      <c r="J18">
+      <c r="N18">
         <v>20831497120.1147</v>
-      </c>
-      <c r="K18">
-        <v>14992480424.0613</v>
-      </c>
-      <c r="L18">
-        <v>4489791043.59869</v>
-      </c>
-      <c r="M18">
-        <v>2507920804.89544</v>
-      </c>
-      <c r="N18">
-        <v>8317155538.27416</v>
       </c>
       <c r="O18">
         <v>83109177967.92</v>
@@ -36835,25 +36835,25 @@
         <v>38322507901.8415</v>
       </c>
       <c r="H19">
+        <v>14891624944.4494</v>
+      </c>
+      <c r="I19">
+        <v>4647778007.0852</v>
+      </c>
+      <c r="J19">
+        <v>2525065266.1502</v>
+      </c>
+      <c r="K19">
+        <v>8286934653.92688</v>
+      </c>
+      <c r="L19">
         <v>10290072256.4503</v>
       </c>
-      <c r="I19">
+      <c r="M19">
         <v>22339810223.1178</v>
       </c>
-      <c r="J19">
+      <c r="N19">
         <v>20947936805.6968</v>
-      </c>
-      <c r="K19">
-        <v>14891624944.4494</v>
-      </c>
-      <c r="L19">
-        <v>4647778007.0852</v>
-      </c>
-      <c r="M19">
-        <v>2525065266.1502</v>
-      </c>
-      <c r="N19">
-        <v>8286934653.92688</v>
       </c>
       <c r="O19">
         <v>83446825081.7899</v>
@@ -36890,25 +36890,25 @@
         <v>37103377275.3857</v>
       </c>
       <c r="H20">
+        <v>14755969127.4312</v>
+      </c>
+      <c r="I20">
+        <v>4484551565.80258</v>
+      </c>
+      <c r="J20">
+        <v>2552104501.9636</v>
+      </c>
+      <c r="K20">
+        <v>8277389406.05354</v>
+      </c>
+      <c r="L20">
         <v>10312931318.1303</v>
       </c>
-      <c r="I20">
+      <c r="M20">
         <v>22353476028.0224</v>
       </c>
-      <c r="J20">
+      <c r="N20">
         <v>20882246692.4294</v>
-      </c>
-      <c r="K20">
-        <v>14755969127.4312</v>
-      </c>
-      <c r="L20">
-        <v>4484551565.80258</v>
-      </c>
-      <c r="M20">
-        <v>2552104501.9636</v>
-      </c>
-      <c r="N20">
-        <v>8277389406.05354</v>
       </c>
       <c r="O20">
         <v>83027945512.6118</v>
@@ -36945,25 +36945,25 @@
         <v>37819474730.8516</v>
       </c>
       <c r="H21">
+        <v>14579541697.7053</v>
+      </c>
+      <c r="I21">
+        <v>4495936549.41892</v>
+      </c>
+      <c r="J21">
+        <v>2584429576.14072</v>
+      </c>
+      <c r="K21">
+        <v>8132700216.40484</v>
+      </c>
+      <c r="L21">
         <v>10346683963.1464</v>
       </c>
-      <c r="I21">
+      <c r="M21">
         <v>22130797403.024</v>
       </c>
-      <c r="J21">
+      <c r="N21">
         <v>21003477455.3285</v>
-      </c>
-      <c r="K21">
-        <v>14579541697.7053</v>
-      </c>
-      <c r="L21">
-        <v>4495936549.41892</v>
-      </c>
-      <c r="M21">
-        <v>2584429576.14072</v>
-      </c>
-      <c r="N21">
-        <v>8132700216.40484</v>
       </c>
       <c r="O21">
         <v>82652754478.9285</v>
@@ -37000,25 +37000,25 @@
         <v>37721390239.9751</v>
       </c>
       <c r="H22">
+        <v>15006843277.2396</v>
+      </c>
+      <c r="I22">
+        <v>4519663498.34328</v>
+      </c>
+      <c r="J22">
+        <v>2667204907.0611</v>
+      </c>
+      <c r="K22">
+        <v>8198863765.2143</v>
+      </c>
+      <c r="L22">
         <v>10390171518.6878</v>
       </c>
-      <c r="I22">
+      <c r="M22">
         <v>22039654043.6175</v>
       </c>
-      <c r="J22">
+      <c r="N22">
         <v>20885816027.311</v>
-      </c>
-      <c r="K22">
-        <v>15006843277.2396</v>
-      </c>
-      <c r="L22">
-        <v>4519663498.34328</v>
-      </c>
-      <c r="M22">
-        <v>2667204907.0611</v>
-      </c>
-      <c r="N22">
-        <v>8198863765.2143</v>
       </c>
       <c r="O22">
         <v>83182992418.4371</v>
@@ -37055,25 +37055,25 @@
         <v>38151306435.2274</v>
       </c>
       <c r="H23">
+        <v>15408042243.8532</v>
+      </c>
+      <c r="I23">
+        <v>4526114959.84871</v>
+      </c>
+      <c r="J23">
+        <v>2700159863.03425</v>
+      </c>
+      <c r="K23">
+        <v>8430720264.93073</v>
+      </c>
+      <c r="L23">
         <v>10429491997.9723</v>
       </c>
-      <c r="I23">
+      <c r="M23">
         <v>22199096992.2953</v>
       </c>
-      <c r="J23">
+      <c r="N23">
         <v>20979172870.6552</v>
-      </c>
-      <c r="K23">
-        <v>15408042243.8532</v>
-      </c>
-      <c r="L23">
-        <v>4526114959.84871</v>
-      </c>
-      <c r="M23">
-        <v>2700159863.03425</v>
-      </c>
-      <c r="N23">
-        <v>8430720264.93073</v>
       </c>
       <c r="O23">
         <v>84124726987.7876</v>
@@ -37110,25 +37110,25 @@
         <v>36309614385.8755</v>
       </c>
       <c r="H24">
+        <v>15991445615.1568</v>
+      </c>
+      <c r="I24">
+        <v>4536172550.69409</v>
+      </c>
+      <c r="J24">
+        <v>2680196872.71491</v>
+      </c>
+      <c r="K24">
+        <v>8275012334.32132</v>
+      </c>
+      <c r="L24">
         <v>10472127607.508</v>
       </c>
-      <c r="I24">
+      <c r="M24">
         <v>22422566466.4915</v>
       </c>
-      <c r="J24">
+      <c r="N24">
         <v>20948203446.5053</v>
-      </c>
-      <c r="K24">
-        <v>15991445615.1568</v>
-      </c>
-      <c r="L24">
-        <v>4536172550.69409</v>
-      </c>
-      <c r="M24">
-        <v>2680196872.71491</v>
-      </c>
-      <c r="N24">
-        <v>8275012334.32132</v>
       </c>
       <c r="O24">
         <v>84987526608.72729</v>
@@ -37165,25 +37165,25 @@
         <v>36956135229.2673</v>
       </c>
       <c r="H25">
+        <v>16292570263.5549</v>
+      </c>
+      <c r="I25">
+        <v>4558261978.02639</v>
+      </c>
+      <c r="J25">
+        <v>2709056096.866</v>
+      </c>
+      <c r="K25">
+        <v>8596118319.004101</v>
+      </c>
+      <c r="L25">
         <v>10503691376.6239</v>
       </c>
-      <c r="I25">
+      <c r="M25">
         <v>22284476897.0167</v>
       </c>
-      <c r="J25">
+      <c r="N25">
         <v>20768506887.5304</v>
-      </c>
-      <c r="K25">
-        <v>16292570263.5549</v>
-      </c>
-      <c r="L25">
-        <v>4558261978.02639</v>
-      </c>
-      <c r="M25">
-        <v>2709056096.866</v>
-      </c>
-      <c r="N25">
-        <v>8596118319.004101</v>
       </c>
       <c r="O25">
         <v>85478190315.12531</v>
@@ -37220,25 +37220,25 @@
         <v>37296232840.1469</v>
       </c>
       <c r="H26">
+        <v>16331765866.2069</v>
+      </c>
+      <c r="I26">
+        <v>4596650537.71228</v>
+      </c>
+      <c r="J26">
+        <v>2666358665.29645</v>
+      </c>
+      <c r="K26">
+        <v>8688246648.226101</v>
+      </c>
+      <c r="L26">
         <v>10532563220.2553</v>
       </c>
-      <c r="I26">
+      <c r="M26">
         <v>22811474644.7297</v>
       </c>
-      <c r="J26">
+      <c r="N26">
         <v>20831310633.0773</v>
-      </c>
-      <c r="K26">
-        <v>16331765866.2069</v>
-      </c>
-      <c r="L26">
-        <v>4596650537.71228</v>
-      </c>
-      <c r="M26">
-        <v>2666358665.29645</v>
-      </c>
-      <c r="N26">
-        <v>8688246648.226101</v>
       </c>
       <c r="O26">
         <v>86006243336.62691</v>
@@ -37275,25 +37275,25 @@
         <v>37044410511.6796</v>
       </c>
       <c r="H27">
+        <v>16088960425.6355</v>
+      </c>
+      <c r="I27">
+        <v>4553487905.89859</v>
+      </c>
+      <c r="J27">
+        <v>2668655656.07434</v>
+      </c>
+      <c r="K27">
+        <v>8844636959.834881</v>
+      </c>
+      <c r="L27">
         <v>10601470074.982</v>
       </c>
-      <c r="I27">
+      <c r="M27">
         <v>22985683235.1844</v>
       </c>
-      <c r="J27">
+      <c r="N27">
         <v>20716272144.035</v>
-      </c>
-      <c r="K27">
-        <v>16088960425.6355</v>
-      </c>
-      <c r="L27">
-        <v>4553487905.89859</v>
-      </c>
-      <c r="M27">
-        <v>2668655656.07434</v>
-      </c>
-      <c r="N27">
-        <v>8844636959.834881</v>
       </c>
       <c r="O27">
         <v>86190317016.7123</v>
@@ -37330,25 +37330,25 @@
         <v>39355247387.1708</v>
       </c>
       <c r="H28">
+        <v>16644014966.5173</v>
+      </c>
+      <c r="I28">
+        <v>4651589764.36949</v>
+      </c>
+      <c r="J28">
+        <v>2792001050.93428</v>
+      </c>
+      <c r="K28">
+        <v>8822713299.79147</v>
+      </c>
+      <c r="L28">
         <v>10685033065.721</v>
       </c>
-      <c r="I28">
+      <c r="M28">
         <v>23163782080.16</v>
       </c>
-      <c r="J28">
+      <c r="N28">
         <v>20743961440.1672</v>
-      </c>
-      <c r="K28">
-        <v>16644014966.5173</v>
-      </c>
-      <c r="L28">
-        <v>4651589764.36949</v>
-      </c>
-      <c r="M28">
-        <v>2792001050.93428</v>
-      </c>
-      <c r="N28">
-        <v>8822713299.79147</v>
       </c>
       <c r="O28">
         <v>87182757570.6508</v>
@@ -37385,25 +37385,25 @@
         <v>39519609571.2612</v>
       </c>
       <c r="H29">
+        <v>16483465825.204</v>
+      </c>
+      <c r="I29">
+        <v>4659472825.62443</v>
+      </c>
+      <c r="J29">
+        <v>2711348021.37419</v>
+      </c>
+      <c r="K29">
+        <v>8840183601.56769</v>
+      </c>
+      <c r="L29">
         <v>10789292506.5036</v>
       </c>
-      <c r="I29">
+      <c r="M29">
         <v>22863780726.1245</v>
       </c>
-      <c r="J29">
+      <c r="N29">
         <v>20674243190.8786</v>
-      </c>
-      <c r="K29">
-        <v>16483465825.204</v>
-      </c>
-      <c r="L29">
-        <v>4659472825.62443</v>
-      </c>
-      <c r="M29">
-        <v>2711348021.37419</v>
-      </c>
-      <c r="N29">
-        <v>8840183601.56769</v>
       </c>
       <c r="O29">
         <v>86777548540.1127</v>
@@ -37440,25 +37440,25 @@
         <v>38846626152.1777</v>
       </c>
       <c r="H30">
+        <v>16716410859.2604</v>
+      </c>
+      <c r="I30">
+        <v>4669926293.11286</v>
+      </c>
+      <c r="J30">
+        <v>2839524035.21092</v>
+      </c>
+      <c r="K30">
+        <v>8948758491.051081</v>
+      </c>
+      <c r="L30">
         <v>10917013633.4893</v>
       </c>
-      <c r="I30">
+      <c r="M30">
         <v>23085968592.7774</v>
       </c>
-      <c r="J30">
+      <c r="N30">
         <v>20620439040.6757</v>
-      </c>
-      <c r="K30">
-        <v>16716410859.2604</v>
-      </c>
-      <c r="L30">
-        <v>4669926293.11286</v>
-      </c>
-      <c r="M30">
-        <v>2839524035.21092</v>
-      </c>
-      <c r="N30">
-        <v>8948758491.051081</v>
       </c>
       <c r="O30">
         <v>87653360774.5634</v>
@@ -37495,25 +37495,25 @@
         <v>39268560466.1938</v>
       </c>
       <c r="H31">
+        <v>16434999096.2502</v>
+      </c>
+      <c r="I31">
+        <v>4680934618.42904</v>
+      </c>
+      <c r="J31">
+        <v>2905133818.94026</v>
+      </c>
+      <c r="K31">
+        <v>8977908371.385189</v>
+      </c>
+      <c r="L31">
         <v>11023190505.6792</v>
       </c>
-      <c r="I31">
+      <c r="M31">
         <v>22945598635.4608</v>
       </c>
-      <c r="J31">
+      <c r="N31">
         <v>20457784504.8945</v>
-      </c>
-      <c r="K31">
-        <v>16434999096.2502</v>
-      </c>
-      <c r="L31">
-        <v>4680934618.42904</v>
-      </c>
-      <c r="M31">
-        <v>2905133818.94026</v>
-      </c>
-      <c r="N31">
-        <v>8977908371.385189</v>
       </c>
       <c r="O31">
         <v>87109425373.4424</v>
@@ -37550,25 +37550,25 @@
         <v>38120419631.7465</v>
       </c>
       <c r="H32">
+        <v>16364096322.3645</v>
+      </c>
+      <c r="I32">
+        <v>4553245994.07657</v>
+      </c>
+      <c r="J32">
+        <v>2871294377.30655</v>
+      </c>
+      <c r="K32">
+        <v>9075425613.58202</v>
+      </c>
+      <c r="L32">
         <v>11089072346.3222</v>
       </c>
-      <c r="I32">
+      <c r="M32">
         <v>22720531946.238</v>
       </c>
-      <c r="J32">
+      <c r="N32">
         <v>20654066890.1229</v>
-      </c>
-      <c r="K32">
-        <v>16364096322.3645</v>
-      </c>
-      <c r="L32">
-        <v>4553245994.07657</v>
-      </c>
-      <c r="M32">
-        <v>2871294377.30655</v>
-      </c>
-      <c r="N32">
-        <v>9075425613.58202</v>
       </c>
       <c r="O32">
         <v>86914378451.2357</v>
@@ -37605,25 +37605,25 @@
         <v>37262307508.6776</v>
       </c>
       <c r="H33">
+        <v>16460532843.0099</v>
+      </c>
+      <c r="I33">
+        <v>4333066763.50554</v>
+      </c>
+      <c r="J33">
+        <v>2905424952.04323</v>
+      </c>
+      <c r="K33">
+        <v>9488649107.363159</v>
+      </c>
+      <c r="L33">
         <v>11106227914.6126</v>
       </c>
-      <c r="I33">
+      <c r="M33">
         <v>22872586580.3281</v>
       </c>
-      <c r="J33">
+      <c r="N33">
         <v>20204071381.2537</v>
-      </c>
-      <c r="K33">
-        <v>16460532843.0099</v>
-      </c>
-      <c r="L33">
-        <v>4333066763.50554</v>
-      </c>
-      <c r="M33">
-        <v>2905424952.04323</v>
-      </c>
-      <c r="N33">
-        <v>9488649107.363159</v>
       </c>
       <c r="O33">
         <v>87081068945.7513</v>
@@ -37660,25 +37660,25 @@
         <v>36538493371.9167</v>
       </c>
       <c r="H34">
+        <v>16516996206.9811</v>
+      </c>
+      <c r="I34">
+        <v>4070301692.42733</v>
+      </c>
+      <c r="J34">
+        <v>2870440022.89601</v>
+      </c>
+      <c r="K34">
+        <v>9142726540.986259</v>
+      </c>
+      <c r="L34">
         <v>11109026858.5307</v>
       </c>
-      <c r="I34">
+      <c r="M34">
         <v>22336297567.9562</v>
       </c>
-      <c r="J34">
+      <c r="N34">
         <v>19931026655.7031</v>
-      </c>
-      <c r="K34">
-        <v>16516996206.9811</v>
-      </c>
-      <c r="L34">
-        <v>4070301692.42733</v>
-      </c>
-      <c r="M34">
-        <v>2870440022.89601</v>
-      </c>
-      <c r="N34">
-        <v>9142726540.986259</v>
       </c>
       <c r="O34">
         <v>85997629491.10989</v>
@@ -37715,25 +37715,25 @@
         <v>31309767880.9595</v>
       </c>
       <c r="H35">
+        <v>14501786648.6509</v>
+      </c>
+      <c r="I35">
+        <v>3781273974.45553</v>
+      </c>
+      <c r="J35">
+        <v>2802669410.89049</v>
+      </c>
+      <c r="K35">
+        <v>9462011261.375521</v>
+      </c>
+      <c r="L35">
         <v>11129891907.0902</v>
       </c>
-      <c r="I35">
+      <c r="M35">
         <v>18788244087.0369</v>
       </c>
-      <c r="J35">
+      <c r="N35">
         <v>19157350079.4975</v>
-      </c>
-      <c r="K35">
-        <v>14501786648.6509</v>
-      </c>
-      <c r="L35">
-        <v>3781273974.45553</v>
-      </c>
-      <c r="M35">
-        <v>2802669410.89049</v>
-      </c>
-      <c r="N35">
-        <v>9462011261.375521</v>
       </c>
       <c r="O35">
         <v>78919563984.7065</v>
@@ -37770,25 +37770,25 @@
         <v>37673417794.9166</v>
       </c>
       <c r="H36">
+        <v>15661960522.5565</v>
+      </c>
+      <c r="I36">
+        <v>3711107663.51172</v>
+      </c>
+      <c r="J36">
+        <v>2850458834.82638</v>
+      </c>
+      <c r="K36">
+        <v>9460301609.233589</v>
+      </c>
+      <c r="L36">
         <v>11185408380.3049</v>
       </c>
-      <c r="I36">
+      <c r="M36">
         <v>20566590370.1122</v>
       </c>
-      <c r="J36">
+      <c r="N36">
         <v>19171169696.1883</v>
-      </c>
-      <c r="K36">
-        <v>15661960522.5565</v>
-      </c>
-      <c r="L36">
-        <v>3711107663.51172</v>
-      </c>
-      <c r="M36">
-        <v>2850458834.82638</v>
-      </c>
-      <c r="N36">
-        <v>9460301609.233589</v>
       </c>
       <c r="O36">
         <v>81950387271.149</v>
@@ -37825,25 +37825,25 @@
         <v>38553705039.772</v>
       </c>
       <c r="H37">
+        <v>16128816842.2442</v>
+      </c>
+      <c r="I37">
+        <v>3742670878.48951</v>
+      </c>
+      <c r="J37">
+        <v>2997085227.64058</v>
+      </c>
+      <c r="K37">
+        <v>9229220193.23604</v>
+      </c>
+      <c r="L37">
         <v>11263042759.2762</v>
       </c>
-      <c r="I37">
+      <c r="M37">
         <v>21751767294.7486</v>
       </c>
-      <c r="J37">
+      <c r="N37">
         <v>19384664674.9489</v>
-      </c>
-      <c r="K37">
-        <v>16128816842.2442</v>
-      </c>
-      <c r="L37">
-        <v>3742670878.48951</v>
-      </c>
-      <c r="M37">
-        <v>2997085227.64058</v>
-      </c>
-      <c r="N37">
-        <v>9229220193.23604</v>
       </c>
       <c r="O37">
         <v>84241628228.7377</v>
@@ -37880,25 +37880,25 @@
         <v>39844130028.5635</v>
       </c>
       <c r="H38">
+        <v>16212121270.644</v>
+      </c>
+      <c r="I38">
+        <v>3895905043.89328</v>
+      </c>
+      <c r="J38">
+        <v>3184495240.76273</v>
+      </c>
+      <c r="K38">
+        <v>8947449561.451441</v>
+      </c>
+      <c r="L38">
         <v>11348207707.8446</v>
       </c>
-      <c r="I38">
+      <c r="M38">
         <v>22250760126.5828</v>
       </c>
-      <c r="J38">
+      <c r="N38">
         <v>19625954838.9971</v>
-      </c>
-      <c r="K38">
-        <v>16212121270.644</v>
-      </c>
-      <c r="L38">
-        <v>3895905043.89328</v>
-      </c>
-      <c r="M38">
-        <v>3184495240.76273</v>
-      </c>
-      <c r="N38">
-        <v>8947449561.451441</v>
       </c>
       <c r="O38">
         <v>85346569811.6451</v>
@@ -37935,25 +37935,25 @@
         <v>39021410482.0663</v>
       </c>
       <c r="H39">
+        <v>16879137383.1723</v>
+      </c>
+      <c r="I39">
+        <v>4125274704.30886</v>
+      </c>
+      <c r="J39">
+        <v>3334232142.26467</v>
+      </c>
+      <c r="K39">
+        <v>8659757827.49095</v>
+      </c>
+      <c r="L39">
         <v>11415422436.0395</v>
       </c>
-      <c r="I39">
+      <c r="M39">
         <v>22375879629.6624</v>
       </c>
-      <c r="J39">
+      <c r="N39">
         <v>19702927552.6727</v>
-      </c>
-      <c r="K39">
-        <v>16879137383.1723</v>
-      </c>
-      <c r="L39">
-        <v>4125274704.30886</v>
-      </c>
-      <c r="M39">
-        <v>3334232142.26467</v>
-      </c>
-      <c r="N39">
-        <v>8659757827.49095</v>
       </c>
       <c r="O39">
         <v>86421024655.8989</v>
@@ -37990,25 +37990,25 @@
         <v>38086417890.3394</v>
       </c>
       <c r="H40">
+        <v>16300100958.1976</v>
+      </c>
+      <c r="I40">
+        <v>4165576784.24676</v>
+      </c>
+      <c r="J40">
+        <v>3403734978.91631</v>
+      </c>
+      <c r="K40">
+        <v>8556088118.93976</v>
+      </c>
+      <c r="L40">
         <v>11455897029.9023</v>
       </c>
-      <c r="I40">
+      <c r="M40">
         <v>23241514648.8427</v>
       </c>
-      <c r="J40">
+      <c r="N40">
         <v>19762025886.43</v>
-      </c>
-      <c r="K40">
-        <v>16300100958.1976</v>
-      </c>
-      <c r="L40">
-        <v>4165576784.24676</v>
-      </c>
-      <c r="M40">
-        <v>3403734978.91631</v>
-      </c>
-      <c r="N40">
-        <v>8556088118.93976</v>
       </c>
       <c r="O40">
         <v>86813592157.0181</v>
@@ -38045,25 +38045,25 @@
         <v>38874239591.2064</v>
       </c>
       <c r="H41">
+        <v>16804660985.3399</v>
+      </c>
+      <c r="I41">
+        <v>4196206589.085</v>
+      </c>
+      <c r="J41">
+        <v>3390770253.25002</v>
+      </c>
+      <c r="K41">
+        <v>8498313115.41213</v>
+      </c>
+      <c r="L41">
         <v>11491428364.6026</v>
       </c>
-      <c r="I41">
+      <c r="M41">
         <v>22996386393.2226</v>
       </c>
-      <c r="J41">
+      <c r="N41">
         <v>19836648944.8678</v>
-      </c>
-      <c r="K41">
-        <v>16804660985.3399</v>
-      </c>
-      <c r="L41">
-        <v>4196206589.085</v>
-      </c>
-      <c r="M41">
-        <v>3390770253.25002</v>
-      </c>
-      <c r="N41">
-        <v>8498313115.41213</v>
       </c>
       <c r="O41">
         <v>87280378199.597</v>
@@ -38100,25 +38100,25 @@
         <v>39946436264.9087</v>
       </c>
       <c r="H42">
+        <v>16836549902.6491</v>
+      </c>
+      <c r="I42">
+        <v>4198453119.3828</v>
+      </c>
+      <c r="J42">
+        <v>3387580867.08791</v>
+      </c>
+      <c r="K42">
+        <v>8484560283.87672</v>
+      </c>
+      <c r="L42">
         <v>11486995882.6103</v>
       </c>
-      <c r="I42">
+      <c r="M42">
         <v>24049767532.1187</v>
       </c>
-      <c r="J42">
+      <c r="N42">
         <v>19923042210.4915</v>
-      </c>
-      <c r="K42">
-        <v>16836549902.6491</v>
-      </c>
-      <c r="L42">
-        <v>4198453119.3828</v>
-      </c>
-      <c r="M42">
-        <v>3387580867.08791</v>
-      </c>
-      <c r="N42">
-        <v>8484560283.87672</v>
       </c>
       <c r="O42">
         <v>88444310442.6703</v>
@@ -38155,25 +38155,25 @@
         <v>40095109833.4805</v>
       </c>
       <c r="H43">
+        <v>17893729796.7542</v>
+      </c>
+      <c r="I43">
+        <v>4213015879.04514</v>
+      </c>
+      <c r="J43">
+        <v>3417881274.08712</v>
+      </c>
+      <c r="K43">
+        <v>8446185872.07238</v>
+      </c>
+      <c r="L43">
         <v>11486543050.1117</v>
       </c>
-      <c r="I43">
+      <c r="M43">
         <v>24721802862.1976</v>
       </c>
-      <c r="J43">
+      <c r="N43">
         <v>19998989917.6721</v>
-      </c>
-      <c r="K43">
-        <v>17893729796.7542</v>
-      </c>
-      <c r="L43">
-        <v>4213015879.04514</v>
-      </c>
-      <c r="M43">
-        <v>3417881274.08712</v>
-      </c>
-      <c r="N43">
-        <v>8446185872.07238</v>
       </c>
       <c r="O43">
         <v>90139301429.9744</v>
@@ -38210,25 +38210,25 @@
         <v>39880682030.7434</v>
       </c>
       <c r="H44">
+        <v>17649716891.5821</v>
+      </c>
+      <c r="I44">
+        <v>4313606905.58071</v>
+      </c>
+      <c r="J44">
+        <v>3476714582.58496</v>
+      </c>
+      <c r="K44">
+        <v>8597531782.49139</v>
+      </c>
+      <c r="L44">
         <v>11504569366.3328</v>
       </c>
-      <c r="I44">
+      <c r="M44">
         <v>25309945784.3195</v>
       </c>
-      <c r="J44">
+      <c r="N44">
         <v>20120177923.3834</v>
-      </c>
-      <c r="K44">
-        <v>17649716891.5821</v>
-      </c>
-      <c r="L44">
-        <v>4313606905.58071</v>
-      </c>
-      <c r="M44">
-        <v>3476714582.58496</v>
-      </c>
-      <c r="N44">
-        <v>8597531782.49139</v>
       </c>
       <c r="O44">
         <v>91076931565.4875</v>
@@ -38265,25 +38265,25 @@
         <v>38701628671.9106</v>
       </c>
       <c r="H45">
+        <v>17615268447.1406</v>
+      </c>
+      <c r="I45">
+        <v>4466561993.57207</v>
+      </c>
+      <c r="J45">
+        <v>3436942398.727</v>
+      </c>
+      <c r="K45">
+        <v>8795718796.565889</v>
+      </c>
+      <c r="L45">
         <v>11527773053.1136</v>
       </c>
-      <c r="I45">
+      <c r="M45">
         <v>25403467375.8416</v>
       </c>
-      <c r="J45">
+      <c r="N45">
         <v>20155888618.5801</v>
-      </c>
-      <c r="K45">
-        <v>17615268447.1406</v>
-      </c>
-      <c r="L45">
-        <v>4466561993.57207</v>
-      </c>
-      <c r="M45">
-        <v>3436942398.727</v>
-      </c>
-      <c r="N45">
-        <v>8795718796.565889</v>
       </c>
       <c r="O45">
         <v>91480493954.98669</v>
@@ -38320,25 +38320,25 @@
         <v>37229522172.2534</v>
       </c>
       <c r="H46">
+        <v>17615415546.9997</v>
+      </c>
+      <c r="I46">
+        <v>4362915874.52258</v>
+      </c>
+      <c r="J46">
+        <v>3466990615.90116</v>
+      </c>
+      <c r="K46">
+        <v>9014847228.6625</v>
+      </c>
+      <c r="L46">
         <v>11533644795.7426</v>
       </c>
-      <c r="I46">
+      <c r="M46">
         <v>25349698843.4362</v>
       </c>
-      <c r="J46">
+      <c r="N46">
         <v>20169460818.2007</v>
-      </c>
-      <c r="K46">
-        <v>17615415546.9997</v>
-      </c>
-      <c r="L46">
-        <v>4362915874.52258</v>
-      </c>
-      <c r="M46">
-        <v>3466990615.90116</v>
-      </c>
-      <c r="N46">
-        <v>9014847228.6625</v>
       </c>
       <c r="O46">
         <v>91572826620.3372</v>
@@ -38375,25 +38375,25 @@
         <v>37764495698.7335</v>
       </c>
       <c r="H47">
+        <v>17685195606.981</v>
+      </c>
+      <c r="I47">
+        <v>4430734531.63524</v>
+      </c>
+      <c r="J47">
+        <v>3527439530.55041</v>
+      </c>
+      <c r="K47">
+        <v>9117854902.4744</v>
+      </c>
+      <c r="L47">
         <v>11544009098.359</v>
       </c>
-      <c r="I47">
+      <c r="M47">
         <v>25758651839.0223</v>
       </c>
-      <c r="J47">
+      <c r="N47">
         <v>20158950930.3218</v>
-      </c>
-      <c r="K47">
-        <v>17685195606.981</v>
-      </c>
-      <c r="L47">
-        <v>4430734531.63524</v>
-      </c>
-      <c r="M47">
-        <v>3527439530.55041</v>
-      </c>
-      <c r="N47">
-        <v>9117854902.4744</v>
       </c>
       <c r="O47">
         <v>92009163284.384</v>
@@ -38430,25 +38430,25 @@
         <v>37913109090.8656</v>
       </c>
       <c r="H48">
+        <v>17910512055.6602</v>
+      </c>
+      <c r="I48">
+        <v>4435793342.29306</v>
+      </c>
+      <c r="J48">
+        <v>3601322681.73007</v>
+      </c>
+      <c r="K48">
+        <v>9230613220.665239</v>
+      </c>
+      <c r="L48">
         <v>11566089712.5125</v>
       </c>
-      <c r="I48">
+      <c r="M48">
         <v>25977343905.9283</v>
       </c>
-      <c r="J48">
+      <c r="N48">
         <v>20082984096.8</v>
-      </c>
-      <c r="K48">
-        <v>17910512055.6602</v>
-      </c>
-      <c r="L48">
-        <v>4435793342.29306</v>
-      </c>
-      <c r="M48">
-        <v>3601322681.73007</v>
-      </c>
-      <c r="N48">
-        <v>9230613220.665239</v>
       </c>
       <c r="O48">
         <v>92898188651.7513</v>
@@ -38485,25 +38485,25 @@
         <v>38130207747.5252</v>
       </c>
       <c r="H49">
+        <v>17737018878.541</v>
+      </c>
+      <c r="I49">
+        <v>4411922655.81543</v>
+      </c>
+      <c r="J49">
+        <v>3648744335.05682</v>
+      </c>
+      <c r="K49">
+        <v>9219720236.8377</v>
+      </c>
+      <c r="L49">
         <v>11589687852.1962</v>
       </c>
-      <c r="I49">
+      <c r="M49">
         <v>26318019733.336</v>
       </c>
-      <c r="J49">
+      <c r="N49">
         <v>20041604008.6974</v>
-      </c>
-      <c r="K49">
-        <v>17737018878.541</v>
-      </c>
-      <c r="L49">
-        <v>4411922655.81543</v>
-      </c>
-      <c r="M49">
-        <v>3648744335.05682</v>
-      </c>
-      <c r="N49">
-        <v>9219720236.8377</v>
       </c>
       <c r="O49">
         <v>92988483637.13361</v>
@@ -38540,25 +38540,25 @@
         <v>38086472027.9596</v>
       </c>
       <c r="H50">
+        <v>18229754877.7629</v>
+      </c>
+      <c r="I50">
+        <v>4474348266.84258</v>
+      </c>
+      <c r="J50">
+        <v>3653847709.57713</v>
+      </c>
+      <c r="K50">
+        <v>9208680478.128</v>
+      </c>
+      <c r="L50">
         <v>11675976865.0657</v>
       </c>
-      <c r="I50">
+      <c r="M50">
         <v>26614134875.5875</v>
       </c>
-      <c r="J50">
+      <c r="N50">
         <v>20044439892.7608</v>
-      </c>
-      <c r="K50">
-        <v>18229754877.7629</v>
-      </c>
-      <c r="L50">
-        <v>4474348266.84258</v>
-      </c>
-      <c r="M50">
-        <v>3653847709.57713</v>
-      </c>
-      <c r="N50">
-        <v>9208680478.128</v>
       </c>
       <c r="O50">
         <v>94017796680.1012</v>
@@ -38595,25 +38595,25 @@
         <v>37371034933.1985</v>
       </c>
       <c r="H51">
+        <v>18612003860.9628</v>
+      </c>
+      <c r="I51">
+        <v>4387859601.61591</v>
+      </c>
+      <c r="J51">
+        <v>3638105832.5265</v>
+      </c>
+      <c r="K51">
+        <v>9400181680.0606</v>
+      </c>
+      <c r="L51">
         <v>11601813523.9181</v>
       </c>
-      <c r="I51">
+      <c r="M51">
         <v>26620736688.6798</v>
       </c>
-      <c r="J51">
+      <c r="N51">
         <v>20029594122.4979</v>
-      </c>
-      <c r="K51">
-        <v>18612003860.9628</v>
-      </c>
-      <c r="L51">
-        <v>4387859601.61591</v>
-      </c>
-      <c r="M51">
-        <v>3638105832.5265</v>
-      </c>
-      <c r="N51">
-        <v>9400181680.0606</v>
       </c>
       <c r="O51">
         <v>94264341436.716</v>
@@ -38650,25 +38650,25 @@
         <v>37844242358.3256</v>
       </c>
       <c r="H52">
+        <v>19348044785.5172</v>
+      </c>
+      <c r="I52">
+        <v>4578701311.83594</v>
+      </c>
+      <c r="J52">
+        <v>3761390066.03693</v>
+      </c>
+      <c r="K52">
+        <v>9630669133.754709</v>
+      </c>
+      <c r="L52">
         <v>11739411829.1986</v>
       </c>
-      <c r="I52">
+      <c r="M52">
         <v>27126346342.528</v>
       </c>
-      <c r="J52">
+      <c r="N52">
         <v>20184049033.6941</v>
-      </c>
-      <c r="K52">
-        <v>19348044785.5172</v>
-      </c>
-      <c r="L52">
-        <v>4578701311.83594</v>
-      </c>
-      <c r="M52">
-        <v>3761390066.03693</v>
-      </c>
-      <c r="N52">
-        <v>9630669133.754709</v>
       </c>
       <c r="O52">
         <v>96366817255.62891</v>
@@ -38705,25 +38705,25 @@
         <v>38294065085.3422</v>
       </c>
       <c r="H53">
+        <v>19455122155.544</v>
+      </c>
+      <c r="I53">
+        <v>4694535826.03497</v>
+      </c>
+      <c r="J53">
+        <v>3708810750.72259</v>
+      </c>
+      <c r="K53">
+        <v>9650471732.18354</v>
+      </c>
+      <c r="L53">
         <v>11809492216.2097</v>
       </c>
-      <c r="I53">
+      <c r="M53">
         <v>27220227960.2153</v>
       </c>
-      <c r="J53">
+      <c r="N53">
         <v>20192081868.8307</v>
-      </c>
-      <c r="K53">
-        <v>19455122155.544</v>
-      </c>
-      <c r="L53">
-        <v>4694535826.03497</v>
-      </c>
-      <c r="M53">
-        <v>3708810750.72259</v>
-      </c>
-      <c r="N53">
-        <v>9650471732.18354</v>
       </c>
       <c r="O53">
         <v>96796011907.6626</v>
@@ -38760,25 +38760,25 @@
         <v>38147886043.0979</v>
       </c>
       <c r="H54">
+        <v>19365512784.7047</v>
+      </c>
+      <c r="I54">
+        <v>4692989942.09887</v>
+      </c>
+      <c r="J54">
+        <v>3706394744.59867</v>
+      </c>
+      <c r="K54">
+        <v>9741500703.62949</v>
+      </c>
+      <c r="L54">
         <v>11825353131.2843</v>
       </c>
-      <c r="I54">
+      <c r="M54">
         <v>27208872452.8426</v>
       </c>
-      <c r="J54">
+      <c r="N54">
         <v>20191477900.7335</v>
-      </c>
-      <c r="K54">
-        <v>19365512784.7047</v>
-      </c>
-      <c r="L54">
-        <v>4692989942.09887</v>
-      </c>
-      <c r="M54">
-        <v>3706394744.59867</v>
-      </c>
-      <c r="N54">
-        <v>9741500703.62949</v>
       </c>
       <c r="O54">
         <v>96788536810.3286</v>
@@ -38815,25 +38815,25 @@
         <v>38173260655.8321</v>
       </c>
       <c r="H55">
+        <v>19144856654.6507</v>
+      </c>
+      <c r="I55">
+        <v>4682245428.99319</v>
+      </c>
+      <c r="J55">
+        <v>3711983446.35107</v>
+      </c>
+      <c r="K55">
+        <v>9857532869.925619</v>
+      </c>
+      <c r="L55">
         <v>11882512589.1015</v>
       </c>
-      <c r="I55">
+      <c r="M55">
         <v>27510176512.3855</v>
       </c>
-      <c r="J55">
+      <c r="N55">
         <v>20207686127.1859</v>
-      </c>
-      <c r="K55">
-        <v>19144856654.6507</v>
-      </c>
-      <c r="L55">
-        <v>4682245428.99319</v>
-      </c>
-      <c r="M55">
-        <v>3711983446.35107</v>
-      </c>
-      <c r="N55">
-        <v>9857532869.925619</v>
       </c>
       <c r="O55">
         <v>96821645587.62061</v>
@@ -38870,25 +38870,25 @@
         <v>39307650977.3642</v>
       </c>
       <c r="H56">
+        <v>19253340053.2755</v>
+      </c>
+      <c r="I56">
+        <v>4622430954.44475</v>
+      </c>
+      <c r="J56">
+        <v>3701362331.93427</v>
+      </c>
+      <c r="K56">
+        <v>9708166012.954691</v>
+      </c>
+      <c r="L56">
         <v>11942926573.5902</v>
       </c>
-      <c r="I56">
+      <c r="M56">
         <v>27606093820.1094</v>
       </c>
-      <c r="J56">
+      <c r="N56">
         <v>20207320735.8156</v>
-      </c>
-      <c r="K56">
-        <v>19253340053.2755</v>
-      </c>
-      <c r="L56">
-        <v>4622430954.44475</v>
-      </c>
-      <c r="M56">
-        <v>3701362331.93427</v>
-      </c>
-      <c r="N56">
-        <v>9708166012.954691</v>
       </c>
       <c r="O56">
         <v>97040179775.69189</v>
@@ -38948,37 +38948,37 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Atividades imobiliárias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Outras atividades de serviços</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Comércio</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Transporte, armazenagem e correio</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Informação e comunicação</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Atividades financeiras, de seguros e serviços relacionados</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -39022,25 +39022,25 @@
         <v>1370719.24683369</v>
       </c>
       <c r="H2">
+        <v>972069.277443459</v>
+      </c>
+      <c r="I2">
+        <v>272821.082158779</v>
+      </c>
+      <c r="J2">
+        <v>64438.089983114</v>
+      </c>
+      <c r="K2">
+        <v>78490.7348175345</v>
+      </c>
+      <c r="L2">
         <v>27920.3848120125</v>
       </c>
-      <c r="I2">
+      <c r="M2">
         <v>1525161.07912863</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <v>555684.899430809</v>
-      </c>
-      <c r="K2">
-        <v>972069.277443459</v>
-      </c>
-      <c r="L2">
-        <v>272821.082158779</v>
-      </c>
-      <c r="M2">
-        <v>64438.089983114</v>
-      </c>
-      <c r="N2">
-        <v>78490.7348175345</v>
       </c>
       <c r="O2">
         <v>3515139.77430754</v>
@@ -39077,25 +39077,25 @@
         <v>1461459.6797196</v>
       </c>
       <c r="H3">
+        <v>987002.628935878</v>
+      </c>
+      <c r="I3">
+        <v>269561.465450385</v>
+      </c>
+      <c r="J3">
+        <v>64487.1258724745</v>
+      </c>
+      <c r="K3">
+        <v>85904.25890052191</v>
+      </c>
+      <c r="L3">
         <v>32886.1699704179</v>
       </c>
-      <c r="I3">
+      <c r="M3">
         <v>1472832.91287487</v>
       </c>
-      <c r="J3">
+      <c r="N3">
         <v>575604.3331852379</v>
-      </c>
-      <c r="K3">
-        <v>987002.628935878</v>
-      </c>
-      <c r="L3">
-        <v>269561.465450385</v>
-      </c>
-      <c r="M3">
-        <v>64487.1258724745</v>
-      </c>
-      <c r="N3">
-        <v>85904.25890052191</v>
       </c>
       <c r="O3">
         <v>3475107.51021124</v>
@@ -39132,25 +39132,25 @@
         <v>1408600.36156835</v>
       </c>
       <c r="H4">
+        <v>1007322.12404922</v>
+      </c>
+      <c r="I4">
+        <v>288310.382620275</v>
+      </c>
+      <c r="J4">
+        <v>71208.4632320302</v>
+      </c>
+      <c r="K4">
+        <v>85541.24523606031</v>
+      </c>
+      <c r="L4">
         <v>40954.2841453051</v>
       </c>
-      <c r="I4">
+      <c r="M4">
         <v>1459339.67747368</v>
       </c>
-      <c r="J4">
+      <c r="N4">
         <v>587708.287780617</v>
-      </c>
-      <c r="K4">
-        <v>1007322.12404922</v>
-      </c>
-      <c r="L4">
-        <v>288310.382620275</v>
-      </c>
-      <c r="M4">
-        <v>71208.4632320302</v>
-      </c>
-      <c r="N4">
-        <v>85541.24523606031</v>
       </c>
       <c r="O4">
         <v>3535881.85464181</v>
@@ -39187,25 +39187,25 @@
         <v>1407907.09127427</v>
       </c>
       <c r="H5">
+        <v>1012843.28490066</v>
+      </c>
+      <c r="I5">
+        <v>297152.523235929</v>
+      </c>
+      <c r="J5">
+        <v>68737.4506425663</v>
+      </c>
+      <c r="K5">
+        <v>85712.1637901358</v>
+      </c>
+      <c r="L5">
         <v>44856.7654527075</v>
       </c>
-      <c r="I5">
+      <c r="M5">
         <v>1441881.77819205</v>
       </c>
-      <c r="J5">
+      <c r="N5">
         <v>591147.975118464</v>
-      </c>
-      <c r="K5">
-        <v>1012843.28490066</v>
-      </c>
-      <c r="L5">
-        <v>297152.523235929</v>
-      </c>
-      <c r="M5">
-        <v>68737.4506425663</v>
-      </c>
-      <c r="N5">
-        <v>85712.1637901358</v>
       </c>
       <c r="O5">
         <v>3553378.63968397</v>
@@ -39242,25 +39242,25 @@
         <v>1429805.28066471</v>
       </c>
       <c r="H6">
+        <v>1021725.66726023</v>
+      </c>
+      <c r="I6">
+        <v>299112.00519471</v>
+      </c>
+      <c r="J6">
+        <v>67030.7090235941</v>
+      </c>
+      <c r="K6">
+        <v>87574.6591093786</v>
+      </c>
+      <c r="L6">
         <v>48440.7912627418</v>
       </c>
-      <c r="I6">
+      <c r="M6">
         <v>1431231.88880954</v>
       </c>
-      <c r="J6">
+      <c r="N6">
         <v>623491.768524822</v>
-      </c>
-      <c r="K6">
-        <v>1021725.66726023</v>
-      </c>
-      <c r="L6">
-        <v>299112.00519471</v>
-      </c>
-      <c r="M6">
-        <v>67030.7090235941</v>
-      </c>
-      <c r="N6">
-        <v>87574.6591093786</v>
       </c>
       <c r="O6">
         <v>3583473.31808183</v>
@@ -39297,25 +39297,25 @@
         <v>1460680.55675465</v>
       </c>
       <c r="H7">
+        <v>1058422.8737414</v>
+      </c>
+      <c r="I7">
+        <v>299025.446183449</v>
+      </c>
+      <c r="J7">
+        <v>65068.381752496</v>
+      </c>
+      <c r="K7">
+        <v>89228.8453889198</v>
+      </c>
+      <c r="L7">
         <v>53991.6614419768</v>
       </c>
-      <c r="I7">
+      <c r="M7">
         <v>1452315.62541315</v>
       </c>
-      <c r="J7">
+      <c r="N7">
         <v>651772.778867689</v>
-      </c>
-      <c r="K7">
-        <v>1058422.8737414</v>
-      </c>
-      <c r="L7">
-        <v>299025.446183449</v>
-      </c>
-      <c r="M7">
-        <v>65068.381752496</v>
-      </c>
-      <c r="N7">
-        <v>89228.8453889198</v>
       </c>
       <c r="O7">
         <v>3660238.74251788</v>
@@ -39352,25 +39352,25 @@
         <v>1453738.66551139</v>
       </c>
       <c r="H8">
+        <v>1091699.1742325</v>
+      </c>
+      <c r="I8">
+        <v>293665.385321726</v>
+      </c>
+      <c r="J8">
+        <v>63882.529593545</v>
+      </c>
+      <c r="K8">
+        <v>89224.0838540348</v>
+      </c>
+      <c r="L8">
         <v>57239.6425379982</v>
       </c>
-      <c r="I8">
+      <c r="M8">
         <v>1498314.7486088</v>
       </c>
-      <c r="J8">
+      <c r="N8">
         <v>624687.414991624</v>
-      </c>
-      <c r="K8">
-        <v>1091699.1742325</v>
-      </c>
-      <c r="L8">
-        <v>293665.385321726</v>
-      </c>
-      <c r="M8">
-        <v>63882.529593545</v>
-      </c>
-      <c r="N8">
-        <v>89224.0838540348</v>
       </c>
       <c r="O8">
         <v>3717016.51147063</v>
@@ -39407,25 +39407,25 @@
         <v>1408352.98530785</v>
       </c>
       <c r="H9">
+        <v>1107277.85678913</v>
+      </c>
+      <c r="I9">
+        <v>284203.117467996</v>
+      </c>
+      <c r="J9">
+        <v>66308.802656078</v>
+      </c>
+      <c r="K9">
+        <v>84081.2396186175</v>
+      </c>
+      <c r="L9">
         <v>41948.2978793317</v>
       </c>
-      <c r="I9">
+      <c r="M9">
         <v>1529548.94689472</v>
       </c>
-      <c r="J9">
+      <c r="N9">
         <v>619171.995942908</v>
-      </c>
-      <c r="K9">
-        <v>1107277.85678913</v>
-      </c>
-      <c r="L9">
-        <v>284203.117467996</v>
-      </c>
-      <c r="M9">
-        <v>66308.802656078</v>
-      </c>
-      <c r="N9">
-        <v>84081.2396186175</v>
       </c>
       <c r="O9">
         <v>3741838.4745219</v>
@@ -39462,25 +39462,25 @@
         <v>1437051.96721462</v>
       </c>
       <c r="H10">
+        <v>1095823.4740465</v>
+      </c>
+      <c r="I10">
+        <v>291341.572007881</v>
+      </c>
+      <c r="J10">
+        <v>73209.2096415843</v>
+      </c>
+      <c r="K10">
+        <v>78627.9213907683</v>
+      </c>
+      <c r="L10">
         <v>44030.5659344536</v>
       </c>
-      <c r="I10">
+      <c r="M10">
         <v>1518321.89677481</v>
       </c>
-      <c r="J10">
+      <c r="N10">
         <v>604433.3290542</v>
-      </c>
-      <c r="K10">
-        <v>1095823.4740465</v>
-      </c>
-      <c r="L10">
-        <v>291341.572007881</v>
-      </c>
-      <c r="M10">
-        <v>73209.2096415843</v>
-      </c>
-      <c r="N10">
-        <v>78627.9213907683</v>
       </c>
       <c r="O10">
         <v>3713814.98848633</v>
@@ -39517,25 +39517,25 @@
         <v>1416504.1597931</v>
       </c>
       <c r="H11">
+        <v>1070951.47937169</v>
+      </c>
+      <c r="I11">
+        <v>267442.136857593</v>
+      </c>
+      <c r="J11">
+        <v>65152.9791158961</v>
+      </c>
+      <c r="K11">
+        <v>78480.75234590771</v>
+      </c>
+      <c r="L11">
         <v>33895.0279701865</v>
       </c>
-      <c r="I11">
+      <c r="M11">
         <v>1624548.67639605</v>
       </c>
-      <c r="J11">
+      <c r="N11">
         <v>597502.474435712</v>
-      </c>
-      <c r="K11">
-        <v>1070951.47937169</v>
-      </c>
-      <c r="L11">
-        <v>267442.136857593</v>
-      </c>
-      <c r="M11">
-        <v>65152.9791158961</v>
-      </c>
-      <c r="N11">
-        <v>78480.75234590771</v>
       </c>
       <c r="O11">
         <v>3731994.70066533</v>
@@ -39572,25 +39572,25 @@
         <v>1404170.14492762</v>
       </c>
       <c r="H12">
+        <v>1050786.56285076</v>
+      </c>
+      <c r="I12">
+        <v>271402.890693015</v>
+      </c>
+      <c r="J12">
+        <v>70113.70530994239</v>
+      </c>
+      <c r="K12">
+        <v>87489.1550785796</v>
+      </c>
+      <c r="L12">
         <v>38008.8572442195</v>
       </c>
-      <c r="I12">
+      <c r="M12">
         <v>1607933.16957604</v>
       </c>
-      <c r="J12">
+      <c r="N12">
         <v>608773.314928366</v>
-      </c>
-      <c r="K12">
-        <v>1050786.56285076</v>
-      </c>
-      <c r="L12">
-        <v>271402.890693015</v>
-      </c>
-      <c r="M12">
-        <v>70113.70530994239</v>
-      </c>
-      <c r="N12">
-        <v>87489.1550785796</v>
       </c>
       <c r="O12">
         <v>3726922.9276544</v>
@@ -39627,25 +39627,25 @@
         <v>1396704.94845623</v>
       </c>
       <c r="H13">
+        <v>1051282.27817741</v>
+      </c>
+      <c r="I13">
+        <v>275637.402302365</v>
+      </c>
+      <c r="J13">
+        <v>72590.24092191469</v>
+      </c>
+      <c r="K13">
+        <v>79012.47920310291</v>
+      </c>
+      <c r="L13">
         <v>40761.2009568112</v>
       </c>
-      <c r="I13">
+      <c r="M13">
         <v>1617259.82889631</v>
       </c>
-      <c r="J13">
+      <c r="N13">
         <v>613126.096396353</v>
-      </c>
-      <c r="K13">
-        <v>1051282.27817741</v>
-      </c>
-      <c r="L13">
-        <v>275637.402302365</v>
-      </c>
-      <c r="M13">
-        <v>72590.24092191469</v>
-      </c>
-      <c r="N13">
-        <v>79012.47920310291</v>
       </c>
       <c r="O13">
         <v>3755467.27200701</v>
@@ -39682,25 +39682,25 @@
         <v>1382561.69563181</v>
       </c>
       <c r="H14">
+        <v>1074603.10560175</v>
+      </c>
+      <c r="I14">
+        <v>265191.062677161</v>
+      </c>
+      <c r="J14">
+        <v>71762.18463125439</v>
+      </c>
+      <c r="K14">
+        <v>89538.1042761162</v>
+      </c>
+      <c r="L14">
         <v>40289.7407790207</v>
       </c>
-      <c r="I14">
+      <c r="M14">
         <v>1626482.48662839</v>
       </c>
-      <c r="J14">
+      <c r="N14">
         <v>638164.904412706</v>
-      </c>
-      <c r="K14">
-        <v>1074603.10560175</v>
-      </c>
-      <c r="L14">
-        <v>265191.062677161</v>
-      </c>
-      <c r="M14">
-        <v>71762.18463125439</v>
-      </c>
-      <c r="N14">
-        <v>89538.1042761162</v>
       </c>
       <c r="O14">
         <v>3814031.5193984</v>
@@ -39737,25 +39737,25 @@
         <v>1374740.36209992</v>
       </c>
       <c r="H15">
+        <v>1081395.77829942</v>
+      </c>
+      <c r="I15">
+        <v>281949.203743122</v>
+      </c>
+      <c r="J15">
+        <v>84665.3642296305</v>
+      </c>
+      <c r="K15">
+        <v>84270.1784756027</v>
+      </c>
+      <c r="L15">
         <v>46013.8153466355</v>
       </c>
-      <c r="I15">
+      <c r="M15">
         <v>1633503.79885558</v>
       </c>
-      <c r="J15">
+      <c r="N15">
         <v>610765.870710721</v>
-      </c>
-      <c r="K15">
-        <v>1081395.77829942</v>
-      </c>
-      <c r="L15">
-        <v>281949.203743122</v>
-      </c>
-      <c r="M15">
-        <v>84665.3642296305</v>
-      </c>
-      <c r="N15">
-        <v>84270.1784756027</v>
       </c>
       <c r="O15">
         <v>3820003.65603485</v>
@@ -39792,25 +39792,25 @@
         <v>1383016.58637243</v>
       </c>
       <c r="H16">
+        <v>1073684.95624882</v>
+      </c>
+      <c r="I16">
+        <v>277076.803275779</v>
+      </c>
+      <c r="J16">
+        <v>80102.1123126595</v>
+      </c>
+      <c r="K16">
+        <v>76002.451476535</v>
+      </c>
+      <c r="L16">
         <v>36093.9295667928</v>
       </c>
-      <c r="I16">
+      <c r="M16">
         <v>1586659.41472698</v>
       </c>
-      <c r="J16">
+      <c r="N16">
         <v>625601.569720806</v>
-      </c>
-      <c r="K16">
-        <v>1073684.95624882</v>
-      </c>
-      <c r="L16">
-        <v>277076.803275779</v>
-      </c>
-      <c r="M16">
-        <v>80102.1123126595</v>
-      </c>
-      <c r="N16">
-        <v>76002.451476535</v>
       </c>
       <c r="O16">
         <v>3743337.0982225</v>
@@ -39847,25 +39847,25 @@
         <v>1380652.41698856</v>
       </c>
       <c r="H17">
+        <v>1079774.09847679</v>
+      </c>
+      <c r="I17">
+        <v>286883.976205563</v>
+      </c>
+      <c r="J17">
+        <v>86309.52464556829</v>
+      </c>
+      <c r="K17">
+        <v>78043.1498455559</v>
+      </c>
+      <c r="L17">
         <v>39009.4885467833</v>
       </c>
-      <c r="I17">
+      <c r="M17">
         <v>1591503.84076739</v>
       </c>
-      <c r="J17">
+      <c r="N17">
         <v>634769.234145086</v>
-      </c>
-      <c r="K17">
-        <v>1079774.09847679</v>
-      </c>
-      <c r="L17">
-        <v>286883.976205563</v>
-      </c>
-      <c r="M17">
-        <v>86309.52464556829</v>
-      </c>
-      <c r="N17">
-        <v>78043.1498455559</v>
       </c>
       <c r="O17">
         <v>3812193.36862001</v>
@@ -39902,25 +39902,25 @@
         <v>1379418.2002968</v>
       </c>
       <c r="H18">
+        <v>1030867.02131758</v>
+      </c>
+      <c r="I18">
+        <v>296185.465400032</v>
+      </c>
+      <c r="J18">
+        <v>58020.8828402193</v>
+      </c>
+      <c r="K18">
+        <v>84933.2421069298</v>
+      </c>
+      <c r="L18">
         <v>39775.4558339736</v>
       </c>
-      <c r="I18">
+      <c r="M18">
         <v>1590211.82416665</v>
       </c>
-      <c r="J18">
+      <c r="N18">
         <v>632127.253226926</v>
-      </c>
-      <c r="K18">
-        <v>1030867.02131758</v>
-      </c>
-      <c r="L18">
-        <v>296185.465400032</v>
-      </c>
-      <c r="M18">
-        <v>58020.8828402193</v>
-      </c>
-      <c r="N18">
-        <v>84933.2421069298</v>
       </c>
       <c r="O18">
         <v>3743482.8457819</v>
@@ -39957,25 +39957,25 @@
         <v>1345229.8290732</v>
       </c>
       <c r="H19">
+        <v>1008529.53642746</v>
+      </c>
+      <c r="I19">
+        <v>284204.71653871</v>
+      </c>
+      <c r="J19">
+        <v>63641.7009384057</v>
+      </c>
+      <c r="K19">
+        <v>86483.59974377661</v>
+      </c>
+      <c r="L19">
         <v>35184.408677233</v>
       </c>
-      <c r="I19">
+      <c r="M19">
         <v>1592437.60852074</v>
       </c>
-      <c r="J19">
+      <c r="N19">
         <v>635713.445370817</v>
-      </c>
-      <c r="K19">
-        <v>1008529.53642746</v>
-      </c>
-      <c r="L19">
-        <v>284204.71653871</v>
-      </c>
-      <c r="M19">
-        <v>63641.7009384057</v>
-      </c>
-      <c r="N19">
-        <v>86483.59974377661</v>
       </c>
       <c r="O19">
         <v>3703318.95103409</v>
@@ -40012,25 +40012,25 @@
         <v>1317736.02643704</v>
       </c>
       <c r="H20">
+        <v>1032764.24021678</v>
+      </c>
+      <c r="I20">
+        <v>281948.98510944</v>
+      </c>
+      <c r="J20">
+        <v>65274.3085326079</v>
+      </c>
+      <c r="K20">
+        <v>91828.52672804509</v>
+      </c>
+      <c r="L20">
         <v>37266.2858038811</v>
       </c>
-      <c r="I20">
+      <c r="M20">
         <v>1602821.45826733</v>
       </c>
-      <c r="J20">
+      <c r="N20">
         <v>644758.731683439</v>
-      </c>
-      <c r="K20">
-        <v>1032764.24021678</v>
-      </c>
-      <c r="L20">
-        <v>281948.98510944</v>
-      </c>
-      <c r="M20">
-        <v>65274.3085326079</v>
-      </c>
-      <c r="N20">
-        <v>91828.52672804509</v>
       </c>
       <c r="O20">
         <v>3732995.74849868</v>
@@ -40067,25 +40067,25 @@
         <v>1318988.79370708</v>
       </c>
       <c r="H21">
+        <v>1002895.23227598</v>
+      </c>
+      <c r="I21">
+        <v>276051.283799024</v>
+      </c>
+      <c r="J21">
+        <v>64519.6332150859</v>
+      </c>
+      <c r="K21">
+        <v>90881.8231216079</v>
+      </c>
+      <c r="L21">
         <v>44955.3845836862</v>
       </c>
-      <c r="I21">
+      <c r="M21">
         <v>1605577.92197702</v>
       </c>
-      <c r="J21">
+      <c r="N21">
         <v>596331.403898019</v>
-      </c>
-      <c r="K21">
-        <v>1002895.23227598</v>
-      </c>
-      <c r="L21">
-        <v>276051.283799024</v>
-      </c>
-      <c r="M21">
-        <v>64519.6332150859</v>
-      </c>
-      <c r="N21">
-        <v>90881.8231216079</v>
       </c>
       <c r="O21">
         <v>3676530.50054904</v>
@@ -40122,25 +40122,25 @@
         <v>1279240.17675411</v>
       </c>
       <c r="H22">
+        <v>1034224.27079067</v>
+      </c>
+      <c r="I22">
+        <v>269438.786815547</v>
+      </c>
+      <c r="J22">
+        <v>68682.12248746199</v>
+      </c>
+      <c r="K22">
+        <v>83042.61290714391</v>
+      </c>
+      <c r="L22">
         <v>41855.4815320932</v>
       </c>
-      <c r="I22">
+      <c r="M22">
         <v>1627719.02526855</v>
       </c>
-      <c r="J22">
+      <c r="N22">
         <v>607700.296208948</v>
-      </c>
-      <c r="K22">
-        <v>1034224.27079067</v>
-      </c>
-      <c r="L22">
-        <v>269438.786815547</v>
-      </c>
-      <c r="M22">
-        <v>68682.12248746199</v>
-      </c>
-      <c r="N22">
-        <v>83042.61290714391</v>
       </c>
       <c r="O22">
         <v>3755142.33627518</v>
@@ -40177,25 +40177,25 @@
         <v>1257331.8241773</v>
       </c>
       <c r="H23">
+        <v>1073088.41142487</v>
+      </c>
+      <c r="I23">
+        <v>292102.11436426</v>
+      </c>
+      <c r="J23">
+        <v>65503.2651654131</v>
+      </c>
+      <c r="K23">
+        <v>77310.4557752408</v>
+      </c>
+      <c r="L23">
         <v>49635.7206496506</v>
       </c>
-      <c r="I23">
+      <c r="M23">
         <v>1649706.09315998</v>
       </c>
-      <c r="J23">
+      <c r="N23">
         <v>614072.851093524</v>
-      </c>
-      <c r="K23">
-        <v>1073088.41142487</v>
-      </c>
-      <c r="L23">
-        <v>292102.11436426</v>
-      </c>
-      <c r="M23">
-        <v>65503.2651654131</v>
-      </c>
-      <c r="N23">
-        <v>77310.4557752408</v>
       </c>
       <c r="O23">
         <v>3810302.43010839</v>
@@ -40232,25 +40232,25 @@
         <v>1291536.32451324</v>
       </c>
       <c r="H24">
+        <v>1060547.97222696</v>
+      </c>
+      <c r="I24">
+        <v>293905.616439377</v>
+      </c>
+      <c r="J24">
+        <v>67123.6390951628</v>
+      </c>
+      <c r="K24">
+        <v>80434.4993467483</v>
+      </c>
+      <c r="L24">
         <v>49269.7838533845</v>
       </c>
-      <c r="I24">
+      <c r="M24">
         <v>1674548.87769091</v>
       </c>
-      <c r="J24">
+      <c r="N24">
         <v>607963.710575365</v>
-      </c>
-      <c r="K24">
-        <v>1060547.97222696</v>
-      </c>
-      <c r="L24">
-        <v>293905.616439377</v>
-      </c>
-      <c r="M24">
-        <v>67123.6390951628</v>
-      </c>
-      <c r="N24">
-        <v>80434.4993467483</v>
       </c>
       <c r="O24">
         <v>3816902.99080575</v>
@@ -40287,25 +40287,25 @@
         <v>1274381.87943288</v>
       </c>
       <c r="H25">
+        <v>1030114.88182435</v>
+      </c>
+      <c r="I25">
+        <v>294890.556041876</v>
+      </c>
+      <c r="J25">
+        <v>65874.369444118</v>
+      </c>
+      <c r="K25">
+        <v>85059.1994155616</v>
+      </c>
+      <c r="L25">
         <v>38019.6474569943</v>
       </c>
-      <c r="I25">
+      <c r="M25">
         <v>1636612.36097737</v>
       </c>
-      <c r="J25">
+      <c r="N25">
         <v>624545.0735506919</v>
-      </c>
-      <c r="K25">
-        <v>1030114.88182435</v>
-      </c>
-      <c r="L25">
-        <v>294890.556041876</v>
-      </c>
-      <c r="M25">
-        <v>65874.369444118</v>
-      </c>
-      <c r="N25">
-        <v>85059.1994155616</v>
       </c>
       <c r="O25">
         <v>3779876.81660788</v>
@@ -40342,25 +40342,25 @@
         <v>1302122.48190835</v>
       </c>
       <c r="H26">
+        <v>1044809.86041318</v>
+      </c>
+      <c r="I26">
+        <v>293621.65119203</v>
+      </c>
+      <c r="J26">
+        <v>69842.8133808464</v>
+      </c>
+      <c r="K26">
+        <v>73212.9358447441</v>
+      </c>
+      <c r="L26">
         <v>42510.8141374747</v>
       </c>
-      <c r="I26">
+      <c r="M26">
         <v>1593245.79697435</v>
       </c>
-      <c r="J26">
+      <c r="N26">
         <v>612321.100309092</v>
-      </c>
-      <c r="K26">
-        <v>1044809.86041318</v>
-      </c>
-      <c r="L26">
-        <v>293621.65119203</v>
-      </c>
-      <c r="M26">
-        <v>69842.8133808464</v>
-      </c>
-      <c r="N26">
-        <v>73212.9358447441</v>
       </c>
       <c r="O26">
         <v>3744291.46087344</v>
@@ -40397,25 +40397,25 @@
         <v>1308755.04432659</v>
       </c>
       <c r="H27">
+        <v>1027888.49044494</v>
+      </c>
+      <c r="I27">
+        <v>282269.742293184</v>
+      </c>
+      <c r="J27">
+        <v>73324.0676627389</v>
+      </c>
+      <c r="K27">
+        <v>77540.79822386061</v>
+      </c>
+      <c r="L27">
         <v>41050.0561374394</v>
       </c>
-      <c r="I27">
+      <c r="M27">
         <v>1601606.88856373</v>
       </c>
-      <c r="J27">
+      <c r="N27">
         <v>608315.438791937</v>
-      </c>
-      <c r="K27">
-        <v>1027888.49044494</v>
-      </c>
-      <c r="L27">
-        <v>282269.742293184</v>
-      </c>
-      <c r="M27">
-        <v>73324.0676627389</v>
-      </c>
-      <c r="N27">
-        <v>77540.79822386061</v>
       </c>
       <c r="O27">
         <v>3699300.28299646</v>
@@ -40452,25 +40452,25 @@
         <v>1303793.78915152</v>
       </c>
       <c r="H28">
+        <v>1023768.8121858</v>
+      </c>
+      <c r="I28">
+        <v>279654.51610983</v>
+      </c>
+      <c r="J28">
+        <v>73594.5745556973</v>
+      </c>
+      <c r="K28">
+        <v>71700.2366498418</v>
+      </c>
+      <c r="L28">
         <v>41986.5195245632</v>
       </c>
-      <c r="I28">
+      <c r="M28">
         <v>1645085.43587908</v>
       </c>
-      <c r="J28">
+      <c r="N28">
         <v>623373.850289403</v>
-      </c>
-      <c r="K28">
-        <v>1023768.8121858</v>
-      </c>
-      <c r="L28">
-        <v>279654.51610983</v>
-      </c>
-      <c r="M28">
-        <v>73594.5745556973</v>
-      </c>
-      <c r="N28">
-        <v>71700.2366498418</v>
       </c>
       <c r="O28">
         <v>3748502.9945585</v>
@@ -40507,25 +40507,25 @@
         <v>1281938.30745646</v>
       </c>
       <c r="H29">
+        <v>1016996.63924128</v>
+      </c>
+      <c r="I29">
+        <v>277442.560311739</v>
+      </c>
+      <c r="J29">
+        <v>80623.7097842482</v>
+      </c>
+      <c r="K29">
+        <v>68326.7474766325</v>
+      </c>
+      <c r="L29">
         <v>43621.8353052853</v>
       </c>
-      <c r="I29">
+      <c r="M29">
         <v>1678815.56148928</v>
       </c>
-      <c r="J29">
+      <c r="N29">
         <v>626033.2719150879</v>
-      </c>
-      <c r="K29">
-        <v>1016996.63924128</v>
-      </c>
-      <c r="L29">
-        <v>277442.560311739</v>
-      </c>
-      <c r="M29">
-        <v>80623.7097842482</v>
-      </c>
-      <c r="N29">
-        <v>68326.7474766325</v>
       </c>
       <c r="O29">
         <v>3804123.23928258</v>
@@ -40562,25 +40562,25 @@
         <v>1281340.69710575</v>
       </c>
       <c r="H30">
+        <v>1034917.92179045</v>
+      </c>
+      <c r="I30">
+        <v>283274.419213176</v>
+      </c>
+      <c r="J30">
+        <v>89252.8809968108</v>
+      </c>
+      <c r="K30">
+        <v>67920.4602010056</v>
+      </c>
+      <c r="L30">
         <v>41516.486610339</v>
       </c>
-      <c r="I30">
+      <c r="M30">
         <v>1701869.64706022</v>
       </c>
-      <c r="J30">
+      <c r="N30">
         <v>625911.96926835</v>
-      </c>
-      <c r="K30">
-        <v>1034917.92179045</v>
-      </c>
-      <c r="L30">
-        <v>283274.419213176</v>
-      </c>
-      <c r="M30">
-        <v>89252.8809968108</v>
-      </c>
-      <c r="N30">
-        <v>67920.4602010056</v>
       </c>
       <c r="O30">
         <v>3863841.22787783</v>
@@ -40617,25 +40617,25 @@
         <v>1288573.31343738</v>
       </c>
       <c r="H31">
+        <v>1052442.53349611</v>
+      </c>
+      <c r="I31">
+        <v>309352.038608137</v>
+      </c>
+      <c r="J31">
+        <v>95512.5908377868</v>
+      </c>
+      <c r="K31">
+        <v>71478.1616041372</v>
+      </c>
+      <c r="L31">
         <v>39225.4458345972</v>
       </c>
-      <c r="I31">
+      <c r="M31">
         <v>1727433.55597452</v>
       </c>
-      <c r="J31">
+      <c r="N31">
         <v>642753.031863824</v>
-      </c>
-      <c r="K31">
-        <v>1052442.53349611</v>
-      </c>
-      <c r="L31">
-        <v>309352.038608137</v>
-      </c>
-      <c r="M31">
-        <v>95512.5908377868</v>
-      </c>
-      <c r="N31">
-        <v>71478.1616041372</v>
       </c>
       <c r="O31">
         <v>3918866.01345806</v>
@@ -40672,25 +40672,25 @@
         <v>1285485.29752752</v>
       </c>
       <c r="H32">
+        <v>1078644.61204148</v>
+      </c>
+      <c r="I32">
+        <v>314483.106977196</v>
+      </c>
+      <c r="J32">
+        <v>87448.28524478769</v>
+      </c>
+      <c r="K32">
+        <v>71088.1022353329</v>
+      </c>
+      <c r="L32">
         <v>34451.6681073118</v>
       </c>
-      <c r="I32">
+      <c r="M32">
         <v>1668554.53915939</v>
       </c>
-      <c r="J32">
+      <c r="N32">
         <v>649510.895190152</v>
-      </c>
-      <c r="K32">
-        <v>1078644.61204148</v>
-      </c>
-      <c r="L32">
-        <v>314483.106977196</v>
-      </c>
-      <c r="M32">
-        <v>87448.28524478769</v>
-      </c>
-      <c r="N32">
-        <v>71088.1022353329</v>
       </c>
       <c r="O32">
         <v>3893580.99391272</v>
@@ -40727,25 +40727,25 @@
         <v>1304427.17959897</v>
       </c>
       <c r="H33">
+        <v>1094735.39474618</v>
+      </c>
+      <c r="I33">
+        <v>313296.766284096</v>
+      </c>
+      <c r="J33">
+        <v>88143.6669483921</v>
+      </c>
+      <c r="K33">
+        <v>61661.1354151804</v>
+      </c>
+      <c r="L33">
         <v>43408.7129116477</v>
       </c>
-      <c r="I33">
+      <c r="M33">
         <v>1717561.5523639</v>
       </c>
-      <c r="J33">
+      <c r="N33">
         <v>631174.771668294</v>
-      </c>
-      <c r="K33">
-        <v>1094735.39474618</v>
-      </c>
-      <c r="L33">
-        <v>313296.766284096</v>
-      </c>
-      <c r="M33">
-        <v>88143.6669483921</v>
-      </c>
-      <c r="N33">
-        <v>61661.1354151804</v>
       </c>
       <c r="O33">
         <v>3965245.19989042</v>
@@ -40782,25 +40782,25 @@
         <v>1262948.95148007</v>
       </c>
       <c r="H34">
+        <v>1018187.43526689</v>
+      </c>
+      <c r="I34">
+        <v>313267.156357905</v>
+      </c>
+      <c r="J34">
+        <v>83798.706976143</v>
+      </c>
+      <c r="K34">
+        <v>58478.2841968724</v>
+      </c>
+      <c r="L34">
         <v>34332.5426807004</v>
       </c>
-      <c r="I34">
+      <c r="M34">
         <v>1678641.94709217</v>
       </c>
-      <c r="J34">
+      <c r="N34">
         <v>676929.837237339</v>
-      </c>
-      <c r="K34">
-        <v>1018187.43526689</v>
-      </c>
-      <c r="L34">
-        <v>313267.156357905</v>
-      </c>
-      <c r="M34">
-        <v>83798.706976143</v>
-      </c>
-      <c r="N34">
-        <v>58478.2841968724</v>
       </c>
       <c r="O34">
         <v>3893189.51910242</v>
@@ -40837,25 +40837,25 @@
         <v>1129805.25923854</v>
       </c>
       <c r="H35">
+        <v>916720.097889585</v>
+      </c>
+      <c r="I35">
+        <v>294808.08930095</v>
+      </c>
+      <c r="J35">
+        <v>78984.1897509173</v>
+      </c>
+      <c r="K35">
+        <v>60033.950260502</v>
+      </c>
+      <c r="L35">
         <v>29652.4324113858</v>
       </c>
-      <c r="I35">
+      <c r="M35">
         <v>1570931.57519538</v>
       </c>
-      <c r="J35">
+      <c r="N35">
         <v>631756.7444695421</v>
-      </c>
-      <c r="K35">
-        <v>916720.097889585</v>
-      </c>
-      <c r="L35">
-        <v>294808.08930095</v>
-      </c>
-      <c r="M35">
-        <v>78984.1897509173</v>
-      </c>
-      <c r="N35">
-        <v>60033.950260502</v>
       </c>
       <c r="O35">
         <v>3561892.87305832</v>
@@ -40892,25 +40892,25 @@
         <v>1121420.76956317</v>
       </c>
       <c r="H36">
+        <v>894297.142662955</v>
+      </c>
+      <c r="I36">
+        <v>266148.402647368</v>
+      </c>
+      <c r="J36">
+        <v>103621.772911662</v>
+      </c>
+      <c r="K36">
+        <v>86914.43002167159</v>
+      </c>
+      <c r="L36">
         <v>26028.5988073751</v>
       </c>
-      <c r="I36">
+      <c r="M36">
         <v>1482625.4671686</v>
       </c>
-      <c r="J36">
+      <c r="N36">
         <v>593578.831404464</v>
-      </c>
-      <c r="K36">
-        <v>894297.142662955</v>
-      </c>
-      <c r="L36">
-        <v>266148.402647368</v>
-      </c>
-      <c r="M36">
-        <v>103621.772911662</v>
-      </c>
-      <c r="N36">
-        <v>86914.43002167159</v>
       </c>
       <c r="O36">
         <v>3436422.66581332</v>
@@ -40947,25 +40947,25 @@
         <v>1079808.88353923</v>
       </c>
       <c r="H37">
+        <v>967327.044275979</v>
+      </c>
+      <c r="I37">
+        <v>259604.262203879</v>
+      </c>
+      <c r="J37">
+        <v>95997.51867846389</v>
+      </c>
+      <c r="K37">
+        <v>104940.437160226</v>
+      </c>
+      <c r="L37">
         <v>25255.8776564565</v>
       </c>
-      <c r="I37">
+      <c r="M37">
         <v>1512787.97363792</v>
       </c>
-      <c r="J37">
+      <c r="N37">
         <v>594842.320430057</v>
-      </c>
-      <c r="K37">
-        <v>967327.044275979</v>
-      </c>
-      <c r="L37">
-        <v>259604.262203879</v>
-      </c>
-      <c r="M37">
-        <v>95997.51867846389</v>
-      </c>
-      <c r="N37">
-        <v>104940.437160226</v>
       </c>
       <c r="O37">
         <v>3580708.03151742</v>
@@ -41002,25 +41002,25 @@
         <v>1088597.3851945</v>
       </c>
       <c r="H38">
+        <v>971368.323545733</v>
+      </c>
+      <c r="I38">
+        <v>254387.656159187</v>
+      </c>
+      <c r="J38">
+        <v>93612.18621833529</v>
+      </c>
+      <c r="K38">
+        <v>114232.266854283</v>
+      </c>
+      <c r="L38">
         <v>26997.6085142258</v>
       </c>
-      <c r="I38">
+      <c r="M38">
         <v>1576065.43426985</v>
       </c>
-      <c r="J38">
+      <c r="N38">
         <v>614920.885209793</v>
-      </c>
-      <c r="K38">
-        <v>971368.323545733</v>
-      </c>
-      <c r="L38">
-        <v>254387.656159187</v>
-      </c>
-      <c r="M38">
-        <v>93612.18621833529</v>
-      </c>
-      <c r="N38">
-        <v>114232.266854283</v>
       </c>
       <c r="O38">
         <v>3668505.14432642</v>
@@ -41057,25 +41057,25 @@
         <v>1144730.93580953</v>
       </c>
       <c r="H39">
+        <v>1043098.57472619</v>
+      </c>
+      <c r="I39">
+        <v>258896.116254398</v>
+      </c>
+      <c r="J39">
+        <v>99958.7497329966</v>
+      </c>
+      <c r="K39">
+        <v>108415.395993612</v>
+      </c>
+      <c r="L39">
         <v>26464.0038476615</v>
       </c>
-      <c r="I39">
+      <c r="M39">
         <v>1528659.13569212</v>
       </c>
-      <c r="J39">
+      <c r="N39">
         <v>621192.3391080539</v>
-      </c>
-      <c r="K39">
-        <v>1043098.57472619</v>
-      </c>
-      <c r="L39">
-        <v>258896.116254398</v>
-      </c>
-      <c r="M39">
-        <v>99958.7497329966</v>
-      </c>
-      <c r="N39">
-        <v>108415.395993612</v>
       </c>
       <c r="O39">
         <v>3664032.61703487</v>
@@ -41112,25 +41112,25 @@
         <v>1164529.90174999</v>
       </c>
       <c r="H40">
+        <v>1054355.72053702</v>
+      </c>
+      <c r="I40">
+        <v>264699.992603928</v>
+      </c>
+      <c r="J40">
+        <v>108715.176799728</v>
+      </c>
+      <c r="K40">
+        <v>89411.87941561551</v>
+      </c>
+      <c r="L40">
         <v>32702.3861550151</v>
       </c>
-      <c r="I40">
+      <c r="M40">
         <v>1596321.01379913</v>
       </c>
-      <c r="J40">
+      <c r="N40">
         <v>631941.294103827</v>
-      </c>
-      <c r="K40">
-        <v>1054355.72053702</v>
-      </c>
-      <c r="L40">
-        <v>264699.992603928</v>
-      </c>
-      <c r="M40">
-        <v>108715.176799728</v>
-      </c>
-      <c r="N40">
-        <v>89411.87941561551</v>
       </c>
       <c r="O40">
         <v>3778625.7108467</v>
@@ -41167,25 +41167,25 @@
         <v>1215399.41511624</v>
       </c>
       <c r="H41">
+        <v>1037641.97125112</v>
+      </c>
+      <c r="I41">
+        <v>260716.804945621</v>
+      </c>
+      <c r="J41">
+        <v>87552.2717734887</v>
+      </c>
+      <c r="K41">
+        <v>85103.456385132</v>
+      </c>
+      <c r="L41">
         <v>38706.4879433794</v>
       </c>
-      <c r="I41">
+      <c r="M41">
         <v>1635479.56222626</v>
       </c>
-      <c r="J41">
+      <c r="N41">
         <v>622542.243363156</v>
-      </c>
-      <c r="K41">
-        <v>1037641.97125112</v>
-      </c>
-      <c r="L41">
-        <v>260716.804945621</v>
-      </c>
-      <c r="M41">
-        <v>87552.2717734887</v>
-      </c>
-      <c r="N41">
-        <v>85103.456385132</v>
       </c>
       <c r="O41">
         <v>3762051.20401026</v>
@@ -41222,25 +41222,25 @@
         <v>1248008.64335862</v>
       </c>
       <c r="H42">
+        <v>1054869.66059407</v>
+      </c>
+      <c r="I42">
+        <v>272574.12882151</v>
+      </c>
+      <c r="J42">
+        <v>90762.84145353681</v>
+      </c>
+      <c r="K42">
+        <v>85987.21025010489</v>
+      </c>
+      <c r="L42">
         <v>54726.2687396762</v>
       </c>
-      <c r="I42">
+      <c r="M42">
         <v>1667404.83666816</v>
       </c>
-      <c r="J42">
+      <c r="N42">
         <v>615330.034118205</v>
-      </c>
-      <c r="K42">
-        <v>1054869.66059407</v>
-      </c>
-      <c r="L42">
-        <v>272574.12882151</v>
-      </c>
-      <c r="M42">
-        <v>90762.84145353681</v>
-      </c>
-      <c r="N42">
-        <v>85987.21025010489</v>
       </c>
       <c r="O42">
         <v>3877379.01011211</v>
@@ -41277,25 +41277,25 @@
         <v>1255046.61884027</v>
       </c>
       <c r="H43">
+        <v>1069857.93404975</v>
+      </c>
+      <c r="I43">
+        <v>312033.368490217</v>
+      </c>
+      <c r="J43">
+        <v>92628.73876355329</v>
+      </c>
+      <c r="K43">
+        <v>91215.85025710511</v>
+      </c>
+      <c r="L43">
         <v>61467.5843922287</v>
       </c>
-      <c r="I43">
+      <c r="M43">
         <v>1727932.85323503</v>
       </c>
-      <c r="J43">
+      <c r="N43">
         <v>630504.550303983</v>
-      </c>
-      <c r="K43">
-        <v>1069857.93404975</v>
-      </c>
-      <c r="L43">
-        <v>312033.368490217</v>
-      </c>
-      <c r="M43">
-        <v>92628.73876355329</v>
-      </c>
-      <c r="N43">
-        <v>91215.85025710511</v>
       </c>
       <c r="O43">
         <v>3963412.37356046</v>
@@ -41332,25 +41332,25 @@
         <v>1355762.9009348</v>
       </c>
       <c r="H44">
+        <v>1083151.07299689</v>
+      </c>
+      <c r="I44">
+        <v>299035.936499901</v>
+      </c>
+      <c r="J44">
+        <v>98610.0673204186</v>
+      </c>
+      <c r="K44">
+        <v>99417.3462982456</v>
+      </c>
+      <c r="L44">
         <v>56935.940808026</v>
       </c>
-      <c r="I44">
+      <c r="M44">
         <v>1756665.48299944</v>
       </c>
-      <c r="J44">
+      <c r="N44">
         <v>626672.969039649</v>
-      </c>
-      <c r="K44">
-        <v>1083151.07299689</v>
-      </c>
-      <c r="L44">
-        <v>299035.936499901</v>
-      </c>
-      <c r="M44">
-        <v>98610.0673204186</v>
-      </c>
-      <c r="N44">
-        <v>99417.3462982456</v>
       </c>
       <c r="O44">
         <v>4005565.40224261</v>
@@ -41387,25 +41387,25 @@
         <v>1354575.05743452</v>
       </c>
       <c r="H45">
+        <v>1074934.58966181</v>
+      </c>
+      <c r="I45">
+        <v>284995.232276772</v>
+      </c>
+      <c r="J45">
+        <v>109324.872374047</v>
+      </c>
+      <c r="K45">
+        <v>99652.1122902435</v>
+      </c>
+      <c r="L45">
         <v>50503.571564026</v>
       </c>
-      <c r="I45">
+      <c r="M45">
         <v>1742514.96807855</v>
       </c>
-      <c r="J45">
+      <c r="N45">
         <v>628334.012793015</v>
-      </c>
-      <c r="K45">
-        <v>1074934.58966181</v>
-      </c>
-      <c r="L45">
-        <v>284995.232276772</v>
-      </c>
-      <c r="M45">
-        <v>109324.872374047</v>
-      </c>
-      <c r="N45">
-        <v>99652.1122902435</v>
       </c>
       <c r="O45">
         <v>3981332.11176561</v>
@@ -41442,25 +41442,25 @@
         <v>1389029.41153857</v>
       </c>
       <c r="H46">
+        <v>1019817.96686445</v>
+      </c>
+      <c r="I46">
+        <v>287805.753512695</v>
+      </c>
+      <c r="J46">
+        <v>99277.80993686539</v>
+      </c>
+      <c r="K46">
+        <v>103501.118429409</v>
+      </c>
+      <c r="L46">
         <v>42520.9957435212</v>
       </c>
-      <c r="I46">
+      <c r="M46">
         <v>1771370.34233562</v>
       </c>
-      <c r="J46">
+      <c r="N46">
         <v>608118.69368723</v>
-      </c>
-      <c r="K46">
-        <v>1019817.96686445</v>
-      </c>
-      <c r="L46">
-        <v>287805.753512695</v>
-      </c>
-      <c r="M46">
-        <v>99277.80993686539</v>
-      </c>
-      <c r="N46">
-        <v>103501.118429409</v>
       </c>
       <c r="O46">
         <v>3957843.23332745</v>
@@ -41497,25 +41497,25 @@
         <v>1384091.76219013</v>
       </c>
       <c r="H47">
+        <v>1053585.86988784</v>
+      </c>
+      <c r="I47">
+        <v>284419.023600832</v>
+      </c>
+      <c r="J47">
+        <v>114737.048394326</v>
+      </c>
+      <c r="K47">
+        <v>108400.381922558</v>
+      </c>
+      <c r="L47">
         <v>48220.4238233323</v>
       </c>
-      <c r="I47">
+      <c r="M47">
         <v>1813442.78997637</v>
       </c>
-      <c r="J47">
+      <c r="N47">
         <v>603074.861859391</v>
-      </c>
-      <c r="K47">
-        <v>1053585.86988784</v>
-      </c>
-      <c r="L47">
-        <v>284419.023600832</v>
-      </c>
-      <c r="M47">
-        <v>114737.048394326</v>
-      </c>
-      <c r="N47">
-        <v>108400.381922558</v>
       </c>
       <c r="O47">
         <v>4006754.29720842</v>
@@ -41552,25 +41552,25 @@
         <v>1329242.05050672</v>
       </c>
       <c r="H48">
+        <v>1023245.3977269</v>
+      </c>
+      <c r="I48">
+        <v>274648.67870362</v>
+      </c>
+      <c r="J48">
+        <v>109346.246313212</v>
+      </c>
+      <c r="K48">
+        <v>104673.689333384</v>
+      </c>
+      <c r="L48">
         <v>55438.5230404268</v>
       </c>
-      <c r="I48">
+      <c r="M48">
         <v>1851950.18366269</v>
       </c>
-      <c r="J48">
+      <c r="N48">
         <v>611381.530082806</v>
-      </c>
-      <c r="K48">
-        <v>1023245.3977269</v>
-      </c>
-      <c r="L48">
-        <v>274648.67870362</v>
-      </c>
-      <c r="M48">
-        <v>109346.246313212</v>
-      </c>
-      <c r="N48">
-        <v>104673.689333384</v>
       </c>
       <c r="O48">
         <v>4029958.18713385</v>
@@ -41607,25 +41607,25 @@
         <v>1328163.30650866</v>
       </c>
       <c r="H49">
+        <v>1042200.78132151</v>
+      </c>
+      <c r="I49">
+        <v>290378.471299847</v>
+      </c>
+      <c r="J49">
+        <v>106281.845529454</v>
+      </c>
+      <c r="K49">
+        <v>116386.147416716</v>
+      </c>
+      <c r="L49">
         <v>49354.8341413881</v>
       </c>
-      <c r="I49">
+      <c r="M49">
         <v>1870145.96869515</v>
       </c>
-      <c r="J49">
+      <c r="N49">
         <v>627380.028535731</v>
-      </c>
-      <c r="K49">
-        <v>1042200.78132151</v>
-      </c>
-      <c r="L49">
-        <v>290378.471299847</v>
-      </c>
-      <c r="M49">
-        <v>106281.845529454</v>
-      </c>
-      <c r="N49">
-        <v>116386.147416716</v>
       </c>
       <c r="O49">
         <v>4096734.66111879</v>
@@ -41662,25 +41662,25 @@
         <v>1340957.74527753</v>
       </c>
       <c r="H50">
+        <v>1087736.19118799</v>
+      </c>
+      <c r="I50">
+        <v>282097.321948747</v>
+      </c>
+      <c r="J50">
+        <v>111881.727939767</v>
+      </c>
+      <c r="K50">
+        <v>90218.695742806</v>
+      </c>
+      <c r="L50">
         <v>56183.4832155233</v>
       </c>
-      <c r="I50">
+      <c r="M50">
         <v>1859276.75823794</v>
       </c>
-      <c r="J50">
+      <c r="N50">
         <v>608194.931289693</v>
-      </c>
-      <c r="K50">
-        <v>1087736.19118799</v>
-      </c>
-      <c r="L50">
-        <v>282097.321948747</v>
-      </c>
-      <c r="M50">
-        <v>111881.727939767</v>
-      </c>
-      <c r="N50">
-        <v>90218.695742806</v>
       </c>
       <c r="O50">
         <v>4111760.76151624</v>
@@ -41717,25 +41717,25 @@
         <v>1337624.76899421</v>
       </c>
       <c r="H51">
+        <v>1100647.0634475</v>
+      </c>
+      <c r="I51">
+        <v>320694.046601179</v>
+      </c>
+      <c r="J51">
+        <v>101585.849204351</v>
+      </c>
+      <c r="K51">
+        <v>83296.880266872</v>
+      </c>
+      <c r="L51">
         <v>54568.9565638486</v>
       </c>
-      <c r="I51">
+      <c r="M51">
         <v>1843076.89813046</v>
       </c>
-      <c r="J51">
+      <c r="N51">
         <v>615387.792082511</v>
-      </c>
-      <c r="K51">
-        <v>1100647.0634475</v>
-      </c>
-      <c r="L51">
-        <v>320694.046601179</v>
-      </c>
-      <c r="M51">
-        <v>101585.849204351</v>
-      </c>
-      <c r="N51">
-        <v>83296.880266872</v>
       </c>
       <c r="O51">
         <v>4105087.65473812</v>
@@ -41772,25 +41772,25 @@
         <v>1336175.74797708</v>
       </c>
       <c r="H52">
+        <v>1147100.85201231</v>
+      </c>
+      <c r="I52">
+        <v>311336.75675867</v>
+      </c>
+      <c r="J52">
+        <v>102945.558109389</v>
+      </c>
+      <c r="K52">
+        <v>89335.2112319172</v>
+      </c>
+      <c r="L52">
         <v>52339.2226757823</v>
       </c>
-      <c r="I52">
+      <c r="M52">
         <v>1839698.78411355</v>
       </c>
-      <c r="J52">
+      <c r="N52">
         <v>647552.596626188</v>
-      </c>
-      <c r="K52">
-        <v>1147100.85201231</v>
-      </c>
-      <c r="L52">
-        <v>311336.75675867</v>
-      </c>
-      <c r="M52">
-        <v>102945.558109389</v>
-      </c>
-      <c r="N52">
-        <v>89335.2112319172</v>
       </c>
       <c r="O52">
         <v>4207623.02659547</v>
@@ -41827,25 +41827,25 @@
         <v>1363797.41612105</v>
       </c>
       <c r="H53">
+        <v>1110287.55715626</v>
+      </c>
+      <c r="I53">
+        <v>345388.903605808</v>
+      </c>
+      <c r="J53">
+        <v>107429.812967977</v>
+      </c>
+      <c r="K53">
+        <v>92541.0837632983</v>
+      </c>
+      <c r="L53">
         <v>58359.7712805024</v>
       </c>
-      <c r="I53">
+      <c r="M53">
         <v>1853958.19809961</v>
       </c>
-      <c r="J53">
+      <c r="N53">
         <v>635615.303555769</v>
-      </c>
-      <c r="K53">
-        <v>1110287.55715626</v>
-      </c>
-      <c r="L53">
-        <v>345388.903605808</v>
-      </c>
-      <c r="M53">
-        <v>107429.812967977</v>
-      </c>
-      <c r="N53">
-        <v>92541.0837632983</v>
       </c>
       <c r="O53">
         <v>4196931.25409384</v>
@@ -41882,25 +41882,25 @@
         <v>1328675.51471117</v>
       </c>
       <c r="H54">
+        <v>1115889.22310658</v>
+      </c>
+      <c r="I54">
+        <v>342805.682670894</v>
+      </c>
+      <c r="J54">
+        <v>103723.327666441</v>
+      </c>
+      <c r="K54">
+        <v>99527.3465636402</v>
+      </c>
+      <c r="L54">
         <v>49927.411515876</v>
       </c>
-      <c r="I54">
+      <c r="M54">
         <v>1875319.05551704</v>
       </c>
-      <c r="J54">
+      <c r="N54">
         <v>662233.322498088</v>
-      </c>
-      <c r="K54">
-        <v>1115889.22310658</v>
-      </c>
-      <c r="L54">
-        <v>342805.682670894</v>
-      </c>
-      <c r="M54">
-        <v>103723.327666441</v>
-      </c>
-      <c r="N54">
-        <v>99527.3465636402</v>
       </c>
       <c r="O54">
         <v>4262789.79423106</v>
@@ -41937,25 +41937,25 @@
         <v>1307235.17249349</v>
       </c>
       <c r="H55">
+        <v>1100210.71353764</v>
+      </c>
+      <c r="I55">
+        <v>341364.392583223</v>
+      </c>
+      <c r="J55">
+        <v>100071.40945919</v>
+      </c>
+      <c r="K55">
+        <v>114146.361698586</v>
+      </c>
+      <c r="L55">
         <v>47513.2794469692</v>
       </c>
-      <c r="I55">
+      <c r="M55">
         <v>1898961.55485536</v>
       </c>
-      <c r="J55">
+      <c r="N55">
         <v>670596.293753622</v>
-      </c>
-      <c r="K55">
-        <v>1100210.71353764</v>
-      </c>
-      <c r="L55">
-        <v>341364.392583223</v>
-      </c>
-      <c r="M55">
-        <v>100071.40945919</v>
-      </c>
-      <c r="N55">
-        <v>114146.361698586</v>
       </c>
       <c r="O55">
         <v>4253171.73953351</v>
@@ -41992,25 +41992,25 @@
         <v>1348568.70330317</v>
       </c>
       <c r="H56">
+        <v>1101064.66343385</v>
+      </c>
+      <c r="I56">
+        <v>366063.24473299</v>
+      </c>
+      <c r="J56">
+        <v>101152.502849675</v>
+      </c>
+      <c r="K56">
+        <v>119251.60131607</v>
+      </c>
+      <c r="L56">
         <v>43916.4415377448</v>
       </c>
-      <c r="I56">
+      <c r="M56">
         <v>1815006.71619131</v>
       </c>
-      <c r="J56">
+      <c r="N56">
         <v>656891.161886064</v>
-      </c>
-      <c r="K56">
-        <v>1101064.66343385</v>
-      </c>
-      <c r="L56">
-        <v>366063.24473299</v>
-      </c>
-      <c r="M56">
-        <v>101152.502849675</v>
-      </c>
-      <c r="N56">
-        <v>119251.60131607</v>
       </c>
       <c r="O56">
         <v>4221456.36391638</v>
@@ -42070,37 +42070,37 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Atividades imobiliárias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Outras atividades de serviços</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Comércio</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Transporte, armazenagem e correio</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Informação e comunicação</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Atividades financeiras, de seguros e serviços relacionados</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -42144,25 +42144,25 @@
         <v>738195366.653945</v>
       </c>
       <c r="H2">
+        <v>540358026.320357</v>
+      </c>
+      <c r="I2">
+        <v>164941216.906689</v>
+      </c>
+      <c r="J2">
+        <v>31972405.3807888</v>
+      </c>
+      <c r="K2">
+        <v>37875054.1301252</v>
+      </c>
+      <c r="L2">
         <v>14554589.5921756</v>
       </c>
-      <c r="I2">
+      <c r="M2">
         <v>723336888.744716</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <v>253513685.875611</v>
-      </c>
-      <c r="K2">
-        <v>540358026.320357</v>
-      </c>
-      <c r="L2">
-        <v>164941216.906689</v>
-      </c>
-      <c r="M2">
-        <v>31972405.3807888</v>
-      </c>
-      <c r="N2">
-        <v>37875054.1301252</v>
       </c>
       <c r="O2">
         <v>1774101590.55631</v>
@@ -42199,25 +42199,25 @@
         <v>785431404.156231</v>
       </c>
       <c r="H3">
+        <v>547828914.058934</v>
+      </c>
+      <c r="I3">
+        <v>163950867.153521</v>
+      </c>
+      <c r="J3">
+        <v>32560965.1459297</v>
+      </c>
+      <c r="K3">
+        <v>41516457.966091</v>
+      </c>
+      <c r="L3">
         <v>17877533.2064083</v>
       </c>
-      <c r="I3">
+      <c r="M3">
         <v>691294341.622835</v>
       </c>
-      <c r="J3">
+      <c r="N3">
         <v>259192879.444502</v>
-      </c>
-      <c r="K3">
-        <v>547828914.058934</v>
-      </c>
-      <c r="L3">
-        <v>163950867.153521</v>
-      </c>
-      <c r="M3">
-        <v>32560965.1459297</v>
-      </c>
-      <c r="N3">
-        <v>41516457.966091</v>
       </c>
       <c r="O3">
         <v>1755596443.9495</v>
@@ -42254,25 +42254,25 @@
         <v>755292815.1193219</v>
       </c>
       <c r="H4">
+        <v>558710707.1564161</v>
+      </c>
+      <c r="I4">
+        <v>166606089.491243</v>
+      </c>
+      <c r="J4">
+        <v>35537490.4386882</v>
+      </c>
+      <c r="K4">
+        <v>40837064.5973346</v>
+      </c>
+      <c r="L4">
         <v>21100296.8580599</v>
       </c>
-      <c r="I4">
+      <c r="M4">
         <v>696305995.903159</v>
       </c>
-      <c r="J4">
+      <c r="N4">
         <v>264828666.359499</v>
-      </c>
-      <c r="K4">
-        <v>558710707.1564161</v>
-      </c>
-      <c r="L4">
-        <v>166606089.491243</v>
-      </c>
-      <c r="M4">
-        <v>35537490.4386882</v>
-      </c>
-      <c r="N4">
-        <v>40837064.5973346</v>
       </c>
       <c r="O4">
         <v>1780460580.17796</v>
@@ -42309,25 +42309,25 @@
         <v>753421869.729176</v>
       </c>
       <c r="H5">
+        <v>558992328.501459</v>
+      </c>
+      <c r="I5">
+        <v>173084695.711681</v>
+      </c>
+      <c r="J5">
+        <v>34751071.6354372</v>
+      </c>
+      <c r="K5">
+        <v>40448244.4707224</v>
+      </c>
+      <c r="L5">
         <v>23110332.7698872</v>
       </c>
-      <c r="I5">
+      <c r="M5">
         <v>676218388.117926</v>
       </c>
-      <c r="J5">
+      <c r="N5">
         <v>267791598.902809</v>
-      </c>
-      <c r="K5">
-        <v>558992328.501459</v>
-      </c>
-      <c r="L5">
-        <v>173084695.711681</v>
-      </c>
-      <c r="M5">
-        <v>34751071.6354372</v>
-      </c>
-      <c r="N5">
-        <v>40448244.4707224</v>
       </c>
       <c r="O5">
         <v>1776480581.17316</v>
@@ -42364,25 +42364,25 @@
         <v>767241076.549323</v>
       </c>
       <c r="H6">
+        <v>563334853.031207</v>
+      </c>
+      <c r="I6">
+        <v>173363151.496521</v>
+      </c>
+      <c r="J6">
+        <v>32488534.7235606</v>
+      </c>
+      <c r="K6">
+        <v>41913056.4861495</v>
+      </c>
+      <c r="L6">
         <v>25212701.5402755</v>
       </c>
-      <c r="I6">
+      <c r="M6">
         <v>666438113.435708</v>
       </c>
-      <c r="J6">
+      <c r="N6">
         <v>282814511.340661</v>
-      </c>
-      <c r="K6">
-        <v>563334853.031207</v>
-      </c>
-      <c r="L6">
-        <v>173363151.496521</v>
-      </c>
-      <c r="M6">
-        <v>32488534.7235606</v>
-      </c>
-      <c r="N6">
-        <v>41913056.4861495</v>
       </c>
       <c r="O6">
         <v>1792572089.29921</v>
@@ -42419,25 +42419,25 @@
         <v>784492948.629701</v>
       </c>
       <c r="H7">
+        <v>584847058.1738091</v>
+      </c>
+      <c r="I7">
+        <v>171807952.704201</v>
+      </c>
+      <c r="J7">
+        <v>31282114.8653597</v>
+      </c>
+      <c r="K7">
+        <v>43189540.6587611</v>
+      </c>
+      <c r="L7">
         <v>26527569.7566286</v>
       </c>
-      <c r="I7">
+      <c r="M7">
         <v>673623059.761672</v>
       </c>
-      <c r="J7">
+      <c r="N7">
         <v>292782839.423735</v>
-      </c>
-      <c r="K7">
-        <v>584847058.1738091</v>
-      </c>
-      <c r="L7">
-        <v>171807952.704201</v>
-      </c>
-      <c r="M7">
-        <v>31282114.8653597</v>
-      </c>
-      <c r="N7">
-        <v>43189540.6587611</v>
       </c>
       <c r="O7">
         <v>1818425303.09349</v>
@@ -42474,25 +42474,25 @@
         <v>779217466.727579</v>
       </c>
       <c r="H8">
+        <v>598052844.191021</v>
+      </c>
+      <c r="I8">
+        <v>172733087.561708</v>
+      </c>
+      <c r="J8">
+        <v>32479776.1562758</v>
+      </c>
+      <c r="K8">
+        <v>42402342.6433637</v>
+      </c>
+      <c r="L8">
         <v>28154017.5528603</v>
       </c>
-      <c r="I8">
+      <c r="M8">
         <v>709567081.565294</v>
       </c>
-      <c r="J8">
+      <c r="N8">
         <v>280988672.853429</v>
-      </c>
-      <c r="K8">
-        <v>598052844.191021</v>
-      </c>
-      <c r="L8">
-        <v>172733087.561708</v>
-      </c>
-      <c r="M8">
-        <v>32479776.1562758</v>
-      </c>
-      <c r="N8">
-        <v>42402342.6433637</v>
       </c>
       <c r="O8">
         <v>1863296679.94552</v>
@@ -42529,25 +42529,25 @@
         <v>750398395.445269</v>
       </c>
       <c r="H9">
+        <v>614188918.8198529</v>
+      </c>
+      <c r="I9">
+        <v>163468086.439688</v>
+      </c>
+      <c r="J9">
+        <v>33846751.2086632</v>
+      </c>
+      <c r="K9">
+        <v>39318460.9030666</v>
+      </c>
+      <c r="L9">
         <v>23094581.7918413</v>
       </c>
-      <c r="I9">
+      <c r="M9">
         <v>723538132.857281</v>
       </c>
-      <c r="J9">
+      <c r="N9">
         <v>277083128.181156</v>
-      </c>
-      <c r="K9">
-        <v>614188918.8198529</v>
-      </c>
-      <c r="L9">
-        <v>163468086.439688</v>
-      </c>
-      <c r="M9">
-        <v>33846751.2086632</v>
-      </c>
-      <c r="N9">
-        <v>39318460.9030666</v>
       </c>
       <c r="O9">
         <v>1875689632.88601</v>
@@ -42584,25 +42584,25 @@
         <v>767513255.42864</v>
       </c>
       <c r="H10">
+        <v>603756127.63829</v>
+      </c>
+      <c r="I10">
+        <v>166257067.618937</v>
+      </c>
+      <c r="J10">
+        <v>36437446.2255163</v>
+      </c>
+      <c r="K10">
+        <v>38019143.785493</v>
+      </c>
+      <c r="L10">
         <v>22613704.0634019</v>
       </c>
-      <c r="I10">
+      <c r="M10">
         <v>728209553.82345</v>
       </c>
-      <c r="J10">
+      <c r="N10">
         <v>271712770.087978</v>
-      </c>
-      <c r="K10">
-        <v>603756127.63829</v>
-      </c>
-      <c r="L10">
-        <v>166257067.618937</v>
-      </c>
-      <c r="M10">
-        <v>36437446.2255163</v>
-      </c>
-      <c r="N10">
-        <v>38019143.785493</v>
       </c>
       <c r="O10">
         <v>1859728860.31444</v>
@@ -42639,25 +42639,25 @@
         <v>755305792.20665</v>
       </c>
       <c r="H11">
+        <v>586034300.83929</v>
+      </c>
+      <c r="I11">
+        <v>153210178.236282</v>
+      </c>
+      <c r="J11">
+        <v>33161337.2720308</v>
+      </c>
+      <c r="K11">
+        <v>37126688.8053991</v>
+      </c>
+      <c r="L11">
         <v>18471831.0377836</v>
       </c>
-      <c r="I11">
+      <c r="M11">
         <v>762463951.35221</v>
       </c>
-      <c r="J11">
+      <c r="N11">
         <v>273302430.028919</v>
-      </c>
-      <c r="K11">
-        <v>586034300.83929</v>
-      </c>
-      <c r="L11">
-        <v>153210178.236282</v>
-      </c>
-      <c r="M11">
-        <v>33161337.2720308</v>
-      </c>
-      <c r="N11">
-        <v>37126688.8053991</v>
       </c>
       <c r="O11">
         <v>1872336338.6198</v>
@@ -42694,25 +42694,25 @@
         <v>748865815.621035</v>
       </c>
       <c r="H12">
+        <v>576389413.134698</v>
+      </c>
+      <c r="I12">
+        <v>151631748.077825</v>
+      </c>
+      <c r="J12">
+        <v>35292746.140465</v>
+      </c>
+      <c r="K12">
+        <v>40925558.4983906</v>
+      </c>
+      <c r="L12">
         <v>20992583.3502761</v>
       </c>
-      <c r="I12">
+      <c r="M12">
         <v>762362967.57319</v>
       </c>
-      <c r="J12">
+      <c r="N12">
         <v>276694825.858656</v>
-      </c>
-      <c r="K12">
-        <v>576389413.134698</v>
-      </c>
-      <c r="L12">
-        <v>151631748.077825</v>
-      </c>
-      <c r="M12">
-        <v>35292746.140465</v>
-      </c>
-      <c r="N12">
-        <v>40925558.4983906</v>
       </c>
       <c r="O12">
         <v>1864660298.43102</v>
@@ -42749,25 +42749,25 @@
         <v>737408437.910785</v>
       </c>
       <c r="H13">
+        <v>576659108.144814</v>
+      </c>
+      <c r="I13">
+        <v>155458152.531807</v>
+      </c>
+      <c r="J13">
+        <v>37073441.9581344</v>
+      </c>
+      <c r="K13">
+        <v>37352499.9159355</v>
+      </c>
+      <c r="L13">
         <v>22443030.4120951</v>
       </c>
-      <c r="I13">
+      <c r="M13">
         <v>761900487.705938</v>
       </c>
-      <c r="J13">
+      <c r="N13">
         <v>276821492.270838</v>
-      </c>
-      <c r="K13">
-        <v>576659108.144814</v>
-      </c>
-      <c r="L13">
-        <v>155458152.531807</v>
-      </c>
-      <c r="M13">
-        <v>37073441.9581344</v>
-      </c>
-      <c r="N13">
-        <v>37352499.9159355</v>
       </c>
       <c r="O13">
         <v>1865581717.80013</v>
@@ -42804,25 +42804,25 @@
         <v>727350335.172179</v>
       </c>
       <c r="H14">
+        <v>587023289.38133</v>
+      </c>
+      <c r="I14">
+        <v>149141543.981379</v>
+      </c>
+      <c r="J14">
+        <v>37849102.4133197</v>
+      </c>
+      <c r="K14">
+        <v>43019458.5592943</v>
+      </c>
+      <c r="L14">
         <v>20974017.9838995</v>
       </c>
-      <c r="I14">
+      <c r="M14">
         <v>764212885.976385</v>
       </c>
-      <c r="J14">
+      <c r="N14">
         <v>285998333.366515</v>
-      </c>
-      <c r="K14">
-        <v>587023289.38133</v>
-      </c>
-      <c r="L14">
-        <v>149141543.981379</v>
-      </c>
-      <c r="M14">
-        <v>37849102.4133197</v>
-      </c>
-      <c r="N14">
-        <v>43019458.5592943</v>
       </c>
       <c r="O14">
         <v>1893748357.96009</v>
@@ -42859,25 +42859,25 @@
         <v>719973514.4513119</v>
       </c>
       <c r="H15">
+        <v>589471197.962148</v>
+      </c>
+      <c r="I15">
+        <v>161896384.720955</v>
+      </c>
+      <c r="J15">
+        <v>41715999.5603163</v>
+      </c>
+      <c r="K15">
+        <v>39444443.3415623</v>
+      </c>
+      <c r="L15">
         <v>22058564.8635508</v>
       </c>
-      <c r="I15">
+      <c r="M15">
         <v>758928829.01519</v>
       </c>
-      <c r="J15">
+      <c r="N15">
         <v>272145451.398217</v>
-      </c>
-      <c r="K15">
-        <v>589471197.962148</v>
-      </c>
-      <c r="L15">
-        <v>161896384.720955</v>
-      </c>
-      <c r="M15">
-        <v>41715999.5603163</v>
-      </c>
-      <c r="N15">
-        <v>39444443.3415623</v>
       </c>
       <c r="O15">
         <v>1882397004.52605</v>
@@ -42914,25 +42914,25 @@
         <v>722510684.940574</v>
       </c>
       <c r="H16">
+        <v>587290508.408848</v>
+      </c>
+      <c r="I16">
+        <v>158337219.322759</v>
+      </c>
+      <c r="J16">
+        <v>40177494.6303349</v>
+      </c>
+      <c r="K16">
+        <v>36344634.0356105</v>
+      </c>
+      <c r="L16">
         <v>17729243.7062873</v>
       </c>
-      <c r="I16">
+      <c r="M16">
         <v>732259860.453647</v>
       </c>
-      <c r="J16">
+      <c r="N16">
         <v>277222131.668924</v>
-      </c>
-      <c r="K16">
-        <v>587290508.408848</v>
-      </c>
-      <c r="L16">
-        <v>158337219.322759</v>
-      </c>
-      <c r="M16">
-        <v>40177494.6303349</v>
-      </c>
-      <c r="N16">
-        <v>36344634.0356105</v>
       </c>
       <c r="O16">
         <v>1848680445.83586</v>
@@ -42969,25 +42969,25 @@
         <v>730095658.372306</v>
       </c>
       <c r="H17">
+        <v>579000439.614911</v>
+      </c>
+      <c r="I17">
+        <v>160617557.514226</v>
+      </c>
+      <c r="J17">
+        <v>45099552.0542053</v>
+      </c>
+      <c r="K17">
+        <v>38339410.6886193</v>
+      </c>
+      <c r="L17">
         <v>18381804.0561172</v>
       </c>
-      <c r="I17">
+      <c r="M17">
         <v>735363012.461079</v>
       </c>
-      <c r="J17">
+      <c r="N17">
         <v>288141442.807977</v>
-      </c>
-      <c r="K17">
-        <v>579000439.614911</v>
-      </c>
-      <c r="L17">
-        <v>160617557.514226</v>
-      </c>
-      <c r="M17">
-        <v>45099552.0542053</v>
-      </c>
-      <c r="N17">
-        <v>38339410.6886193</v>
       </c>
       <c r="O17">
         <v>1868432744.63051</v>
@@ -43024,25 +43024,25 @@
         <v>729349109.2519391</v>
       </c>
       <c r="H18">
+        <v>560868234.5414</v>
+      </c>
+      <c r="I18">
+        <v>166894717.629737</v>
+      </c>
+      <c r="J18">
+        <v>26861147.738931</v>
+      </c>
+      <c r="K18">
+        <v>40168610.5470211</v>
+      </c>
+      <c r="L18">
         <v>18973511.6357471</v>
       </c>
-      <c r="I18">
+      <c r="M18">
         <v>737154586.8246779</v>
       </c>
-      <c r="J18">
+      <c r="N18">
         <v>286201021.254456</v>
-      </c>
-      <c r="K18">
-        <v>560868234.5414</v>
-      </c>
-      <c r="L18">
-        <v>166894717.629737</v>
-      </c>
-      <c r="M18">
-        <v>26861147.738931</v>
-      </c>
-      <c r="N18">
-        <v>40168610.5470211</v>
       </c>
       <c r="O18">
         <v>1852224560.39749</v>
@@ -43079,25 +43079,25 @@
         <v>718140258.015336</v>
       </c>
       <c r="H19">
+        <v>554256248.527279</v>
+      </c>
+      <c r="I19">
+        <v>159354426.492455</v>
+      </c>
+      <c r="J19">
+        <v>33758248.1548859</v>
+      </c>
+      <c r="K19">
+        <v>42977088.7877619</v>
+      </c>
+      <c r="L19">
         <v>17919121.8548821</v>
       </c>
-      <c r="I19">
+      <c r="M19">
         <v>745534693.130796</v>
       </c>
-      <c r="J19">
+      <c r="N19">
         <v>288299566.423514</v>
-      </c>
-      <c r="K19">
-        <v>554256248.527279</v>
-      </c>
-      <c r="L19">
-        <v>159354426.492455</v>
-      </c>
-      <c r="M19">
-        <v>33758248.1548859</v>
-      </c>
-      <c r="N19">
-        <v>42977088.7877619</v>
       </c>
       <c r="O19">
         <v>1833953324.38553</v>
@@ -43134,25 +43134,25 @@
         <v>705716060.31955</v>
       </c>
       <c r="H20">
+        <v>571994782.548562</v>
+      </c>
+      <c r="I20">
+        <v>157957130.416737</v>
+      </c>
+      <c r="J20">
+        <v>33700879.6076236</v>
+      </c>
+      <c r="K20">
+        <v>44662713.1646159</v>
+      </c>
+      <c r="L20">
         <v>19519755.806345</v>
       </c>
-      <c r="I20">
+      <c r="M20">
         <v>756951683.844331</v>
       </c>
-      <c r="J20">
+      <c r="N20">
         <v>292998081.077317</v>
-      </c>
-      <c r="K20">
-        <v>571994782.548562</v>
-      </c>
-      <c r="L20">
-        <v>157957130.416737</v>
-      </c>
-      <c r="M20">
-        <v>33700879.6076236</v>
-      </c>
-      <c r="N20">
-        <v>44662713.1646159</v>
       </c>
       <c r="O20">
         <v>1866408590.48129</v>
@@ -43189,25 +43189,25 @@
         <v>700776987.7512701</v>
       </c>
       <c r="H21">
+        <v>544136999.299386</v>
+      </c>
+      <c r="I21">
+        <v>153563012.265572</v>
+      </c>
+      <c r="J21">
+        <v>32812899.7667874</v>
+      </c>
+      <c r="K21">
+        <v>44035420.2393474</v>
+      </c>
+      <c r="L21">
         <v>24118690.3037257</v>
       </c>
-      <c r="I21">
+      <c r="M21">
         <v>754083473.61194</v>
       </c>
-      <c r="J21">
+      <c r="N21">
         <v>272935906.547492</v>
-      </c>
-      <c r="K21">
-        <v>544136999.299386</v>
-      </c>
-      <c r="L21">
-        <v>153563012.265572</v>
-      </c>
-      <c r="M21">
-        <v>32812899.7667874</v>
-      </c>
-      <c r="N21">
-        <v>44035420.2393474</v>
       </c>
       <c r="O21">
         <v>1819976708.51849</v>
@@ -43244,25 +43244,25 @@
         <v>681399274.5102</v>
       </c>
       <c r="H22">
+        <v>560748018.853379</v>
+      </c>
+      <c r="I22">
+        <v>151158041.243167</v>
+      </c>
+      <c r="J22">
+        <v>33656649.2971018</v>
+      </c>
+      <c r="K22">
+        <v>41347224.046832</v>
+      </c>
+      <c r="L22">
         <v>20791182.0159935</v>
       </c>
-      <c r="I22">
+      <c r="M22">
         <v>764354111.700677</v>
       </c>
-      <c r="J22">
+      <c r="N22">
         <v>278307755.196964</v>
-      </c>
-      <c r="K22">
-        <v>560748018.853379</v>
-      </c>
-      <c r="L22">
-        <v>151158041.243167</v>
-      </c>
-      <c r="M22">
-        <v>33656649.2971018</v>
-      </c>
-      <c r="N22">
-        <v>41347224.046832</v>
       </c>
       <c r="O22">
         <v>1853596699.92953</v>
@@ -43299,25 +43299,25 @@
         <v>666563515.151863</v>
       </c>
       <c r="H23">
+        <v>577030505.270155</v>
+      </c>
+      <c r="I23">
+        <v>164025978.559413</v>
+      </c>
+      <c r="J23">
+        <v>32268394.9060253</v>
+      </c>
+      <c r="K23">
+        <v>37431513.5999811</v>
+      </c>
+      <c r="L23">
         <v>25894601.8775804</v>
       </c>
-      <c r="I23">
+      <c r="M23">
         <v>757624311.111817</v>
       </c>
-      <c r="J23">
+      <c r="N23">
         <v>279400522.236048</v>
-      </c>
-      <c r="K23">
-        <v>577030505.270155</v>
-      </c>
-      <c r="L23">
-        <v>164025978.559413</v>
-      </c>
-      <c r="M23">
-        <v>32268394.9060253</v>
-      </c>
-      <c r="N23">
-        <v>37431513.5999811</v>
       </c>
       <c r="O23">
         <v>1877263940.34692</v>
@@ -43354,25 +43354,25 @@
         <v>682373586.652254</v>
       </c>
       <c r="H24">
+        <v>565998075.476377</v>
+      </c>
+      <c r="I24">
+        <v>162847372.935742</v>
+      </c>
+      <c r="J24">
+        <v>33652993.9205728</v>
+      </c>
+      <c r="K24">
+        <v>40049551.8311759</v>
+      </c>
+      <c r="L24">
         <v>24704313.3393113</v>
       </c>
-      <c r="I24">
+      <c r="M24">
         <v>774069917.130628</v>
       </c>
-      <c r="J24">
+      <c r="N24">
         <v>278519233.198231</v>
-      </c>
-      <c r="K24">
-        <v>565998075.476377</v>
-      </c>
-      <c r="L24">
-        <v>162847372.935742</v>
-      </c>
-      <c r="M24">
-        <v>33652993.9205728</v>
-      </c>
-      <c r="N24">
-        <v>40049551.8311759</v>
       </c>
       <c r="O24">
         <v>1872518260.68423</v>
@@ -43409,25 +43409,25 @@
         <v>671101350.160015</v>
       </c>
       <c r="H25">
+        <v>553697083.980875</v>
+      </c>
+      <c r="I25">
+        <v>166133745.413312</v>
+      </c>
+      <c r="J25">
+        <v>33710836.7740008</v>
+      </c>
+      <c r="K25">
+        <v>40421590.7874811</v>
+      </c>
+      <c r="L25">
         <v>19798271.5842738</v>
       </c>
-      <c r="I25">
+      <c r="M25">
         <v>753971462.3589571</v>
       </c>
-      <c r="J25">
+      <c r="N25">
         <v>289129373.104777</v>
-      </c>
-      <c r="K25">
-        <v>553697083.980875</v>
-      </c>
-      <c r="L25">
-        <v>166133745.413312</v>
-      </c>
-      <c r="M25">
-        <v>33710836.7740008</v>
-      </c>
-      <c r="N25">
-        <v>40421590.7874811</v>
       </c>
       <c r="O25">
         <v>1856255550.549</v>
@@ -43464,25 +43464,25 @@
         <v>690092417.419142</v>
       </c>
       <c r="H26">
+        <v>559435392.669136</v>
+      </c>
+      <c r="I26">
+        <v>163810208.40701</v>
+      </c>
+      <c r="J26">
+        <v>34361423.7712988</v>
+      </c>
+      <c r="K26">
+        <v>34681845.4458076</v>
+      </c>
+      <c r="L26">
         <v>21110199.3741218</v>
       </c>
-      <c r="I26">
+      <c r="M26">
         <v>727596050.354755</v>
       </c>
-      <c r="J26">
+      <c r="N26">
         <v>278692563.054294</v>
-      </c>
-      <c r="K26">
-        <v>559435392.669136</v>
-      </c>
-      <c r="L26">
-        <v>163810208.40701</v>
-      </c>
-      <c r="M26">
-        <v>34361423.7712988</v>
-      </c>
-      <c r="N26">
-        <v>34681845.4458076</v>
       </c>
       <c r="O26">
         <v>1836113271.92329</v>
@@ -43519,25 +43519,25 @@
         <v>697493655.15307</v>
       </c>
       <c r="H27">
+        <v>552753584.975989</v>
+      </c>
+      <c r="I27">
+        <v>158545017.631856</v>
+      </c>
+      <c r="J27">
+        <v>37191355.2998227</v>
+      </c>
+      <c r="K27">
+        <v>38300451.6842963</v>
+      </c>
+      <c r="L27">
         <v>20393380.8261783</v>
       </c>
-      <c r="I27">
+      <c r="M27">
         <v>755040154.8740979</v>
       </c>
-      <c r="J27">
+      <c r="N27">
         <v>279546321.897124</v>
-      </c>
-      <c r="K27">
-        <v>552753584.975989</v>
-      </c>
-      <c r="L27">
-        <v>158545017.631856</v>
-      </c>
-      <c r="M27">
-        <v>37191355.2998227</v>
-      </c>
-      <c r="N27">
-        <v>38300451.6842963</v>
       </c>
       <c r="O27">
         <v>1829275992.11604</v>
@@ -43574,25 +43574,25 @@
         <v>691143512.107669</v>
       </c>
       <c r="H28">
+        <v>547146430.287374</v>
+      </c>
+      <c r="I28">
+        <v>156680583.681271</v>
+      </c>
+      <c r="J28">
+        <v>37433908.8195124</v>
+      </c>
+      <c r="K28">
+        <v>34365583.6056707</v>
+      </c>
+      <c r="L28">
         <v>22017217.7896186</v>
       </c>
-      <c r="I28">
+      <c r="M28">
         <v>763717401.8239011</v>
       </c>
-      <c r="J28">
+      <c r="N28">
         <v>289085798.418544</v>
-      </c>
-      <c r="K28">
-        <v>547146430.287374</v>
-      </c>
-      <c r="L28">
-        <v>156680583.681271</v>
-      </c>
-      <c r="M28">
-        <v>37433908.8195124</v>
-      </c>
-      <c r="N28">
-        <v>34365583.6056707</v>
       </c>
       <c r="O28">
         <v>1845251525.02677</v>
@@ -43629,25 +43629,25 @@
         <v>674830606.329464</v>
       </c>
       <c r="H29">
+        <v>548020674.9888771</v>
+      </c>
+      <c r="I29">
+        <v>156119435.300189</v>
+      </c>
+      <c r="J29">
+        <v>41371240.7386416</v>
+      </c>
+      <c r="K29">
+        <v>33330956.7791681</v>
+      </c>
+      <c r="L29">
         <v>23010700.1939222</v>
       </c>
-      <c r="I29">
+      <c r="M29">
         <v>787490054.683931</v>
       </c>
-      <c r="J29">
+      <c r="N29">
         <v>289312332.311651</v>
-      </c>
-      <c r="K29">
-        <v>548020674.9888771</v>
-      </c>
-      <c r="L29">
-        <v>156119435.300189</v>
-      </c>
-      <c r="M29">
-        <v>41371240.7386416</v>
-      </c>
-      <c r="N29">
-        <v>33330956.7791681</v>
       </c>
       <c r="O29">
         <v>1880432070.22977</v>
@@ -43684,25 +43684,25 @@
         <v>673571702.834558</v>
       </c>
       <c r="H30">
+        <v>555913291.646546</v>
+      </c>
+      <c r="I30">
+        <v>160398187.310209</v>
+      </c>
+      <c r="J30">
+        <v>46259650.6868996</v>
+      </c>
+      <c r="K30">
+        <v>33385986.9094201</v>
+      </c>
+      <c r="L30">
         <v>21752110.6018379</v>
       </c>
-      <c r="I30">
+      <c r="M30">
         <v>795777302.452513</v>
       </c>
-      <c r="J30">
+      <c r="N30">
         <v>290981934.349932</v>
-      </c>
-      <c r="K30">
-        <v>555913291.646546</v>
-      </c>
-      <c r="L30">
-        <v>160398187.310209</v>
-      </c>
-      <c r="M30">
-        <v>46259650.6868996</v>
-      </c>
-      <c r="N30">
-        <v>33385986.9094201</v>
       </c>
       <c r="O30">
         <v>1909190804.48049</v>
@@ -43739,25 +43739,25 @@
         <v>678672352.437245</v>
       </c>
       <c r="H31">
+        <v>567773626.244294</v>
+      </c>
+      <c r="I31">
+        <v>174881383.672276</v>
+      </c>
+      <c r="J31">
+        <v>48801820.882107</v>
+      </c>
+      <c r="K31">
+        <v>35160521.845311</v>
+      </c>
+      <c r="L31">
         <v>20151554.8471041</v>
       </c>
-      <c r="I31">
+      <c r="M31">
         <v>786830221.729694</v>
       </c>
-      <c r="J31">
+      <c r="N31">
         <v>296285922.226373</v>
-      </c>
-      <c r="K31">
-        <v>567773626.244294</v>
-      </c>
-      <c r="L31">
-        <v>174881383.672276</v>
-      </c>
-      <c r="M31">
-        <v>48801820.882107</v>
-      </c>
-      <c r="N31">
-        <v>35160521.845311</v>
       </c>
       <c r="O31">
         <v>1928881076.26528</v>
@@ -43794,25 +43794,25 @@
         <v>677520689.130424</v>
       </c>
       <c r="H32">
+        <v>576138425.061595</v>
+      </c>
+      <c r="I32">
+        <v>181537962.031477</v>
+      </c>
+      <c r="J32">
+        <v>45016564.3571493</v>
+      </c>
+      <c r="K32">
+        <v>34831862.669557</v>
+      </c>
+      <c r="L32">
         <v>18274263.7060342</v>
       </c>
-      <c r="I32">
+      <c r="M32">
         <v>767315582.987342</v>
       </c>
-      <c r="J32">
+      <c r="N32">
         <v>300595850.914841</v>
-      </c>
-      <c r="K32">
-        <v>576138425.061595</v>
-      </c>
-      <c r="L32">
-        <v>181537962.031477</v>
-      </c>
-      <c r="M32">
-        <v>45016564.3571493</v>
-      </c>
-      <c r="N32">
-        <v>34831862.669557</v>
       </c>
       <c r="O32">
         <v>1918536057.63666</v>
@@ -43849,25 +43849,25 @@
         <v>681585591.462265</v>
       </c>
       <c r="H33">
+        <v>580298110.67732</v>
+      </c>
+      <c r="I33">
+        <v>179672003.268289</v>
+      </c>
+      <c r="J33">
+        <v>46315964.6368684</v>
+      </c>
+      <c r="K33">
+        <v>29579882.6602403</v>
+      </c>
+      <c r="L33">
         <v>22718893.486205</v>
       </c>
-      <c r="I33">
+      <c r="M33">
         <v>796311444.990604</v>
       </c>
-      <c r="J33">
+      <c r="N33">
         <v>290674494.169949</v>
-      </c>
-      <c r="K33">
-        <v>580298110.67732</v>
-      </c>
-      <c r="L33">
-        <v>179672003.268289</v>
-      </c>
-      <c r="M33">
-        <v>46315964.6368684</v>
-      </c>
-      <c r="N33">
-        <v>29579882.6602403</v>
       </c>
       <c r="O33">
         <v>1948974295.15899</v>
@@ -43904,25 +43904,25 @@
         <v>660411623.889938</v>
       </c>
       <c r="H34">
+        <v>544556644.910637</v>
+      </c>
+      <c r="I34">
+        <v>178468989.283828</v>
+      </c>
+      <c r="J34">
+        <v>44652396.83228</v>
+      </c>
+      <c r="K34">
+        <v>28336944.6587414</v>
+      </c>
+      <c r="L34">
         <v>17378019.4605081</v>
       </c>
-      <c r="I34">
+      <c r="M34">
         <v>772238528.451037</v>
       </c>
-      <c r="J34">
+      <c r="N34">
         <v>307272767.380749</v>
-      </c>
-      <c r="K34">
-        <v>544556644.910637</v>
-      </c>
-      <c r="L34">
-        <v>178468989.283828</v>
-      </c>
-      <c r="M34">
-        <v>44652396.83228</v>
-      </c>
-      <c r="N34">
-        <v>28336944.6587414</v>
       </c>
       <c r="O34">
         <v>1909377233.16163</v>
@@ -43959,25 +43959,25 @@
         <v>595021914.9253</v>
       </c>
       <c r="H35">
+        <v>490092230.354854</v>
+      </c>
+      <c r="I35">
+        <v>162000872.47874</v>
+      </c>
+      <c r="J35">
+        <v>41704514.4988458</v>
+      </c>
+      <c r="K35">
+        <v>29177418.0268327</v>
+      </c>
+      <c r="L35">
         <v>15521180.5940385</v>
       </c>
-      <c r="I35">
+      <c r="M35">
         <v>728312612.887718</v>
       </c>
-      <c r="J35">
+      <c r="N35">
         <v>291800546.163984</v>
-      </c>
-      <c r="K35">
-        <v>490092230.354854</v>
-      </c>
-      <c r="L35">
-        <v>162000872.47874</v>
-      </c>
-      <c r="M35">
-        <v>41704514.4988458</v>
-      </c>
-      <c r="N35">
-        <v>29177418.0268327</v>
       </c>
       <c r="O35">
         <v>1752240952.06815</v>
@@ -44014,25 +44014,25 @@
         <v>590111687.524639</v>
       </c>
       <c r="H36">
+        <v>483119627.415885</v>
+      </c>
+      <c r="I36">
+        <v>145689754.19372</v>
+      </c>
+      <c r="J36">
+        <v>51557465.376771</v>
+      </c>
+      <c r="K36">
+        <v>41596933.5362993</v>
+      </c>
+      <c r="L36">
         <v>12962849.2971324</v>
       </c>
-      <c r="I36">
+      <c r="M36">
         <v>673532270.509964</v>
       </c>
-      <c r="J36">
+      <c r="N36">
         <v>273548717.375949</v>
-      </c>
-      <c r="K36">
-        <v>483119627.415885</v>
-      </c>
-      <c r="L36">
-        <v>145689754.19372</v>
-      </c>
-      <c r="M36">
-        <v>51557465.376771</v>
-      </c>
-      <c r="N36">
-        <v>41596933.5362993</v>
       </c>
       <c r="O36">
         <v>1675177287.10908</v>
@@ -44069,25 +44069,25 @@
         <v>568409918.007805</v>
       </c>
       <c r="H37">
+        <v>528798977.956776</v>
+      </c>
+      <c r="I37">
+        <v>144162859.339693</v>
+      </c>
+      <c r="J37">
+        <v>50560599.0532598</v>
+      </c>
+      <c r="K37">
+        <v>51234851.2222959</v>
+      </c>
+      <c r="L37">
         <v>12623645.9978195</v>
       </c>
-      <c r="I37">
+      <c r="M37">
         <v>702206247.739013</v>
       </c>
-      <c r="J37">
+      <c r="N37">
         <v>277357618.614268</v>
-      </c>
-      <c r="K37">
-        <v>528798977.956776</v>
-      </c>
-      <c r="L37">
-        <v>144162859.339693</v>
-      </c>
-      <c r="M37">
-        <v>50560599.0532598</v>
-      </c>
-      <c r="N37">
-        <v>51234851.2222959</v>
       </c>
       <c r="O37">
         <v>1772872349.26945</v>
@@ -44124,25 +44124,25 @@
         <v>576403741.046301</v>
       </c>
       <c r="H38">
+        <v>530172198.091914</v>
+      </c>
+      <c r="I38">
+        <v>139491623.961053</v>
+      </c>
+      <c r="J38">
+        <v>50262413.0413402</v>
+      </c>
+      <c r="K38">
+        <v>56621538.5988604</v>
+      </c>
+      <c r="L38">
         <v>13563298.7612551</v>
       </c>
-      <c r="I38">
+      <c r="M38">
         <v>732994302.4512891</v>
       </c>
-      <c r="J38">
+      <c r="N38">
         <v>283568439.738662</v>
-      </c>
-      <c r="K38">
-        <v>530172198.091914</v>
-      </c>
-      <c r="L38">
-        <v>139491623.961053</v>
-      </c>
-      <c r="M38">
-        <v>50262413.0413402</v>
-      </c>
-      <c r="N38">
-        <v>56621538.5988604</v>
       </c>
       <c r="O38">
         <v>1822006376.54031</v>
@@ -44179,25 +44179,25 @@
         <v>605240463.876428</v>
       </c>
       <c r="H39">
+        <v>562702831.08727</v>
+      </c>
+      <c r="I39">
+        <v>142038768.864038</v>
+      </c>
+      <c r="J39">
+        <v>53561484.0573555</v>
+      </c>
+      <c r="K39">
+        <v>55685380.0381576</v>
+      </c>
+      <c r="L39">
         <v>13402036.0351041</v>
       </c>
-      <c r="I39">
+      <c r="M39">
         <v>722624269.080045</v>
       </c>
-      <c r="J39">
+      <c r="N39">
         <v>288715185.190789</v>
-      </c>
-      <c r="K39">
-        <v>562702831.08727</v>
-      </c>
-      <c r="L39">
-        <v>142038768.864038</v>
-      </c>
-      <c r="M39">
-        <v>53561484.0573555</v>
-      </c>
-      <c r="N39">
-        <v>55685380.0381576</v>
       </c>
       <c r="O39">
         <v>1824410300.4477</v>
@@ -44234,25 +44234,25 @@
         <v>612562885.566907</v>
       </c>
       <c r="H40">
+        <v>569280919.2426749</v>
+      </c>
+      <c r="I40">
+        <v>148370372.570974</v>
+      </c>
+      <c r="J40">
+        <v>55523978.9055572</v>
+      </c>
+      <c r="K40">
+        <v>44892904.316759</v>
+      </c>
+      <c r="L40">
         <v>16440502.5143283</v>
       </c>
-      <c r="I40">
+      <c r="M40">
         <v>745445423.008065</v>
       </c>
-      <c r="J40">
+      <c r="N40">
         <v>297218344.50881</v>
-      </c>
-      <c r="K40">
-        <v>569280919.2426749</v>
-      </c>
-      <c r="L40">
-        <v>148370372.570974</v>
-      </c>
-      <c r="M40">
-        <v>55523978.9055572</v>
-      </c>
-      <c r="N40">
-        <v>44892904.316759</v>
       </c>
       <c r="O40">
         <v>1875868282.10997</v>
@@ -44289,25 +44289,25 @@
         <v>638355460.348598</v>
       </c>
       <c r="H41">
+        <v>554882969.615383</v>
+      </c>
+      <c r="I41">
+        <v>146212884.560081</v>
+      </c>
+      <c r="J41">
+        <v>46839898.5282247</v>
+      </c>
+      <c r="K41">
+        <v>42619745.258878</v>
+      </c>
+      <c r="L41">
         <v>19677302.24887</v>
       </c>
-      <c r="I41">
+      <c r="M41">
         <v>767959930.842779</v>
       </c>
-      <c r="J41">
+      <c r="N41">
         <v>289302076.95794</v>
-      </c>
-      <c r="K41">
-        <v>554882969.615383</v>
-      </c>
-      <c r="L41">
-        <v>146212884.560081</v>
-      </c>
-      <c r="M41">
-        <v>46839898.5282247</v>
-      </c>
-      <c r="N41">
-        <v>42619745.258878</v>
       </c>
       <c r="O41">
         <v>1858409731.7224</v>
@@ -44344,25 +44344,25 @@
         <v>655560242.752618</v>
       </c>
       <c r="H42">
+        <v>565974340.813411</v>
+      </c>
+      <c r="I42">
+        <v>148942706.012282</v>
+      </c>
+      <c r="J42">
+        <v>46545713.2564346</v>
+      </c>
+      <c r="K42">
+        <v>42174456.5908935</v>
+      </c>
+      <c r="L42">
         <v>27784829.4448457</v>
       </c>
-      <c r="I42">
+      <c r="M42">
         <v>784649786.223696</v>
       </c>
-      <c r="J42">
+      <c r="N42">
         <v>288138413.813965</v>
-      </c>
-      <c r="K42">
-        <v>565974340.813411</v>
-      </c>
-      <c r="L42">
-        <v>148942706.012282</v>
-      </c>
-      <c r="M42">
-        <v>46545713.2564346</v>
-      </c>
-      <c r="N42">
-        <v>42174456.5908935</v>
       </c>
       <c r="O42">
         <v>1922659755.7793</v>
@@ -44399,25 +44399,25 @@
         <v>665791058.277915</v>
       </c>
       <c r="H43">
+        <v>574595769.015188</v>
+      </c>
+      <c r="I43">
+        <v>175899239.847147</v>
+      </c>
+      <c r="J43">
+        <v>47784986.4826352</v>
+      </c>
+      <c r="K43">
+        <v>43597260.9781143</v>
+      </c>
+      <c r="L43">
         <v>30481310.352544</v>
       </c>
-      <c r="I43">
+      <c r="M43">
         <v>805750616.828476</v>
       </c>
-      <c r="J43">
+      <c r="N43">
         <v>292904734.035202</v>
-      </c>
-      <c r="K43">
-        <v>574595769.015188</v>
-      </c>
-      <c r="L43">
-        <v>175899239.847147</v>
-      </c>
-      <c r="M43">
-        <v>47784986.4826352</v>
-      </c>
-      <c r="N43">
-        <v>43597260.9781143</v>
       </c>
       <c r="O43">
         <v>1968128831.65651</v>
@@ -44454,25 +44454,25 @@
         <v>716344851.262143</v>
       </c>
       <c r="H44">
+        <v>583043327.027298</v>
+      </c>
+      <c r="I44">
+        <v>171281308.525334</v>
+      </c>
+      <c r="J44">
+        <v>49916438.1943816</v>
+      </c>
+      <c r="K44">
+        <v>48170761.7983177</v>
+      </c>
+      <c r="L44">
         <v>29925342.6739936</v>
       </c>
-      <c r="I44">
+      <c r="M44">
         <v>822137001.931307</v>
       </c>
-      <c r="J44">
+      <c r="N44">
         <v>290009879.9193</v>
-      </c>
-      <c r="K44">
-        <v>583043327.027298</v>
-      </c>
-      <c r="L44">
-        <v>171281308.525334</v>
-      </c>
-      <c r="M44">
-        <v>49916438.1943816</v>
-      </c>
-      <c r="N44">
-        <v>48170761.7983177</v>
       </c>
       <c r="O44">
         <v>1977979733.06085</v>
@@ -44509,25 +44509,25 @@
         <v>715095608.230128</v>
       </c>
       <c r="H45">
+        <v>577078541.230679</v>
+      </c>
+      <c r="I45">
+        <v>161679196.220338</v>
+      </c>
+      <c r="J45">
+        <v>57821036.4845414</v>
+      </c>
+      <c r="K45">
+        <v>47896369.5995692</v>
+      </c>
+      <c r="L45">
         <v>26583683.3494753</v>
       </c>
-      <c r="I45">
+      <c r="M45">
         <v>809754462.960415</v>
       </c>
-      <c r="J45">
+      <c r="N45">
         <v>297027370.885861</v>
-      </c>
-      <c r="K45">
-        <v>577078541.230679</v>
-      </c>
-      <c r="L45">
-        <v>161679196.220338</v>
-      </c>
-      <c r="M45">
-        <v>57821036.4845414</v>
-      </c>
-      <c r="N45">
-        <v>47896369.5995692</v>
       </c>
       <c r="O45">
         <v>1974373802.73227</v>
@@ -44564,25 +44564,25 @@
         <v>728988429.720035</v>
       </c>
       <c r="H46">
+        <v>553662596.310416</v>
+      </c>
+      <c r="I46">
+        <v>160276777.723444</v>
+      </c>
+      <c r="J46">
+        <v>50039486.515841</v>
+      </c>
+      <c r="K46">
+        <v>49569426.5806657</v>
+      </c>
+      <c r="L46">
         <v>21955153.5512201</v>
       </c>
-      <c r="I46">
+      <c r="M46">
         <v>819893299.302138</v>
       </c>
-      <c r="J46">
+      <c r="N46">
         <v>282440313.939261</v>
-      </c>
-      <c r="K46">
-        <v>553662596.310416</v>
-      </c>
-      <c r="L46">
-        <v>160276777.723444</v>
-      </c>
-      <c r="M46">
-        <v>50039486.515841</v>
-      </c>
-      <c r="N46">
-        <v>49569426.5806657</v>
       </c>
       <c r="O46">
         <v>1953254140.78468</v>
@@ -44619,25 +44619,25 @@
         <v>725658360.982915</v>
       </c>
       <c r="H47">
+        <v>567425674.271552</v>
+      </c>
+      <c r="I47">
+        <v>158162923.0692</v>
+      </c>
+      <c r="J47">
+        <v>58904075.3434478</v>
+      </c>
+      <c r="K47">
+        <v>52772354.1846799</v>
+      </c>
+      <c r="L47">
         <v>24597976.9637527</v>
       </c>
-      <c r="I47">
+      <c r="M47">
         <v>836978545.9041981</v>
       </c>
-      <c r="J47">
+      <c r="N47">
         <v>280061506.703844</v>
-      </c>
-      <c r="K47">
-        <v>567425674.271552</v>
-      </c>
-      <c r="L47">
-        <v>158162923.0692</v>
-      </c>
-      <c r="M47">
-        <v>58904075.3434478</v>
-      </c>
-      <c r="N47">
-        <v>52772354.1846799</v>
       </c>
       <c r="O47">
         <v>1972376759.68145</v>
@@ -44674,25 +44674,25 @@
         <v>698628607.69038</v>
       </c>
       <c r="H48">
+        <v>552411290.080242</v>
+      </c>
+      <c r="I48">
+        <v>152841181.232064</v>
+      </c>
+      <c r="J48">
+        <v>56450630.078929</v>
+      </c>
+      <c r="K48">
+        <v>52402927.0398562</v>
+      </c>
+      <c r="L48">
         <v>26580773.9586296</v>
       </c>
-      <c r="I48">
+      <c r="M48">
         <v>863118848.8284431</v>
       </c>
-      <c r="J48">
+      <c r="N48">
         <v>279738406.384615</v>
-      </c>
-      <c r="K48">
-        <v>552411290.080242</v>
-      </c>
-      <c r="L48">
-        <v>152841181.232064</v>
-      </c>
-      <c r="M48">
-        <v>56450630.078929</v>
-      </c>
-      <c r="N48">
-        <v>52402927.0398562</v>
       </c>
       <c r="O48">
         <v>1975917961.62768</v>
@@ -44729,25 +44729,25 @@
         <v>701847165.555344</v>
       </c>
       <c r="H49">
+        <v>560258693.177668</v>
+      </c>
+      <c r="I49">
+        <v>159710577.527304</v>
+      </c>
+      <c r="J49">
+        <v>54448572.9728995</v>
+      </c>
+      <c r="K49">
+        <v>57791056.4004889</v>
+      </c>
+      <c r="L49">
         <v>26560562.5176846</v>
       </c>
-      <c r="I49">
+      <c r="M49">
         <v>853414895.490388</v>
       </c>
-      <c r="J49">
+      <c r="N49">
         <v>291645766.061906</v>
-      </c>
-      <c r="K49">
-        <v>560258693.177668</v>
-      </c>
-      <c r="L49">
-        <v>159710577.527304</v>
-      </c>
-      <c r="M49">
-        <v>54448572.9728995</v>
-      </c>
-      <c r="N49">
-        <v>57791056.4004889</v>
       </c>
       <c r="O49">
         <v>2002850842.7638</v>
@@ -44784,25 +44784,25 @@
         <v>710884921.33857</v>
       </c>
       <c r="H50">
+        <v>586653684.749441</v>
+      </c>
+      <c r="I50">
+        <v>157517237.023592</v>
+      </c>
+      <c r="J50">
+        <v>58348823.4626647</v>
+      </c>
+      <c r="K50">
+        <v>42926986.8750206</v>
+      </c>
+      <c r="L50">
         <v>28403568.2682698</v>
       </c>
-      <c r="I50">
+      <c r="M50">
         <v>846430282.309832</v>
       </c>
-      <c r="J50">
+      <c r="N50">
         <v>284831167.265993</v>
-      </c>
-      <c r="K50">
-        <v>586653684.749441</v>
-      </c>
-      <c r="L50">
-        <v>157517237.023592</v>
-      </c>
-      <c r="M50">
-        <v>58348823.4626647</v>
-      </c>
-      <c r="N50">
-        <v>42926986.8750206</v>
       </c>
       <c r="O50">
         <v>2027010850.33374</v>
@@ -44839,25 +44839,25 @@
         <v>713051347.674818</v>
       </c>
       <c r="H51">
+        <v>588469952.250088</v>
+      </c>
+      <c r="I51">
+        <v>179530522.080808</v>
+      </c>
+      <c r="J51">
+        <v>52791329.5619851</v>
+      </c>
+      <c r="K51">
+        <v>40034348.456518</v>
+      </c>
+      <c r="L51">
         <v>29065124.1697053</v>
       </c>
-      <c r="I51">
+      <c r="M51">
         <v>852622957.184901</v>
       </c>
-      <c r="J51">
+      <c r="N51">
         <v>290213262.786242</v>
-      </c>
-      <c r="K51">
-        <v>588469952.250088</v>
-      </c>
-      <c r="L51">
-        <v>179530522.080808</v>
-      </c>
-      <c r="M51">
-        <v>52791329.5619851</v>
-      </c>
-      <c r="N51">
-        <v>40034348.456518</v>
       </c>
       <c r="O51">
         <v>2021289859.47727</v>
@@ -44894,25 +44894,25 @@
         <v>715422136.835848</v>
       </c>
       <c r="H52">
+        <v>615679235.672847</v>
+      </c>
+      <c r="I52">
+        <v>173142747.529768</v>
+      </c>
+      <c r="J52">
+        <v>52624003.7801075</v>
+      </c>
+      <c r="K52">
+        <v>45667031.1330777</v>
+      </c>
+      <c r="L52">
         <v>27737807.7673705</v>
       </c>
-      <c r="I52">
+      <c r="M52">
         <v>847343740.413341</v>
       </c>
-      <c r="J52">
+      <c r="N52">
         <v>303188852.470907</v>
-      </c>
-      <c r="K52">
-        <v>615679235.672847</v>
-      </c>
-      <c r="L52">
-        <v>173142747.529768</v>
-      </c>
-      <c r="M52">
-        <v>52624003.7801075</v>
-      </c>
-      <c r="N52">
-        <v>45667031.1330777</v>
       </c>
       <c r="O52">
         <v>2064146490.74451</v>
@@ -44949,25 +44949,25 @@
         <v>727195693.08979</v>
       </c>
       <c r="H53">
+        <v>596311030.93893</v>
+      </c>
+      <c r="I53">
+        <v>192478368.77445</v>
+      </c>
+      <c r="J53">
+        <v>55653982.6066958</v>
+      </c>
+      <c r="K53">
+        <v>47427838.1591842</v>
+      </c>
+      <c r="L53">
         <v>30606471.4131728</v>
       </c>
-      <c r="I53">
+      <c r="M53">
         <v>859786216.548649</v>
       </c>
-      <c r="J53">
+      <c r="N53">
         <v>295447000.22814</v>
-      </c>
-      <c r="K53">
-        <v>596311030.93893</v>
-      </c>
-      <c r="L53">
-        <v>192478368.77445</v>
-      </c>
-      <c r="M53">
-        <v>55653982.6066958</v>
-      </c>
-      <c r="N53">
-        <v>47427838.1591842</v>
       </c>
       <c r="O53">
         <v>2077058811.47836</v>
@@ -45004,25 +45004,25 @@
         <v>701694500.625811</v>
       </c>
       <c r="H54">
+        <v>603084376.541281</v>
+      </c>
+      <c r="I54">
+        <v>192579941.007948</v>
+      </c>
+      <c r="J54">
+        <v>54040875.4503104</v>
+      </c>
+      <c r="K54">
+        <v>50077443.9071663</v>
+      </c>
+      <c r="L54">
         <v>24610302.8151272</v>
       </c>
-      <c r="I54">
+      <c r="M54">
         <v>869736629.9418</v>
       </c>
-      <c r="J54">
+      <c r="N54">
         <v>306763630.403923</v>
-      </c>
-      <c r="K54">
-        <v>603084376.541281</v>
-      </c>
-      <c r="L54">
-        <v>192579941.007948</v>
-      </c>
-      <c r="M54">
-        <v>54040875.4503104</v>
-      </c>
-      <c r="N54">
-        <v>50077443.9071663</v>
       </c>
       <c r="O54">
         <v>2100788229.94118</v>
@@ -45059,25 +45059,25 @@
         <v>693406078.4317451</v>
       </c>
       <c r="H55">
+        <v>596479560.752079</v>
+      </c>
+      <c r="I55">
+        <v>187858745.25061</v>
+      </c>
+      <c r="J55">
+        <v>50831772.0027001</v>
+      </c>
+      <c r="K55">
+        <v>55156277.4701901</v>
+      </c>
+      <c r="L55">
         <v>23393386.3532869</v>
       </c>
-      <c r="I55">
+      <c r="M55">
         <v>872533634.369872</v>
       </c>
-      <c r="J55">
+      <c r="N55">
         <v>312134516.192303</v>
-      </c>
-      <c r="K55">
-        <v>596479560.752079</v>
-      </c>
-      <c r="L55">
-        <v>187858745.25061</v>
-      </c>
-      <c r="M55">
-        <v>50831772.0027001</v>
-      </c>
-      <c r="N55">
-        <v>55156277.4701901</v>
       </c>
       <c r="O55">
         <v>2103570763.33268</v>
@@ -45114,25 +45114,25 @@
         <v>719933206.707925</v>
       </c>
       <c r="H56">
+        <v>595613918.385362</v>
+      </c>
+      <c r="I56">
+        <v>198849337.712661</v>
+      </c>
+      <c r="J56">
+        <v>50361819.2947658</v>
+      </c>
+      <c r="K56">
+        <v>62610736.7496288</v>
+      </c>
+      <c r="L56">
         <v>22212560.3423691</v>
       </c>
-      <c r="I56">
+      <c r="M56">
         <v>845460219.8727289</v>
       </c>
-      <c r="J56">
+      <c r="N56">
         <v>303893094.680951</v>
-      </c>
-      <c r="K56">
-        <v>595613918.385362</v>
-      </c>
-      <c r="L56">
-        <v>198849337.712661</v>
-      </c>
-      <c r="M56">
-        <v>50361819.2947658</v>
-      </c>
-      <c r="N56">
-        <v>62610736.7496288</v>
       </c>
       <c r="O56">
         <v>2077193460.37924</v>
@@ -45192,37 +45192,37 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Comércio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Informação e comunicação</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Atividades financeiras, de seguros e serviços relacionados</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Atividades imobiliárias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Outras atividades de serviços</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Adm., defesa, saúde e educação públicas e seguridade social</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Comércio</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Transporte, armazenagem e correio</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Informação e comunicação</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Atividades financeiras, de seguros e serviços relacionados</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -45266,25 +45266,25 @@
         <v>703534471.265469</v>
       </c>
       <c r="H2">
+        <v>526611934.791947</v>
+      </c>
+      <c r="I2">
+        <v>160719147.300328</v>
+      </c>
+      <c r="J2">
+        <v>30324772.7951471</v>
+      </c>
+      <c r="K2">
+        <v>35981451.5161079</v>
+      </c>
+      <c r="L2">
         <v>13615146.3048959</v>
       </c>
-      <c r="I2">
+      <c r="M2">
         <v>685607322.895228</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <v>233369394.840776</v>
-      </c>
-      <c r="K2">
-        <v>526611934.791947</v>
-      </c>
-      <c r="L2">
-        <v>160719147.300328</v>
-      </c>
-      <c r="M2">
-        <v>30324772.7951471</v>
-      </c>
-      <c r="N2">
-        <v>35981451.5161079</v>
       </c>
       <c r="O2">
         <v>1686560054.35173</v>
@@ -45321,25 +45321,25 @@
         <v>737428679.94041</v>
       </c>
       <c r="H3">
+        <v>530992637.919014</v>
+      </c>
+      <c r="I3">
+        <v>156572377.112535</v>
+      </c>
+      <c r="J3">
+        <v>30705400.8029358</v>
+      </c>
+      <c r="K3">
+        <v>40673705.3436429</v>
+      </c>
+      <c r="L3">
         <v>16355602.3413502</v>
       </c>
-      <c r="I3">
+      <c r="M3">
         <v>657922723.914042</v>
       </c>
-      <c r="J3">
+      <c r="N3">
         <v>238239005.325631</v>
-      </c>
-      <c r="K3">
-        <v>530992637.919014</v>
-      </c>
-      <c r="L3">
-        <v>156572377.112535</v>
-      </c>
-      <c r="M3">
-        <v>30705400.8029358</v>
-      </c>
-      <c r="N3">
-        <v>40673705.3436429</v>
       </c>
       <c r="O3">
         <v>1667455652.50748</v>
@@ -45376,25 +45376,25 @@
         <v>719095344.147553</v>
       </c>
       <c r="H4">
+        <v>538254849.7970999</v>
+      </c>
+      <c r="I4">
+        <v>157823102.494514</v>
+      </c>
+      <c r="J4">
+        <v>34015180.030842</v>
+      </c>
+      <c r="K4">
+        <v>37943244.2729754</v>
+      </c>
+      <c r="L4">
         <v>20341137.9003249</v>
       </c>
-      <c r="I4">
+      <c r="M4">
         <v>659753090.932901</v>
       </c>
-      <c r="J4">
+      <c r="N4">
         <v>245507964.045954</v>
-      </c>
-      <c r="K4">
-        <v>538254849.7970999</v>
-      </c>
-      <c r="L4">
-        <v>157823102.494514</v>
-      </c>
-      <c r="M4">
-        <v>34015180.030842</v>
-      </c>
-      <c r="N4">
-        <v>37943244.2729754</v>
       </c>
       <c r="O4">
         <v>1697029246.72972</v>
@@ -45431,25 +45431,25 @@
         <v>704863357.163136</v>
       </c>
       <c r="H5">
+        <v>538142095.424318</v>
+      </c>
+      <c r="I5">
+        <v>165757263.647705</v>
+      </c>
+      <c r="J5">
+        <v>32749749.8295236</v>
+      </c>
+      <c r="K5">
+        <v>38870895.9634897</v>
+      </c>
+      <c r="L5">
         <v>21865451.5960646</v>
       </c>
-      <c r="I5">
+      <c r="M5">
         <v>641836823.3358181</v>
       </c>
-      <c r="J5">
+      <c r="N5">
         <v>244965796.899992</v>
-      </c>
-      <c r="K5">
-        <v>538142095.424318</v>
-      </c>
-      <c r="L5">
-        <v>165757263.647705</v>
-      </c>
-      <c r="M5">
-        <v>32749749.8295236</v>
-      </c>
-      <c r="N5">
-        <v>38870895.9634897</v>
       </c>
       <c r="O5">
         <v>1685697273.72718</v>
@@ -45486,25 +45486,25 @@
         <v>707071359.473299</v>
       </c>
       <c r="H6">
+        <v>535987853.691256</v>
+      </c>
+      <c r="I6">
+        <v>164952052.679385</v>
+      </c>
+      <c r="J6">
+        <v>31183494.5032782</v>
+      </c>
+      <c r="K6">
+        <v>40323037.6949918</v>
+      </c>
+      <c r="L6">
         <v>22682683.5062202</v>
       </c>
-      <c r="I6">
+      <c r="M6">
         <v>630180072.218464</v>
       </c>
-      <c r="J6">
+      <c r="N6">
         <v>262286750.542302</v>
-      </c>
-      <c r="K6">
-        <v>535987853.691256</v>
-      </c>
-      <c r="L6">
-        <v>164952052.679385</v>
-      </c>
-      <c r="M6">
-        <v>31183494.5032782</v>
-      </c>
-      <c r="N6">
-        <v>40323037.6949918</v>
       </c>
       <c r="O6">
         <v>1692228371.83774</v>
@@ -45541,25 +45541,25 @@
         <v>740293864.516166</v>
       </c>
       <c r="H7">
+        <v>564384245.7238131</v>
+      </c>
+      <c r="I7">
+        <v>164022431.292105</v>
+      </c>
+      <c r="J7">
+        <v>30325882.5369205</v>
+      </c>
+      <c r="K7">
+        <v>41122800.3134662</v>
+      </c>
+      <c r="L7">
         <v>25452487.6080173</v>
       </c>
-      <c r="I7">
+      <c r="M7">
         <v>641612379.501209</v>
       </c>
-      <c r="J7">
+      <c r="N7">
         <v>271946392.873169</v>
-      </c>
-      <c r="K7">
-        <v>564384245.7238131</v>
-      </c>
-      <c r="L7">
-        <v>164022431.292105</v>
-      </c>
-      <c r="M7">
-        <v>30325882.5369205</v>
-      </c>
-      <c r="N7">
-        <v>41122800.3134662</v>
       </c>
       <c r="O7">
         <v>1737332703.01931</v>
@@ -45596,25 +45596,25 @@
         <v>732048671.4510961</v>
       </c>
       <c r="H8">
+        <v>577209065.1119829</v>
+      </c>
+      <c r="I8">
+        <v>166910466.049422</v>
+      </c>
+      <c r="J8">
+        <v>29850442.4522559</v>
+      </c>
+      <c r="K8">
+        <v>40626873.0810401</v>
+      </c>
+      <c r="L8">
         <v>27234573.1888926</v>
       </c>
-      <c r="I8">
+      <c r="M8">
         <v>680631122.944963</v>
       </c>
-      <c r="J8">
+      <c r="N8">
         <v>264726062.656457</v>
-      </c>
-      <c r="K8">
-        <v>577209065.1119829</v>
-      </c>
-      <c r="L8">
-        <v>166910466.049422</v>
-      </c>
-      <c r="M8">
-        <v>29850442.4522559</v>
-      </c>
-      <c r="N8">
-        <v>40626873.0810401</v>
       </c>
       <c r="O8">
         <v>1781091457.53379</v>
@@ -45651,25 +45651,25 @@
         <v>713622014.684018</v>
       </c>
       <c r="H9">
+        <v>597050309.793286</v>
+      </c>
+      <c r="I9">
+        <v>159759600.604784</v>
+      </c>
+      <c r="J9">
+        <v>32961709.9798264</v>
+      </c>
+      <c r="K9">
+        <v>37608659.5282145</v>
+      </c>
+      <c r="L9">
         <v>22246248.84344</v>
       </c>
-      <c r="I9">
+      <c r="M9">
         <v>692521596.183907</v>
       </c>
-      <c r="J9">
+      <c r="N9">
         <v>258882592.237452</v>
-      </c>
-      <c r="K9">
-        <v>597050309.793286</v>
-      </c>
-      <c r="L9">
-        <v>159759600.604784</v>
-      </c>
-      <c r="M9">
-        <v>32961709.9798264</v>
-      </c>
-      <c r="N9">
-        <v>37608659.5282145</v>
       </c>
       <c r="O9">
         <v>1802933414.02596</v>
@@ -45706,25 +45706,25 @@
         <v>715604255.272693</v>
       </c>
       <c r="H10">
+        <v>584091792.292088</v>
+      </c>
+      <c r="I10">
+        <v>154211012.528451</v>
+      </c>
+      <c r="J10">
+        <v>34116739.4823918</v>
+      </c>
+      <c r="K10">
+        <v>36255735.7576918</v>
+      </c>
+      <c r="L10">
         <v>22038955.2527366</v>
       </c>
-      <c r="I10">
+      <c r="M10">
         <v>692325302.097378</v>
       </c>
-      <c r="J10">
+      <c r="N10">
         <v>250119638.078063</v>
-      </c>
-      <c r="K10">
-        <v>584091792.292088</v>
-      </c>
-      <c r="L10">
-        <v>154211012.528451</v>
-      </c>
-      <c r="M10">
-        <v>34116739.4823918</v>
-      </c>
-      <c r="N10">
-        <v>36255735.7576918</v>
       </c>
       <c r="O10">
         <v>1780788015.5433</v>
@@ -45761,25 +45761,25 @@
         <v>702616451.167357</v>
       </c>
       <c r="H11">
+        <v>564409314.992209</v>
+      </c>
+      <c r="I11">
+        <v>144611643.24731</v>
+      </c>
+      <c r="J11">
+        <v>32874240.8502794</v>
+      </c>
+      <c r="K11">
+        <v>36272666.0350951</v>
+      </c>
+      <c r="L11">
         <v>17634845.3703214</v>
       </c>
-      <c r="I11">
+      <c r="M11">
         <v>735231990.876315</v>
       </c>
-      <c r="J11">
+      <c r="N11">
         <v>253207805.656218</v>
-      </c>
-      <c r="K11">
-        <v>564409314.992209</v>
-      </c>
-      <c r="L11">
-        <v>144611643.24731</v>
-      </c>
-      <c r="M11">
-        <v>32874240.8502794</v>
-      </c>
-      <c r="N11">
-        <v>36272666.0350951</v>
       </c>
       <c r="O11">
         <v>1781458307.57497</v>
@@ -45816,25 +45816,25 @@
         <v>703021705.083727</v>
       </c>
       <c r="H12">
+        <v>557579212.384495</v>
+      </c>
+      <c r="I12">
+        <v>149386495.858397</v>
+      </c>
+      <c r="J12">
+        <v>34244162.987285</v>
+      </c>
+      <c r="K12">
+        <v>40028827.128866</v>
+      </c>
+      <c r="L12">
         <v>20637855.3513944</v>
       </c>
-      <c r="I12">
+      <c r="M12">
         <v>730566094.477897</v>
       </c>
-      <c r="J12">
+      <c r="N12">
         <v>256463685.038767</v>
-      </c>
-      <c r="K12">
-        <v>557579212.384495</v>
-      </c>
-      <c r="L12">
-        <v>149386495.858397</v>
-      </c>
-      <c r="M12">
-        <v>34244162.987285</v>
-      </c>
-      <c r="N12">
-        <v>40028827.128866</v>
       </c>
       <c r="O12">
         <v>1780355576.29935</v>
@@ -45871,25 +45871,25 @@
         <v>693082677.552429</v>
       </c>
       <c r="H13">
+        <v>555403915.751642</v>
+      </c>
+      <c r="I13">
+        <v>147517935.334511</v>
+      </c>
+      <c r="J13">
+        <v>35558599.3589865</v>
+      </c>
+      <c r="K13">
+        <v>36039023.4238832</v>
+      </c>
+      <c r="L13">
         <v>22269919.3777979</v>
       </c>
-      <c r="I13">
+      <c r="M13">
         <v>727830419.089758</v>
       </c>
-      <c r="J13">
+      <c r="N13">
         <v>256485515.47433</v>
-      </c>
-      <c r="K13">
-        <v>555403915.751642</v>
-      </c>
-      <c r="L13">
-        <v>147517935.334511</v>
-      </c>
-      <c r="M13">
-        <v>35558599.3589865</v>
-      </c>
-      <c r="N13">
-        <v>36039023.4238832</v>
       </c>
       <c r="O13">
         <v>1784167055.89377</v>
@@ -45926,25 +45926,25 @@
         <v>690005231.637816</v>
       </c>
       <c r="H14">
+        <v>574155375.537962</v>
+      </c>
+      <c r="I14">
+        <v>143634026.576859</v>
+      </c>
+      <c r="J14">
+        <v>37620794.5810638</v>
+      </c>
+      <c r="K14">
+        <v>40408644.5902362</v>
+      </c>
+      <c r="L14">
         <v>21613092.6649616</v>
       </c>
-      <c r="I14">
+      <c r="M14">
         <v>731073704.851171</v>
       </c>
-      <c r="J14">
+      <c r="N14">
         <v>260880806.895894</v>
-      </c>
-      <c r="K14">
-        <v>574155375.537962</v>
-      </c>
-      <c r="L14">
-        <v>143634026.576859</v>
-      </c>
-      <c r="M14">
-        <v>37620794.5810638</v>
-      </c>
-      <c r="N14">
-        <v>40408644.5902362</v>
       </c>
       <c r="O14">
         <v>1816676862.12768</v>
@@ -45981,25 +45981,25 @@
         <v>665079100.164544</v>
       </c>
       <c r="H15">
+        <v>569492774.726541</v>
+      </c>
+      <c r="I15">
+        <v>156769725.382116</v>
+      </c>
+      <c r="J15">
+        <v>40061845.4845502</v>
+      </c>
+      <c r="K15">
+        <v>37491386.9946869</v>
+      </c>
+      <c r="L15">
         <v>21227583.5331682</v>
       </c>
-      <c r="I15">
+      <c r="M15">
         <v>724826462.321098</v>
       </c>
-      <c r="J15">
+      <c r="N15">
         <v>254842150.773539</v>
-      </c>
-      <c r="K15">
-        <v>569492774.726541</v>
-      </c>
-      <c r="L15">
-        <v>156769725.382116</v>
-      </c>
-      <c r="M15">
-        <v>40061845.4845502</v>
-      </c>
-      <c r="N15">
-        <v>37491386.9946869</v>
       </c>
       <c r="O15">
         <v>1800999249.6793</v>
@@ -46036,25 +46036,25 @@
         <v>668341487.203418</v>
       </c>
       <c r="H16">
+        <v>564908008.5072629</v>
+      </c>
+      <c r="I16">
+        <v>151129193.375135</v>
+      </c>
+      <c r="J16">
+        <v>37456081.7864383</v>
+      </c>
+      <c r="K16">
+        <v>34812677.6511834</v>
+      </c>
+      <c r="L16">
         <v>16262435.5012269</v>
       </c>
-      <c r="I16">
+      <c r="M16">
         <v>696659775.889302</v>
       </c>
-      <c r="J16">
+      <c r="N16">
         <v>258509431.156383</v>
-      </c>
-      <c r="K16">
-        <v>564908008.5072629</v>
-      </c>
-      <c r="L16">
-        <v>151129193.375135</v>
-      </c>
-      <c r="M16">
-        <v>37456081.7864383</v>
-      </c>
-      <c r="N16">
-        <v>34812677.6511834</v>
       </c>
       <c r="O16">
         <v>1749932435.57118</v>
@@ -46091,25 +46091,25 @@
         <v>691944938.546779</v>
       </c>
       <c r="H17">
+        <v>557773804.794091</v>
+      </c>
+      <c r="I17">
+        <v>157004835.075938</v>
+      </c>
+      <c r="J17">
+        <v>42575892.7448167</v>
+      </c>
+      <c r="K17">
+        <v>36082849.7266163</v>
+      </c>
+      <c r="L17">
         <v>17126405.6437068</v>
       </c>
-      <c r="I17">
+      <c r="M17">
         <v>711791515.7373379</v>
       </c>
-      <c r="J17">
+      <c r="N17">
         <v>269157317.520988</v>
-      </c>
-      <c r="K17">
-        <v>557773804.794091</v>
-      </c>
-      <c r="L17">
-        <v>157004835.075938</v>
-      </c>
-      <c r="M17">
-        <v>42575892.7448167</v>
-      </c>
-      <c r="N17">
-        <v>36082849.7266163</v>
       </c>
       <c r="O17">
         <v>1797334903.06036</v>
@@ -46146,25 +46146,25 @@
         <v>696160488.396648</v>
       </c>
       <c r="H18">
+        <v>536823429.397032</v>
+      </c>
+      <c r="I18">
+        <v>159640572.950083</v>
+      </c>
+      <c r="J18">
+        <v>26423987.0861826</v>
+      </c>
+      <c r="K18">
+        <v>37891351.9583044</v>
+      </c>
+      <c r="L18">
         <v>17518632.2852033</v>
       </c>
-      <c r="I18">
+      <c r="M18">
         <v>714251263.232322</v>
       </c>
-      <c r="J18">
+      <c r="N18">
         <v>270579528.095362</v>
-      </c>
-      <c r="K18">
-        <v>536823429.397032</v>
-      </c>
-      <c r="L18">
-        <v>159640572.950083</v>
-      </c>
-      <c r="M18">
-        <v>26423987.0861826</v>
-      </c>
-      <c r="N18">
-        <v>37891351.9583044</v>
       </c>
       <c r="O18">
         <v>1759552601.99422</v>
@@ -46201,25 +46201,25 @@
         <v>683150946.5405051</v>
       </c>
       <c r="H19">
+        <v>535102413.867145</v>
+      </c>
+      <c r="I19">
+        <v>152710071.937302</v>
+      </c>
+      <c r="J19">
+        <v>34209976.3407052</v>
+      </c>
+      <c r="K19">
+        <v>39691034.0243675</v>
+      </c>
+      <c r="L19">
         <v>16948914.6477224</v>
       </c>
-      <c r="I19">
+      <c r="M19">
         <v>707917798.849027</v>
       </c>
-      <c r="J19">
+      <c r="N19">
         <v>269270690.402059</v>
-      </c>
-      <c r="K19">
-        <v>535102413.867145</v>
-      </c>
-      <c r="L19">
-        <v>152710071.937302</v>
-      </c>
-      <c r="M19">
-        <v>34209976.3407052</v>
-      </c>
-      <c r="N19">
-        <v>39691034.0243675</v>
       </c>
       <c r="O19">
         <v>1754105926.37421</v>
@@ -46256,25 +46256,25 @@
         <v>661680805.994148</v>
       </c>
       <c r="H20">
+        <v>543968780.323815</v>
+      </c>
+      <c r="I20">
+        <v>141151608.043951</v>
+      </c>
+      <c r="J20">
+        <v>31607317.9998139</v>
+      </c>
+      <c r="K20">
+        <v>40837314.0574341</v>
+      </c>
+      <c r="L20">
         <v>18972638.6044202</v>
       </c>
-      <c r="I20">
+      <c r="M20">
         <v>718281352.140893</v>
       </c>
-      <c r="J20">
+      <c r="N20">
         <v>270762233.925898</v>
-      </c>
-      <c r="K20">
-        <v>543968780.323815</v>
-      </c>
-      <c r="L20">
-        <v>141151608.043951</v>
-      </c>
-      <c r="M20">
-        <v>31607317.9998139</v>
-      </c>
-      <c r="N20">
-        <v>40837314.0574341</v>
       </c>
       <c r="O20">
         <v>1755390963.63232</v>
@@ -46311,25 +46311,25 @@
         <v>671403784.90842</v>
       </c>
       <c r="H21">
+        <v>522592511.30172</v>
+      </c>
+      <c r="I21">
+        <v>141018518.489902</v>
+      </c>
+      <c r="J21">
+        <v>30959472.6392717</v>
+      </c>
+      <c r="K21">
+        <v>41137931.9723006</v>
+      </c>
+      <c r="L21">
         <v>23629149.4594568</v>
       </c>
-      <c r="I21">
+      <c r="M21">
         <v>717938097.799931</v>
       </c>
-      <c r="J21">
+      <c r="N21">
         <v>251097171.115317</v>
-      </c>
-      <c r="K21">
-        <v>522592511.30172</v>
-      </c>
-      <c r="L21">
-        <v>141018518.489902</v>
-      </c>
-      <c r="M21">
-        <v>30959472.6392717</v>
-      </c>
-      <c r="N21">
-        <v>41137931.9723006</v>
       </c>
       <c r="O21">
         <v>1744772347.52984</v>
@@ -46366,25 +46366,25 @@
         <v>634540439.179731</v>
       </c>
       <c r="H22">
+        <v>544945607.826547</v>
+      </c>
+      <c r="I22">
+        <v>150534300.899003</v>
+      </c>
+      <c r="J22">
+        <v>32670259.0844874</v>
+      </c>
+      <c r="K22">
+        <v>38839376.7893798</v>
+      </c>
+      <c r="L22">
         <v>19906842.8617732</v>
       </c>
-      <c r="I22">
+      <c r="M22">
         <v>724360757.74225</v>
       </c>
-      <c r="J22">
+      <c r="N22">
         <v>260337132.31331</v>
-      </c>
-      <c r="K22">
-        <v>544945607.826547</v>
-      </c>
-      <c r="L22">
-        <v>150534300.899003</v>
-      </c>
-      <c r="M22">
-        <v>32670259.0844874</v>
-      </c>
-      <c r="N22">
-        <v>38839376.7893798</v>
       </c>
       <c r="O22">
         <v>1767463283.93404</v>
@@ -46421,25 +46421,25 @@
         <v>620501993.124454</v>
       </c>
       <c r="H23">
+        <v>547398343.335909</v>
+      </c>
+      <c r="I23">
+        <v>157062173.852688</v>
+      </c>
+      <c r="J23">
+        <v>31313170.512776</v>
+      </c>
+      <c r="K23">
+        <v>35175817.1312921</v>
+      </c>
+      <c r="L23">
         <v>24956410.8517264</v>
       </c>
-      <c r="I23">
+      <c r="M23">
         <v>720470490.227529</v>
       </c>
-      <c r="J23">
+      <c r="N23">
         <v>255303301.771137</v>
-      </c>
-      <c r="K23">
-        <v>547398343.335909</v>
-      </c>
-      <c r="L23">
-        <v>157062173.852688</v>
-      </c>
-      <c r="M23">
-        <v>31313170.512776</v>
-      </c>
-      <c r="N23">
-        <v>35175817.1312921</v>
       </c>
       <c r="O23">
         <v>1768429529.19835</v>
@@ -46476,25 +46476,25 @@
         <v>645798661.1530401</v>
       </c>
       <c r="H24">
+        <v>539689245.006516</v>
+      </c>
+      <c r="I24">
+        <v>153386547.77077</v>
+      </c>
+      <c r="J24">
+        <v>32431446.5603738</v>
+      </c>
+      <c r="K24">
+        <v>38093198.2916582</v>
+      </c>
+      <c r="L24">
         <v>23777479.4528351</v>
       </c>
-      <c r="I24">
+      <c r="M24">
         <v>738617030.472051</v>
       </c>
-      <c r="J24">
+      <c r="N24">
         <v>253986125.772635</v>
-      </c>
-      <c r="K24">
-        <v>539689245.006516</v>
-      </c>
-      <c r="L24">
-        <v>153386547.77077</v>
-      </c>
-      <c r="M24">
-        <v>32431446.5603738</v>
-      </c>
-      <c r="N24">
-        <v>38093198.2916582</v>
       </c>
       <c r="O24">
         <v>1777441114.21148</v>
@@ -46531,25 +46531,25 @@
         <v>634762144.7904299</v>
       </c>
       <c r="H25">
+        <v>531595925.724689</v>
+      </c>
+      <c r="I25">
+        <v>155656159.052289</v>
+      </c>
+      <c r="J25">
+        <v>32009842.4126045</v>
+      </c>
+      <c r="K25">
+        <v>37541231.5513335</v>
+      </c>
+      <c r="L25">
         <v>16812200.8777958</v>
       </c>
-      <c r="I25">
+      <c r="M25">
         <v>718790914.489804</v>
       </c>
-      <c r="J25">
+      <c r="N25">
         <v>265772540.640328</v>
-      </c>
-      <c r="K25">
-        <v>531595925.724689</v>
-      </c>
-      <c r="L25">
-        <v>155656159.052289</v>
-      </c>
-      <c r="M25">
-        <v>32009842.4126045</v>
-      </c>
-      <c r="N25">
-        <v>37541231.5513335</v>
       </c>
       <c r="O25">
         <v>1775687720.31349</v>
@@ -46586,25 +46586,25 @@
         <v>640759792.0384409</v>
       </c>
       <c r="H26">
+        <v>546428820.076098</v>
+      </c>
+      <c r="I26">
+        <v>156910451.860598</v>
+      </c>
+      <c r="J26">
+        <v>32779832.4144127</v>
+      </c>
+      <c r="K26">
+        <v>33433020.4980522</v>
+      </c>
+      <c r="L26">
         <v>19112565.1642792</v>
       </c>
-      <c r="I26">
+      <c r="M26">
         <v>706576822.372115</v>
       </c>
-      <c r="J26">
+      <c r="N26">
         <v>261663297.543976</v>
-      </c>
-      <c r="K26">
-        <v>546428820.076098</v>
-      </c>
-      <c r="L26">
-        <v>156910451.860598</v>
-      </c>
-      <c r="M26">
-        <v>32779832.4144127</v>
-      </c>
-      <c r="N26">
-        <v>33433020.4980522</v>
       </c>
       <c r="O26">
         <v>1751268179.40731</v>
@@ -46641,25 +46641,25 @@
         <v>658309667.853068</v>
       </c>
       <c r="H27">
+        <v>531172896.666564</v>
+      </c>
+      <c r="I27">
+        <v>150151239.205004</v>
+      </c>
+      <c r="J27">
+        <v>36965951.6524186</v>
+      </c>
+      <c r="K27">
+        <v>35539491.4086585</v>
+      </c>
+      <c r="L27">
         <v>19460287.488726</v>
       </c>
-      <c r="I27">
+      <c r="M27">
         <v>717780253.673591</v>
       </c>
-      <c r="J27">
+      <c r="N27">
         <v>259762296.912862</v>
-      </c>
-      <c r="K27">
-        <v>531172896.666564</v>
-      </c>
-      <c r="L27">
-        <v>150151239.205004</v>
-      </c>
-      <c r="M27">
-        <v>36965951.6524186</v>
-      </c>
-      <c r="N27">
-        <v>35539491.4086585</v>
       </c>
       <c r="O27">
         <v>1749451370.2268</v>
@@ -46696,25 +46696,25 @@
         <v>648795666.935582</v>
       </c>
       <c r="H28">
+        <v>520387952.775332</v>
+      </c>
+      <c r="I28">
+        <v>151712831.486236</v>
+      </c>
+      <c r="J28">
+        <v>36548769.3151163</v>
+      </c>
+      <c r="K28">
+        <v>31905552.0579025</v>
+      </c>
+      <c r="L28">
         <v>20971260.8523233</v>
       </c>
-      <c r="I28">
+      <c r="M28">
         <v>727374439.914229</v>
       </c>
-      <c r="J28">
+      <c r="N28">
         <v>264534166.686642</v>
-      </c>
-      <c r="K28">
-        <v>520387952.775332</v>
-      </c>
-      <c r="L28">
-        <v>151712831.486236</v>
-      </c>
-      <c r="M28">
-        <v>36548769.3151163</v>
-      </c>
-      <c r="N28">
-        <v>31905552.0579025</v>
       </c>
       <c r="O28">
         <v>1751167877.6975</v>
@@ -46751,25 +46751,25 @@
         <v>635786180.043058</v>
       </c>
       <c r="H29">
+        <v>523496868.528554</v>
+      </c>
+      <c r="I29">
+        <v>151219481.843331</v>
+      </c>
+      <c r="J29">
+        <v>39447129.2578705</v>
+      </c>
+      <c r="K29">
+        <v>32325549.7932557</v>
+      </c>
+      <c r="L29">
         <v>21603223.662319</v>
       </c>
-      <c r="I29">
+      <c r="M29">
         <v>748101766.459321</v>
       </c>
-      <c r="J29">
+      <c r="N29">
         <v>269019022.641084</v>
-      </c>
-      <c r="K29">
-        <v>523496868.528554</v>
-      </c>
-      <c r="L29">
-        <v>151219481.843331</v>
-      </c>
-      <c r="M29">
-        <v>39447129.2578705</v>
-      </c>
-      <c r="N29">
-        <v>32325549.7932557</v>
       </c>
       <c r="O29">
         <v>1793134722.34913</v>
@@ -46806,25 +46806,25 @@
         <v>639066193.039609</v>
       </c>
       <c r="H30">
+        <v>535142570.253511</v>
+      </c>
+      <c r="I30">
+        <v>155385518.233767</v>
+      </c>
+      <c r="J30">
+        <v>43770377.6634122</v>
+      </c>
+      <c r="K30">
+        <v>32702776.7225425</v>
+      </c>
+      <c r="L30">
         <v>21512872.0209914</v>
       </c>
-      <c r="I30">
+      <c r="M30">
         <v>759839925.336319</v>
       </c>
-      <c r="J30">
+      <c r="N30">
         <v>268941966.18967</v>
-      </c>
-      <c r="K30">
-        <v>535142570.253511</v>
-      </c>
-      <c r="L30">
-        <v>155385518.233767</v>
-      </c>
-      <c r="M30">
-        <v>43770377.6634122</v>
-      </c>
-      <c r="N30">
-        <v>32702776.7225425</v>
       </c>
       <c r="O30">
         <v>1821581695.56377</v>
@@ -46861,25 +46861,25 @@
         <v>643973412.30047</v>
       </c>
       <c r="H31">
+        <v>546186768.509218</v>
+      </c>
+      <c r="I31">
+        <v>167939426.883074</v>
+      </c>
+      <c r="J31">
+        <v>46435811.7849565</v>
+      </c>
+      <c r="K31">
+        <v>32803311.0689454</v>
+      </c>
+      <c r="L31">
         <v>19455609.6454375</v>
       </c>
-      <c r="I31">
+      <c r="M31">
         <v>751254146.835209</v>
       </c>
-      <c r="J31">
+      <c r="N31">
         <v>278416737.976</v>
-      </c>
-      <c r="K31">
-        <v>546186768.509218</v>
-      </c>
-      <c r="L31">
-        <v>167939426.883074</v>
-      </c>
-      <c r="M31">
-        <v>46435811.7849565</v>
-      </c>
-      <c r="N31">
-        <v>32803311.0689454</v>
       </c>
       <c r="O31">
         <v>1840980616.67067</v>
@@ -46916,25 +46916,25 @@
         <v>638422913.514552</v>
       </c>
       <c r="H32">
+        <v>558273713.20681</v>
+      </c>
+      <c r="I32">
+        <v>180139049.164689</v>
+      </c>
+      <c r="J32">
+        <v>42923437.6090244</v>
+      </c>
+      <c r="K32">
+        <v>33310757.1270601</v>
+      </c>
+      <c r="L32">
         <v>17499178.7832778</v>
       </c>
-      <c r="I32">
+      <c r="M32">
         <v>741402220.560798</v>
       </c>
-      <c r="J32">
+      <c r="N32">
         <v>282923831.650852</v>
-      </c>
-      <c r="K32">
-        <v>558273713.20681</v>
-      </c>
-      <c r="L32">
-        <v>180139049.164689</v>
-      </c>
-      <c r="M32">
-        <v>42923437.6090244</v>
-      </c>
-      <c r="N32">
-        <v>33310757.1270601</v>
       </c>
       <c r="O32">
         <v>1845640886.06405</v>
@@ -46971,25 +46971,25 @@
         <v>643900366.6204309</v>
       </c>
       <c r="H33">
+        <v>558531843.187826</v>
+      </c>
+      <c r="I33">
+        <v>173798273.959456</v>
+      </c>
+      <c r="J33">
+        <v>45169153.4658764</v>
+      </c>
+      <c r="K33">
+        <v>28416182.0999479</v>
+      </c>
+      <c r="L33">
         <v>21559874.3835475</v>
       </c>
-      <c r="I33">
+      <c r="M33">
         <v>759165709.962019</v>
       </c>
-      <c r="J33">
+      <c r="N33">
         <v>270960622.467471</v>
-      </c>
-      <c r="K33">
-        <v>558531843.187826</v>
-      </c>
-      <c r="L33">
-        <v>173798273.959456</v>
-      </c>
-      <c r="M33">
-        <v>45169153.4658764</v>
-      </c>
-      <c r="N33">
-        <v>28416182.0999479</v>
       </c>
       <c r="O33">
         <v>1864882479.57185</v>
@@ -47026,25 +47026,25 @@
         <v>601394188.790139</v>
       </c>
       <c r="H34">
+        <v>504897349.134393</v>
+      </c>
+      <c r="I34">
+        <v>166181942.242736</v>
+      </c>
+      <c r="J34">
+        <v>43202332.4604856</v>
+      </c>
+      <c r="K34">
+        <v>26037010.5404743</v>
+      </c>
+      <c r="L34">
         <v>14572059.494825</v>
       </c>
-      <c r="I34">
+      <c r="M34">
         <v>692213994.130759</v>
       </c>
-      <c r="J34">
+      <c r="N34">
         <v>266616423.026741</v>
-      </c>
-      <c r="K34">
-        <v>504897349.134393</v>
-      </c>
-      <c r="L34">
-        <v>166181942.242736</v>
-      </c>
-      <c r="M34">
-        <v>43202332.4604856</v>
-      </c>
-      <c r="N34">
-        <v>26037010.5404743</v>
       </c>
       <c r="O34">
         <v>1711078950.29523</v>
@@ -47081,25 +47081,25 @@
         <v>471178962.764437</v>
       </c>
       <c r="H35">
+        <v>401018779.663221</v>
+      </c>
+      <c r="I35">
+        <v>131015694.961548</v>
+      </c>
+      <c r="J35">
+        <v>35985124.8818389</v>
+      </c>
+      <c r="K35">
+        <v>26779690.579529</v>
+      </c>
+      <c r="L35">
         <v>13568663.7970596</v>
       </c>
-      <c r="I35">
+      <c r="M35">
         <v>544963786.009958</v>
       </c>
-      <c r="J35">
+      <c r="N35">
         <v>224327993.060687</v>
-      </c>
-      <c r="K35">
-        <v>401018779.663221</v>
-      </c>
-      <c r="L35">
-        <v>131015694.961548</v>
-      </c>
-      <c r="M35">
-        <v>35985124.8818389</v>
-      </c>
-      <c r="N35">
-        <v>26779690.579529</v>
       </c>
       <c r="O35">
         <v>1373233600.22912</v>
@@ -47136,25 +47136,25 @@
         <v>524314974.962112</v>
       </c>
       <c r="H36">
+        <v>437915780.310884</v>
+      </c>
+      <c r="I36">
+        <v>131772493.918246</v>
+      </c>
+      <c r="J36">
+        <v>47405878.7313424</v>
+      </c>
+      <c r="K36">
+        <v>40334847.5398381</v>
+      </c>
+      <c r="L36">
         <v>11879409.5941416</v>
       </c>
-      <c r="I36">
+      <c r="M36">
         <v>594063744.898737</v>
       </c>
-      <c r="J36">
+      <c r="N36">
         <v>238378480.30576</v>
-      </c>
-      <c r="K36">
-        <v>437915780.310884</v>
-      </c>
-      <c r="L36">
-        <v>131772493.918246</v>
-      </c>
-      <c r="M36">
-        <v>47405878.7313424</v>
-      </c>
-      <c r="N36">
-        <v>40334847.5398381</v>
       </c>
       <c r="O36">
         <v>1490560762.07664</v>
@@ -47191,25 +47191,25 @@
         <v>531290203.068905</v>
       </c>
       <c r="H37">
+        <v>506719690.646716</v>
+      </c>
+      <c r="I37">
+        <v>139223269.409343</v>
+      </c>
+      <c r="J37">
+        <v>48750477.9878651</v>
+      </c>
+      <c r="K37">
+        <v>48146375.300096</v>
+      </c>
+      <c r="L37">
         <v>11863098.5553099</v>
       </c>
-      <c r="I37">
+      <c r="M37">
         <v>651408827.172464</v>
       </c>
-      <c r="J37">
+      <c r="N37">
         <v>251279352.508347</v>
-      </c>
-      <c r="K37">
-        <v>506719690.646716</v>
-      </c>
-      <c r="L37">
-        <v>139223269.409343</v>
-      </c>
-      <c r="M37">
-        <v>48750477.9878651</v>
-      </c>
-      <c r="N37">
-        <v>48146375.300096</v>
       </c>
       <c r="O37">
         <v>1662337484.7663</v>
@@ -47246,25 +47246,25 @@
         <v>550879221.629162</v>
       </c>
       <c r="H38">
+        <v>517031972.372858</v>
+      </c>
+      <c r="I38">
+        <v>131377073.090921</v>
+      </c>
+      <c r="J38">
+        <v>50021770.867763</v>
+      </c>
+      <c r="K38">
+        <v>55736619.2423426</v>
+      </c>
+      <c r="L38">
         <v>13118004.2988119</v>
       </c>
-      <c r="I38">
+      <c r="M38">
         <v>696504993.861611</v>
       </c>
-      <c r="J38">
+      <c r="N38">
         <v>273561988.556472</v>
-      </c>
-      <c r="K38">
-        <v>517031972.372858</v>
-      </c>
-      <c r="L38">
-        <v>131377073.090921</v>
-      </c>
-      <c r="M38">
-        <v>50021770.867763</v>
-      </c>
-      <c r="N38">
-        <v>55736619.2423426</v>
       </c>
       <c r="O38">
         <v>1743428894.63069</v>
@@ -47301,25 +47301,25 @@
         <v>566792063.673833</v>
       </c>
       <c r="H39">
+        <v>540421250.875393</v>
+      </c>
+      <c r="I39">
+        <v>134749001.829931</v>
+      </c>
+      <c r="J39">
+        <v>51877433.1615517</v>
+      </c>
+      <c r="K39">
+        <v>53593716.0009238</v>
+      </c>
+      <c r="L39">
         <v>13207410.400434</v>
       </c>
-      <c r="I39">
+      <c r="M39">
         <v>678976592.853914</v>
       </c>
-      <c r="J39">
+      <c r="N39">
         <v>270510359.635291</v>
-      </c>
-      <c r="K39">
-        <v>540421250.875393</v>
-      </c>
-      <c r="L39">
-        <v>134749001.829931</v>
-      </c>
-      <c r="M39">
-        <v>51877433.1615517</v>
-      </c>
-      <c r="N39">
-        <v>53593716.0009238</v>
       </c>
       <c r="O39">
         <v>1739833294.54479</v>
@@ -47356,25 +47356,25 @@
         <v>579136304.8317209</v>
       </c>
       <c r="H40">
+        <v>550605623.581606</v>
+      </c>
+      <c r="I40">
+        <v>145929970.147427</v>
+      </c>
+      <c r="J40">
+        <v>54495499.494501</v>
+      </c>
+      <c r="K40">
+        <v>43266017.2214927</v>
+      </c>
+      <c r="L40">
         <v>16023088.8207894</v>
       </c>
-      <c r="I40">
+      <c r="M40">
         <v>713422508.550369</v>
       </c>
-      <c r="J40">
+      <c r="N40">
         <v>279724999.917433</v>
-      </c>
-      <c r="K40">
-        <v>550605623.581606</v>
-      </c>
-      <c r="L40">
-        <v>145929970.147427</v>
-      </c>
-      <c r="M40">
-        <v>54495499.494501</v>
-      </c>
-      <c r="N40">
-        <v>43266017.2214927</v>
       </c>
       <c r="O40">
         <v>1794967664.17917</v>
@@ -47411,25 +47411,25 @@
         <v>610693264.445043</v>
       </c>
       <c r="H41">
+        <v>540690244.975121</v>
+      </c>
+      <c r="I41">
+        <v>130684503.377448</v>
+      </c>
+      <c r="J41">
+        <v>45274326.2016774</v>
+      </c>
+      <c r="K41">
+        <v>41316949.3553132</v>
+      </c>
+      <c r="L41">
         <v>18944005.4421632</v>
       </c>
-      <c r="I41">
+      <c r="M41">
         <v>742247837.818381</v>
       </c>
-      <c r="J41">
+      <c r="N41">
         <v>276587509.579143</v>
-      </c>
-      <c r="K41">
-        <v>540690244.975121</v>
-      </c>
-      <c r="L41">
-        <v>130684503.377448</v>
-      </c>
-      <c r="M41">
-        <v>45274326.2016774</v>
-      </c>
-      <c r="N41">
-        <v>41316949.3553132</v>
       </c>
       <c r="O41">
         <v>1799512048.18761</v>
@@ -47466,25 +47466,25 @@
         <v>621821057.9155689</v>
       </c>
       <c r="H42">
+        <v>547045585.578198</v>
+      </c>
+      <c r="I42">
+        <v>153605598.874227</v>
+      </c>
+      <c r="J42">
+        <v>45244609.5598165</v>
+      </c>
+      <c r="K42">
+        <v>39709582.4610323</v>
+      </c>
+      <c r="L42">
         <v>27572922.1844135</v>
       </c>
-      <c r="I42">
+      <c r="M42">
         <v>747978143.414341</v>
       </c>
-      <c r="J42">
+      <c r="N42">
         <v>273703142.865981</v>
-      </c>
-      <c r="K42">
-        <v>547045585.578198</v>
-      </c>
-      <c r="L42">
-        <v>153605598.874227</v>
-      </c>
-      <c r="M42">
-        <v>45244609.5598165</v>
-      </c>
-      <c r="N42">
-        <v>39709582.4610323</v>
       </c>
       <c r="O42">
         <v>1842041941.55755</v>
@@ -47521,25 +47521,25 @@
         <v>637465666.111518</v>
       </c>
       <c r="H43">
+        <v>553288105.888352</v>
+      </c>
+      <c r="I43">
+        <v>163871428.016512</v>
+      </c>
+      <c r="J43">
+        <v>46516774.2431904</v>
+      </c>
+      <c r="K43">
+        <v>42483843.927979</v>
+      </c>
+      <c r="L43">
         <v>29017603.0981568</v>
       </c>
-      <c r="I43">
+      <c r="M43">
         <v>780934068.5233901</v>
       </c>
-      <c r="J43">
+      <c r="N43">
         <v>275505972.29958</v>
-      </c>
-      <c r="K43">
-        <v>553288105.888352</v>
-      </c>
-      <c r="L43">
-        <v>163871428.016512</v>
-      </c>
-      <c r="M43">
-        <v>46516774.2431904</v>
-      </c>
-      <c r="N43">
-        <v>42483843.927979</v>
       </c>
       <c r="O43">
         <v>1885375701.57804</v>
@@ -47576,25 +47576,25 @@
         <v>675307804.363055</v>
       </c>
       <c r="H44">
+        <v>560660488.074351</v>
+      </c>
+      <c r="I44">
+        <v>154331530.458588</v>
+      </c>
+      <c r="J44">
+        <v>48244421.6858151</v>
+      </c>
+      <c r="K44">
+        <v>46449530.970202</v>
+      </c>
+      <c r="L44">
         <v>28317302.8584479</v>
       </c>
-      <c r="I44">
+      <c r="M44">
         <v>790144491.6572191</v>
       </c>
-      <c r="J44">
+      <c r="N44">
         <v>270881602.263444</v>
-      </c>
-      <c r="K44">
-        <v>560660488.074351</v>
-      </c>
-      <c r="L44">
-        <v>154331530.458588</v>
-      </c>
-      <c r="M44">
-        <v>48244421.6858151</v>
-      </c>
-      <c r="N44">
-        <v>46449530.970202</v>
       </c>
       <c r="O44">
         <v>1894310643.42606</v>
@@ -47631,25 +47631,25 @@
         <v>672914592.3724149</v>
       </c>
       <c r="H45">
+        <v>556001753.52855</v>
+      </c>
+      <c r="I45">
+        <v>149621691.244655</v>
+      </c>
+      <c r="J45">
+        <v>54806708.3682843</v>
+      </c>
+      <c r="K45">
+        <v>44264942.3956135</v>
+      </c>
+      <c r="L45">
         <v>25396122.1038335</v>
       </c>
-      <c r="I45">
+      <c r="M45">
         <v>772215245.333781</v>
       </c>
-      <c r="J45">
+      <c r="N45">
         <v>274578523.353646</v>
-      </c>
-      <c r="K45">
-        <v>556001753.52855</v>
-      </c>
-      <c r="L45">
-        <v>149621691.244655</v>
-      </c>
-      <c r="M45">
-        <v>54806708.3682843</v>
-      </c>
-      <c r="N45">
-        <v>44264942.3956135</v>
       </c>
       <c r="O45">
         <v>1889011296.27562</v>
@@ -47686,25 +47686,25 @@
         <v>690833929.6924731</v>
       </c>
       <c r="H46">
+        <v>545001259.024471</v>
+      </c>
+      <c r="I46">
+        <v>161564740.689869</v>
+      </c>
+      <c r="J46">
+        <v>47841323.875335</v>
+      </c>
+      <c r="K46">
+        <v>49049434.7129724</v>
+      </c>
+      <c r="L46">
         <v>21384996.9798114</v>
       </c>
-      <c r="I46">
+      <c r="M46">
         <v>791227349.8319</v>
       </c>
-      <c r="J46">
+      <c r="N46">
         <v>266718757.563908</v>
-      </c>
-      <c r="K46">
-        <v>545001259.024471</v>
-      </c>
-      <c r="L46">
-        <v>161564740.689869</v>
-      </c>
-      <c r="M46">
-        <v>47841323.875335</v>
-      </c>
-      <c r="N46">
-        <v>49049434.7129724</v>
       </c>
       <c r="O46">
         <v>1879672675.88136</v>
@@ -47741,25 +47741,25 @@
         <v>694876431.052353</v>
       </c>
       <c r="H47">
+        <v>547376793.203145</v>
+      </c>
+      <c r="I47">
+        <v>147488898.951762</v>
+      </c>
+      <c r="J47">
+        <v>56854789.8202735</v>
+      </c>
+      <c r="K47">
+        <v>50621630.8783089</v>
+      </c>
+      <c r="L47">
         <v>24024986.8386</v>
       </c>
-      <c r="I47">
+      <c r="M47">
         <v>804262421.560488</v>
       </c>
-      <c r="J47">
+      <c r="N47">
         <v>263990015.125856</v>
-      </c>
-      <c r="K47">
-        <v>547376793.203145</v>
-      </c>
-      <c r="L47">
-        <v>147488898.951762</v>
-      </c>
-      <c r="M47">
-        <v>56854789.8202735</v>
-      </c>
-      <c r="N47">
-        <v>50621630.8783089</v>
       </c>
       <c r="O47">
         <v>1886519401.66159</v>
@@ -47796,25 +47796,25 @@
         <v>653493739.75225</v>
       </c>
       <c r="H48">
+        <v>529426399.577249</v>
+      </c>
+      <c r="I48">
+        <v>144339429.622886</v>
+      </c>
+      <c r="J48">
+        <v>55257154.9592537</v>
+      </c>
+      <c r="K48">
+        <v>50169916.8615187</v>
+      </c>
+      <c r="L48">
         <v>25698908.1088504</v>
       </c>
-      <c r="I48">
+      <c r="M48">
         <v>816734285.039508</v>
       </c>
-      <c r="J48">
+      <c r="N48">
         <v>259183502.011715</v>
-      </c>
-      <c r="K48">
-        <v>529426399.577249</v>
-      </c>
-      <c r="L48">
-        <v>144339429.622886</v>
-      </c>
-      <c r="M48">
-        <v>55257154.9592537</v>
-      </c>
-      <c r="N48">
-        <v>50169916.8615187</v>
       </c>
       <c r="O48">
         <v>1889286461.39019</v>
@@ -47851,25 +47851,25 @@
         <v>657247377.475192</v>
       </c>
       <c r="H49">
+        <v>540063453.707027</v>
+      </c>
+      <c r="I49">
+        <v>151928652.002461</v>
+      </c>
+      <c r="J49">
+        <v>51645072.4714205</v>
+      </c>
+      <c r="K49">
+        <v>54316818.1473</v>
+      </c>
+      <c r="L49">
         <v>25129756.1105188</v>
       </c>
-      <c r="I49">
+      <c r="M49">
         <v>806138783.4480979</v>
       </c>
-      <c r="J49">
+      <c r="N49">
         <v>269735400.402631</v>
-      </c>
-      <c r="K49">
-        <v>540063453.707027</v>
-      </c>
-      <c r="L49">
-        <v>151928652.002461</v>
-      </c>
-      <c r="M49">
-        <v>51645072.4714205</v>
-      </c>
-      <c r="N49">
-        <v>54316818.1473</v>
       </c>
       <c r="O49">
         <v>1909337746.78735</v>
@@ -47906,25 +47906,25 @@
         <v>672604178.791177</v>
       </c>
       <c r="H50">
+        <v>568283938.008371</v>
+      </c>
+      <c r="I50">
+        <v>157562637.821717</v>
+      </c>
+      <c r="J50">
+        <v>56865902.5031954</v>
+      </c>
+      <c r="K50">
+        <v>44288647.044603</v>
+      </c>
+      <c r="L50">
         <v>26869209.5286768</v>
       </c>
-      <c r="I50">
+      <c r="M50">
         <v>805874189.574087</v>
       </c>
-      <c r="J50">
+      <c r="N50">
         <v>258623970.379252</v>
-      </c>
-      <c r="K50">
-        <v>568283938.008371</v>
-      </c>
-      <c r="L50">
-        <v>157562637.821717</v>
-      </c>
-      <c r="M50">
-        <v>56865902.5031954</v>
-      </c>
-      <c r="N50">
-        <v>44288647.044603</v>
       </c>
       <c r="O50">
         <v>1915844656.52481</v>
@@ -47961,25 +47961,25 @@
         <v>662452866.612612</v>
       </c>
       <c r="H51">
+        <v>560732071.1404999</v>
+      </c>
+      <c r="I51">
+        <v>167430501.262001</v>
+      </c>
+      <c r="J51">
+        <v>51870722.0555691</v>
+      </c>
+      <c r="K51">
+        <v>37978018.3110758</v>
+      </c>
+      <c r="L51">
         <v>27573016.3123892</v>
       </c>
-      <c r="I51">
+      <c r="M51">
         <v>792451948.855441</v>
       </c>
-      <c r="J51">
+      <c r="N51">
         <v>268035903.057762</v>
-      </c>
-      <c r="K51">
-        <v>560732071.1404999</v>
-      </c>
-      <c r="L51">
-        <v>167430501.262001</v>
-      </c>
-      <c r="M51">
-        <v>51870722.0555691</v>
-      </c>
-      <c r="N51">
-        <v>37978018.3110758</v>
       </c>
       <c r="O51">
         <v>1899113897.32105</v>
@@ -48016,25 +48016,25 @@
         <v>675848764.749218</v>
       </c>
       <c r="H52">
+        <v>598384603.936614</v>
+      </c>
+      <c r="I52">
+        <v>170242080.259353</v>
+      </c>
+      <c r="J52">
+        <v>50185568.2526108</v>
+      </c>
+      <c r="K52">
+        <v>42625172.5463265</v>
+      </c>
+      <c r="L52">
         <v>27474552.7621857</v>
       </c>
-      <c r="I52">
+      <c r="M52">
         <v>805747628.4476089</v>
       </c>
-      <c r="J52">
+      <c r="N52">
         <v>284622883.488811</v>
-      </c>
-      <c r="K52">
-        <v>598384603.936614</v>
-      </c>
-      <c r="L52">
-        <v>170242080.259353</v>
-      </c>
-      <c r="M52">
-        <v>50185568.2526108</v>
-      </c>
-      <c r="N52">
-        <v>42625172.5463265</v>
       </c>
       <c r="O52">
         <v>1982870698.46066</v>
@@ -48071,25 +48071,25 @@
         <v>690557815.256233</v>
       </c>
       <c r="H53">
+        <v>580876740.218981</v>
+      </c>
+      <c r="I53">
+        <v>183675982.85031</v>
+      </c>
+      <c r="J53">
+        <v>53784948.5334653</v>
+      </c>
+      <c r="K53">
+        <v>44600290.1470346</v>
+      </c>
+      <c r="L53">
         <v>29322356.4998264</v>
       </c>
-      <c r="I53">
+      <c r="M53">
         <v>820581348.41433</v>
       </c>
-      <c r="J53">
+      <c r="N53">
         <v>278721020.593473</v>
-      </c>
-      <c r="K53">
-        <v>580876740.218981</v>
-      </c>
-      <c r="L53">
-        <v>183675982.85031</v>
-      </c>
-      <c r="M53">
-        <v>53784948.5334653</v>
-      </c>
-      <c r="N53">
-        <v>44600290.1470346</v>
       </c>
       <c r="O53">
         <v>1992036618.7082</v>
@@ -48126,25 +48126,25 @@
         <v>662271453.298228</v>
       </c>
       <c r="H54">
+        <v>586317969.517892</v>
+      </c>
+      <c r="I54">
+        <v>180189908.72772</v>
+      </c>
+      <c r="J54">
+        <v>51484152.7965525</v>
+      </c>
+      <c r="K54">
+        <v>48143829.291512</v>
+      </c>
+      <c r="L54">
         <v>24439973.6621436</v>
       </c>
-      <c r="I54">
+      <c r="M54">
         <v>829399029.108266</v>
       </c>
-      <c r="J54">
+      <c r="N54">
         <v>291767644.52856</v>
-      </c>
-      <c r="K54">
-        <v>586317969.517892</v>
-      </c>
-      <c r="L54">
-        <v>180189908.72772</v>
-      </c>
-      <c r="M54">
-        <v>51484152.7965525</v>
-      </c>
-      <c r="N54">
-        <v>48143829.291512</v>
       </c>
       <c r="O54">
         <v>2012326125.67051</v>
@@ -48181,25 +48181,25 @@
         <v>668900912.1494091</v>
       </c>
       <c r="H55">
+        <v>573867173.224189</v>
+      </c>
+      <c r="I55">
+        <v>179114983.576393</v>
+      </c>
+      <c r="J55">
+        <v>48876311.9046486</v>
+      </c>
+      <c r="K55">
+        <v>54995401.185193</v>
+      </c>
+      <c r="L55">
         <v>23077287.9308106</v>
       </c>
-      <c r="I55">
+      <c r="M55">
         <v>856969520.449288</v>
       </c>
-      <c r="J55">
+      <c r="N55">
         <v>294995432.031184</v>
-      </c>
-      <c r="K55">
-        <v>573867173.224189</v>
-      </c>
-      <c r="L55">
-        <v>179114983.576393</v>
-      </c>
-      <c r="M55">
-        <v>48876311.9046486</v>
-      </c>
-      <c r="N55">
-        <v>54995401.185193</v>
       </c>
       <c r="O55">
         <v>2024674558.38551</v>
@@ -48236,25 +48236,25 @@
         <v>686823518.46332</v>
       </c>
       <c r="H56">
+        <v>575961119.351796</v>
+      </c>
+      <c r="I56">
+        <v>198457959.844863</v>
+      </c>
+      <c r="J56">
+        <v>49542176.0024145</v>
+      </c>
+      <c r="K56">
+        <v>58070221.8713486</v>
+      </c>
+      <c r="L56">
         <v>21434310.563798</v>
       </c>
-      <c r="I56">
+      <c r="M56">
         <v>809946742.766775</v>
       </c>
-      <c r="J56">
+      <c r="N56">
         <v>289227047.425063</v>
-      </c>
-      <c r="K56">
-        <v>575961119.351796</v>
-      </c>
-      <c r="L56">
-        <v>198457959.844863</v>
-      </c>
-      <c r="M56">
-        <v>49542176.0024145</v>
-      </c>
-      <c r="N56">
-        <v>58070221.8713486</v>
       </c>
       <c r="O56">
         <v>2007852569.63498</v>

--- a/Dados/table_PROD_RS_1_aux.xlsx
+++ b/Dados/table_PROD_RS_1_aux.xlsx
@@ -6586,52 +6586,52 @@
         </is>
       </c>
       <c r="B5">
-        <v>131291241.5574411</v>
+        <v>1693657016.09099</v>
       </c>
       <c r="C5">
-        <v>2772419.18845992</v>
+        <v>35764207.53113297</v>
       </c>
       <c r="D5">
-        <v>159328000.3621346</v>
+        <v>2055331204.671537</v>
       </c>
       <c r="E5">
-        <v>7702385.468944971</v>
+        <v>99360772.54939012</v>
       </c>
       <c r="F5">
-        <v>65279932.46213016</v>
+        <v>842111128.761479</v>
       </c>
       <c r="G5">
-        <v>235082737.4816697</v>
+        <v>3032567313.513539</v>
       </c>
       <c r="H5">
-        <v>170987099.9468098</v>
+        <v>2205733589.313847</v>
       </c>
       <c r="I5">
-        <v>52224431.83748957</v>
+        <v>673695170.7036154</v>
       </c>
       <c r="J5">
-        <v>10456921.77095584</v>
+        <v>134894290.8453303</v>
       </c>
       <c r="K5">
-        <v>12446724.00046067</v>
+        <v>160562739.6059426</v>
       </c>
       <c r="L5">
-        <v>5936208.38715127</v>
+        <v>76577088.19425139</v>
       </c>
       <c r="M5">
-        <v>215923941.6035263</v>
+        <v>2785418846.685489</v>
       </c>
       <c r="N5">
-        <v>81050861.24758258</v>
+        <v>1045556110.093815</v>
       </c>
       <c r="O5">
-        <v>549026188.7939761</v>
+        <v>7082437835.442291</v>
       </c>
       <c r="P5">
-        <v>915400167.8330868</v>
+        <v>11808662165.04682</v>
       </c>
       <c r="Q5">
-        <v>697121856.6409118</v>
+        <v>8992871950.667763</v>
       </c>
     </row>
     <row r="6">
@@ -6641,52 +6641,52 @@
         </is>
       </c>
       <c r="B6">
-        <v>130842339.6069331</v>
+        <v>1687866180.929437</v>
       </c>
       <c r="C6">
-        <v>2873063.40556605</v>
+        <v>37062517.93180205</v>
       </c>
       <c r="D6">
-        <v>159452714.7696756</v>
+        <v>2056940020.528816</v>
       </c>
       <c r="E6">
-        <v>7684574.547880881</v>
+        <v>99131011.66766337</v>
       </c>
       <c r="F6">
-        <v>67352221.31514865</v>
+        <v>868843654.9654176</v>
       </c>
       <c r="G6">
-        <v>237362574.0382712</v>
+        <v>3061977205.093699</v>
       </c>
       <c r="H6">
-        <v>172777502.719432</v>
+        <v>2228829785.080672</v>
       </c>
       <c r="I6">
-        <v>52482654.21942319</v>
+        <v>677026239.4305592</v>
       </c>
       <c r="J6">
-        <v>10478978.21476661</v>
+        <v>135178818.9704893</v>
       </c>
       <c r="K6">
-        <v>12774069.04422191</v>
+        <v>164785490.6704626</v>
       </c>
       <c r="L6">
-        <v>6805204.03749773</v>
+        <v>87787132.08372071</v>
       </c>
       <c r="M6">
-        <v>212071608.5184864</v>
+        <v>2735723749.888475</v>
       </c>
       <c r="N6">
-        <v>83294594.84057541</v>
+        <v>1074500273.443423</v>
       </c>
       <c r="O6">
-        <v>550684611.5944033</v>
+        <v>7103831489.567802</v>
       </c>
       <c r="P6">
-        <v>918889525.2396077</v>
+        <v>11853674875.59094</v>
       </c>
       <c r="Q6">
-        <v>697947386.7546012</v>
+        <v>9003521289.134356</v>
       </c>
     </row>
     <row r="7">
@@ -6696,52 +6696,52 @@
         </is>
       </c>
       <c r="B7">
-        <v>128599433.1831076</v>
+        <v>1658932688.062088</v>
       </c>
       <c r="C7">
-        <v>2934016.79203935</v>
+        <v>37848816.61730761</v>
       </c>
       <c r="D7">
-        <v>159476451.6987268</v>
+        <v>2057246226.913576</v>
       </c>
       <c r="E7">
-        <v>8074400.66983876</v>
+        <v>104159768.64092</v>
       </c>
       <c r="F7">
-        <v>66751042.5699582</v>
+        <v>861088449.1524607</v>
       </c>
       <c r="G7">
-        <v>237235911.7305632</v>
+        <v>3060343261.324265</v>
       </c>
       <c r="H7">
-        <v>175665992.2919004</v>
+        <v>2266091300.565515</v>
       </c>
       <c r="I7">
-        <v>53098459.42127262</v>
+        <v>684970126.5344168</v>
       </c>
       <c r="J7">
-        <v>10404933.15025596</v>
+        <v>134223637.6383019</v>
       </c>
       <c r="K7">
-        <v>12890404.54884089</v>
+        <v>166286218.6800475</v>
       </c>
       <c r="L7">
-        <v>7430449.40898817</v>
+        <v>95852797.3759474</v>
       </c>
       <c r="M7">
-        <v>210223771.236254</v>
+        <v>2711886648.947676</v>
       </c>
       <c r="N7">
-        <v>85895095.55242445</v>
+        <v>1108046732.626275</v>
       </c>
       <c r="O7">
-        <v>555609105.6099365</v>
+        <v>7167357462.36818</v>
       </c>
       <c r="P7">
-        <v>921444450.5236073</v>
+        <v>11886633411.75453</v>
       </c>
       <c r="Q7">
-        <v>699519472.379087</v>
+        <v>9023801193.690222</v>
       </c>
     </row>
     <row r="8">
@@ -6751,52 +6751,52 @@
         </is>
       </c>
       <c r="B8">
-        <v>127690767.3229534</v>
+        <v>1647210898.466098</v>
       </c>
       <c r="C8">
-        <v>2845024.27391361</v>
+        <v>36700813.13348557</v>
       </c>
       <c r="D8">
-        <v>159464318.2317336</v>
+        <v>2057089705.189364</v>
       </c>
       <c r="E8">
-        <v>8317266.319347519</v>
+        <v>107292735.519583</v>
       </c>
       <c r="F8">
-        <v>68424024.14600657</v>
+        <v>882669911.4834847</v>
       </c>
       <c r="G8">
-        <v>239050632.9710014</v>
+        <v>3083753165.325918</v>
       </c>
       <c r="H8">
-        <v>178712049.4349527</v>
+        <v>2305385437.71089</v>
       </c>
       <c r="I8">
-        <v>53782784.37331786</v>
+        <v>693797918.4158005</v>
       </c>
       <c r="J8">
-        <v>10159515.13332438</v>
+        <v>131057745.2198845</v>
       </c>
       <c r="K8">
-        <v>13015613.40109401</v>
+        <v>167901412.8741127</v>
       </c>
       <c r="L8">
-        <v>7970540.04159506</v>
+        <v>102819966.5365763</v>
       </c>
       <c r="M8">
-        <v>211328646.9128817</v>
+        <v>2726139545.176174</v>
       </c>
       <c r="N8">
-        <v>87169087.60063326</v>
+        <v>1124481230.048169</v>
       </c>
       <c r="O8">
-        <v>562138236.8977989</v>
+        <v>7251583255.981606</v>
       </c>
       <c r="P8">
-        <v>928879637.1917539</v>
+        <v>11982547319.77362</v>
       </c>
       <c r="Q8">
-        <v>706049242.226572</v>
+        <v>9108035224.72278</v>
       </c>
     </row>
     <row r="9">
@@ -6806,52 +6806,52 @@
         </is>
       </c>
       <c r="B9">
-        <v>126747676.1585412</v>
+        <v>1635045022.445182</v>
       </c>
       <c r="C9">
-        <v>2831941.52387637</v>
+        <v>36532045.65800517</v>
       </c>
       <c r="D9">
-        <v>159079728.0232578</v>
+        <v>2052128491.500026</v>
       </c>
       <c r="E9">
-        <v>8093165.28177697</v>
+        <v>104401832.1349229</v>
       </c>
       <c r="F9">
-        <v>68901651.58272633</v>
+        <v>888831305.4171697</v>
       </c>
       <c r="G9">
-        <v>238906486.4116375</v>
+        <v>3081893674.710124</v>
       </c>
       <c r="H9">
-        <v>182946384.0940431</v>
+        <v>2360008354.813156</v>
       </c>
       <c r="I9">
-        <v>53016596.36730317</v>
+        <v>683914093.1382109</v>
       </c>
       <c r="J9">
-        <v>10082982.45646401</v>
+        <v>130070473.6883858</v>
       </c>
       <c r="K9">
-        <v>12931233.61574933</v>
+        <v>166812913.6431664</v>
       </c>
       <c r="L9">
-        <v>7979226.50792678</v>
+        <v>102932021.9522555</v>
       </c>
       <c r="M9">
-        <v>214995644.4833845</v>
+        <v>2773443813.83566</v>
       </c>
       <c r="N9">
-        <v>87920839.73643503</v>
+        <v>1134178832.600012</v>
       </c>
       <c r="O9">
-        <v>569872907.2613059</v>
+        <v>7351360503.670847</v>
       </c>
       <c r="P9">
-        <v>935527069.8314847</v>
+        <v>12068299200.82615</v>
       </c>
       <c r="Q9">
-        <v>712879327.4285816</v>
+        <v>9196143323.828703</v>
       </c>
     </row>
     <row r="10">
@@ -6861,52 +6861,52 @@
         </is>
       </c>
       <c r="B10">
-        <v>122213643.8443585</v>
+        <v>1576556005.592225</v>
       </c>
       <c r="C10">
-        <v>2871466.91324268</v>
+        <v>37041923.18083058</v>
       </c>
       <c r="D10">
-        <v>159331205.8513637</v>
+        <v>2055372555.482592</v>
       </c>
       <c r="E10">
-        <v>7717464.8744187</v>
+        <v>99555296.88000123</v>
       </c>
       <c r="F10">
-        <v>69005220.04053889</v>
+        <v>890167338.5229517</v>
       </c>
       <c r="G10">
-        <v>238925357.679564</v>
+        <v>3082137114.066375</v>
       </c>
       <c r="H10">
-        <v>186117638.8962763</v>
+        <v>2400917541.761965</v>
       </c>
       <c r="I10">
-        <v>52401240.97273269</v>
+        <v>675976008.5482517</v>
       </c>
       <c r="J10">
-        <v>10370341.03129575</v>
+        <v>133777399.3037152</v>
       </c>
       <c r="K10">
-        <v>12615790.00158284</v>
+        <v>162743691.0204186</v>
       </c>
       <c r="L10">
-        <v>7760537.88193722</v>
+        <v>100110938.6769901</v>
       </c>
       <c r="M10">
-        <v>218804321.4339382</v>
+        <v>2822575746.497803</v>
       </c>
       <c r="N10">
-        <v>87025889.65178877</v>
+        <v>1122633976.508075</v>
       </c>
       <c r="O10">
-        <v>575095759.8695518</v>
+        <v>7418735302.317218</v>
       </c>
       <c r="P10">
-        <v>936234761.3934743</v>
+        <v>12077428421.97582</v>
       </c>
       <c r="Q10">
-        <v>719234690.0153898</v>
+        <v>9278127501.198528</v>
       </c>
     </row>
     <row r="11">
@@ -6916,52 +6916,52 @@
         </is>
       </c>
       <c r="B11">
-        <v>119788620.4950595</v>
+        <v>1545273204.386268</v>
       </c>
       <c r="C11">
-        <v>2454260.3184503</v>
+        <v>31659958.10800887</v>
       </c>
       <c r="D11">
-        <v>158311424.0959623</v>
+        <v>2042217370.837914</v>
       </c>
       <c r="E11">
-        <v>7136406.61161709</v>
+        <v>92059645.28986047</v>
       </c>
       <c r="F11">
-        <v>68628868.33999771</v>
+        <v>885312401.5859705</v>
       </c>
       <c r="G11">
-        <v>236530959.3660274</v>
+        <v>3051249375.821754</v>
       </c>
       <c r="H11">
-        <v>186224780.8922558</v>
+        <v>2402299673.510099</v>
       </c>
       <c r="I11">
-        <v>51066866.42404594</v>
+        <v>658762576.8701925</v>
       </c>
       <c r="J11">
-        <v>10557237.68274517</v>
+        <v>136188366.1074127</v>
       </c>
       <c r="K11">
-        <v>12148177.31275648</v>
+        <v>156711487.3345586</v>
       </c>
       <c r="L11">
-        <v>7205813.89991194</v>
+        <v>92954999.30886403</v>
       </c>
       <c r="M11">
-        <v>226738160.6370859</v>
+        <v>2924922272.218408</v>
       </c>
       <c r="N11">
-        <v>85492645.40484098</v>
+        <v>1102855125.722449</v>
       </c>
       <c r="O11">
-        <v>579433682.2536421</v>
+        <v>7474694501.071983</v>
       </c>
       <c r="P11">
-        <v>935753262.1147289</v>
+        <v>12071217081.28</v>
       </c>
       <c r="Q11">
-        <v>723266182.3149165</v>
+        <v>9330133751.862423</v>
       </c>
     </row>
     <row r="12">
@@ -6971,52 +6971,52 @@
         </is>
       </c>
       <c r="B12">
-        <v>118362295.9294441</v>
+        <v>1526873617.489829</v>
       </c>
       <c r="C12">
-        <v>2380187.0020108</v>
+        <v>30704412.32593932</v>
       </c>
       <c r="D12">
-        <v>157734074.5012679</v>
+        <v>2034769561.066356</v>
       </c>
       <c r="E12">
-        <v>6796797.12018349</v>
+        <v>87678682.85036702</v>
       </c>
       <c r="F12">
-        <v>67316018.23186359</v>
+        <v>868376635.1910403</v>
       </c>
       <c r="G12">
-        <v>234227076.8553258</v>
+        <v>3021529291.433703</v>
       </c>
       <c r="H12">
-        <v>184522694.6054034</v>
+        <v>2380342760.409704</v>
       </c>
       <c r="I12">
-        <v>49415436.99431237</v>
+        <v>637459137.2266296</v>
       </c>
       <c r="J12">
-        <v>10760980.5814273</v>
+        <v>138816649.5004122</v>
       </c>
       <c r="K12">
-        <v>12047338.01818712</v>
+        <v>155410660.4346139</v>
       </c>
       <c r="L12">
-        <v>6613869.32136924</v>
+        <v>85318914.2456632</v>
       </c>
       <c r="M12">
-        <v>230733466.3505424</v>
+        <v>2976461715.921997</v>
       </c>
       <c r="N12">
-        <v>85167204.03718624</v>
+        <v>1098656932.079702</v>
       </c>
       <c r="O12">
-        <v>579260989.9084281</v>
+        <v>7472466769.818723</v>
       </c>
       <c r="P12">
-        <v>931850362.693198</v>
+        <v>12020869678.74225</v>
       </c>
       <c r="Q12">
-        <v>721706993.4051983</v>
+        <v>9310020214.927059</v>
       </c>
     </row>
     <row r="13">
@@ -7026,52 +7026,52 @@
         </is>
       </c>
       <c r="B13">
-        <v>114728008.0333817</v>
+        <v>1479991303.630624</v>
       </c>
       <c r="C13">
-        <v>2404276.61701017</v>
+        <v>31015168.3594312</v>
       </c>
       <c r="D13">
-        <v>156145567.566002</v>
+        <v>2014277821.601426</v>
       </c>
       <c r="E13">
-        <v>6753847.81383101</v>
+        <v>87124636.79842003</v>
       </c>
       <c r="F13">
-        <v>68049648.59029785</v>
+        <v>877840466.8148422</v>
       </c>
       <c r="G13">
-        <v>233353340.587141</v>
+        <v>3010258093.574119</v>
       </c>
       <c r="H13">
-        <v>181583408.0815606</v>
+        <v>2342425964.252132</v>
       </c>
       <c r="I13">
-        <v>48619747.63787924</v>
+        <v>627194744.5286422</v>
       </c>
       <c r="J13">
-        <v>10999533.12901894</v>
+        <v>141893977.3643443</v>
       </c>
       <c r="K13">
-        <v>11891758.62709886</v>
+        <v>153403686.2895753</v>
       </c>
       <c r="L13">
-        <v>6567369.293287911</v>
+        <v>84719063.88341404</v>
       </c>
       <c r="M13">
-        <v>233746081.4448139</v>
+        <v>3015324450.6381</v>
       </c>
       <c r="N13">
-        <v>85187826.40590961</v>
+        <v>1098922960.636234</v>
       </c>
       <c r="O13">
-        <v>578595724.6195692</v>
+        <v>7463884847.592443</v>
       </c>
       <c r="P13">
-        <v>926677073.2400919</v>
+        <v>11954134244.79719</v>
       </c>
       <c r="Q13">
-        <v>720193869.5075126</v>
+        <v>9290500916.646912</v>
       </c>
     </row>
     <row r="14">
@@ -7081,52 +7081,52 @@
         </is>
       </c>
       <c r="B14">
-        <v>115316439.9604184</v>
+        <v>1487582075.489397</v>
       </c>
       <c r="C14">
-        <v>2358478.67137188</v>
+        <v>30424374.86069725</v>
       </c>
       <c r="D14">
-        <v>153889817.2182038</v>
+        <v>1985178642.114829</v>
       </c>
       <c r="E14">
-        <v>7153399.90215454</v>
+        <v>92278858.73779356</v>
       </c>
       <c r="F14">
-        <v>66776504.62650644</v>
+        <v>861416909.681933</v>
       </c>
       <c r="G14">
-        <v>230178200.4182366</v>
+        <v>2969298785.395252</v>
       </c>
       <c r="H14">
-        <v>180344306.0339225</v>
+        <v>2326441547.8376</v>
       </c>
       <c r="I14">
-        <v>47380526.05595585</v>
+        <v>611208786.1218305</v>
       </c>
       <c r="J14">
-        <v>11090974.79622965</v>
+        <v>143073574.8713625</v>
       </c>
       <c r="K14">
-        <v>12289454.58650172</v>
+        <v>158533964.1658722</v>
       </c>
       <c r="L14">
-        <v>6439282.29268258</v>
+        <v>83066741.57560527</v>
       </c>
       <c r="M14">
-        <v>237427173.5492387</v>
+        <v>3062810538.785179</v>
       </c>
       <c r="N14">
-        <v>86253248.98652954</v>
+        <v>1112666911.926231</v>
       </c>
       <c r="O14">
-        <v>581224966.3010607</v>
+        <v>7497802065.283683</v>
       </c>
       <c r="P14">
-        <v>926719606.6797156</v>
+        <v>11954682926.16833</v>
       </c>
       <c r="Q14">
-        <v>718710635.4400849</v>
+        <v>9271367197.177095</v>
       </c>
     </row>
     <row r="15">
@@ -7136,52 +7136,52 @@
         </is>
       </c>
       <c r="B15">
-        <v>114700654.2499466</v>
+        <v>1479638439.824311</v>
       </c>
       <c r="C15">
-        <v>2623491.50012125</v>
+        <v>33843040.35156413</v>
       </c>
       <c r="D15">
-        <v>150964512.0344971</v>
+        <v>1947442205.245013</v>
       </c>
       <c r="E15">
-        <v>7714746.38361426</v>
+        <v>99520228.34862396</v>
       </c>
       <c r="F15">
-        <v>66001169.26650726</v>
+        <v>851415083.5379437</v>
       </c>
       <c r="G15">
-        <v>227303919.1847399</v>
+        <v>2932220557.483144</v>
       </c>
       <c r="H15">
-        <v>180601394.7695467</v>
+        <v>2329757992.527153</v>
       </c>
       <c r="I15">
-        <v>48106341.55660678</v>
+        <v>620571806.0802275</v>
       </c>
       <c r="J15">
-        <v>11799703.45209289</v>
+        <v>152216174.5319983</v>
       </c>
       <c r="K15">
-        <v>12463731.99309433</v>
+        <v>160782142.7109168</v>
       </c>
       <c r="L15">
-        <v>6715889.28628258</v>
+        <v>86634971.79304528</v>
       </c>
       <c r="M15">
-        <v>236338012.9073372</v>
+        <v>3048760366.50465</v>
       </c>
       <c r="N15">
-        <v>86159609.90297359</v>
+        <v>1111458967.748359</v>
       </c>
       <c r="O15">
-        <v>582184683.8679341</v>
+        <v>7510182421.89635</v>
       </c>
       <c r="P15">
-        <v>924189257.3026205</v>
+        <v>11922041419.20381</v>
       </c>
       <c r="Q15">
-        <v>716613103.8634177</v>
+        <v>9244309039.838089</v>
       </c>
     </row>
     <row r="16">
@@ -7191,52 +7191,52 @@
         </is>
       </c>
       <c r="B16">
-        <v>113689126.0787627</v>
+        <v>1466589726.416039</v>
       </c>
       <c r="C16">
-        <v>2850095.59865163</v>
+        <v>36766233.22260603</v>
       </c>
       <c r="D16">
-        <v>149476144.1283943</v>
+        <v>1928242259.256286</v>
       </c>
       <c r="E16">
-        <v>8130341.34157939</v>
+        <v>104881403.3063741</v>
       </c>
       <c r="F16">
-        <v>64889302.41563528</v>
+        <v>837072001.1616951</v>
       </c>
       <c r="G16">
-        <v>225345883.4842606</v>
+        <v>2906961896.946962</v>
       </c>
       <c r="H16">
-        <v>181409966.5553397</v>
+        <v>2340188568.563882</v>
       </c>
       <c r="I16">
-        <v>48493964.97506987</v>
+        <v>625572148.1784012</v>
       </c>
       <c r="J16">
-        <v>12164286.7785398</v>
+        <v>156919299.4431634</v>
       </c>
       <c r="K16">
-        <v>12121839.57511161</v>
+        <v>156371730.5189398</v>
       </c>
       <c r="L16">
-        <v>6436857.51014862</v>
+        <v>83035461.88091721</v>
       </c>
       <c r="M16">
-        <v>233824997.7955039</v>
+        <v>3016342471.562</v>
       </c>
       <c r="N16">
-        <v>86202185.20705415</v>
+        <v>1112008189.170999</v>
       </c>
       <c r="O16">
-        <v>580654098.3967676</v>
+        <v>7490437869.318302</v>
       </c>
       <c r="P16">
-        <v>919689107.9597909</v>
+        <v>11863989492.6813</v>
       </c>
       <c r="Q16">
-        <v>713360939.1638255</v>
+        <v>9202356115.21335</v>
       </c>
     </row>
     <row r="17">
@@ -7246,52 +7246,52 @@
         </is>
       </c>
       <c r="B17">
-        <v>112802241.2146832</v>
+        <v>1455148911.669414</v>
       </c>
       <c r="C17">
-        <v>2998017.77125975</v>
+        <v>38674429.24925078</v>
       </c>
       <c r="D17">
-        <v>149097043.7219423</v>
+        <v>1923351864.013055</v>
       </c>
       <c r="E17">
-        <v>8800728.55697668</v>
+        <v>113529398.3849992</v>
       </c>
       <c r="F17">
-        <v>64014306.54870287</v>
+        <v>825784554.478267</v>
       </c>
       <c r="G17">
-        <v>224910096.5988816</v>
+        <v>2901340246.125573</v>
       </c>
       <c r="H17">
-        <v>181588066.0530292</v>
+        <v>2342486052.084077</v>
       </c>
       <c r="I17">
-        <v>49318949.92739433</v>
+        <v>636214454.0633869</v>
       </c>
       <c r="J17">
-        <v>12773569.42662237</v>
+        <v>164779045.6034286</v>
       </c>
       <c r="K17">
-        <v>12194161.2818561</v>
+        <v>157304680.5359437</v>
       </c>
       <c r="L17">
-        <v>6127873.70378429</v>
+        <v>79049570.77881734</v>
       </c>
       <c r="M17">
-        <v>231858788.0300083</v>
+        <v>2990978365.587107</v>
       </c>
       <c r="N17">
-        <v>87107866.0682894</v>
+        <v>1123691472.280933</v>
       </c>
       <c r="O17">
-        <v>580969274.490984</v>
+        <v>7494503640.933693</v>
       </c>
       <c r="P17">
-        <v>918681612.3045487</v>
+        <v>11850992798.72868</v>
       </c>
       <c r="Q17">
-        <v>712643631.3177919</v>
+        <v>9193102843.999516</v>
       </c>
     </row>
     <row r="18">
@@ -7301,52 +7301,52 @@
         </is>
       </c>
       <c r="B18">
-        <v>113143221.537675</v>
+        <v>1459547557.836007</v>
       </c>
       <c r="C18">
-        <v>2983935.16133585</v>
+        <v>38492763.58123247</v>
       </c>
       <c r="D18">
-        <v>147894805.3591982</v>
+        <v>1907842989.133657</v>
       </c>
       <c r="E18">
-        <v>9012976.11112245</v>
+        <v>116267391.8334796</v>
       </c>
       <c r="F18">
-        <v>65064494.88462498</v>
+        <v>839331984.0116622</v>
       </c>
       <c r="G18">
-        <v>224956211.5162815</v>
+        <v>2901935128.560031</v>
       </c>
       <c r="H18">
-        <v>179603401.4679316</v>
+        <v>2316883878.936318</v>
       </c>
       <c r="I18">
-        <v>50848117.55736561</v>
+        <v>655940716.4900165</v>
       </c>
       <c r="J18">
-        <v>11899703.7636502</v>
+        <v>153506178.5510876</v>
       </c>
       <c r="K18">
-        <v>11966453.7497945</v>
+        <v>154367253.3723491</v>
       </c>
       <c r="L18">
-        <v>5962268.36218708</v>
+        <v>76913261.87221333</v>
       </c>
       <c r="M18">
-        <v>230230312.9152077</v>
+        <v>2969971036.60618</v>
       </c>
       <c r="N18">
-        <v>87092172.01120235</v>
+        <v>1123489018.94451</v>
       </c>
       <c r="O18">
-        <v>577602429.8273392</v>
+        <v>7451071344.772676</v>
       </c>
       <c r="P18">
-        <v>915701862.8812957</v>
+        <v>11812554031.16871</v>
       </c>
       <c r="Q18">
-        <v>709504200.9702312</v>
+        <v>9152604192.515982</v>
       </c>
     </row>
     <row r="19">
@@ -7356,52 +7356,52 @@
         </is>
       </c>
       <c r="B19">
-        <v>113562546.9965351</v>
+        <v>1464956856.255302</v>
       </c>
       <c r="C19">
-        <v>2846279.43761497</v>
+        <v>36717004.74523311</v>
       </c>
       <c r="D19">
-        <v>146509295.4166858</v>
+        <v>1889969910.875247</v>
       </c>
       <c r="E19">
-        <v>8821688.770045839</v>
+        <v>113799785.1335913</v>
       </c>
       <c r="F19">
-        <v>66562312.21128404</v>
+        <v>858653827.5255642</v>
       </c>
       <c r="G19">
-        <v>224739575.8356307</v>
+        <v>2899140528.279636</v>
       </c>
       <c r="H19">
-        <v>176876916.2451909</v>
+        <v>2281712219.562963</v>
       </c>
       <c r="I19">
-        <v>50758316.7208659</v>
+        <v>654782285.6991701</v>
       </c>
       <c r="J19">
-        <v>11333894.63183914</v>
+        <v>146207240.7507249</v>
       </c>
       <c r="K19">
-        <v>12233897.69772909</v>
+        <v>157817280.3007053</v>
       </c>
       <c r="L19">
-        <v>5682191.73274824</v>
+        <v>73300273.35245231</v>
       </c>
       <c r="M19">
-        <v>228788875.6370167</v>
+        <v>2951376495.717516</v>
       </c>
       <c r="N19">
-        <v>88353061.72935081</v>
+        <v>1139754496.308625</v>
       </c>
       <c r="O19">
-        <v>574027154.3947408</v>
+        <v>7404950291.692157</v>
       </c>
       <c r="P19">
-        <v>912329277.2269068</v>
+        <v>11769047676.2271</v>
       </c>
       <c r="Q19">
-        <v>704731476.7682724</v>
+        <v>9091036050.310715</v>
       </c>
     </row>
     <row r="20">
@@ -7411,52 +7411,52 @@
         </is>
       </c>
       <c r="B20">
-        <v>114491553.6225518</v>
+        <v>1476941041.730919</v>
       </c>
       <c r="C20">
-        <v>2885893.72605731</v>
+        <v>37228029.0661393</v>
       </c>
       <c r="D20">
-        <v>144337087.3132343</v>
+        <v>1861948426.340722</v>
       </c>
       <c r="E20">
-        <v>8475288.34554583</v>
+        <v>109331219.6575412</v>
       </c>
       <c r="F20">
-        <v>67830730.05123428</v>
+        <v>875016417.6609222</v>
       </c>
       <c r="G20">
-        <v>223528999.4360717</v>
+        <v>2883524092.725325</v>
       </c>
       <c r="H20">
-        <v>175661196.1317103</v>
+        <v>2266029430.099063</v>
       </c>
       <c r="I20">
-        <v>49918033.71628334</v>
+        <v>643942634.940055</v>
       </c>
       <c r="J20">
-        <v>10812045.93124696</v>
+        <v>139475392.5130858</v>
       </c>
       <c r="K20">
-        <v>12869368.9060445</v>
+        <v>166014858.8879741</v>
       </c>
       <c r="L20">
-        <v>5787071.15795433</v>
+        <v>74653217.93761085</v>
       </c>
       <c r="M20">
-        <v>230433104.2686709</v>
+        <v>2972587045.065854</v>
       </c>
       <c r="N20">
-        <v>89576526.88641888</v>
+        <v>1155537196.834804</v>
       </c>
       <c r="O20">
-        <v>575057346.9983292</v>
+        <v>7418239776.278446</v>
       </c>
       <c r="P20">
-        <v>913077900.056953</v>
+        <v>11778704910.73469</v>
       </c>
       <c r="Q20">
-        <v>703222748.3900276</v>
+        <v>9071573454.231358</v>
       </c>
     </row>
     <row r="21">
@@ -7466,52 +7466,52 @@
         </is>
       </c>
       <c r="B21">
-        <v>115784658.7293149</v>
+        <v>1493622097.608162</v>
       </c>
       <c r="C21">
-        <v>2566911.96781719</v>
+        <v>33113164.38484176</v>
       </c>
       <c r="D21">
-        <v>142687222.9929281</v>
+        <v>1840665176.608772</v>
       </c>
       <c r="E21">
-        <v>8316950.12687548</v>
+        <v>107288656.6366937</v>
       </c>
       <c r="F21">
-        <v>67780130.87459789</v>
+        <v>874363688.2823129</v>
       </c>
       <c r="G21">
-        <v>221351215.9622187</v>
+        <v>2855430685.912621</v>
       </c>
       <c r="H21">
-        <v>172924484.9099412</v>
+        <v>2230725855.338242</v>
       </c>
       <c r="I21">
-        <v>48541413.37105655</v>
+        <v>626184232.4866295</v>
       </c>
       <c r="J21">
-        <v>9854570.61171177</v>
+        <v>127123960.8910818</v>
       </c>
       <c r="K21">
-        <v>13308509.74990273</v>
+        <v>171679775.7737452</v>
       </c>
       <c r="L21">
-        <v>6247077.91004685</v>
+        <v>80587305.03960437</v>
       </c>
       <c r="M21">
-        <v>231932944.4611817</v>
+        <v>2991934983.549244</v>
       </c>
       <c r="N21">
-        <v>88436460.9407063</v>
+        <v>1140830346.135111</v>
       </c>
       <c r="O21">
-        <v>571245461.9545472</v>
+        <v>7369066459.213658</v>
       </c>
       <c r="P21">
-        <v>908381336.646081</v>
+        <v>11718119242.73445</v>
       </c>
       <c r="Q21">
-        <v>697913139.0660126</v>
+        <v>9003079493.951563</v>
       </c>
     </row>
     <row r="22">
@@ -7521,52 +7521,52 @@
         </is>
       </c>
       <c r="B22">
-        <v>114424898.9423222</v>
+        <v>1476081196.355957</v>
       </c>
       <c r="C22">
-        <v>2300902.77122159</v>
+        <v>29681645.74875851</v>
       </c>
       <c r="D22">
-        <v>140818249.1053465</v>
+        <v>1816555413.45897</v>
       </c>
       <c r="E22">
-        <v>8109670.85362098</v>
+        <v>104614754.0117106</v>
       </c>
       <c r="F22">
-        <v>66230443.52542068</v>
+        <v>854372721.4779269</v>
       </c>
       <c r="G22">
-        <v>217459266.2556098</v>
+        <v>2805224534.697367</v>
       </c>
       <c r="H22">
-        <v>172974613.0155523</v>
+        <v>2231372507.900624</v>
       </c>
       <c r="I22">
-        <v>47426936.85080473</v>
+        <v>611807485.375381</v>
       </c>
       <c r="J22">
-        <v>10365038.56937487</v>
+        <v>133708997.5449358</v>
       </c>
       <c r="K22">
-        <v>13407020.83229467</v>
+        <v>172950568.7366012</v>
       </c>
       <c r="L22">
-        <v>6404580.30916718</v>
+        <v>82619085.98825663</v>
       </c>
       <c r="M22">
-        <v>233398215.6783957</v>
+        <v>3010836982.251305</v>
       </c>
       <c r="N22">
-        <v>87793305.34109657</v>
+        <v>1132533638.900146</v>
       </c>
       <c r="O22">
-        <v>571769710.596686</v>
+        <v>7375829266.697249</v>
       </c>
       <c r="P22">
-        <v>903653875.7946181</v>
+        <v>11657134997.75057</v>
       </c>
       <c r="Q22">
-        <v>695031091.202032</v>
+        <v>8965901076.506212</v>
       </c>
     </row>
     <row r="23">
@@ -7576,52 +7576,52 @@
         </is>
       </c>
       <c r="B23">
-        <v>114348221.5362875</v>
+        <v>1475092057.818109</v>
       </c>
       <c r="C23">
-        <v>2338055.39525967</v>
+        <v>30160914.59884974</v>
       </c>
       <c r="D23">
-        <v>139483887.3776954</v>
+        <v>1799342147.172271</v>
       </c>
       <c r="E23">
-        <v>8400247.931504721</v>
+        <v>108363198.3164109</v>
       </c>
       <c r="F23">
-        <v>63228857.80683273</v>
+        <v>815652265.7081423</v>
       </c>
       <c r="G23">
-        <v>213451048.5112926</v>
+        <v>2753518525.795674</v>
       </c>
       <c r="H23">
-        <v>174744235.4071059</v>
+        <v>2254200636.751667</v>
       </c>
       <c r="I23">
-        <v>47846944.59101686</v>
+        <v>617225585.2241175</v>
       </c>
       <c r="J23">
-        <v>10270757.80635806</v>
+        <v>132492775.702019</v>
       </c>
       <c r="K23">
-        <v>12987177.74643875</v>
+        <v>167534592.9290599</v>
       </c>
       <c r="L23">
-        <v>7012944.61557954</v>
+        <v>90466985.54097606</v>
       </c>
       <c r="M23">
-        <v>235220715.0938912</v>
+        <v>3034347224.711196</v>
       </c>
       <c r="N23">
-        <v>87099058.33764438</v>
+        <v>1123577852.555613</v>
       </c>
       <c r="O23">
-        <v>575181833.5980347</v>
+        <v>7419845653.414648</v>
       </c>
       <c r="P23">
-        <v>902981103.645615</v>
+        <v>11648456237.02843</v>
       </c>
       <c r="Q23">
-        <v>694520879.1561033</v>
+        <v>8959319341.113731</v>
       </c>
     </row>
     <row r="24">
@@ -7631,52 +7631,52 @@
         </is>
       </c>
       <c r="B24">
-        <v>114348126.9598527</v>
+        <v>1475090837.782099</v>
       </c>
       <c r="C24">
-        <v>2020115.33816233</v>
+        <v>26059487.86229406</v>
       </c>
       <c r="D24">
-        <v>138817291.5690255</v>
+        <v>1790743061.240429</v>
       </c>
       <c r="E24">
-        <v>9101487.660672201</v>
+        <v>117409190.8226714</v>
       </c>
       <c r="F24">
-        <v>61844456.82129007</v>
+        <v>797793492.9946419</v>
       </c>
       <c r="G24">
-        <v>211783351.3891501</v>
+        <v>2732005232.920036</v>
       </c>
       <c r="H24">
-        <v>174277895.9105458</v>
+        <v>2248184857.24604</v>
       </c>
       <c r="I24">
-        <v>48635759.81330234</v>
+        <v>627401301.5916002</v>
       </c>
       <c r="J24">
-        <v>10271339.67317983</v>
+        <v>132500281.7840198</v>
       </c>
       <c r="K24">
-        <v>12637055.48730254</v>
+        <v>163018015.7862028</v>
       </c>
       <c r="L24">
-        <v>7367591.56871484</v>
+        <v>95041931.23642144</v>
       </c>
       <c r="M24">
-        <v>236111138.0965558</v>
+        <v>3045833681.44557</v>
       </c>
       <c r="N24">
-        <v>85969274.80828685</v>
+        <v>1109003645.0269</v>
       </c>
       <c r="O24">
-        <v>575270055.357888</v>
+        <v>7420983714.116755</v>
       </c>
       <c r="P24">
-        <v>901401533.7068908</v>
+        <v>11628079784.81889</v>
       </c>
       <c r="Q24">
-        <v>693716540.3700362</v>
+        <v>8948943370.773468</v>
       </c>
     </row>
     <row r="25">
@@ -7686,52 +7686,52 @@
         </is>
       </c>
       <c r="B25">
-        <v>112896306.474921</v>
+        <v>1456362353.52648</v>
       </c>
       <c r="C25">
-        <v>2126578.24333975</v>
+        <v>27432859.33908277</v>
       </c>
       <c r="D25">
-        <v>137196397.486758</v>
+        <v>1769833527.579178</v>
       </c>
       <c r="E25">
-        <v>9436832.604774071</v>
+        <v>121735140.6015855</v>
       </c>
       <c r="F25">
-        <v>60726700.29445508</v>
+        <v>783374433.7984706</v>
       </c>
       <c r="G25">
-        <v>209486508.6293269</v>
+        <v>2702375961.318317</v>
       </c>
       <c r="H25">
-        <v>174948346.0802983</v>
+        <v>2256833664.435848</v>
       </c>
       <c r="I25">
-        <v>49916178.12191322</v>
+        <v>643918697.7726805</v>
       </c>
       <c r="J25">
-        <v>10339258.05417783</v>
+        <v>133376428.898894</v>
       </c>
       <c r="K25">
-        <v>12351692.41531259</v>
+        <v>159336832.1575324</v>
       </c>
       <c r="L25">
-        <v>7032752.10883475</v>
+        <v>90722502.20396827</v>
       </c>
       <c r="M25">
-        <v>236279136.5547456</v>
+        <v>3048000861.556219</v>
       </c>
       <c r="N25">
-        <v>87275129.62505549</v>
+        <v>1125849172.163216</v>
       </c>
       <c r="O25">
-        <v>578142492.9603379</v>
+        <v>7458038159.188359</v>
       </c>
       <c r="P25">
-        <v>900525308.0645857</v>
+        <v>11616776474.03316</v>
       </c>
       <c r="Q25">
-        <v>693321119.8557744</v>
+        <v>8943842446.13949</v>
       </c>
     </row>
     <row r="26">
@@ -7741,52 +7741,52 @@
         </is>
       </c>
       <c r="B26">
-        <v>110496018.8090051</v>
+        <v>1425398642.636166</v>
       </c>
       <c r="C26">
-        <v>2355279.50155069</v>
+        <v>30383105.5700039</v>
       </c>
       <c r="D26">
-        <v>136323467.3933719</v>
+        <v>1758572729.374497</v>
       </c>
       <c r="E26">
-        <v>9678573.51300345</v>
+        <v>124853598.3177445</v>
       </c>
       <c r="F26">
-        <v>61607127.0480085</v>
+        <v>794731938.9193097</v>
       </c>
       <c r="G26">
-        <v>209964447.4559345</v>
+        <v>2708541372.181555</v>
       </c>
       <c r="H26">
-        <v>174880483.0332644</v>
+        <v>2255958231.129111</v>
       </c>
       <c r="I26">
-        <v>50556649.21254985</v>
+        <v>652180774.8418931</v>
       </c>
       <c r="J26">
-        <v>10377646.38528724</v>
+        <v>133871638.3702054</v>
       </c>
       <c r="K26">
-        <v>11816831.18339524</v>
+        <v>152437122.2657986</v>
       </c>
       <c r="L26">
-        <v>7064980.418437241</v>
+        <v>91138247.39784041</v>
       </c>
       <c r="M26">
-        <v>234861965.412983</v>
+        <v>3029719353.82748</v>
       </c>
       <c r="N26">
-        <v>87256365.91759133</v>
+        <v>1125607120.336928</v>
       </c>
       <c r="O26">
-        <v>576814921.5635084</v>
+        <v>7440912488.169258</v>
       </c>
       <c r="P26">
-        <v>897275387.8284481</v>
+        <v>11574852502.98698</v>
       </c>
       <c r="Q26">
-        <v>692458022.6834142</v>
+        <v>8932708492.616043</v>
       </c>
     </row>
     <row r="27">
@@ -7796,52 +7796,52 @@
         </is>
       </c>
       <c r="B27">
-        <v>108627224.8262284</v>
+        <v>1401291200.258347</v>
       </c>
       <c r="C27">
-        <v>2329961.89880614</v>
+        <v>30056508.4945992</v>
       </c>
       <c r="D27">
-        <v>137487929.8205998</v>
+        <v>1773594294.685737</v>
       </c>
       <c r="E27">
-        <v>9724677.15892981</v>
+        <v>125448335.3501946</v>
       </c>
       <c r="F27">
-        <v>62916801.17709159</v>
+        <v>811626735.1844815</v>
       </c>
       <c r="G27">
-        <v>212459370.0554273</v>
+        <v>2740725873.715013</v>
       </c>
       <c r="H27">
-        <v>173052633.3183087</v>
+        <v>2232378969.806181</v>
       </c>
       <c r="I27">
-        <v>50178497.7255197</v>
+        <v>647302620.6592041</v>
       </c>
       <c r="J27">
-        <v>10754215.02394495</v>
+        <v>138729373.8088899</v>
       </c>
       <c r="K27">
-        <v>11884578.27388365</v>
+        <v>153311059.7330991</v>
       </c>
       <c r="L27">
-        <v>6661552.244671401</v>
+        <v>85934023.95626107</v>
       </c>
       <c r="M27">
-        <v>233303875.2168273</v>
+        <v>3009619990.297072</v>
       </c>
       <c r="N27">
-        <v>87265468.28968883</v>
+        <v>1125724540.936986</v>
       </c>
       <c r="O27">
-        <v>573100820.0928446</v>
+        <v>7393000579.197696</v>
       </c>
       <c r="P27">
-        <v>894187414.9745002</v>
+        <v>11535017653.17105</v>
       </c>
       <c r="Q27">
-        <v>691633169.6139115</v>
+        <v>8922067888.019459</v>
       </c>
     </row>
     <row r="28">
@@ -7851,52 +7851,52 @@
         </is>
       </c>
       <c r="B28">
-        <v>106545630.679455</v>
+        <v>1374438635.76497</v>
       </c>
       <c r="C28">
-        <v>2159825.6727266</v>
+        <v>27861751.17817314</v>
       </c>
       <c r="D28">
-        <v>137483949.041438</v>
+        <v>1773542942.63455</v>
       </c>
       <c r="E28">
-        <v>9648275.1321858</v>
+        <v>124462749.2051968</v>
       </c>
       <c r="F28">
-        <v>63918844.47439402</v>
+        <v>824553093.7196828</v>
       </c>
       <c r="G28">
-        <v>213210894.3207445</v>
+        <v>2750420536.737604</v>
       </c>
       <c r="H28">
-        <v>171589638.4000911</v>
+        <v>2213506335.361175</v>
       </c>
       <c r="I28">
-        <v>50022807.53459712</v>
+        <v>645294217.1963029</v>
       </c>
       <c r="J28">
-        <v>11076873.03460792</v>
+        <v>142891662.1464422</v>
       </c>
       <c r="K28">
-        <v>11452895.91085452</v>
+        <v>147742357.2500233</v>
       </c>
       <c r="L28">
-        <v>6452523.773295891</v>
+        <v>83237556.67551699</v>
       </c>
       <c r="M28">
-        <v>232295850.5536499</v>
+        <v>2996616472.142084</v>
       </c>
       <c r="N28">
-        <v>88087574.63319461</v>
+        <v>1136329712.76821</v>
       </c>
       <c r="O28">
-        <v>570978163.840291</v>
+        <v>7365618313.539755</v>
       </c>
       <c r="P28">
-        <v>890734688.8404906</v>
+        <v>11490477486.04233</v>
       </c>
       <c r="Q28">
-        <v>689648959.754545</v>
+        <v>8896471580.83363</v>
       </c>
     </row>
     <row r="29">
@@ -7906,52 +7906,52 @@
         </is>
       </c>
       <c r="B29">
-        <v>106373844.9442034</v>
+        <v>1372222599.780224</v>
       </c>
       <c r="C29">
-        <v>1792667.68822664</v>
+        <v>23125413.17812366</v>
       </c>
       <c r="D29">
-        <v>137904452.8013743</v>
+        <v>1778967441.137728</v>
       </c>
       <c r="E29">
-        <v>9400314.64948778</v>
+        <v>121264058.9783924</v>
       </c>
       <c r="F29">
-        <v>64397423.44545153</v>
+        <v>830726762.4463247</v>
       </c>
       <c r="G29">
-        <v>213494858.5845402</v>
+        <v>2754083675.740569</v>
       </c>
       <c r="H29">
-        <v>171051140.6046569</v>
+        <v>2206559713.800075</v>
       </c>
       <c r="I29">
-        <v>49395769.49286105</v>
+        <v>637205426.4579076</v>
       </c>
       <c r="J29">
-        <v>11663850.02641414</v>
+        <v>150463665.3407424</v>
       </c>
       <c r="K29">
-        <v>10899373.07652639</v>
+        <v>140601912.6871904</v>
       </c>
       <c r="L29">
-        <v>6693785.8440784</v>
+        <v>86349837.38861136</v>
       </c>
       <c r="M29">
-        <v>235177518.4010169</v>
+        <v>3033789987.373118</v>
       </c>
       <c r="N29">
-        <v>88162288.07967918</v>
+        <v>1137293516.227861</v>
       </c>
       <c r="O29">
-        <v>573043725.525233</v>
+        <v>7392264059.275506</v>
       </c>
       <c r="P29">
-        <v>892912429.0539767</v>
+        <v>11518570334.7963</v>
       </c>
       <c r="Q29">
-        <v>691682510.1860157</v>
+        <v>8922704381.399603</v>
       </c>
     </row>
     <row r="30">
@@ -7961,52 +7961,52 @@
         </is>
       </c>
       <c r="B30">
-        <v>107545185.7254146</v>
+        <v>1387332895.857848</v>
       </c>
       <c r="C30">
-        <v>1495306.56783962</v>
+        <v>19289454.7251311</v>
       </c>
       <c r="D30">
-        <v>137666707.8525163</v>
+        <v>1775900531.29746</v>
       </c>
       <c r="E30">
-        <v>9307525.861461161</v>
+        <v>120067083.612849</v>
       </c>
       <c r="F30">
-        <v>63607933.57977176</v>
+        <v>820542343.1790557</v>
       </c>
       <c r="G30">
-        <v>212077473.8615888</v>
+        <v>2735799412.814496</v>
       </c>
       <c r="H30">
-        <v>170833703.4158289</v>
+        <v>2203754774.064193</v>
       </c>
       <c r="I30">
-        <v>48979631.75045358</v>
+        <v>631837249.5808512</v>
       </c>
       <c r="J30">
-        <v>12578577.33174207</v>
+        <v>162263647.5794727</v>
       </c>
       <c r="K30">
-        <v>10791470.96186999</v>
+        <v>139209975.4081229</v>
       </c>
       <c r="L30">
-        <v>6768427.1103237</v>
+        <v>87312709.72317573</v>
       </c>
       <c r="M30">
-        <v>239513726.1490352</v>
+        <v>3089727067.322554</v>
       </c>
       <c r="N30">
-        <v>89033440.18136261</v>
+        <v>1148531378.339578</v>
       </c>
       <c r="O30">
-        <v>578498976.9006159</v>
+        <v>7462636802.017945</v>
       </c>
       <c r="P30">
-        <v>898121636.4876194</v>
+        <v>11585769110.69029</v>
       </c>
       <c r="Q30">
-        <v>694774583.4705186</v>
+        <v>8962592126.76969</v>
       </c>
     </row>
     <row r="31">
@@ -8016,52 +8016,52 @@
         </is>
       </c>
       <c r="B31">
-        <v>109089587.4427743</v>
+        <v>1407255678.011788</v>
       </c>
       <c r="C31">
-        <v>1472968.93347926</v>
+        <v>19001299.24188246</v>
       </c>
       <c r="D31">
-        <v>136129275.052359</v>
+        <v>1756067648.175431</v>
       </c>
       <c r="E31">
-        <v>9094699.27955913</v>
+        <v>117321620.7063128</v>
       </c>
       <c r="F31">
-        <v>63991214.89283669</v>
+        <v>825486672.1175933</v>
       </c>
       <c r="G31">
-        <v>210688158.1582341</v>
+        <v>2717877240.24122</v>
       </c>
       <c r="H31">
-        <v>172029047.3744988</v>
+        <v>2219174711.131035</v>
       </c>
       <c r="I31">
-        <v>50226062.00426456</v>
+        <v>647916199.8550129</v>
       </c>
       <c r="J31">
-        <v>13453658.33060616</v>
+        <v>173552192.4648195</v>
       </c>
       <c r="K31">
-        <v>10554774.89145235</v>
+        <v>136156596.0997353</v>
       </c>
       <c r="L31">
-        <v>6746172.37927295</v>
+        <v>87025623.69262105</v>
       </c>
       <c r="M31">
-        <v>242866500.4644023</v>
+        <v>3132977855.99079</v>
       </c>
       <c r="N31">
-        <v>90356553.4648536</v>
+        <v>1165599539.696611</v>
       </c>
       <c r="O31">
-        <v>586232768.9093506</v>
+        <v>7562402718.930623</v>
       </c>
       <c r="P31">
-        <v>906010514.5103593</v>
+        <v>11687535637.18364</v>
       </c>
       <c r="Q31">
-        <v>699818201.2234584</v>
+        <v>9027654795.782614</v>
       </c>
     </row>
     <row r="32">
@@ -8071,52 +8071,52 @@
         </is>
       </c>
       <c r="B32">
-        <v>108688960.6978928</v>
+        <v>1402087593.002817</v>
       </c>
       <c r="C32">
-        <v>1624430.31590017</v>
+        <v>20955151.07511219</v>
       </c>
       <c r="D32">
-        <v>136065558.5789517</v>
+        <v>1755245705.668476</v>
       </c>
       <c r="E32">
-        <v>8535893.116765959</v>
+        <v>110113021.2062809</v>
       </c>
       <c r="F32">
-        <v>63499638.51671889</v>
+        <v>819145336.8656738</v>
       </c>
       <c r="G32">
-        <v>209725520.5283366</v>
+        <v>2705459214.815543</v>
       </c>
       <c r="H32">
-        <v>174293181.1282701</v>
+        <v>2248382036.554684</v>
       </c>
       <c r="I32">
-        <v>52359554.53441551</v>
+        <v>675438253.4939601</v>
       </c>
       <c r="J32">
-        <v>14076229.35510358</v>
+        <v>181583358.6808362</v>
       </c>
       <c r="K32">
-        <v>10597469.2283286</v>
+        <v>136707353.0454389</v>
       </c>
       <c r="L32">
-        <v>6473534.32079492</v>
+        <v>83508592.73825446</v>
       </c>
       <c r="M32">
-        <v>243183871.0991325</v>
+        <v>3137071937.178809</v>
       </c>
       <c r="N32">
-        <v>91257864.46108887</v>
+        <v>1177226451.548046</v>
       </c>
       <c r="O32">
-        <v>592241704.127134</v>
+        <v>7639917983.240028</v>
       </c>
       <c r="P32">
-        <v>910656185.3533635</v>
+        <v>11747464791.05839</v>
       </c>
       <c r="Q32">
-        <v>704235825.8735869</v>
+        <v>9084642153.769272</v>
       </c>
     </row>
     <row r="33">
@@ -8126,52 +8126,52 @@
         </is>
       </c>
       <c r="B33">
-        <v>107266796.1118822</v>
+        <v>1383741669.843281</v>
       </c>
       <c r="C33">
-        <v>1890724.95801566</v>
+        <v>24390351.95840202</v>
       </c>
       <c r="D33">
-        <v>137390539.3233927</v>
+        <v>1772337957.271766</v>
       </c>
       <c r="E33">
-        <v>7690925.122453639</v>
+        <v>99212934.07965195</v>
       </c>
       <c r="F33">
-        <v>63224005.3606239</v>
+        <v>815589669.1520483</v>
       </c>
       <c r="G33">
-        <v>210196194.764486</v>
+        <v>2711530912.461869</v>
       </c>
       <c r="H33">
-        <v>176695190.0192297</v>
+        <v>2279367951.248063</v>
       </c>
       <c r="I33">
-        <v>54224620.01302592</v>
+        <v>699497598.1680344</v>
       </c>
       <c r="J33">
-        <v>14461226.26397158</v>
+        <v>186549818.8052334</v>
       </c>
       <c r="K33">
-        <v>10302168.55997068</v>
+        <v>132897974.4236218</v>
       </c>
       <c r="L33">
-        <v>6442034.57839164</v>
+        <v>83102246.06125215</v>
       </c>
       <c r="M33">
-        <v>243838692.402527</v>
+        <v>3145519131.992598</v>
       </c>
       <c r="N33">
-        <v>91388305.897312</v>
+        <v>1178909146.075325</v>
       </c>
       <c r="O33">
-        <v>597352237.7344285</v>
+        <v>7705843866.774128</v>
       </c>
       <c r="P33">
-        <v>914815228.6107968</v>
+        <v>11801116449.07928</v>
       </c>
       <c r="Q33">
-        <v>709718092.0232108</v>
+        <v>9155363387.099419</v>
       </c>
     </row>
     <row r="34">
@@ -8181,52 +8181,52 @@
         </is>
       </c>
       <c r="B34">
-        <v>105804556.2085769</v>
+        <v>1364878775.090643</v>
       </c>
       <c r="C34">
-        <v>1919722.49822381</v>
+        <v>24764420.22708715</v>
       </c>
       <c r="D34">
-        <v>137109650.2492104</v>
+        <v>1768714488.214814</v>
       </c>
       <c r="E34">
-        <v>6848669.76334876</v>
+        <v>88347839.947199</v>
       </c>
       <c r="F34">
-        <v>63247787.84192166</v>
+        <v>815896463.1607894</v>
       </c>
       <c r="G34">
-        <v>209125830.3527046</v>
+        <v>2697723211.549889</v>
       </c>
       <c r="H34">
-        <v>175867302.6180188</v>
+        <v>2268688203.772442</v>
       </c>
       <c r="I34">
-        <v>56019934.57130156</v>
+        <v>722657155.9697902</v>
       </c>
       <c r="J34">
-        <v>14324742.38939615</v>
+        <v>184789176.8232103</v>
       </c>
       <c r="K34">
-        <v>9892365.59515018</v>
+        <v>127611516.1774373</v>
       </c>
       <c r="L34">
-        <v>6078105.33521614</v>
+        <v>78407558.82428822</v>
       </c>
       <c r="M34">
-        <v>242510665.3610689</v>
+        <v>3128387583.157789</v>
       </c>
       <c r="N34">
-        <v>92577350.68568859</v>
+        <v>1194247823.845383</v>
       </c>
       <c r="O34">
-        <v>597270466.5558404</v>
+        <v>7704789018.570341</v>
       </c>
       <c r="P34">
-        <v>912200853.1171219</v>
+        <v>11767391005.21087</v>
       </c>
       <c r="Q34">
-        <v>707740840.8876402</v>
+        <v>9129856847.45056</v>
       </c>
     </row>
     <row r="35">
@@ -8236,52 +8236,52 @@
         </is>
       </c>
       <c r="B35">
-        <v>105140806.5015677</v>
+        <v>1356316403.870224</v>
       </c>
       <c r="C35">
-        <v>1719109.20421082</v>
+        <v>22176508.73431958</v>
       </c>
       <c r="D35">
-        <v>133289012.6963421</v>
+        <v>1719428263.782813</v>
       </c>
       <c r="E35">
-        <v>6767525.45114821</v>
+        <v>87301078.31981191</v>
       </c>
       <c r="F35">
-        <v>60906979.0934957</v>
+        <v>785700030.3060945</v>
       </c>
       <c r="G35">
-        <v>202682626.4451968</v>
+        <v>2614605881.143039</v>
       </c>
       <c r="H35">
-        <v>169878606.6192357</v>
+        <v>2191434025.388141</v>
       </c>
       <c r="I35">
-        <v>55011634.47921169</v>
+        <v>709650084.7818308</v>
       </c>
       <c r="J35">
-        <v>13759281.99249792</v>
+        <v>177494737.7032232</v>
       </c>
       <c r="K35">
-        <v>9441827.441094581</v>
+        <v>121799573.9901201</v>
       </c>
       <c r="L35">
-        <v>5734961.40308717</v>
+        <v>73981002.09982449</v>
       </c>
       <c r="M35">
-        <v>237572869.4076141</v>
+        <v>3064690015.358222</v>
       </c>
       <c r="N35">
-        <v>92274149.88868235</v>
+        <v>1190336533.564002</v>
       </c>
       <c r="O35">
-        <v>583673331.2314235</v>
+        <v>7529385972.885364</v>
       </c>
       <c r="P35">
-        <v>891496764.1781881</v>
+        <v>11500308257.89863</v>
       </c>
       <c r="Q35">
-        <v>688346846.3848507</v>
+        <v>8879674318.364574</v>
       </c>
     </row>
     <row r="36">
@@ -8291,52 +8291,52 @@
         </is>
       </c>
       <c r="B36">
-        <v>106789430.6172024</v>
+        <v>1377583654.961911</v>
       </c>
       <c r="C36">
-        <v>1566030.49827694</v>
+        <v>20201793.42777253</v>
       </c>
       <c r="D36">
-        <v>129486126.2439263</v>
+        <v>1670371028.546649</v>
       </c>
       <c r="E36">
-        <v>6626439.74536934</v>
+        <v>85481072.7152645</v>
       </c>
       <c r="F36">
-        <v>58231118.22742927</v>
+        <v>751181425.1338376</v>
       </c>
       <c r="G36">
-        <v>195909714.7150018</v>
+        <v>2527235319.823524</v>
       </c>
       <c r="H36">
-        <v>162667157.7510633</v>
+        <v>2098406334.988716</v>
       </c>
       <c r="I36">
-        <v>52069085.37076323</v>
+        <v>671691201.2828456</v>
       </c>
       <c r="J36">
-        <v>14283084.70750293</v>
+        <v>184251792.7267878</v>
       </c>
       <c r="K36">
-        <v>9967109.184215069</v>
+        <v>128575708.4763744</v>
       </c>
       <c r="L36">
-        <v>5352648.32256923</v>
+        <v>69049163.36114307</v>
       </c>
       <c r="M36">
-        <v>230339392.6893654</v>
+        <v>2971378165.692813</v>
       </c>
       <c r="N36">
-        <v>90149713.91087671</v>
+        <v>1162931309.45031</v>
       </c>
       <c r="O36">
-        <v>564828191.9363558</v>
+        <v>7286283675.978991</v>
       </c>
       <c r="P36">
-        <v>867527337.2685601</v>
+        <v>11191102650.76443</v>
       </c>
       <c r="Q36">
-        <v>665235544.4179118</v>
+        <v>8581538522.991062</v>
       </c>
     </row>
     <row r="37">
@@ -8346,52 +8346,52 @@
         </is>
       </c>
       <c r="B37">
-        <v>110840131.6884345</v>
+        <v>1429837698.780805</v>
       </c>
       <c r="C37">
-        <v>1302058.07154814</v>
+        <v>16796549.12297101</v>
       </c>
       <c r="D37">
-        <v>123394936.0741042</v>
+        <v>1591794675.355944</v>
       </c>
       <c r="E37">
-        <v>7124481.97061727</v>
+        <v>91905817.42096278</v>
       </c>
       <c r="F37">
-        <v>55254024.86049213</v>
+        <v>712776920.7003485</v>
       </c>
       <c r="G37">
-        <v>187075500.9767617</v>
+        <v>2413273962.600225</v>
       </c>
       <c r="H37">
-        <v>158596834.6035907</v>
+        <v>2045899166.38632</v>
       </c>
       <c r="I37">
-        <v>49528492.64994369</v>
+        <v>638917555.1842737</v>
       </c>
       <c r="J37">
-        <v>14614048.26879882</v>
+        <v>188521222.6675048</v>
       </c>
       <c r="K37">
-        <v>11643520.23205022</v>
+        <v>150201410.9934478</v>
       </c>
       <c r="L37">
-        <v>4552345.25595348</v>
+        <v>58725253.80179989</v>
       </c>
       <c r="M37">
-        <v>222903536.7928797</v>
+        <v>2875455624.628149</v>
       </c>
       <c r="N37">
-        <v>89123158.13045299</v>
+        <v>1149688739.882843</v>
       </c>
       <c r="O37">
-        <v>550961935.9336696</v>
+        <v>7107408973.544337</v>
       </c>
       <c r="P37">
-        <v>848877568.5988659</v>
+        <v>10950520634.92537</v>
       </c>
       <c r="Q37">
-        <v>644361933.5240248</v>
+        <v>8312268942.459921</v>
       </c>
     </row>
     <row r="38">
@@ -8401,52 +8401,52 @@
         </is>
       </c>
       <c r="B38">
-        <v>113138285.7108243</v>
+        <v>1459483885.669633</v>
       </c>
       <c r="C38">
-        <v>1376701.60377926</v>
+        <v>17759450.68875245</v>
       </c>
       <c r="D38">
-        <v>119420347.1035236</v>
+        <v>1540522477.635455</v>
       </c>
       <c r="E38">
-        <v>7681686.26309181</v>
+        <v>99093752.79388435</v>
       </c>
       <c r="F38">
-        <v>52166791.19032894</v>
+        <v>672951606.3552433</v>
       </c>
       <c r="G38">
-        <v>180645526.1607236</v>
+        <v>2330327287.473335</v>
       </c>
       <c r="H38">
-        <v>157548576.6518709</v>
+        <v>2032376638.809135</v>
       </c>
       <c r="I38">
-        <v>45931164.19376144</v>
+        <v>592512018.0995226</v>
       </c>
       <c r="J38">
-        <v>15060054.51895442</v>
+        <v>194274703.294512</v>
       </c>
       <c r="K38">
-        <v>13900182.86656179</v>
+        <v>179312358.9786471</v>
       </c>
       <c r="L38">
-        <v>4228126.0265588</v>
+        <v>54542825.74260852</v>
       </c>
       <c r="M38">
-        <v>220529629.0580446</v>
+        <v>2844832214.848775</v>
       </c>
       <c r="N38">
-        <v>87283793.28393422</v>
+        <v>1125960933.362751</v>
       </c>
       <c r="O38">
-        <v>544481526.5996861</v>
+        <v>7023811693.135951</v>
       </c>
       <c r="P38">
-        <v>838265338.4712341</v>
+        <v>10813622866.27892</v>
       </c>
       <c r="Q38">
-        <v>633615133.4499167</v>
+        <v>8173635221.503926</v>
       </c>
     </row>
     <row r="39">
@@ -8456,52 +8456,52 @@
         </is>
       </c>
       <c r="B39">
-        <v>117682106.8178985</v>
+        <v>1518099177.95089</v>
       </c>
       <c r="C39">
-        <v>1562111.68050538</v>
+        <v>20151240.6785194</v>
       </c>
       <c r="D39">
-        <v>119542859.5283919</v>
+        <v>1542102887.916256</v>
       </c>
       <c r="E39">
-        <v>7697652.14968787</v>
+        <v>99299712.73097353</v>
       </c>
       <c r="F39">
-        <v>52606508.51723989</v>
+        <v>678623959.8723946</v>
       </c>
       <c r="G39">
-        <v>181409131.875825</v>
+        <v>2340177801.198143</v>
       </c>
       <c r="H39">
-        <v>163171181.975982</v>
+        <v>2104908247.490168</v>
       </c>
       <c r="I39">
-        <v>44355781.86395722</v>
+        <v>572189586.0450481</v>
       </c>
       <c r="J39">
-        <v>15955466.80048195</v>
+        <v>205825521.7262172</v>
       </c>
       <c r="K39">
-        <v>15916019.74450632</v>
+        <v>205316654.7041315</v>
       </c>
       <c r="L39">
-        <v>4075026.13293252</v>
+        <v>52567837.11482951</v>
       </c>
       <c r="M39">
-        <v>219571909.5611635</v>
+        <v>2832477633.339009</v>
       </c>
       <c r="N39">
-        <v>87088404.9572688</v>
+        <v>1123440423.948768</v>
       </c>
       <c r="O39">
-        <v>550133791.0362923</v>
+        <v>7096725904.368171</v>
       </c>
       <c r="P39">
-        <v>849225029.7300159</v>
+        <v>10955002883.5172</v>
       </c>
       <c r="Q39">
-        <v>640379491.821916</v>
+        <v>8260895444.502716</v>
       </c>
     </row>
     <row r="40">
@@ -8511,52 +8511,52 @@
         </is>
       </c>
       <c r="B40">
-        <v>120443854.4497379</v>
+        <v>1553725722.401619</v>
       </c>
       <c r="C40">
-        <v>1750033.67193863</v>
+        <v>22575434.36800833</v>
       </c>
       <c r="D40">
-        <v>119960121.3112348</v>
+        <v>1547485564.914929</v>
       </c>
       <c r="E40">
-        <v>7451481.78790153</v>
+        <v>96124115.06392974</v>
       </c>
       <c r="F40">
-        <v>53892442.47944486</v>
+        <v>695212507.9848387</v>
       </c>
       <c r="G40">
-        <v>183054079.2505199</v>
+        <v>2361397622.331707</v>
       </c>
       <c r="H40">
-        <v>169856754.595071</v>
+        <v>2191152134.276417</v>
       </c>
       <c r="I40">
-        <v>44931067.21085633</v>
+        <v>579610767.0200467</v>
       </c>
       <c r="J40">
-        <v>16257420.94084346</v>
+        <v>209720730.1368806</v>
       </c>
       <c r="K40">
-        <v>16177690.84562421</v>
+        <v>208692211.9085523</v>
       </c>
       <c r="L40">
-        <v>4339438.37596388</v>
+        <v>55978755.04993405</v>
       </c>
       <c r="M40">
-        <v>225272279.3903839</v>
+        <v>2906012404.135952</v>
       </c>
       <c r="N40">
-        <v>88920555.50245614</v>
+        <v>1147075165.981684</v>
       </c>
       <c r="O40">
-        <v>565755206.8611989</v>
+        <v>7298242168.509466</v>
       </c>
       <c r="P40">
-        <v>869253140.5614567</v>
+        <v>11213365513.24279</v>
       </c>
       <c r="Q40">
-        <v>655549292.2332987</v>
+        <v>8456585869.809553</v>
       </c>
     </row>
     <row r="41">
@@ -8566,52 +8566,52 @@
         </is>
       </c>
       <c r="B41">
-        <v>120460390.4525282</v>
+        <v>1553939036.837614</v>
       </c>
       <c r="C41">
-        <v>2049525.75774476</v>
+        <v>26438882.27490741</v>
       </c>
       <c r="D41">
-        <v>123715087.8099643</v>
+        <v>1595924632.74854</v>
       </c>
       <c r="E41">
-        <v>7186464.54145368</v>
+        <v>92705392.58475247</v>
       </c>
       <c r="F41">
-        <v>55670688.41784033</v>
+        <v>718151880.5901403</v>
       </c>
       <c r="G41">
-        <v>188621766.5270031</v>
+        <v>2433220788.19834</v>
       </c>
       <c r="H41">
-        <v>171833383.3793209</v>
+        <v>2216650645.593239</v>
       </c>
       <c r="I41">
-        <v>44015577.86427899</v>
+        <v>567800954.449199</v>
       </c>
       <c r="J41">
-        <v>15983730.38325783</v>
+        <v>206190121.944026</v>
       </c>
       <c r="K41">
-        <v>15498091.17828617</v>
+        <v>199925376.1998916</v>
       </c>
       <c r="L41">
-        <v>4891479.55115176</v>
+        <v>63100086.2098577</v>
       </c>
       <c r="M41">
-        <v>230087929.1757031</v>
+        <v>2968134286.36657</v>
       </c>
       <c r="N41">
-        <v>89817353.85847184</v>
+        <v>1158643864.774287</v>
       </c>
       <c r="O41">
-        <v>572127545.3904705</v>
+        <v>7380445335.537069</v>
       </c>
       <c r="P41">
-        <v>881209702.3700018</v>
+        <v>11367605160.57302</v>
       </c>
       <c r="Q41">
-        <v>666040478.5078499</v>
+        <v>8591922172.751265</v>
       </c>
     </row>
     <row r="42">
@@ -8621,52 +8621,52 @@
         </is>
       </c>
       <c r="B42">
-        <v>121968333.7387799</v>
+        <v>1573391505.23026</v>
       </c>
       <c r="C42">
-        <v>2135013.47037004</v>
+        <v>27541673.76777352</v>
       </c>
       <c r="D42">
-        <v>127384133.1902674</v>
+        <v>1643255318.154449</v>
       </c>
       <c r="E42">
-        <v>7195853.4701865</v>
+        <v>92826509.76540585</v>
       </c>
       <c r="F42">
-        <v>58080466.83599789</v>
+        <v>749238022.1843729</v>
       </c>
       <c r="G42">
-        <v>194795466.9668218</v>
+        <v>2512861523.872002</v>
       </c>
       <c r="H42">
-        <v>174643465.1478199</v>
+        <v>2252900700.406877</v>
       </c>
       <c r="I42">
-        <v>45903912.63512942</v>
+        <v>592160472.9931695</v>
       </c>
       <c r="J42">
-        <v>15718606.43687868</v>
+        <v>202770023.035735</v>
       </c>
       <c r="K42">
-        <v>14340881.85256191</v>
+        <v>184997375.8980486</v>
       </c>
       <c r="L42">
-        <v>6024542.92220501</v>
+        <v>77716603.69644463</v>
       </c>
       <c r="M42">
-        <v>233264350.9643304</v>
+        <v>3009110127.439862</v>
       </c>
       <c r="N42">
-        <v>90171744.22133735</v>
+        <v>1163215500.455252</v>
       </c>
       <c r="O42">
-        <v>580067504.1802626</v>
+        <v>7482870803.925387</v>
       </c>
       <c r="P42">
-        <v>896831304.8858643</v>
+        <v>11569123833.02765</v>
       </c>
       <c r="Q42">
-        <v>678666684.0035421</v>
+        <v>8754800223.645693</v>
       </c>
     </row>
     <row r="43">
@@ -8676,52 +8676,52 @@
         </is>
       </c>
       <c r="B43">
-        <v>119267877.1566773</v>
+        <v>1538555615.321137</v>
       </c>
       <c r="C43">
-        <v>2100963.51916995</v>
+        <v>27102429.39729235</v>
       </c>
       <c r="D43">
-        <v>131634204.6907254</v>
+        <v>1698081240.510358</v>
       </c>
       <c r="E43">
-        <v>6830686.57921023</v>
+        <v>88115856.87181197</v>
       </c>
       <c r="F43">
-        <v>58858611.04743545</v>
+        <v>759276082.5119174</v>
       </c>
       <c r="G43">
-        <v>199424465.8365411</v>
+        <v>2572575609.29138</v>
       </c>
       <c r="H43">
-        <v>175572055.3195821</v>
+        <v>2264879513.622609</v>
       </c>
       <c r="I43">
-        <v>48452503.94879802</v>
+        <v>625037300.9394944</v>
       </c>
       <c r="J43">
-        <v>15247285.36717452</v>
+        <v>196689981.2365513</v>
       </c>
       <c r="K43">
-        <v>13431636.59006361</v>
+        <v>173268112.0118206</v>
       </c>
       <c r="L43">
-        <v>7341412.32573851</v>
+        <v>94704219.00202678</v>
       </c>
       <c r="M43">
-        <v>240705007.9936121</v>
+        <v>3105094603.117596</v>
       </c>
       <c r="N43">
-        <v>90546746.36762187</v>
+        <v>1168053028.142322</v>
       </c>
       <c r="O43">
-        <v>591296647.9125907</v>
+        <v>7627726758.072421</v>
       </c>
       <c r="P43">
-        <v>909988990.9058092</v>
+        <v>11738857982.68494</v>
       </c>
       <c r="Q43">
-        <v>692832955.0557714</v>
+        <v>8937545120.21945</v>
       </c>
     </row>
     <row r="44">
@@ -8731,52 +8731,52 @@
         </is>
       </c>
       <c r="B44">
-        <v>117799684.6996458</v>
+        <v>1519615932.625431</v>
       </c>
       <c r="C44">
-        <v>1888947.79332693</v>
+        <v>24367426.5339174</v>
       </c>
       <c r="D44">
-        <v>138034072.4399759</v>
+        <v>1780639534.475689</v>
       </c>
       <c r="E44">
-        <v>6857541.45986292</v>
+        <v>88462284.83223167</v>
       </c>
       <c r="F44">
-        <v>60451718.68625509</v>
+        <v>779827171.0526906</v>
       </c>
       <c r="G44">
-        <v>207232280.3794208</v>
+        <v>2673296416.894528</v>
       </c>
       <c r="H44">
-        <v>176634237.4195427</v>
+        <v>2278581662.712101</v>
       </c>
       <c r="I44">
-        <v>48982586.40807701</v>
+        <v>631875364.6641934</v>
       </c>
       <c r="J44">
-        <v>14790431.79059562</v>
+        <v>190796570.0986835</v>
       </c>
       <c r="K44">
-        <v>13685925.58157512</v>
+        <v>176548440.002319</v>
       </c>
       <c r="L44">
-        <v>8370842.44123296</v>
+        <v>107983867.4919052</v>
       </c>
       <c r="M44">
-        <v>246791409.0565509</v>
+        <v>3183609176.829506</v>
       </c>
       <c r="N44">
-        <v>89955780.12353906</v>
+        <v>1160429563.593654</v>
       </c>
       <c r="O44">
-        <v>599211212.8211133</v>
+        <v>7729824645.392363</v>
       </c>
       <c r="P44">
-        <v>924243177.90018</v>
+        <v>11922736994.91232</v>
       </c>
       <c r="Q44">
-        <v>708116870.6357622</v>
+        <v>9134707631.201332</v>
       </c>
     </row>
     <row r="45">
@@ -8786,52 +8786,52 @@
         </is>
       </c>
       <c r="B45">
-        <v>115850904.0435487</v>
+        <v>1494476662.161779</v>
       </c>
       <c r="C45">
-        <v>1604253.59730362</v>
+        <v>20694871.4052167</v>
       </c>
       <c r="D45">
-        <v>143114597.8556399</v>
+        <v>1846178312.337755</v>
       </c>
       <c r="E45">
-        <v>6664515.79931898</v>
+        <v>85972253.81121485</v>
       </c>
       <c r="F45">
-        <v>62055650.67817909</v>
+        <v>800517893.7485102</v>
       </c>
       <c r="G45">
-        <v>213439017.9304416</v>
+        <v>2753363331.302697</v>
       </c>
       <c r="H45">
-        <v>178333589.8392365</v>
+        <v>2300503308.926151</v>
       </c>
       <c r="I45">
-        <v>50613803.21558765</v>
+        <v>652918061.4810807</v>
       </c>
       <c r="J45">
-        <v>15656960.16249319</v>
+        <v>201974786.0961621</v>
       </c>
       <c r="K45">
-        <v>14083973.97200771</v>
+        <v>181683264.2388995</v>
       </c>
       <c r="L45">
-        <v>8902060.69408715</v>
+        <v>114836582.9537242</v>
       </c>
       <c r="M45">
-        <v>249617509.9936244</v>
+        <v>3220065878.917754</v>
       </c>
       <c r="N45">
-        <v>90539733.77476734</v>
+        <v>1167962565.694499</v>
       </c>
       <c r="O45">
-        <v>607747631.651804</v>
+        <v>7839944448.308271</v>
       </c>
       <c r="P45">
-        <v>937037553.6257943</v>
+        <v>12087784441.77275</v>
       </c>
       <c r="Q45">
-        <v>721744855.113391</v>
+        <v>9310508630.962744</v>
       </c>
     </row>
     <row r="46">
@@ -8841,52 +8841,52 @@
         </is>
       </c>
       <c r="B46">
-        <v>113682736.9613001</v>
+        <v>1466507306.800771</v>
       </c>
       <c r="C46">
-        <v>1605036.88124514</v>
+        <v>20704975.7680623</v>
       </c>
       <c r="D46">
-        <v>147657732.9826351</v>
+        <v>1904784755.475993</v>
       </c>
       <c r="E46">
-        <v>6301804.58269222</v>
+        <v>81293279.11672963</v>
       </c>
       <c r="F46">
-        <v>63660256.80346587</v>
+        <v>821217312.7647098</v>
       </c>
       <c r="G46">
-        <v>219224831.2500383</v>
+        <v>2828000323.125494</v>
       </c>
       <c r="H46">
-        <v>177387867.16748</v>
+        <v>2288303486.460492</v>
       </c>
       <c r="I46">
-        <v>51064829.1724401</v>
+        <v>658736296.3244773</v>
       </c>
       <c r="J46">
-        <v>15965270.00837463</v>
+        <v>205951983.1080327</v>
       </c>
       <c r="K46">
-        <v>14675726.8795845</v>
+        <v>189316876.74664</v>
       </c>
       <c r="L46">
-        <v>8397765.007897511</v>
+        <v>108331168.6018779</v>
       </c>
       <c r="M46">
-        <v>252903516.4707131</v>
+        <v>3262455362.472199</v>
       </c>
       <c r="N46">
-        <v>90112532.07030746</v>
+        <v>1162451663.706966</v>
       </c>
       <c r="O46">
-        <v>610507506.7767973</v>
+        <v>7875546837.420686</v>
       </c>
       <c r="P46">
-        <v>943415074.9881357</v>
+        <v>12170054467.34695</v>
       </c>
       <c r="Q46">
-        <v>731222040.9486306</v>
+        <v>9432764328.237335</v>
       </c>
     </row>
     <row r="47">
@@ -8896,52 +8896,52 @@
         </is>
       </c>
       <c r="B47">
-        <v>112617302.677504</v>
+        <v>1452763204.539802</v>
       </c>
       <c r="C47">
-        <v>1511869.99889355</v>
+        <v>19503122.9857268</v>
       </c>
       <c r="D47">
-        <v>149743169.8925543</v>
+        <v>1931686891.61395</v>
       </c>
       <c r="E47">
-        <v>6080572.7959284</v>
+        <v>78439389.06747636</v>
       </c>
       <c r="F47">
-        <v>66323260.45234922</v>
+        <v>855570059.835305</v>
       </c>
       <c r="G47">
-        <v>223658873.1397254</v>
+        <v>2885199463.502459</v>
       </c>
       <c r="H47">
-        <v>176844761.4012975</v>
+        <v>2281297422.076737</v>
       </c>
       <c r="I47">
-        <v>49650510.61765517</v>
+        <v>640491586.9677517</v>
       </c>
       <c r="J47">
-        <v>16805527.32385777</v>
+        <v>216791302.4777652</v>
       </c>
       <c r="K47">
-        <v>15382545.02799236</v>
+        <v>198434830.8611014</v>
       </c>
       <c r="L47">
-        <v>7963862.60182195</v>
+        <v>102733827.5635032</v>
       </c>
       <c r="M47">
-        <v>255107937.5930636</v>
+        <v>3290892394.950521</v>
       </c>
       <c r="N47">
-        <v>89131497.92277481</v>
+        <v>1149796323.203795</v>
       </c>
       <c r="O47">
-        <v>610886642.4884632</v>
+        <v>7880437688.101175</v>
       </c>
       <c r="P47">
-        <v>947162818.3056927</v>
+        <v>12218400356.14344</v>
       </c>
       <c r="Q47">
-        <v>737450155.1035918</v>
+        <v>9513107000.836334</v>
       </c>
     </row>
     <row r="48">
@@ -8951,52 +8951,52 @@
         </is>
       </c>
       <c r="B48">
-        <v>109510674.4859377</v>
+        <v>1412687700.868596</v>
       </c>
       <c r="C48">
-        <v>1699532.43124115</v>
+        <v>21923968.36301083</v>
       </c>
       <c r="D48">
-        <v>148087452.5589838</v>
+        <v>1910328138.010891</v>
       </c>
       <c r="E48">
-        <v>6269648.260560339</v>
+        <v>80878462.56122838</v>
       </c>
       <c r="F48">
-        <v>66185800.0387266</v>
+        <v>853796820.4995731</v>
       </c>
       <c r="G48">
-        <v>222242433.2895119</v>
+        <v>2866927389.434704</v>
       </c>
       <c r="H48">
-        <v>174488017.1568014</v>
+        <v>2250895421.322738</v>
       </c>
       <c r="I48">
-        <v>48752234.87839459</v>
+        <v>628903829.9312903</v>
       </c>
       <c r="J48">
-        <v>17267311.92930195</v>
+        <v>222748323.8879952</v>
       </c>
       <c r="K48">
-        <v>15703377.3941196</v>
+        <v>202573568.3841428</v>
       </c>
       <c r="L48">
-        <v>7734834.15864661</v>
+        <v>99779360.64654127</v>
       </c>
       <c r="M48">
-        <v>258170082.8666706</v>
+        <v>3330394068.980051</v>
       </c>
       <c r="N48">
-        <v>88325946.18725909</v>
+        <v>1139404705.815642</v>
       </c>
       <c r="O48">
-        <v>610441804.5711938</v>
+        <v>7874699278.9684</v>
       </c>
       <c r="P48">
-        <v>942194912.3466434</v>
+        <v>12154314369.2717</v>
       </c>
       <c r="Q48">
-        <v>736623457.5148001</v>
+        <v>9502442601.940922</v>
       </c>
     </row>
     <row r="49">
@@ -9006,52 +9006,52 @@
         </is>
       </c>
       <c r="B49">
-        <v>106347309.2702644</v>
+        <v>1371880289.586411</v>
       </c>
       <c r="C49">
-        <v>1839764.98149414</v>
+        <v>23732968.26127441</v>
       </c>
       <c r="D49">
-        <v>146577838.1311935</v>
+        <v>1890854111.892396</v>
       </c>
       <c r="E49">
-        <v>6366897.21113095</v>
+        <v>82132974.02358925</v>
       </c>
       <c r="F49">
-        <v>66585847.84051295</v>
+        <v>858957437.142617</v>
       </c>
       <c r="G49">
-        <v>221370348.1643315</v>
+        <v>2855677491.319876</v>
       </c>
       <c r="H49">
-        <v>173142359.3369261</v>
+        <v>2233536435.446346</v>
       </c>
       <c r="I49">
-        <v>48963570.87133363</v>
+        <v>631630064.2402039</v>
       </c>
       <c r="J49">
-        <v>17038652.88101723</v>
+        <v>219798622.1651223</v>
       </c>
       <c r="K49">
-        <v>16464147.18444061</v>
+        <v>212387498.6792839</v>
       </c>
       <c r="L49">
-        <v>7737078.731912971</v>
+        <v>99808315.64167732</v>
       </c>
       <c r="M49">
-        <v>261330172.6182146</v>
+        <v>3371159226.774969</v>
       </c>
       <c r="N49">
-        <v>87884655.77141634</v>
+        <v>1133712059.451271</v>
       </c>
       <c r="O49">
-        <v>612560637.3952615</v>
+        <v>7902032222.398874</v>
       </c>
       <c r="P49">
-        <v>940278294.8298573</v>
+        <v>12129590003.30516</v>
       </c>
       <c r="Q49">
-        <v>738309251.0562637</v>
+        <v>9524189338.625801</v>
       </c>
     </row>
     <row r="50">
@@ -9061,52 +9061,52 @@
         </is>
       </c>
       <c r="B50">
-        <v>102197046.8474496</v>
+        <v>1318341904.3321</v>
       </c>
       <c r="C50">
-        <v>1806674.63666498</v>
+        <v>23306102.81297825</v>
       </c>
       <c r="D50">
-        <v>145108316.747228</v>
+        <v>1871897286.039242</v>
       </c>
       <c r="E50">
-        <v>6294748.654971329</v>
+        <v>81202257.64913015</v>
       </c>
       <c r="F50">
-        <v>66839747.53912728</v>
+        <v>862232743.2547419</v>
       </c>
       <c r="G50">
-        <v>220049487.5779916</v>
+        <v>2838638389.756092</v>
       </c>
       <c r="H50">
-        <v>175690920.9617805</v>
+        <v>2266412880.406969</v>
       </c>
       <c r="I50">
-        <v>48575040.39809107</v>
+        <v>626618021.1353748</v>
       </c>
       <c r="J50">
-        <v>17711468.88890891</v>
+        <v>228477948.666925</v>
       </c>
       <c r="K50">
-        <v>15934941.9737899</v>
+        <v>205560751.4618897</v>
       </c>
       <c r="L50">
-        <v>8208445.15312647</v>
+        <v>105888942.4753315</v>
       </c>
       <c r="M50">
-        <v>263745588.2730121</v>
+        <v>3402318088.721856</v>
       </c>
       <c r="N50">
-        <v>88069200.32121944</v>
+        <v>1136092684.143731</v>
       </c>
       <c r="O50">
-        <v>617935605.9699285</v>
+        <v>7971369317.012078</v>
       </c>
       <c r="P50">
-        <v>940182140.3953696</v>
+        <v>12128349611.10027</v>
       </c>
       <c r="Q50">
-        <v>741707448.0735741</v>
+        <v>9568026080.149105</v>
       </c>
     </row>
     <row r="51">
@@ -9116,52 +9116,52 @@
         </is>
       </c>
       <c r="B51">
-        <v>98180546.52761659</v>
+        <v>1266529050.206254</v>
       </c>
       <c r="C51">
-        <v>1719558.0505405</v>
+        <v>22182298.85197245</v>
       </c>
       <c r="D51">
-        <v>145235751.6182343</v>
+        <v>1873541195.875222</v>
       </c>
       <c r="E51">
-        <v>6258001.596026611</v>
+        <v>80728220.58874328</v>
       </c>
       <c r="F51">
-        <v>65683845.38688876</v>
+        <v>847321605.490865</v>
       </c>
       <c r="G51">
-        <v>218897156.6516902</v>
+        <v>2823773320.806803</v>
       </c>
       <c r="H51">
-        <v>177357021.2451864</v>
+        <v>2287905574.062905</v>
       </c>
       <c r="I51">
-        <v>50150599.45189427</v>
+        <v>646942732.9294361</v>
       </c>
       <c r="J51">
-        <v>17226114.6284619</v>
+        <v>222216878.7071585</v>
       </c>
       <c r="K51">
-        <v>14963413.46430151</v>
+        <v>193028033.6894895</v>
       </c>
       <c r="L51">
-        <v>8569077.43540192</v>
+        <v>110541098.9166848</v>
       </c>
       <c r="M51">
-        <v>264640287.9514348</v>
+        <v>3413859714.573509</v>
       </c>
       <c r="N51">
-        <v>88888606.90382937</v>
+        <v>1146663029.059399</v>
       </c>
       <c r="O51">
-        <v>621795121.0805104</v>
+        <v>8021157061.938584</v>
       </c>
       <c r="P51">
-        <v>938872824.2598169</v>
+        <v>12111459432.95164</v>
       </c>
       <c r="Q51">
-        <v>743234593.3929691</v>
+        <v>9587726254.769302</v>
       </c>
     </row>
     <row r="52">
@@ -9171,52 +9171,52 @@
         </is>
       </c>
       <c r="B52">
-        <v>96457448.94747166</v>
+        <v>1244301091.422385</v>
       </c>
       <c r="C52">
-        <v>1517548.89660274</v>
+        <v>19576380.76617535</v>
       </c>
       <c r="D52">
-        <v>146236568.785339</v>
+        <v>1886451737.330873</v>
       </c>
       <c r="E52">
-        <v>6056579.54508561</v>
+        <v>78129876.13160437</v>
       </c>
       <c r="F52">
-        <v>66301387.93513554</v>
+        <v>855287904.3632486</v>
       </c>
       <c r="G52">
-        <v>220112085.1621629</v>
+        <v>2839445898.591901</v>
       </c>
       <c r="H52">
-        <v>182297603.796678</v>
+        <v>2351639088.977147</v>
       </c>
       <c r="I52">
-        <v>52258149.44417402</v>
+        <v>674130127.829845</v>
       </c>
       <c r="J52">
-        <v>16884598.60364906</v>
+        <v>217811321.9870729</v>
       </c>
       <c r="K52">
-        <v>14447011.33631765</v>
+        <v>186366446.2384977</v>
       </c>
       <c r="L52">
-        <v>8673507.70892</v>
+        <v>111888249.445068</v>
       </c>
       <c r="M52">
-        <v>263492832.7121965</v>
+        <v>3399057541.987335</v>
       </c>
       <c r="N52">
-        <v>90702960.9300601</v>
+        <v>1170068195.997775</v>
       </c>
       <c r="O52">
-        <v>628756664.5319954</v>
+        <v>8110960972.462741</v>
       </c>
       <c r="P52">
-        <v>945326198.6416298</v>
+        <v>12194707962.47702</v>
       </c>
       <c r="Q52">
-        <v>749492281.0551782</v>
+        <v>9668450425.611799</v>
       </c>
     </row>
     <row r="53">
@@ -9226,52 +9226,52 @@
         </is>
       </c>
       <c r="B53">
-        <v>95206699.03176701</v>
+        <v>1228166417.509794</v>
       </c>
       <c r="C53">
-        <v>1502631.0745112</v>
+        <v>19383940.86119448</v>
       </c>
       <c r="D53">
-        <v>148353251.509463</v>
+        <v>1913756944.472072</v>
       </c>
       <c r="E53">
-        <v>6019253.04351005</v>
+        <v>77648364.26127964</v>
       </c>
       <c r="F53">
-        <v>66412356.91279308</v>
+        <v>856719404.1750307</v>
       </c>
       <c r="G53">
-        <v>222287492.5402773</v>
+        <v>2867508653.769577</v>
       </c>
       <c r="H53">
-        <v>185018206.5391024</v>
+        <v>2386734864.354422</v>
       </c>
       <c r="I53">
-        <v>55100883.50121056</v>
+        <v>710801397.1656162</v>
       </c>
       <c r="J53">
-        <v>17001732.17050011</v>
+        <v>219322344.9994514</v>
       </c>
       <c r="K53">
-        <v>13648884.38774459</v>
+        <v>176070608.6019052</v>
       </c>
       <c r="L53">
-        <v>8993949.030413799</v>
+        <v>116021942.492338</v>
       </c>
       <c r="M53">
-        <v>264019462.6182593</v>
+        <v>3405851067.775545</v>
       </c>
       <c r="N53">
-        <v>90987815.89193994</v>
+        <v>1173742825.006025</v>
       </c>
       <c r="O53">
-        <v>634770934.1391709</v>
+        <v>8188545050.395305</v>
       </c>
       <c r="P53">
-        <v>952265125.711215</v>
+        <v>12284220121.67467</v>
       </c>
       <c r="Q53">
-        <v>757076661.7570943</v>
+        <v>9766288936.666515</v>
       </c>
     </row>
     <row r="54">
@@ -9281,52 +9281,52 @@
         </is>
       </c>
       <c r="B54">
-        <v>94144984.68467438</v>
+        <v>1214470302.4323</v>
       </c>
       <c r="C54">
-        <v>1272808.21221124</v>
+        <v>16419225.937525</v>
       </c>
       <c r="D54">
-        <v>149455322.3232227</v>
+        <v>1927973657.969573</v>
       </c>
       <c r="E54">
-        <v>5997440.378719</v>
+        <v>77366980.8854751</v>
       </c>
       <c r="F54">
-        <v>64898821.13590002</v>
+        <v>837194792.6531103</v>
       </c>
       <c r="G54">
-        <v>221624392.0500529</v>
+        <v>2858954657.445683</v>
       </c>
       <c r="H54">
-        <v>186298819.0890058</v>
+        <v>2403254766.248175</v>
       </c>
       <c r="I54">
-        <v>57428652.01543505</v>
+        <v>740829610.9991121</v>
       </c>
       <c r="J54">
-        <v>16700790.3558228</v>
+        <v>215440195.5901141</v>
       </c>
       <c r="K54">
-        <v>14219538.18495002</v>
+        <v>183432042.5858553</v>
       </c>
       <c r="L54">
-        <v>8672574.9968</v>
+        <v>111876217.45872</v>
       </c>
       <c r="M54">
-        <v>264761226.8681252</v>
+        <v>3415419826.598815</v>
       </c>
       <c r="N54">
-        <v>92651741.36788499</v>
+        <v>1195207463.645716</v>
       </c>
       <c r="O54">
-        <v>640733342.8780239</v>
+        <v>8265460123.126508</v>
       </c>
       <c r="P54">
-        <v>956502719.6127512</v>
+        <v>12338885083.00449</v>
       </c>
       <c r="Q54">
-        <v>761033418.5633918</v>
+        <v>9817331099.467754</v>
       </c>
     </row>
     <row r="55">
@@ -9336,52 +9336,52 @@
         </is>
       </c>
       <c r="B55">
-        <v>93420783.47558089</v>
+        <v>1205128106.834993</v>
       </c>
       <c r="C55">
-        <v>1110909.081836</v>
+        <v>14330727.1556844</v>
       </c>
       <c r="D55">
-        <v>149540360.5469504</v>
+        <v>1929070651.05566</v>
       </c>
       <c r="E55">
-        <v>5619396.1359349</v>
+        <v>72490210.15356022</v>
       </c>
       <c r="F55">
-        <v>63672209.89199374</v>
+        <v>821371507.6067193</v>
       </c>
       <c r="G55">
-        <v>219942875.656715</v>
+        <v>2837263095.971624</v>
       </c>
       <c r="H55">
-        <v>186951411.3979237</v>
+        <v>2411673207.033216</v>
       </c>
       <c r="I55">
-        <v>58030729.20786856</v>
+        <v>748596406.7815045</v>
       </c>
       <c r="J55">
-        <v>16528994.29107987</v>
+        <v>213224026.3549303</v>
       </c>
       <c r="K55">
-        <v>15366021.93335562</v>
+        <v>198221682.9402875</v>
       </c>
       <c r="L55">
-        <v>8243230.6136598</v>
+        <v>106337674.9162114</v>
       </c>
       <c r="M55">
-        <v>267574315.8542635</v>
+        <v>3451708674.519999</v>
       </c>
       <c r="N55">
-        <v>94393112.3777741</v>
+        <v>1217671149.673286</v>
       </c>
       <c r="O55">
-        <v>647087815.6759251</v>
+        <v>8347432822.219435</v>
       </c>
       <c r="P55">
-        <v>960451474.8082211</v>
+        <v>12389824025.02605</v>
       </c>
       <c r="Q55">
-        <v>764394348.3412063</v>
+        <v>9860687093.601563</v>
       </c>
     </row>
     <row r="56">
@@ -9391,52 +9391,52 @@
         </is>
       </c>
       <c r="B56">
-        <v>92993065.31167209</v>
+        <v>1199610542.52057</v>
       </c>
       <c r="C56">
-        <v>1051511.79002769</v>
+        <v>13564502.0913572</v>
       </c>
       <c r="D56">
-        <v>150426022.6775321</v>
+        <v>1940495692.540164</v>
       </c>
       <c r="E56">
-        <v>5381427.18135571</v>
+        <v>69420410.63948867</v>
       </c>
       <c r="F56">
-        <v>63431734.96233409</v>
+        <v>818269381.0141097</v>
       </c>
       <c r="G56">
-        <v>220290696.6112496</v>
+        <v>2841749986.28512</v>
       </c>
       <c r="H56">
-        <v>185417471.2646337</v>
+        <v>2391885379.313776</v>
       </c>
       <c r="I56">
-        <v>60066835.45716632</v>
+        <v>774862177.3974456</v>
       </c>
       <c r="J56">
-        <v>16325226.44197568</v>
+        <v>210595421.1014863</v>
       </c>
       <c r="K56">
-        <v>16677347.55189956</v>
+        <v>215137783.4195043</v>
       </c>
       <c r="L56">
-        <v>7824421.79354928</v>
+        <v>100935041.1367857</v>
       </c>
       <c r="M56">
-        <v>267290643.8043881</v>
+        <v>3448049305.076606</v>
       </c>
       <c r="N56">
-        <v>94447063.28747584</v>
+        <v>1218367116.408438</v>
       </c>
       <c r="O56">
-        <v>648049009.6010885</v>
+        <v>8359832223.854042</v>
       </c>
       <c r="P56">
-        <v>961332771.5240103</v>
+        <v>12401192752.65973</v>
       </c>
       <c r="Q56">
-        <v>766068221.1313131</v>
+        <v>9882280052.593939</v>
       </c>
     </row>
   </sheetData>
@@ -9564,52 +9564,52 @@
         </is>
       </c>
       <c r="B5">
-        <v>123955983.5851155</v>
+        <v>1599032188.247989</v>
       </c>
       <c r="C5">
-        <v>2536859.70965648</v>
+        <v>32725490.2545686</v>
       </c>
       <c r="D5">
-        <v>150166591.4156167</v>
+        <v>1937149029.261456</v>
       </c>
       <c r="E5">
-        <v>7357288.421755889</v>
+        <v>94909020.64065097</v>
       </c>
       <c r="F5">
-        <v>61164375.22664642</v>
+        <v>789020440.4237388</v>
       </c>
       <c r="G5">
-        <v>221225114.7736755</v>
+        <v>2853803980.580414</v>
       </c>
       <c r="H5">
-        <v>165401309.9180031</v>
+        <v>2133676897.94224</v>
       </c>
       <c r="I5">
-        <v>49690467.19902172</v>
+        <v>641007026.8673801</v>
       </c>
       <c r="J5">
-        <v>9910570.64738421</v>
+        <v>127846361.3512563</v>
       </c>
       <c r="K5">
-        <v>11888117.72196227</v>
+        <v>153356718.6133133</v>
       </c>
       <c r="L5">
-        <v>5608377.15193392</v>
+        <v>72348065.25994757</v>
       </c>
       <c r="M5">
-        <v>204888776.4655287</v>
+        <v>2643065216.405321</v>
       </c>
       <c r="N5">
-        <v>74624567.7718925</v>
+        <v>962656924.2574133</v>
       </c>
       <c r="O5">
-        <v>522012186.8757265</v>
+        <v>6733957210.696872</v>
       </c>
       <c r="P5">
-        <v>867193285.2345173</v>
+        <v>11186793379.52527</v>
       </c>
       <c r="Q5">
-        <v>663004356.7255754</v>
+        <v>8552756201.759924</v>
       </c>
     </row>
     <row r="6">
@@ -9619,52 +9619,52 @@
         </is>
       </c>
       <c r="B6">
-        <v>122783613.6225989</v>
+        <v>1583908615.731525</v>
       </c>
       <c r="C6">
-        <v>2579509.34408559</v>
+        <v>33275670.53870411</v>
       </c>
       <c r="D6">
-        <v>149523076.6437398</v>
+        <v>1928847688.704243</v>
       </c>
       <c r="E6">
-        <v>7218447.48516063</v>
+        <v>93117972.55857213</v>
       </c>
       <c r="F6">
-        <v>62517922.84020076</v>
+        <v>806481204.6385899</v>
       </c>
       <c r="G6">
-        <v>221838956.3131867</v>
+        <v>2861722536.440109</v>
       </c>
       <c r="H6">
-        <v>166153930.2075276</v>
+        <v>2143385699.677106</v>
       </c>
       <c r="I6">
-        <v>50008991.42100993</v>
+        <v>645115989.3310281</v>
       </c>
       <c r="J6">
-        <v>9966049.6960066</v>
+        <v>128562041.0784851</v>
       </c>
       <c r="K6">
-        <v>12117361.88675038</v>
+        <v>156313968.3390799</v>
       </c>
       <c r="L6">
-        <v>6322588.16595438</v>
+        <v>81561387.34081151</v>
       </c>
       <c r="M6">
-        <v>200694556.7824337</v>
+        <v>2588959782.493395</v>
       </c>
       <c r="N6">
-        <v>76477218.93961263</v>
+        <v>986556124.321003</v>
       </c>
       <c r="O6">
-        <v>521740697.0992953</v>
+        <v>6730454992.580909</v>
       </c>
       <c r="P6">
-        <v>866363267.0350808</v>
+        <v>11176086144.75254</v>
       </c>
       <c r="Q6">
-        <v>660779846.306915</v>
+        <v>8524060017.359204</v>
       </c>
     </row>
     <row r="7">
@@ -9674,52 +9674,52 @@
         </is>
       </c>
       <c r="B7">
-        <v>121121809.4356565</v>
+        <v>1562471341.719969</v>
       </c>
       <c r="C7">
-        <v>2723779.02405763</v>
+        <v>35136749.41034343</v>
       </c>
       <c r="D7">
-        <v>150193001.7590104</v>
+        <v>1937489722.691234</v>
       </c>
       <c r="E7">
-        <v>7558361.45797218</v>
+        <v>97502862.80784112</v>
       </c>
       <c r="F7">
-        <v>61882295.98916577</v>
+        <v>798281618.2602384</v>
       </c>
       <c r="G7">
-        <v>222357438.230206</v>
+        <v>2868410953.169657</v>
       </c>
       <c r="H7">
-        <v>168762988.8848205</v>
+        <v>2177042556.614185</v>
       </c>
       <c r="I7">
-        <v>50623341.48044666</v>
+        <v>653041105.0977619</v>
       </c>
       <c r="J7">
-        <v>9949014.098254601</v>
+        <v>128342281.8674843</v>
       </c>
       <c r="K7">
-        <v>12266563.1075802</v>
+        <v>158238664.0877846</v>
       </c>
       <c r="L7">
-        <v>6992496.90412288</v>
+        <v>90203210.06318516</v>
       </c>
       <c r="M7">
-        <v>199439190.9117477</v>
+        <v>2572765562.761545</v>
       </c>
       <c r="N7">
-        <v>79413055.33863507</v>
+        <v>1024428413.868392</v>
       </c>
       <c r="O7">
-        <v>527446650.7256077</v>
+        <v>6804061794.360339</v>
       </c>
       <c r="P7">
-        <v>870925898.3914701</v>
+        <v>11234944089.24996</v>
       </c>
       <c r="Q7">
-        <v>663398536.7130557</v>
+        <v>8557841123.598419</v>
       </c>
     </row>
     <row r="8">
@@ -9729,52 +9729,52 @@
         </is>
       </c>
       <c r="B8">
-        <v>119539560.7614953</v>
+        <v>1542060333.82329</v>
       </c>
       <c r="C8">
-        <v>2626412.15638554</v>
+        <v>33880716.81737347</v>
       </c>
       <c r="D8">
-        <v>150095956.3236329</v>
+        <v>1936237836.574864</v>
       </c>
       <c r="E8">
-        <v>7819738.77672943</v>
+        <v>100874630.2198097</v>
       </c>
       <c r="F8">
-        <v>63309982.81640461</v>
+        <v>816698778.3316195</v>
       </c>
       <c r="G8">
-        <v>223852090.0731525</v>
+        <v>2887691961.943667</v>
       </c>
       <c r="H8">
-        <v>171784651.5957881</v>
+        <v>2216022005.585667</v>
       </c>
       <c r="I8">
-        <v>51298350.40380611</v>
+        <v>661748720.2090988</v>
       </c>
       <c r="J8">
-        <v>9626240.197214879</v>
+        <v>124178498.5440719</v>
       </c>
       <c r="K8">
-        <v>12469108.93642603</v>
+        <v>160851505.2798958</v>
       </c>
       <c r="L8">
-        <v>7523111.92468651</v>
+        <v>97048143.82845598</v>
       </c>
       <c r="M8">
-        <v>201082298.7017878</v>
+        <v>2593961653.253062</v>
       </c>
       <c r="N8">
-        <v>80956396.73000933</v>
+        <v>1044337517.81712</v>
       </c>
       <c r="O8">
-        <v>534740158.4897188</v>
+        <v>6898148044.517373</v>
       </c>
       <c r="P8">
-        <v>878131809.3243666</v>
+        <v>11327900340.28433</v>
       </c>
       <c r="Q8">
-        <v>670112739.9081753</v>
+        <v>8644454344.815462</v>
       </c>
     </row>
     <row r="9">
@@ -9784,52 +9784,52 @@
         </is>
       </c>
       <c r="B9">
-        <v>119307968.7389078</v>
+        <v>1539072796.73191</v>
       </c>
       <c r="C9">
-        <v>2654235.10799254</v>
+        <v>34239632.89310376</v>
       </c>
       <c r="D9">
-        <v>150118470.1996418</v>
+        <v>1936528265.575379</v>
       </c>
       <c r="E9">
-        <v>7644232.120207271</v>
+        <v>98610594.35067379</v>
       </c>
       <c r="F9">
-        <v>64234622.87065266</v>
+        <v>828626635.0314194</v>
       </c>
       <c r="G9">
-        <v>224651560.2984943</v>
+        <v>2898005127.850576</v>
       </c>
       <c r="H9">
-        <v>176275405.4072924</v>
+        <v>2273952729.754072</v>
       </c>
       <c r="I9">
-        <v>50780075.44420237</v>
+        <v>655062973.2302107</v>
       </c>
       <c r="J9">
-        <v>9636065.60022272</v>
+        <v>124305246.2428731</v>
       </c>
       <c r="K9">
-        <v>12377840.10089497</v>
+        <v>159674137.3015451</v>
       </c>
       <c r="L9">
-        <v>7565122.4649307</v>
+        <v>97590079.79760604</v>
       </c>
       <c r="M9">
-        <v>205039863.6793797</v>
+        <v>2645014241.463998</v>
       </c>
       <c r="N9">
-        <v>82068953.32912533</v>
+        <v>1058689497.945717</v>
       </c>
       <c r="O9">
-        <v>543743326.0260483</v>
+        <v>7014288905.736023</v>
       </c>
       <c r="P9">
-        <v>887702855.0634503</v>
+        <v>11451366830.31851</v>
       </c>
       <c r="Q9">
-        <v>678760810.5304863</v>
+        <v>8756014455.843273</v>
       </c>
     </row>
     <row r="10">
@@ -9839,52 +9839,52 @@
         </is>
       </c>
       <c r="B10">
-        <v>116052725.9028154</v>
+        <v>1497080164.146319</v>
       </c>
       <c r="C10">
-        <v>2659870.56856559</v>
+        <v>34312330.33449611</v>
       </c>
       <c r="D10">
-        <v>150980131.3763023</v>
+        <v>1947643694.7543</v>
       </c>
       <c r="E10">
-        <v>7294421.64229862</v>
+        <v>94098039.1856522</v>
       </c>
       <c r="F10">
-        <v>64866810.55287064</v>
+        <v>836781856.1320312</v>
       </c>
       <c r="G10">
-        <v>225801234.1400371</v>
+        <v>2912835920.406479</v>
       </c>
       <c r="H10">
-        <v>180065342.7243313</v>
+        <v>2322842921.143874</v>
       </c>
       <c r="I10">
-        <v>49965670.2811706</v>
+        <v>644557146.6271007</v>
       </c>
       <c r="J10">
-        <v>9850224.79160776</v>
+        <v>127067899.8117401</v>
       </c>
       <c r="K10">
-        <v>12181724.53765542</v>
+        <v>157144246.5357549</v>
       </c>
       <c r="L10">
-        <v>7511200.14183569</v>
+        <v>96894481.8296804</v>
       </c>
       <c r="M10">
-        <v>210007668.1613732</v>
+        <v>2709098919.281715</v>
       </c>
       <c r="N10">
-        <v>81454462.16604199</v>
+        <v>1050762561.941942</v>
       </c>
       <c r="O10">
-        <v>551036292.804016</v>
+        <v>7108368177.171806</v>
       </c>
       <c r="P10">
-        <v>892890252.8468686</v>
+        <v>11518284261.72461</v>
       </c>
       <c r="Q10">
-        <v>687871864.6361754</v>
+        <v>8873547053.806664</v>
       </c>
     </row>
     <row r="11">
@@ -9894,52 +9894,52 @@
         </is>
       </c>
       <c r="B11">
-        <v>113262927.3469141</v>
+        <v>1461091762.775192</v>
       </c>
       <c r="C11">
-        <v>2184032.95624178</v>
+        <v>28174025.13551896</v>
       </c>
       <c r="D11">
-        <v>148812207.7624098</v>
+        <v>1919677480.135087</v>
       </c>
       <c r="E11">
-        <v>6816964.07036263</v>
+        <v>87938836.50767793</v>
       </c>
       <c r="F11">
-        <v>64481247.02894932</v>
+        <v>831808086.6734463</v>
       </c>
       <c r="G11">
-        <v>222294451.8179635</v>
+        <v>2867598428.45173</v>
       </c>
       <c r="H11">
-        <v>180083140.3840127</v>
+        <v>2323072510.953764</v>
       </c>
       <c r="I11">
-        <v>48604871.38869966</v>
+        <v>627002840.9142256</v>
       </c>
       <c r="J11">
-        <v>10073823.96046418</v>
+        <v>129952329.0899879</v>
       </c>
       <c r="K11">
-        <v>11683280.98575103</v>
+        <v>150714324.7161883</v>
       </c>
       <c r="L11">
-        <v>6960742.18974173</v>
+        <v>89793574.24766831</v>
       </c>
       <c r="M11">
-        <v>217245196.0878552</v>
+        <v>2802463029.533333</v>
       </c>
       <c r="N11">
-        <v>79634885.92783159</v>
+        <v>1027290028.469028</v>
       </c>
       <c r="O11">
-        <v>554285940.9243562</v>
+        <v>7150288637.924195</v>
       </c>
       <c r="P11">
-        <v>889843320.0892339</v>
+        <v>11478978829.15112</v>
       </c>
       <c r="Q11">
-        <v>689984764.6247463</v>
+        <v>8900803463.659227</v>
       </c>
     </row>
     <row r="12">
@@ -9949,52 +9949,52 @@
         </is>
       </c>
       <c r="B12">
-        <v>111116945.4877574</v>
+        <v>1433408596.792071</v>
       </c>
       <c r="C12">
-        <v>2091172.30867991</v>
+        <v>26976122.78197084</v>
       </c>
       <c r="D12">
-        <v>148168314.2412637</v>
+        <v>1911371253.712301</v>
       </c>
       <c r="E12">
-        <v>6512808.99957316</v>
+        <v>84015236.09449376</v>
       </c>
       <c r="F12">
-        <v>63222604.63481815</v>
+        <v>815571599.7891542</v>
       </c>
       <c r="G12">
-        <v>219994900.1843349</v>
+        <v>2837934212.37792</v>
       </c>
       <c r="H12">
-        <v>178546433.8149293</v>
+        <v>2303248996.212588</v>
       </c>
       <c r="I12">
-        <v>47165760.17264844</v>
+        <v>608438306.2271649</v>
       </c>
       <c r="J12">
-        <v>10410273.44418898</v>
+        <v>134292527.4300378</v>
       </c>
       <c r="K12">
-        <v>11638534.32042797</v>
+        <v>150137092.7335208</v>
       </c>
       <c r="L12">
-        <v>6402451.95319142</v>
+        <v>82591630.19616932</v>
       </c>
       <c r="M12">
-        <v>220897456.1571814</v>
+        <v>2849577184.427641</v>
       </c>
       <c r="N12">
-        <v>78956207.7149881</v>
+        <v>1018535079.523347</v>
       </c>
       <c r="O12">
-        <v>554017117.5775557</v>
+        <v>7146820816.750468</v>
       </c>
       <c r="P12">
-        <v>885128963.2496479</v>
+        <v>11418163625.92046</v>
       </c>
       <c r="Q12">
-        <v>688653358.0937109</v>
+        <v>8883628319.408871</v>
       </c>
     </row>
     <row r="13">
@@ -10004,52 +10004,52 @@
         </is>
       </c>
       <c r="B13">
-        <v>107803576.4472004</v>
+        <v>1390666136.168885</v>
       </c>
       <c r="C13">
-        <v>2094965.79453744</v>
+        <v>27025058.74953298</v>
       </c>
       <c r="D13">
-        <v>146276465.7570952</v>
+        <v>1886966408.266528</v>
       </c>
       <c r="E13">
-        <v>6444823.51578275</v>
+        <v>83138223.35359748</v>
       </c>
       <c r="F13">
-        <v>63771628.29850463</v>
+        <v>822654005.0507097</v>
       </c>
       <c r="G13">
-        <v>218587883.36592</v>
+        <v>2819783695.420368</v>
       </c>
       <c r="H13">
-        <v>175278416.080255</v>
+        <v>2261091567.435289</v>
       </c>
       <c r="I13">
-        <v>46126354.72334593</v>
+        <v>595029975.9311625</v>
       </c>
       <c r="J13">
-        <v>10601460.92238748</v>
+        <v>136758845.8987985</v>
       </c>
       <c r="K13">
-        <v>11526831.39233766</v>
+        <v>148696124.9611558</v>
       </c>
       <c r="L13">
-        <v>6409025.17465725</v>
+        <v>82676424.75307852</v>
       </c>
       <c r="M13">
-        <v>223717559.7329851</v>
+        <v>2885956520.555508</v>
       </c>
       <c r="N13">
-        <v>78834739.76405987</v>
+        <v>1016968142.956372</v>
       </c>
       <c r="O13">
-        <v>552494387.7900283</v>
+        <v>7127177602.491365</v>
       </c>
       <c r="P13">
-        <v>878885847.6031487</v>
+        <v>11337627434.08062</v>
       </c>
       <c r="Q13">
-        <v>685838506.2172312</v>
+        <v>8847316730.202282</v>
       </c>
     </row>
     <row r="14">
@@ -10059,52 +10059,52 @@
         </is>
       </c>
       <c r="B14">
-        <v>108220535.5503481</v>
+        <v>1396044908.599491</v>
       </c>
       <c r="C14">
-        <v>2191003.17427093</v>
+        <v>28263940.948095</v>
       </c>
       <c r="D14">
-        <v>144928076.5956818</v>
+        <v>1869572188.084295</v>
       </c>
       <c r="E14">
-        <v>6885809.23613185</v>
+        <v>88826939.14610086</v>
       </c>
       <c r="F14">
-        <v>62659130.20629372</v>
+        <v>808302779.661189</v>
       </c>
       <c r="G14">
-        <v>216664019.2123783</v>
+        <v>2794965847.83968</v>
       </c>
       <c r="H14">
-        <v>174540823.5468494</v>
+        <v>2251576623.754357</v>
       </c>
       <c r="I14">
-        <v>45340065.50735456</v>
+        <v>584886845.0448738</v>
       </c>
       <c r="J14">
-        <v>10855312.96180888</v>
+        <v>140033537.2073345</v>
       </c>
       <c r="K14">
-        <v>11850832.3994977</v>
+        <v>152875737.9535203</v>
       </c>
       <c r="L14">
-        <v>6385015.80446472</v>
+        <v>82366703.87759489</v>
       </c>
       <c r="M14">
-        <v>226910825.0372982</v>
+        <v>2927149642.981146</v>
       </c>
       <c r="N14">
-        <v>79602765.99833143</v>
+        <v>1026875681.378475</v>
       </c>
       <c r="O14">
-        <v>555485641.255605</v>
+        <v>7165764772.197305</v>
       </c>
       <c r="P14">
-        <v>880370196.0183313</v>
+        <v>11356775528.63647</v>
       </c>
       <c r="Q14">
-        <v>686161878.6651869</v>
+        <v>8851488234.78091</v>
       </c>
     </row>
     <row r="15">
@@ -10114,52 +10114,52 @@
         </is>
       </c>
       <c r="B15">
-        <v>107629145.2819052</v>
+        <v>1388415974.136577</v>
       </c>
       <c r="C15">
-        <v>2492151.50382714</v>
+        <v>32148754.39937011</v>
       </c>
       <c r="D15">
-        <v>141867052.9087834</v>
+        <v>1830084982.523306</v>
       </c>
       <c r="E15">
-        <v>7424488.79037077</v>
+        <v>95775905.39578293</v>
       </c>
       <c r="F15">
-        <v>61755244.14359539</v>
+        <v>796642649.4523805</v>
       </c>
       <c r="G15">
-        <v>213538937.3465767</v>
+        <v>2754652291.770839</v>
       </c>
       <c r="H15">
-        <v>174951712.1149791</v>
+        <v>2256877086.283231</v>
       </c>
       <c r="I15">
-        <v>46371133.45251936</v>
+        <v>598187621.5374997</v>
       </c>
       <c r="J15">
-        <v>11448380.87488418</v>
+        <v>147684113.2860059</v>
       </c>
       <c r="K15">
-        <v>11935915.43337403</v>
+        <v>153973309.090525</v>
       </c>
       <c r="L15">
-        <v>6667197.99961239</v>
+        <v>86006854.19499983</v>
       </c>
       <c r="M15">
-        <v>226069441.2796488</v>
+        <v>2916295792.50747</v>
       </c>
       <c r="N15">
-        <v>79674005.07682167</v>
+        <v>1027794665.491</v>
       </c>
       <c r="O15">
-        <v>557117786.2318398</v>
+        <v>7186819442.390734</v>
       </c>
       <c r="P15">
-        <v>878285868.8603215</v>
+        <v>11329887708.29815</v>
       </c>
       <c r="Q15">
-        <v>684315520.5019822</v>
+        <v>8827670214.475571</v>
       </c>
     </row>
     <row r="16">
@@ -10169,52 +10169,52 @@
         </is>
       </c>
       <c r="B16">
-        <v>106777040.4979495</v>
+        <v>1377423822.423549</v>
       </c>
       <c r="C16">
-        <v>2768126.81424195</v>
+        <v>35708835.90372115</v>
       </c>
       <c r="D16">
-        <v>140142595.0558865</v>
+        <v>1807839476.220936</v>
       </c>
       <c r="E16">
-        <v>7766179.35107514</v>
+        <v>100183713.6288693</v>
       </c>
       <c r="F16">
-        <v>60160503.01358151</v>
+        <v>776070488.8752015</v>
       </c>
       <c r="G16">
-        <v>210837404.2347851</v>
+        <v>2719802514.628728</v>
       </c>
       <c r="H16">
-        <v>175498008.4103935</v>
+        <v>2263924308.494076</v>
       </c>
       <c r="I16">
-        <v>46450287.77255129</v>
+        <v>599208712.2659117</v>
       </c>
       <c r="J16">
-        <v>11693605.80730686</v>
+        <v>150847514.9142585</v>
       </c>
       <c r="K16">
-        <v>11530194.1887926</v>
+        <v>148739505.0354246</v>
       </c>
       <c r="L16">
-        <v>6298296.77127961</v>
+        <v>81248028.34950697</v>
       </c>
       <c r="M16">
-        <v>223149765.0512092</v>
+        <v>2878631969.160598</v>
       </c>
       <c r="N16">
-        <v>79842182.91785458</v>
+        <v>1029964159.640324</v>
       </c>
       <c r="O16">
-        <v>554462340.9193877</v>
+        <v>7152564197.860102</v>
       </c>
       <c r="P16">
-        <v>872076785.6521223</v>
+        <v>11249790534.91238</v>
       </c>
       <c r="Q16">
-        <v>679159265.4650385</v>
+        <v>8761154524.498997</v>
       </c>
     </row>
     <row r="17">
@@ -10224,52 +10224,52 @@
         </is>
       </c>
       <c r="B17">
-        <v>106241997.9040006</v>
+        <v>1370521772.961607</v>
       </c>
       <c r="C17">
-        <v>2925029.03406839</v>
+        <v>37732874.53948223</v>
       </c>
       <c r="D17">
-        <v>140284741.0859932</v>
+        <v>1809673160.009313</v>
       </c>
       <c r="E17">
-        <v>8409641.705129759</v>
+        <v>108484377.9961739</v>
       </c>
       <c r="F17">
-        <v>59331843.12890658</v>
+        <v>765380776.3628949</v>
       </c>
       <c r="G17">
-        <v>210951254.954098</v>
+        <v>2721271188.907864</v>
       </c>
       <c r="H17">
-        <v>175671725.2439413</v>
+        <v>2266165255.646842</v>
       </c>
       <c r="I17">
-        <v>47148433.38450993</v>
+        <v>608214790.6601781</v>
       </c>
       <c r="J17">
-        <v>12219613.64185119</v>
+        <v>157633015.9798804</v>
       </c>
       <c r="K17">
-        <v>11545378.2102926</v>
+        <v>148935378.9127745</v>
       </c>
       <c r="L17">
-        <v>5898249.76362544</v>
+        <v>76087421.95076819</v>
       </c>
       <c r="M17">
-        <v>222036346.148135</v>
+        <v>2864268865.310942</v>
       </c>
       <c r="N17">
-        <v>80904045.34727392</v>
+        <v>1043662184.979834</v>
       </c>
       <c r="O17">
-        <v>555423791.7396295</v>
+        <v>7164966913.441221</v>
       </c>
       <c r="P17">
-        <v>872617044.5977279</v>
+        <v>11256759875.31069</v>
       </c>
       <c r="Q17">
-        <v>679572751.5828279</v>
+        <v>8766488495.41848</v>
       </c>
     </row>
     <row r="18">
@@ -10279,52 +10279,52 @@
         </is>
       </c>
       <c r="B18">
-        <v>106947489.2113899</v>
+        <v>1379622610.82693</v>
       </c>
       <c r="C18">
-        <v>2913353.5516346</v>
+        <v>37582260.81608634</v>
       </c>
       <c r="D18">
-        <v>138585859.951144</v>
+        <v>1787757593.369757</v>
       </c>
       <c r="E18">
-        <v>8632936.48106852</v>
+        <v>111364880.6057839</v>
       </c>
       <c r="F18">
-        <v>60265473.36897302</v>
+        <v>777424606.459752</v>
       </c>
       <c r="G18">
-        <v>210397623.3528201</v>
+        <v>2714129341.251379</v>
       </c>
       <c r="H18">
-        <v>172781546.1209413</v>
+        <v>2228881944.960144</v>
       </c>
       <c r="I18">
-        <v>48354444.84704691</v>
+        <v>623772338.5269052</v>
       </c>
       <c r="J18">
-        <v>11332146.88679635</v>
+        <v>146184694.8396729</v>
       </c>
       <c r="K18">
-        <v>11225994.54412336</v>
+        <v>144815329.6191913</v>
       </c>
       <c r="L18">
-        <v>5578907.09359861</v>
+        <v>71967901.50742207</v>
       </c>
       <c r="M18">
-        <v>220966457.9684491</v>
+        <v>2850467307.792994</v>
       </c>
       <c r="N18">
-        <v>81337289.40148686</v>
+        <v>1049251033.279181</v>
       </c>
       <c r="O18">
-        <v>551576786.8624426</v>
+        <v>7115340550.52551</v>
       </c>
       <c r="P18">
-        <v>868921899.4266527</v>
+        <v>11209092502.60382</v>
       </c>
       <c r="Q18">
-        <v>675058213.7201772</v>
+        <v>8708250956.990286</v>
       </c>
     </row>
     <row r="19">
@@ -10334,52 +10334,52 @@
         </is>
       </c>
       <c r="B19">
-        <v>108363534.5793526</v>
+        <v>1397889596.073648</v>
       </c>
       <c r="C19">
-        <v>2743627.2052527</v>
+        <v>35392790.94775983</v>
       </c>
       <c r="D19">
-        <v>138633683.7358944</v>
+        <v>1788374520.193037</v>
       </c>
       <c r="E19">
-        <v>8465589.33478749</v>
+        <v>109206102.4187586</v>
       </c>
       <c r="F19">
-        <v>62172328.17870998</v>
+        <v>802023033.5053588</v>
       </c>
       <c r="G19">
-        <v>212015228.4546445</v>
+        <v>2734996447.064914</v>
       </c>
       <c r="H19">
-        <v>170147197.7374087</v>
+        <v>2194898850.812572</v>
       </c>
       <c r="I19">
-        <v>48157669.2434855</v>
+        <v>621233933.240963</v>
       </c>
       <c r="J19">
-        <v>10927491.13363655</v>
+        <v>140964635.6239115</v>
       </c>
       <c r="K19">
-        <v>11505016.12153364</v>
+        <v>148414707.967784</v>
       </c>
       <c r="L19">
-        <v>5279272.6508048</v>
+        <v>68102617.19538192</v>
       </c>
       <c r="M19">
-        <v>219575396.9317811</v>
+        <v>2832522620.419976</v>
       </c>
       <c r="N19">
-        <v>82714493.73824999</v>
+        <v>1067016969.223425</v>
       </c>
       <c r="O19">
-        <v>548306537.5569003</v>
+        <v>7073154334.484014</v>
       </c>
       <c r="P19">
-        <v>868685300.5908974</v>
+        <v>11206040377.62258</v>
       </c>
       <c r="Q19">
-        <v>672327999.6224899</v>
+        <v>8673031195.130121</v>
       </c>
     </row>
     <row r="20">
@@ -10389,52 +10389,52 @@
         </is>
       </c>
       <c r="B20">
-        <v>110036300.552118</v>
+        <v>1419468277.122323</v>
       </c>
       <c r="C20">
-        <v>2759541.65919375</v>
+        <v>35598087.40359937</v>
       </c>
       <c r="D20">
-        <v>136848731.4493778</v>
+        <v>1765348635.696974</v>
       </c>
       <c r="E20">
-        <v>8170999.497239321</v>
+        <v>105405893.5143872</v>
       </c>
       <c r="F20">
-        <v>63726832.65050225</v>
+        <v>822076141.1914791</v>
       </c>
       <c r="G20">
-        <v>211506105.2563131</v>
+        <v>2728428757.806439</v>
       </c>
       <c r="H20">
-        <v>168512030.0741868</v>
+        <v>2173805187.95701</v>
       </c>
       <c r="I20">
-        <v>47349755.81359189</v>
+        <v>610811849.9953353</v>
       </c>
       <c r="J20">
-        <v>10456463.87219037</v>
+        <v>134888383.9512558</v>
       </c>
       <c r="K20">
-        <v>11975337.8301194</v>
+        <v>154481858.0085402</v>
       </c>
       <c r="L20">
-        <v>5457562.71406961</v>
+        <v>70402559.01149797</v>
       </c>
       <c r="M20">
-        <v>220899085.9360948</v>
+        <v>2849598208.575623</v>
       </c>
       <c r="N20">
-        <v>83699215.49778605</v>
+        <v>1079719879.92144</v>
       </c>
       <c r="O20">
-        <v>548349451.7380389</v>
+        <v>7073707927.420702</v>
       </c>
       <c r="P20">
-        <v>869891857.5464702</v>
+        <v>11221604962.34947</v>
       </c>
       <c r="Q20">
-        <v>670698778.7824962</v>
+        <v>8652014246.294201</v>
       </c>
     </row>
     <row r="21">
@@ -10444,52 +10444,52 @@
         </is>
       </c>
       <c r="B21">
-        <v>111562229.2255841</v>
+        <v>1439152757.010034</v>
       </c>
       <c r="C21">
-        <v>2398440.77359463</v>
+        <v>30939885.97937073</v>
       </c>
       <c r="D21">
-        <v>135462747.5476158</v>
+        <v>1747469443.364244</v>
       </c>
       <c r="E21">
-        <v>7968708.775547121</v>
+        <v>102796343.2045579</v>
       </c>
       <c r="F21">
-        <v>63744065.93993428</v>
+        <v>822298450.6251522</v>
       </c>
       <c r="G21">
-        <v>209573963.0366918</v>
+        <v>2703504123.173324</v>
       </c>
       <c r="H21">
-        <v>165744423.9735495</v>
+        <v>2138103069.258788</v>
       </c>
       <c r="I21">
-        <v>46039164.94207455</v>
+        <v>593905227.7527617</v>
       </c>
       <c r="J21">
-        <v>9548249.23890375</v>
+        <v>123172415.1818584</v>
       </c>
       <c r="K21">
-        <v>12380682.81279047</v>
+        <v>159710808.2849971</v>
       </c>
       <c r="L21">
-        <v>5975048.28787524</v>
+        <v>77078122.9135906</v>
       </c>
       <c r="M21">
-        <v>221453905.9955592</v>
+        <v>2856755387.342714</v>
       </c>
       <c r="N21">
-        <v>82328150.50178765</v>
+        <v>1062033141.473061</v>
       </c>
       <c r="O21">
-        <v>543469625.7525403</v>
+        <v>7010758172.20777</v>
       </c>
       <c r="P21">
-        <v>864605818.0148163</v>
+        <v>11153415052.39113</v>
       </c>
       <c r="Q21">
-        <v>664740389.9995692</v>
+        <v>8575151030.994443</v>
       </c>
     </row>
     <row r="22">
@@ -10499,52 +10499,52 @@
         </is>
       </c>
       <c r="B22">
-        <v>109905853.3666501</v>
+        <v>1417785508.429786</v>
       </c>
       <c r="C22">
-        <v>2134948.23101694</v>
+        <v>27540832.18011853</v>
       </c>
       <c r="D22">
-        <v>134058161.8587424</v>
+        <v>1729350287.977777</v>
       </c>
       <c r="E22">
-        <v>7787606.19256746</v>
+        <v>100460119.8841202</v>
       </c>
       <c r="F22">
-        <v>62208831.94475479</v>
+        <v>802493932.0873369</v>
       </c>
       <c r="G22">
-        <v>206189548.2270817</v>
+        <v>2659845172.129354</v>
       </c>
       <c r="H22">
-        <v>166395965.7464876</v>
+        <v>2146507958.12969</v>
       </c>
       <c r="I22">
-        <v>45317324.72894306</v>
+        <v>584593489.0033655</v>
       </c>
       <c r="J22">
-        <v>10014506.33949913</v>
+        <v>129187131.7795388</v>
       </c>
       <c r="K22">
-        <v>12543066.38177477</v>
+        <v>161805556.3248945</v>
       </c>
       <c r="L22">
-        <v>6177204.72765898</v>
+        <v>79685940.98680083</v>
       </c>
       <c r="M22">
-        <v>222590194.1170782</v>
+        <v>2871413504.110309</v>
       </c>
       <c r="N22">
-        <v>81773410.00111589</v>
+        <v>1054876989.014395</v>
       </c>
       <c r="O22">
-        <v>544811672.0425576</v>
+        <v>7028070569.348993</v>
       </c>
       <c r="P22">
-        <v>860907073.6362894</v>
+        <v>11105701249.90813</v>
       </c>
       <c r="Q22">
-        <v>663050605.5408643</v>
+        <v>8553352811.47715</v>
       </c>
     </row>
     <row r="23">
@@ -10554,52 +10554,52 @@
         </is>
       </c>
       <c r="B23">
-        <v>109109674.8581512</v>
+        <v>1407514805.670151</v>
       </c>
       <c r="C23">
-        <v>2193254.48617129</v>
+        <v>28292982.87160964</v>
       </c>
       <c r="D23">
-        <v>131886725.666456</v>
+        <v>1701338761.097282</v>
       </c>
       <c r="E23">
-        <v>7927609.10069648</v>
+        <v>102266157.3989846</v>
       </c>
       <c r="F23">
-        <v>58927944.86598135</v>
+        <v>760170488.7711594</v>
       </c>
       <c r="G23">
-        <v>200935534.1193051</v>
+        <v>2592068390.139036</v>
       </c>
       <c r="H23">
-        <v>167382195.2988973</v>
+        <v>2159230319.355775</v>
       </c>
       <c r="I23">
-        <v>45733415.38684289</v>
+        <v>589961058.4902734</v>
       </c>
       <c r="J23">
-        <v>9822400.27607627</v>
+        <v>126708963.5613839</v>
       </c>
       <c r="K23">
-        <v>12116352.8722035</v>
+        <v>156300952.0514252</v>
       </c>
       <c r="L23">
-        <v>6795085.24840055</v>
+        <v>87656599.7043671</v>
       </c>
       <c r="M23">
-        <v>223496510.4052218</v>
+        <v>2883104984.227362</v>
       </c>
       <c r="N23">
-        <v>80415861.32939427</v>
+        <v>1037364611.149186</v>
       </c>
       <c r="O23">
-        <v>545761820.8170366</v>
+        <v>7040327488.539773</v>
       </c>
       <c r="P23">
-        <v>855807029.7944928</v>
+        <v>11039910684.34896</v>
       </c>
       <c r="Q23">
-        <v>659486408.3585467</v>
+        <v>8507374667.825253</v>
       </c>
     </row>
     <row r="24">
@@ -10609,52 +10609,52 @@
         </is>
       </c>
       <c r="B24">
-        <v>108964535.0586959</v>
+        <v>1405642502.257177</v>
       </c>
       <c r="C24">
-        <v>1911314.55896017</v>
+        <v>24655957.8105862</v>
       </c>
       <c r="D24">
-        <v>130954408.6309637</v>
+        <v>1689311871.339432</v>
       </c>
       <c r="E24">
-        <v>8602606.195020579</v>
+        <v>110973619.9157655</v>
       </c>
       <c r="F24">
-        <v>57709959.46864699</v>
+        <v>744458477.1455462</v>
       </c>
       <c r="G24">
-        <v>199178288.8535914</v>
+        <v>2569399926.211329</v>
       </c>
       <c r="H24">
-        <v>167058291.6963988</v>
+        <v>2155051962.883544</v>
       </c>
       <c r="I24">
-        <v>46672927.3340468</v>
+        <v>602080762.6092037</v>
       </c>
       <c r="J24">
-        <v>9881560.115742229</v>
+        <v>127472125.4930748</v>
       </c>
       <c r="K24">
-        <v>11896599.7808952</v>
+        <v>153466137.1735481</v>
       </c>
       <c r="L24">
-        <v>7131071.48502055</v>
+        <v>91990822.1567651</v>
       </c>
       <c r="M24">
-        <v>224572035.3985901</v>
+        <v>2896979256.641812</v>
       </c>
       <c r="N24">
-        <v>79095000.33998445</v>
+        <v>1020325504.385799</v>
       </c>
       <c r="O24">
-        <v>546307486.1506782</v>
+        <v>7047366571.343748</v>
       </c>
       <c r="P24">
-        <v>854450310.0629653</v>
+        <v>11022408999.81225</v>
       </c>
       <c r="Q24">
-        <v>659259703.1792645</v>
+        <v>8504450171.012513</v>
       </c>
     </row>
     <row r="25">
@@ -10664,52 +10664,52 @@
         </is>
       </c>
       <c r="B25">
-        <v>107471043.9631148</v>
+        <v>1386376467.124181</v>
       </c>
       <c r="C25">
-        <v>2059672.53042558</v>
+        <v>26569775.64248998</v>
       </c>
       <c r="D25">
-        <v>129123410.2155039</v>
+        <v>1665691991.78</v>
       </c>
       <c r="E25">
-        <v>8932991.96283791</v>
+        <v>115235596.320609</v>
       </c>
       <c r="F25">
-        <v>56362863.38754957</v>
+        <v>727080937.6993895</v>
       </c>
       <c r="G25">
-        <v>196478938.0963169</v>
+        <v>2534578301.442489</v>
       </c>
       <c r="H25">
-        <v>167668583.1154553</v>
+        <v>2162924722.189374</v>
       </c>
       <c r="I25">
-        <v>47830714.091943</v>
+        <v>617016211.7860646</v>
       </c>
       <c r="J25">
-        <v>9955540.13521996</v>
+        <v>128426467.7443375</v>
       </c>
       <c r="K25">
-        <v>11604917.06263672</v>
+        <v>149703430.1080137</v>
       </c>
       <c r="L25">
-        <v>6593360.5354663</v>
+        <v>85054350.90751527</v>
       </c>
       <c r="M25">
-        <v>224855588.7050794</v>
+        <v>2900637094.295525</v>
       </c>
       <c r="N25">
-        <v>80247208.43999436</v>
+        <v>1035188988.875927</v>
       </c>
       <c r="O25">
-        <v>548755912.0857952</v>
+        <v>7078951265.906757</v>
       </c>
       <c r="P25">
-        <v>852705894.145227</v>
+        <v>10999906034.47343</v>
       </c>
       <c r="Q25">
-        <v>658394281.2066514</v>
+        <v>8493286227.565804</v>
       </c>
     </row>
     <row r="26">
@@ -10719,52 +10719,52 @@
         </is>
       </c>
       <c r="B26">
-        <v>104924228.6749098</v>
+        <v>1353522549.906337</v>
       </c>
       <c r="C26">
-        <v>2274397.38329936</v>
+        <v>29339726.24456175</v>
       </c>
       <c r="D26">
-        <v>127952414.4355274</v>
+        <v>1650586146.218303</v>
       </c>
       <c r="E26">
-        <v>9196656.96240589</v>
+        <v>118636874.815036</v>
       </c>
       <c r="F26">
-        <v>56940485.87766919</v>
+        <v>734532267.8219326</v>
       </c>
       <c r="G26">
-        <v>196363954.6589018</v>
+        <v>2533095015.099833</v>
       </c>
       <c r="H26">
-        <v>167819785.8727574</v>
+        <v>2164875237.75857</v>
       </c>
       <c r="I26">
-        <v>48237681.81656202</v>
+        <v>622266095.43365</v>
       </c>
       <c r="J26">
-        <v>9949737.303325329</v>
+        <v>128351611.2128967</v>
       </c>
       <c r="K26">
-        <v>11073579.37014346</v>
+        <v>142849173.8748506</v>
       </c>
       <c r="L26">
-        <v>6537601.18862066</v>
+        <v>84335055.33320652</v>
       </c>
       <c r="M26">
-        <v>223696309.8635307</v>
+        <v>2885682397.239546</v>
       </c>
       <c r="N26">
-        <v>80057727.80844738</v>
+        <v>1032744688.728971</v>
       </c>
       <c r="O26">
-        <v>547372423.223387</v>
+        <v>7061104259.581693</v>
       </c>
       <c r="P26">
-        <v>848660606.5571985</v>
+        <v>10947721824.58786</v>
       </c>
       <c r="Q26">
-        <v>657141048.8852206</v>
+        <v>8477119530.619347</v>
       </c>
     </row>
     <row r="27">
@@ -10774,52 +10774,52 @@
         </is>
       </c>
       <c r="B27">
-        <v>103776721.763821</v>
+        <v>1338719710.753291</v>
       </c>
       <c r="C27">
-        <v>2244131.46985639</v>
+        <v>28949295.96114744</v>
       </c>
       <c r="D27">
-        <v>129774724.985132</v>
+        <v>1674093952.308203</v>
       </c>
       <c r="E27">
-        <v>9437637.62110571</v>
+        <v>121745525.3122637</v>
       </c>
       <c r="F27">
-        <v>58283414.0389191</v>
+        <v>751856041.1020564</v>
       </c>
       <c r="G27">
-        <v>199739908.1150132</v>
+        <v>2576644814.683671</v>
       </c>
       <c r="H27">
-        <v>166624531.9974817</v>
+        <v>2149456462.767514</v>
       </c>
       <c r="I27">
-        <v>47756389.72110062</v>
+        <v>616057427.4021981</v>
       </c>
       <c r="J27">
-        <v>10403558.56246967</v>
+        <v>134205905.4558588</v>
       </c>
       <c r="K27">
-        <v>11234707.92068244</v>
+        <v>144927732.1768035</v>
       </c>
       <c r="L27">
-        <v>6123357.79714013</v>
+        <v>78991315.58310768</v>
       </c>
       <c r="M27">
-        <v>223334599.3062505</v>
+        <v>2881016331.050631</v>
       </c>
       <c r="N27">
-        <v>80739007.95744172</v>
+        <v>1041533202.650998</v>
       </c>
       <c r="O27">
-        <v>546216153.2625668</v>
+        <v>7046188377.087112</v>
       </c>
       <c r="P27">
-        <v>849732783.1414011</v>
+        <v>10961552902.52407</v>
       </c>
       <c r="Q27">
-        <v>659093695.6229981</v>
+        <v>8502308673.536676</v>
       </c>
     </row>
     <row r="28">
@@ -10829,52 +10829,52 @@
         </is>
       </c>
       <c r="B28">
-        <v>101910651.0676199</v>
+        <v>1314647398.772297</v>
       </c>
       <c r="C28">
-        <v>2059131.09132358</v>
+        <v>26562791.07807418</v>
       </c>
       <c r="D28">
-        <v>129586228.6363</v>
+        <v>1671662349.40827</v>
       </c>
       <c r="E28">
-        <v>9363141.12224862</v>
+        <v>120784520.4770072</v>
       </c>
       <c r="F28">
-        <v>59001379.89830228</v>
+        <v>761117800.6880994</v>
       </c>
       <c r="G28">
-        <v>200009880.7481745</v>
+        <v>2580127461.651451</v>
       </c>
       <c r="H28">
-        <v>165117631.8725399</v>
+        <v>2130017451.155765</v>
       </c>
       <c r="I28">
-        <v>47648133.14227971</v>
+        <v>614660917.5354083</v>
       </c>
       <c r="J28">
-        <v>10731143.23222517</v>
+        <v>138431747.6957047</v>
       </c>
       <c r="K28">
-        <v>10748704.81672443</v>
+        <v>138658292.1357452</v>
       </c>
       <c r="L28">
-        <v>5910335.998211</v>
+        <v>76243334.37692191</v>
       </c>
       <c r="M28">
-        <v>222239425.9463666</v>
+        <v>2866888594.708129</v>
       </c>
       <c r="N28">
-        <v>81587467.9396773</v>
+        <v>1052478336.421837</v>
       </c>
       <c r="O28">
-        <v>543982842.9480242</v>
+        <v>7017378674.029511</v>
       </c>
       <c r="P28">
-        <v>845903374.7638184</v>
+        <v>10912153534.45326</v>
       </c>
       <c r="Q28">
-        <v>656494919.7583102</v>
+        <v>8468784464.882202</v>
       </c>
     </row>
     <row r="29">
@@ -10884,52 +10884,52 @@
         </is>
       </c>
       <c r="B29">
-        <v>101483215.2847061</v>
+        <v>1309133477.172709</v>
       </c>
       <c r="C29">
-        <v>1711294.47999551</v>
+        <v>22075698.79194208</v>
       </c>
       <c r="D29">
-        <v>130165045.3317423</v>
+        <v>1679129084.779475</v>
       </c>
       <c r="E29">
-        <v>9220802.48524021</v>
+        <v>118948352.0595987</v>
       </c>
       <c r="F29">
-        <v>59636761.68778625</v>
+        <v>769314225.7724427</v>
       </c>
       <c r="G29">
-        <v>200733903.9847643</v>
+        <v>2589467361.403459</v>
       </c>
       <c r="H29">
-        <v>164397264.7647878</v>
+        <v>2120724715.465763</v>
       </c>
       <c r="I29">
-        <v>47298827.80496597</v>
+        <v>610154878.6840611</v>
       </c>
       <c r="J29">
-        <v>11301403.40359877</v>
+        <v>145788103.9064241</v>
       </c>
       <c r="K29">
-        <v>10325322.7629485</v>
+        <v>133196663.6420356</v>
       </c>
       <c r="L29">
-        <v>6273108.21835709</v>
+        <v>80923096.01680647</v>
       </c>
       <c r="M29">
-        <v>224864530.3208174</v>
+        <v>2900752441.138544</v>
       </c>
       <c r="N29">
-        <v>81825254.13815367</v>
+        <v>1055545778.382182</v>
       </c>
       <c r="O29">
-        <v>546285711.4136292</v>
+        <v>7047085677.235817</v>
       </c>
       <c r="P29">
-        <v>848502830.6830995</v>
+        <v>10945686515.81198</v>
       </c>
       <c r="Q29">
-        <v>658921253.0418828</v>
+        <v>8500084164.240288</v>
       </c>
     </row>
     <row r="30">
@@ -10939,52 +10939,52 @@
         </is>
       </c>
       <c r="B30">
-        <v>102986434.3729228</v>
+        <v>1328525003.410704</v>
       </c>
       <c r="C30">
-        <v>1426003.83653441</v>
+        <v>18395449.49129389</v>
       </c>
       <c r="D30">
-        <v>130410167.9866703</v>
+        <v>1682291167.028047</v>
       </c>
       <c r="E30">
-        <v>9170314.144099571</v>
+        <v>118297052.4588845</v>
       </c>
       <c r="F30">
-        <v>59234120.35059723</v>
+        <v>764120152.5227044</v>
       </c>
       <c r="G30">
-        <v>200240606.3179016</v>
+        <v>2583103821.50093</v>
       </c>
       <c r="H30">
-        <v>163564338.7448695</v>
+        <v>2109979969.808817</v>
       </c>
       <c r="I30">
-        <v>47118667.39124201</v>
+        <v>607830809.3470219</v>
       </c>
       <c r="J30">
-        <v>12141906.64042575</v>
+        <v>156630595.6614922</v>
       </c>
       <c r="K30">
-        <v>10352893.89558903</v>
+        <v>133552331.2530985</v>
       </c>
       <c r="L30">
-        <v>6488989.614457469</v>
+        <v>83707966.02650136</v>
       </c>
       <c r="M30">
-        <v>228916847.149009</v>
+        <v>2953027328.222217</v>
       </c>
       <c r="N30">
-        <v>82501263.72655508</v>
+        <v>1064266302.072561</v>
       </c>
       <c r="O30">
-        <v>551084907.1621478</v>
+        <v>7108995302.391706</v>
       </c>
       <c r="P30">
-        <v>854311947.8529721</v>
+        <v>11020624127.30334</v>
       </c>
       <c r="Q30">
-        <v>662335260.1390369</v>
+        <v>8544124855.793576</v>
       </c>
     </row>
     <row r="31">
@@ -10994,52 +10994,52 @@
         </is>
       </c>
       <c r="B31">
-        <v>104034540.4397832</v>
+        <v>1342045571.673204</v>
       </c>
       <c r="C31">
-        <v>1410173.04231299</v>
+        <v>18191232.24583757</v>
       </c>
       <c r="D31">
-        <v>128985075.738232</v>
+        <v>1663907477.023193</v>
       </c>
       <c r="E31">
-        <v>8896863.41900355</v>
+        <v>114769538.1051458</v>
       </c>
       <c r="F31">
-        <v>59522290.14339885</v>
+        <v>767837542.8498452</v>
       </c>
       <c r="G31">
-        <v>198814402.3429474</v>
+        <v>2564705790.224022</v>
       </c>
       <c r="H31">
-        <v>164787589.3460307</v>
+        <v>2125759902.563796</v>
       </c>
       <c r="I31">
-        <v>48549038.88398785</v>
+        <v>626282601.6034433</v>
       </c>
       <c r="J31">
-        <v>12877759.12543562</v>
+        <v>166123092.7181195</v>
       </c>
       <c r="K31">
-        <v>10071702.03025938</v>
+        <v>129924956.190346</v>
       </c>
       <c r="L31">
-        <v>6480926.29925403</v>
+        <v>83603949.26037699</v>
       </c>
       <c r="M31">
-        <v>231456821.9751945</v>
+        <v>2985793003.480009</v>
       </c>
       <c r="N31">
-        <v>83836183.35564686</v>
+        <v>1081486765.287845</v>
       </c>
       <c r="O31">
-        <v>558060021.0158088</v>
+        <v>7198974271.103934</v>
       </c>
       <c r="P31">
-        <v>860908963.7985394</v>
+        <v>11105725633.00116</v>
       </c>
       <c r="Q31">
-        <v>666557313.7038554</v>
+        <v>8598589346.779736</v>
       </c>
     </row>
     <row r="32">
@@ -11049,52 +11049,52 @@
         </is>
       </c>
       <c r="B32">
-        <v>104110257.0352691</v>
+        <v>1343022315.754972</v>
       </c>
       <c r="C32">
-        <v>1568953.82261277</v>
+        <v>20239504.31170473</v>
       </c>
       <c r="D32">
-        <v>129486080.2556366</v>
+        <v>1670370435.297712</v>
       </c>
       <c r="E32">
-        <v>8374794.40724212</v>
+        <v>108034847.8534234</v>
       </c>
       <c r="F32">
-        <v>59206754.58259921</v>
+        <v>763767134.1155298</v>
       </c>
       <c r="G32">
-        <v>198636583.0680907</v>
+        <v>2562411921.57837</v>
       </c>
       <c r="H32">
-        <v>167714270.2083758</v>
+        <v>2163514085.688048</v>
       </c>
       <c r="I32">
-        <v>50774691.27736341</v>
+        <v>654993517.477988</v>
       </c>
       <c r="J32">
-        <v>13383830.51749098</v>
+        <v>172651413.6756336</v>
       </c>
       <c r="K32">
-        <v>10172863.73383144</v>
+        <v>131229942.1664256</v>
       </c>
       <c r="L32">
-        <v>6227575.12825842</v>
+        <v>80335719.15453362</v>
       </c>
       <c r="M32">
-        <v>232588199.7258682</v>
+        <v>3000387776.463699</v>
       </c>
       <c r="N32">
-        <v>85293541.26838894</v>
+        <v>1100286682.362217</v>
       </c>
       <c r="O32">
-        <v>566154971.8595772</v>
+        <v>7303399136.988545</v>
       </c>
       <c r="P32">
-        <v>868901811.962937</v>
+        <v>11208833374.32189</v>
       </c>
       <c r="Q32">
-        <v>673270438.5310206</v>
+        <v>8685188657.050167</v>
       </c>
     </row>
     <row r="33">
@@ -11104,52 +11104,52 @@
         </is>
       </c>
       <c r="B33">
-        <v>102174440.3740937</v>
+        <v>1318050280.825809</v>
       </c>
       <c r="C33">
-        <v>1811356.12278338</v>
+        <v>23366493.9839056</v>
       </c>
       <c r="D33">
-        <v>131168470.2508268</v>
+        <v>1692073266.235665</v>
       </c>
       <c r="E33">
-        <v>7512417.35486259</v>
+        <v>96910183.87772742</v>
       </c>
       <c r="F33">
-        <v>58743569.76124892</v>
+        <v>757792049.9201111</v>
       </c>
       <c r="G33">
-        <v>199235813.4897217</v>
+        <v>2570141994.017409</v>
       </c>
       <c r="H33">
-        <v>170339162.2363604</v>
+        <v>2197375192.849049</v>
       </c>
       <c r="I33">
-        <v>52557272.04183592</v>
+        <v>677988809.3396834</v>
       </c>
       <c r="J33">
-        <v>13829104.17144683</v>
+        <v>178395443.8116641</v>
       </c>
       <c r="K33">
-        <v>9850144.51235736</v>
+        <v>127066864.2094099</v>
       </c>
       <c r="L33">
-        <v>6213106.39543472</v>
+        <v>80149072.5011079</v>
       </c>
       <c r="M33">
-        <v>233476536.448547</v>
+        <v>3011847320.186256</v>
       </c>
       <c r="N33">
-        <v>85422984.42458972</v>
+        <v>1101956499.077208</v>
       </c>
       <c r="O33">
-        <v>571688310.230572</v>
+        <v>7374779201.974379</v>
       </c>
       <c r="P33">
-        <v>873098564.0943873</v>
+        <v>11262971476.8176</v>
       </c>
       <c r="Q33">
-        <v>679288032.9002692</v>
+        <v>8762815624.413473</v>
       </c>
     </row>
     <row r="34">
@@ -11159,52 +11159,52 @@
         </is>
       </c>
       <c r="B34">
-        <v>99999430.61942062</v>
+        <v>1289992654.990526</v>
       </c>
       <c r="C34">
-        <v>1817183.90657845</v>
+        <v>23441672.39486201</v>
       </c>
       <c r="D34">
-        <v>129113015.4858677</v>
+        <v>1665557899.767694</v>
       </c>
       <c r="E34">
-        <v>6579951.29956717</v>
+        <v>84881371.7644165</v>
       </c>
       <c r="F34">
-        <v>58145042.13504493</v>
+        <v>750071043.5420797</v>
       </c>
       <c r="G34">
-        <v>195655192.8270583</v>
+        <v>2523951987.469051</v>
       </c>
       <c r="H34">
-        <v>168040895.2108716</v>
+        <v>2167727548.220243</v>
       </c>
       <c r="I34">
-        <v>53334994.68481916</v>
+        <v>688021431.4341673</v>
       </c>
       <c r="J34">
-        <v>13771365.50034828</v>
+        <v>177650614.9544928</v>
       </c>
       <c r="K34">
-        <v>9334809.68114181</v>
+        <v>120419044.8867294</v>
       </c>
       <c r="L34">
-        <v>5653186.42342324</v>
+        <v>72926104.8621598</v>
       </c>
       <c r="M34">
-        <v>228337330.7340472</v>
+        <v>2945551566.469209</v>
       </c>
       <c r="N34">
-        <v>85200517.14303488</v>
+        <v>1099086671.14515</v>
       </c>
       <c r="O34">
-        <v>563673099.3776863</v>
+        <v>7271382981.972153</v>
       </c>
       <c r="P34">
-        <v>859327722.824165</v>
+        <v>11085327624.43173</v>
       </c>
       <c r="Q34">
-        <v>668474588.6382862</v>
+        <v>8623322193.433893</v>
       </c>
     </row>
     <row r="35">
@@ -11214,52 +11214,52 @@
         </is>
       </c>
       <c r="B35">
-        <v>99091464.80526732</v>
+        <v>1278279895.987948</v>
       </c>
       <c r="C35">
-        <v>1598323.91400222</v>
+        <v>20618378.49062864</v>
       </c>
       <c r="D35">
-        <v>121042233.7597784</v>
+        <v>1561444815.501142</v>
       </c>
       <c r="E35">
-        <v>6294267.93440672</v>
+        <v>81196056.3538467</v>
       </c>
       <c r="F35">
-        <v>53355549.54581177</v>
+        <v>688286589.1409719</v>
       </c>
       <c r="G35">
-        <v>182290375.1539991</v>
+        <v>2351545839.486589</v>
       </c>
       <c r="H35">
-        <v>156846683.978973</v>
+        <v>2023322223.328751</v>
       </c>
       <c r="I35">
-        <v>50466482.05939038</v>
+        <v>651017618.5661359</v>
       </c>
       <c r="J35">
-        <v>12962439.50323378</v>
+        <v>167215469.5917158</v>
       </c>
       <c r="K35">
-        <v>8881558.60113031</v>
+        <v>114572105.954581</v>
       </c>
       <c r="L35">
-        <v>5205025.38669357</v>
+        <v>67144827.48834705</v>
       </c>
       <c r="M35">
-        <v>212248961.5057303</v>
+        <v>2738011603.423921</v>
       </c>
       <c r="N35">
-        <v>80949187.54161273</v>
+        <v>1044244519.286804</v>
       </c>
       <c r="O35">
-        <v>527560338.5767641</v>
+        <v>6805528367.640257</v>
       </c>
       <c r="P35">
-        <v>808942178.5360305</v>
+        <v>10435354103.11479</v>
       </c>
       <c r="Q35">
-        <v>623696500.8024569</v>
+        <v>8045684860.351694</v>
       </c>
     </row>
     <row r="36">
@@ -11269,52 +11269,52 @@
         </is>
       </c>
       <c r="B36">
-        <v>100716176.8491455</v>
+        <v>1299238681.353977</v>
       </c>
       <c r="C36">
-        <v>1378372.0441091</v>
+        <v>17780999.36900739</v>
       </c>
       <c r="D36">
-        <v>115696160.2030079</v>
+        <v>1492480466.618802</v>
       </c>
       <c r="E36">
-        <v>6076426.75757784</v>
+        <v>78385905.17275414</v>
       </c>
       <c r="F36">
-        <v>50263857.02235265</v>
+        <v>648403755.5883492</v>
       </c>
       <c r="G36">
-        <v>173414816.0270475</v>
+        <v>2237051126.748913</v>
       </c>
       <c r="H36">
-        <v>147477841.9754297</v>
+        <v>1902464161.483042</v>
       </c>
       <c r="I36">
-        <v>46691595.90375389</v>
+        <v>602321587.1584252</v>
       </c>
       <c r="J36">
-        <v>13317117.22349673</v>
+        <v>171790812.1831079</v>
       </c>
       <c r="K36">
-        <v>9421451.898424011</v>
+        <v>121536729.4896697</v>
       </c>
       <c r="L36">
-        <v>4792397.44094577</v>
+        <v>61821926.98820043</v>
       </c>
       <c r="M36">
-        <v>200890167.1881531</v>
+        <v>2591483156.727175</v>
       </c>
       <c r="N36">
-        <v>77353337.50914007</v>
+        <v>997858053.8679069</v>
       </c>
       <c r="O36">
-        <v>499943909.1393433</v>
+        <v>6449276427.897529</v>
       </c>
       <c r="P36">
-        <v>774074902.0155362</v>
+        <v>9985566236.000418</v>
       </c>
       <c r="Q36">
-        <v>591212990.2163048</v>
+        <v>7626647573.790332</v>
       </c>
     </row>
     <row r="37">
@@ -11324,52 +11324,52 @@
         </is>
       </c>
       <c r="B37">
-        <v>105388150.4148267</v>
+        <v>1359507140.351265</v>
       </c>
       <c r="C37">
-        <v>1044690.57002966</v>
+        <v>13476508.35338262</v>
       </c>
       <c r="D37">
-        <v>109510145.4264954</v>
+        <v>1412680876.001791</v>
       </c>
       <c r="E37">
-        <v>6563294.43358545</v>
+        <v>84666498.19325231</v>
       </c>
       <c r="F37">
-        <v>47582219.2199963</v>
+        <v>613810627.9379523</v>
       </c>
       <c r="G37">
-        <v>164700349.6501068</v>
+        <v>2124634510.486378</v>
       </c>
       <c r="H37">
-        <v>143411488.5275888</v>
+        <v>1850008202.005896</v>
       </c>
       <c r="I37">
-        <v>43954198.69267925</v>
+        <v>567009163.1355623</v>
       </c>
       <c r="J37">
-        <v>13595620.02225798</v>
+        <v>175383498.2871279</v>
       </c>
       <c r="K37">
-        <v>10959663.21340922</v>
+        <v>141379655.4529789</v>
       </c>
       <c r="L37">
-        <v>4030365.29133395</v>
+        <v>51991712.25820795</v>
       </c>
       <c r="M37">
-        <v>192470010.1773918</v>
+        <v>2482863131.288355</v>
       </c>
       <c r="N37">
-        <v>75809332.18979894</v>
+        <v>977940385.2484063</v>
       </c>
       <c r="O37">
-        <v>484230678.1144601</v>
+        <v>6246575747.676536</v>
       </c>
       <c r="P37">
-        <v>754319178.1793935</v>
+        <v>9730717398.514177</v>
       </c>
       <c r="Q37">
-        <v>569091330.2834339</v>
+        <v>7341278160.656298</v>
       </c>
     </row>
     <row r="38">
@@ -11379,52 +11379,52 @@
         </is>
       </c>
       <c r="B38">
-        <v>108585712.8715441</v>
+        <v>1400755696.042918</v>
       </c>
       <c r="C38">
-        <v>1096402.51431606</v>
+        <v>14143592.43467718</v>
       </c>
       <c r="D38">
-        <v>108106527.1192248</v>
+        <v>1394574199.838001</v>
       </c>
       <c r="E38">
-        <v>6956504.70140314</v>
+        <v>89738910.64810051</v>
       </c>
       <c r="F38">
-        <v>45309014.54112862</v>
+        <v>584486287.5805593</v>
       </c>
       <c r="G38">
-        <v>161468448.8760726</v>
+        <v>2082942990.501337</v>
       </c>
       <c r="H38">
-        <v>144401384.3808429</v>
+        <v>1862777858.512873</v>
       </c>
       <c r="I38">
-        <v>41367629.44867035</v>
+        <v>533642419.8878475</v>
       </c>
       <c r="J38">
-        <v>14127378.52868355</v>
+        <v>182243183.0200178</v>
       </c>
       <c r="K38">
-        <v>13254288.85316651</v>
+        <v>170980326.205848</v>
       </c>
       <c r="L38">
-        <v>3906845.20731221</v>
+        <v>50398303.17432751</v>
       </c>
       <c r="M38">
-        <v>192837389.1800238</v>
+        <v>2487602320.422307</v>
       </c>
       <c r="N38">
-        <v>76221742.13099863</v>
+        <v>983260473.4898823</v>
       </c>
       <c r="O38">
-        <v>486116657.729698</v>
+        <v>6270904884.713104</v>
       </c>
       <c r="P38">
-        <v>756170819.4773147</v>
+        <v>9754603571.25736</v>
       </c>
       <c r="Q38">
-        <v>567456519.2674599</v>
+        <v>7320189098.550233</v>
       </c>
     </row>
     <row r="39">
@@ -11434,52 +11434,52 @@
         </is>
       </c>
       <c r="B39">
-        <v>113962330.3634845</v>
+        <v>1470114061.68895</v>
       </c>
       <c r="C39">
-        <v>1321469.31731694</v>
+        <v>17046954.19338853</v>
       </c>
       <c r="D39">
-        <v>112267866.4167982</v>
+        <v>1448255476.776696</v>
       </c>
       <c r="E39">
-        <v>7181043.06833449</v>
+        <v>92635455.58151492</v>
       </c>
       <c r="F39">
-        <v>48039383.23743252</v>
+        <v>619708043.7628795</v>
       </c>
       <c r="G39">
-        <v>168809762.0398821</v>
+        <v>2177645930.314479</v>
       </c>
       <c r="H39">
-        <v>155220843.7193559</v>
+        <v>2002348883.979692</v>
       </c>
       <c r="I39">
-        <v>41677989.76412698</v>
+        <v>537646067.9572381</v>
       </c>
       <c r="J39">
-        <v>15348879.63025953</v>
+        <v>198000547.230348</v>
       </c>
       <c r="K39">
-        <v>15323141.89937581</v>
+        <v>197668530.501948</v>
       </c>
       <c r="L39">
-        <v>3880494.91447237</v>
+        <v>50058384.39669357</v>
       </c>
       <c r="M39">
-        <v>203181506.8191523</v>
+        <v>2621041437.967065</v>
       </c>
       <c r="N39">
-        <v>80026490.37172601</v>
+        <v>1032341725.795266</v>
       </c>
       <c r="O39">
-        <v>514659347.118469</v>
+        <v>6639105577.82825</v>
       </c>
       <c r="P39">
-        <v>797431439.5218357</v>
+        <v>10286865569.83168</v>
       </c>
       <c r="Q39">
-        <v>599562123.8721528</v>
+        <v>7734351397.950771</v>
       </c>
     </row>
     <row r="40">
@@ -11489,52 +11489,52 @@
         </is>
       </c>
       <c r="B40">
-        <v>117260220.1777914</v>
+        <v>1512656840.293509</v>
       </c>
       <c r="C40">
-        <v>1591023.37491123</v>
+        <v>20524201.53635487</v>
       </c>
       <c r="D40">
-        <v>114227878.7479122</v>
+        <v>1473539635.848068</v>
       </c>
       <c r="E40">
-        <v>7035243.785143221</v>
+        <v>90754644.82834755</v>
       </c>
       <c r="F40">
-        <v>50188604.42490945</v>
+        <v>647432997.081332</v>
       </c>
       <c r="G40">
-        <v>173042750.3328761</v>
+        <v>2232251479.294102</v>
       </c>
       <c r="H40">
-        <v>163937573.3929534</v>
+        <v>2114794696.769099</v>
       </c>
       <c r="I40">
-        <v>42709573.62341871</v>
+        <v>550953499.7421014</v>
       </c>
       <c r="J40">
-        <v>15891678.72734587</v>
+        <v>205002655.5827617</v>
       </c>
       <c r="K40">
-        <v>15564470.20061247</v>
+        <v>200781665.5879009</v>
       </c>
       <c r="L40">
-        <v>4200105.81644046</v>
+        <v>54181365.03208194</v>
       </c>
       <c r="M40">
-        <v>212617176.0716491</v>
+        <v>2742761571.324274</v>
       </c>
       <c r="N40">
-        <v>83301778.89108524</v>
+        <v>1074592947.695</v>
       </c>
       <c r="O40">
-        <v>538222356.7235053</v>
+        <v>6943068401.733218</v>
       </c>
       <c r="P40">
-        <v>828525327.2341729</v>
+        <v>10687976721.32083</v>
       </c>
       <c r="Q40">
-        <v>623763222.3488557</v>
+        <v>8046545568.30024</v>
       </c>
     </row>
     <row r="41">
@@ -11544,52 +11544,52 @@
         </is>
       </c>
       <c r="B41">
-        <v>117216207.3829644</v>
+        <v>1512089075.24024</v>
       </c>
       <c r="C41">
-        <v>1995959.98510548</v>
+        <v>25747883.80786069</v>
       </c>
       <c r="D41">
-        <v>118215022.9276762</v>
+        <v>1524973795.767022</v>
       </c>
       <c r="E41">
-        <v>6798712.21836064</v>
+        <v>87703387.61685225</v>
       </c>
       <c r="F41">
-        <v>52220070.84534126</v>
+        <v>673638913.9049022</v>
       </c>
       <c r="G41">
-        <v>179229765.9764835</v>
+        <v>2312063981.096638</v>
       </c>
       <c r="H41">
-        <v>166548843.7284903</v>
+        <v>2148480084.097525</v>
       </c>
       <c r="I41">
-        <v>42064200.89369909</v>
+        <v>542628191.5287182</v>
       </c>
       <c r="J41">
-        <v>15636595.83295449</v>
+        <v>201712086.2451129</v>
       </c>
       <c r="K41">
-        <v>15039784.4520351</v>
+        <v>194013219.4312528</v>
       </c>
       <c r="L41">
-        <v>4759919.46806754</v>
+        <v>61402961.13807127</v>
       </c>
       <c r="M41">
-        <v>219454358.5063266</v>
+        <v>2830961224.731613</v>
       </c>
       <c r="N41">
-        <v>85309950.39902771</v>
+        <v>1100498360.147457</v>
       </c>
       <c r="O41">
-        <v>548813653.2806008</v>
+        <v>7079696127.319751</v>
       </c>
       <c r="P41">
-        <v>845259626.6400487</v>
+        <v>10903849183.65663</v>
       </c>
       <c r="Q41">
-        <v>637973549.3899891</v>
+        <v>8229858787.13086</v>
       </c>
     </row>
     <row r="42">
@@ -11599,52 +11599,52 @@
         </is>
       </c>
       <c r="B42">
-        <v>118045196.1464588</v>
+        <v>1522783030.289318</v>
       </c>
       <c r="C42">
-        <v>2100355.32195764</v>
+        <v>27094583.65325356</v>
       </c>
       <c r="D42">
-        <v>121453897.1000887</v>
+        <v>1566755272.591145</v>
       </c>
       <c r="E42">
-        <v>6924268.507121691</v>
+        <v>89323063.74186981</v>
       </c>
       <c r="F42">
-        <v>54338642.73559266</v>
+        <v>700968491.2891454</v>
       </c>
       <c r="G42">
-        <v>184817163.6647607</v>
+        <v>2384141411.275413</v>
       </c>
       <c r="H42">
-        <v>168899665.6921781</v>
+        <v>2178805687.429097</v>
       </c>
       <c r="I42">
-        <v>43779650.36513062</v>
+        <v>564757489.7101849</v>
       </c>
       <c r="J42">
-        <v>15277106.65800659</v>
+        <v>197074675.888285</v>
       </c>
       <c r="K42">
-        <v>13792720.55954587</v>
+        <v>177926095.2181417</v>
       </c>
       <c r="L42">
-        <v>5887631.12224602</v>
+        <v>75950441.47697365</v>
       </c>
       <c r="M42">
-        <v>223522244.1728119</v>
+        <v>2883436949.829274</v>
       </c>
       <c r="N42">
-        <v>85277911.94596818</v>
+        <v>1100085064.10299</v>
       </c>
       <c r="O42">
-        <v>556436930.5158873</v>
+        <v>7178036403.654946</v>
       </c>
       <c r="P42">
-        <v>859299290.3271068</v>
+        <v>11084960845.21968</v>
       </c>
       <c r="Q42">
-        <v>650088551.1124337</v>
+        <v>8386142309.350394</v>
       </c>
     </row>
     <row r="43">
@@ -11654,52 +11654,52 @@
         </is>
       </c>
       <c r="B43">
-        <v>114330406.02468</v>
+        <v>1474862237.718371</v>
       </c>
       <c r="C43">
-        <v>2078923.86889499</v>
+        <v>26818117.90874537</v>
       </c>
       <c r="D43">
-        <v>126011986.9239318</v>
+        <v>1625554631.31872</v>
       </c>
       <c r="E43">
-        <v>6568026.30076395</v>
+        <v>84727539.27985495</v>
       </c>
       <c r="F43">
-        <v>55503097.70171221</v>
+        <v>715989960.3520875</v>
       </c>
       <c r="G43">
-        <v>190162034.7953029</v>
+        <v>2453090248.859408</v>
       </c>
       <c r="H43">
-        <v>169908064.3047049</v>
+        <v>2191814029.530694</v>
       </c>
       <c r="I43">
-        <v>46024660.65596671</v>
+        <v>593718122.4619706</v>
       </c>
       <c r="J43">
-        <v>14843924.16901571</v>
+        <v>191486621.7803026</v>
       </c>
       <c r="K43">
-        <v>12897662.35263471</v>
+        <v>166379844.3489878</v>
       </c>
       <c r="L43">
-        <v>7099699.4278555</v>
+        <v>91586122.61933595</v>
       </c>
       <c r="M43">
-        <v>231305940.2280366</v>
+        <v>2983846628.941672</v>
       </c>
       <c r="N43">
-        <v>85735052.0572792</v>
+        <v>1105982171.538902</v>
       </c>
       <c r="O43">
-        <v>567815003.1954932</v>
+        <v>7324813541.221863</v>
       </c>
       <c r="P43">
-        <v>872307444.0154762</v>
+        <v>11252766027.79964</v>
       </c>
       <c r="Q43">
-        <v>665142286.5056614</v>
+        <v>8580335495.923032</v>
       </c>
     </row>
     <row r="44">
@@ -11709,52 +11709,52 @@
         </is>
       </c>
       <c r="B44">
-        <v>112514740.9017548</v>
+        <v>1451440157.632637</v>
       </c>
       <c r="C44">
-        <v>1859693.99542457</v>
+        <v>23990052.54097695</v>
       </c>
       <c r="D44">
-        <v>132394416.6482952</v>
+        <v>1707887974.763008</v>
       </c>
       <c r="E44">
-        <v>6429676.75540098</v>
+        <v>82942830.14467265</v>
       </c>
       <c r="F44">
-        <v>56927076.89107473</v>
+        <v>734359291.8948641</v>
       </c>
       <c r="G44">
-        <v>197610864.2901955</v>
+        <v>2549180149.343522</v>
       </c>
       <c r="H44">
-        <v>170665583.2977157</v>
+        <v>2201586024.540533</v>
       </c>
       <c r="I44">
-        <v>46638604.90960732</v>
+        <v>601638003.3339344</v>
       </c>
       <c r="J44">
-        <v>14349545.84180682</v>
+        <v>185109141.359308</v>
       </c>
       <c r="K44">
-        <v>13179663.59918512</v>
+        <v>170017660.4294881</v>
       </c>
       <c r="L44">
-        <v>8059986.701129301</v>
+        <v>103973828.444568</v>
       </c>
       <c r="M44">
-        <v>237543805.8429666</v>
+        <v>3064315095.374269</v>
       </c>
       <c r="N44">
-        <v>85003355.4090547</v>
+        <v>1096543284.776806</v>
       </c>
       <c r="O44">
-        <v>575440545.6014656</v>
+        <v>7423183038.258906</v>
       </c>
       <c r="P44">
-        <v>885566150.7934159</v>
+        <v>11423803345.23507</v>
       </c>
       <c r="Q44">
-        <v>679988067.781477</v>
+        <v>8771846074.381054</v>
       </c>
     </row>
     <row r="45">
@@ -11764,52 +11764,52 @@
         </is>
       </c>
       <c r="B45">
-        <v>110931033.9294276</v>
+        <v>1431010337.689616</v>
       </c>
       <c r="C45">
-        <v>1565335.39477898</v>
+        <v>20192826.59264884</v>
       </c>
       <c r="D45">
-        <v>135899681.1588426</v>
+        <v>1753105886.949069</v>
       </c>
       <c r="E45">
-        <v>6199268.08714078</v>
+        <v>79970558.32411607</v>
       </c>
       <c r="F45">
-        <v>58303627.9557162</v>
+        <v>752116800.628739</v>
       </c>
       <c r="G45">
-        <v>201967912.5964785</v>
+        <v>2605386072.494573</v>
       </c>
       <c r="H45">
-        <v>171859458.049183</v>
+        <v>2216987008.834461</v>
       </c>
       <c r="I45">
-        <v>48180048.18184682</v>
+        <v>621522621.5458241</v>
       </c>
       <c r="J45">
-        <v>15100045.29375353</v>
+        <v>194790584.2894205</v>
       </c>
       <c r="K45">
-        <v>13439221.9891518</v>
+        <v>173365963.6600582</v>
       </c>
       <c r="L45">
-        <v>8566042.37414965</v>
+        <v>110501946.6265305</v>
       </c>
       <c r="M45">
-        <v>239521297.0699035</v>
+        <v>3089824732.201755</v>
       </c>
       <c r="N45">
-        <v>84864166.90661129</v>
+        <v>1094747753.095286</v>
       </c>
       <c r="O45">
-        <v>581530279.8645997</v>
+        <v>7501740610.253336</v>
       </c>
       <c r="P45">
-        <v>894429226.3905058</v>
+        <v>11538137020.43752</v>
       </c>
       <c r="Q45">
-        <v>690067983.1803172</v>
+        <v>8901876983.026093</v>
       </c>
     </row>
     <row r="46">
@@ -11819,52 +11819,52 @@
         </is>
       </c>
       <c r="B46">
-        <v>109189013.5770964</v>
+        <v>1408538275.144544</v>
       </c>
       <c r="C46">
-        <v>1562724.00892522</v>
+        <v>20159139.71513534</v>
       </c>
       <c r="D46">
-        <v>140259997.1231121</v>
+        <v>1809353962.888146</v>
       </c>
       <c r="E46">
-        <v>5778672.28486983</v>
+        <v>74544872.47482081</v>
       </c>
       <c r="F46">
-        <v>60318869.66003827</v>
+        <v>778113418.6144937</v>
       </c>
       <c r="G46">
-        <v>207920263.0769454</v>
+        <v>2682171393.692596</v>
       </c>
       <c r="H46">
-        <v>171693320.6547418</v>
+        <v>2214843836.446169</v>
       </c>
       <c r="I46">
-        <v>48813730.93405096</v>
+        <v>629697129.0492574</v>
       </c>
       <c r="J46">
-        <v>15321878.08012383</v>
+        <v>197652227.2335974</v>
       </c>
       <c r="K46">
-        <v>14131051.22077407</v>
+        <v>182290560.7479855</v>
       </c>
       <c r="L46">
-        <v>8040334.677491331</v>
+        <v>103720317.3396382</v>
       </c>
       <c r="M46">
-        <v>242966651.9002832</v>
+        <v>3134269809.513653</v>
       </c>
       <c r="N46">
-        <v>84339594.50703517</v>
+        <v>1087980769.140754</v>
       </c>
       <c r="O46">
-        <v>585306561.9745004</v>
+        <v>7550454649.471056</v>
       </c>
       <c r="P46">
-        <v>902415838.6285422</v>
+        <v>11641164318.3082</v>
       </c>
       <c r="Q46">
-        <v>700846895.8669192</v>
+        <v>9040924956.683258</v>
       </c>
     </row>
     <row r="47">
@@ -11874,52 +11874,52 @@
         </is>
       </c>
       <c r="B47">
-        <v>108778050.4849942</v>
+        <v>1403236851.256426</v>
       </c>
       <c r="C47">
-        <v>1497574.02509251</v>
+        <v>19318704.92369338</v>
       </c>
       <c r="D47">
-        <v>142025632.788865</v>
+        <v>1832130662.976359</v>
       </c>
       <c r="E47">
-        <v>5548155.977966189</v>
+        <v>71571212.11576384</v>
       </c>
       <c r="F47">
-        <v>63119850.45051857</v>
+        <v>814246070.8116896</v>
       </c>
       <c r="G47">
-        <v>212191213.2424423</v>
+        <v>2737266650.827506</v>
       </c>
       <c r="H47">
-        <v>171258206.9705544</v>
+        <v>2209230869.920152</v>
       </c>
       <c r="I47">
-        <v>47463140.73893731</v>
+        <v>612274515.5322913</v>
       </c>
       <c r="J47">
-        <v>16108686.43490673</v>
+        <v>207802055.0102968</v>
       </c>
       <c r="K47">
-        <v>14701882.80642715</v>
+        <v>189654288.2029102</v>
       </c>
       <c r="L47">
-        <v>7669434.07596168</v>
+        <v>98935699.57990567</v>
       </c>
       <c r="M47">
-        <v>244789999.6433815</v>
+        <v>3157790995.399621</v>
       </c>
       <c r="N47">
-        <v>83437258.11664303</v>
+        <v>1076340629.704695</v>
       </c>
       <c r="O47">
-        <v>585428608.7868118</v>
+        <v>7552029053.349873</v>
       </c>
       <c r="P47">
-        <v>906397872.5142484</v>
+        <v>11692532555.4338</v>
       </c>
       <c r="Q47">
-        <v>706513129.8366494</v>
+        <v>9114019374.892778</v>
       </c>
     </row>
     <row r="48">
@@ -11929,52 +11929,52 @@
         </is>
       </c>
       <c r="B48">
-        <v>105088759.984763</v>
+        <v>1355645003.803443</v>
       </c>
       <c r="C48">
-        <v>1685236.45744011</v>
+        <v>21739550.30097742</v>
       </c>
       <c r="D48">
-        <v>139961063.1148366</v>
+        <v>1805497714.181393</v>
       </c>
       <c r="E48">
-        <v>5849935.19966031</v>
+        <v>75464164.075618</v>
       </c>
       <c r="F48">
-        <v>62522486.29208908</v>
+        <v>806540073.1679492</v>
       </c>
       <c r="G48">
-        <v>210018721.0640261</v>
+        <v>2709241501.725937</v>
       </c>
       <c r="H48">
-        <v>168830099.0263767</v>
+        <v>2177908277.440259</v>
       </c>
       <c r="I48">
-        <v>46702465.91139103</v>
+        <v>602461810.2569444</v>
       </c>
       <c r="J48">
-        <v>16620568.09036647</v>
+        <v>214405328.3657275</v>
       </c>
       <c r="K48">
-        <v>15046340.08497226</v>
+        <v>194097787.0961422</v>
       </c>
       <c r="L48">
-        <v>7492074.414216541</v>
+        <v>96647759.94339338</v>
       </c>
       <c r="M48">
-        <v>246907272.0923196</v>
+        <v>3185103809.990922</v>
       </c>
       <c r="N48">
-        <v>82495061.61816111</v>
+        <v>1064186294.874278</v>
       </c>
       <c r="O48">
-        <v>584093881.2378037</v>
+        <v>7534811067.967668</v>
       </c>
       <c r="P48">
-        <v>899201362.2865928</v>
+        <v>11599697573.49705</v>
       </c>
       <c r="Q48">
-        <v>704125466.2694521</v>
+        <v>9083218514.875933</v>
       </c>
     </row>
     <row r="49">
@@ -11984,52 +11984,52 @@
         </is>
       </c>
       <c r="B49">
-        <v>101232233.0742725</v>
+        <v>1305895806.658115</v>
       </c>
       <c r="C49">
-        <v>1823381.57093886</v>
+        <v>23521622.26511129</v>
       </c>
       <c r="D49">
-        <v>138366017.424576</v>
+        <v>1784921624.77703</v>
       </c>
       <c r="E49">
-        <v>5968273.89187655</v>
+        <v>76990733.2052075</v>
       </c>
       <c r="F49">
-        <v>62722455.30576183</v>
+        <v>809119673.4443276</v>
       </c>
       <c r="G49">
-        <v>208880128.1931532</v>
+        <v>2694553653.691677</v>
       </c>
       <c r="H49">
-        <v>167562378.3046069</v>
+        <v>2161554680.129429</v>
       </c>
       <c r="I49">
-        <v>46928694.08071259</v>
+        <v>605380153.6411924</v>
       </c>
       <c r="J49">
-        <v>16406969.09450738</v>
+        <v>211649901.3191452</v>
       </c>
       <c r="K49">
-        <v>15863638.11379067</v>
+        <v>204640931.6678997</v>
       </c>
       <c r="L49">
-        <v>7481811.3575117</v>
+        <v>96515366.51190093</v>
       </c>
       <c r="M49">
-        <v>249372000.6116918</v>
+        <v>3216898807.890824</v>
       </c>
       <c r="N49">
-        <v>82112008.36370398</v>
+        <v>1059244907.891781</v>
       </c>
       <c r="O49">
-        <v>585727499.926525</v>
+        <v>7555884749.052173</v>
       </c>
       <c r="P49">
-        <v>895839861.1939508</v>
+        <v>11556334209.40197</v>
       </c>
       <c r="Q49">
-        <v>705013808.3984625</v>
+        <v>9094678128.340166</v>
       </c>
     </row>
     <row r="50">
@@ -12039,52 +12039,52 @@
         </is>
       </c>
       <c r="B50">
-        <v>96564880.25952157</v>
+        <v>1245686955.347828</v>
       </c>
       <c r="C50">
-        <v>1778532.56351978</v>
+        <v>22943070.06940516</v>
       </c>
       <c r="D50">
-        <v>135581883.2285733</v>
+        <v>1749006293.648596</v>
       </c>
       <c r="E50">
-        <v>5992061.13817651</v>
+        <v>77297588.68247698</v>
       </c>
       <c r="F50">
-        <v>62519223.61527222</v>
+        <v>806497984.6370118</v>
       </c>
       <c r="G50">
-        <v>205871700.5455418</v>
+        <v>2655744937.037489</v>
       </c>
       <c r="H50">
-        <v>169388265.3647152</v>
+        <v>2185108623.204825</v>
       </c>
       <c r="I50">
-        <v>46647542.68198633</v>
+        <v>601753300.5976237</v>
       </c>
       <c r="J50">
-        <v>17118270.66171902</v>
+        <v>220825691.5361754</v>
       </c>
       <c r="K50">
-        <v>15353561.87229379</v>
+        <v>198060948.1525899</v>
       </c>
       <c r="L50">
-        <v>7863807.27657432</v>
+        <v>101443113.8678087</v>
       </c>
       <c r="M50">
-        <v>250300117.7575739</v>
+        <v>3228871519.072703</v>
       </c>
       <c r="N50">
-        <v>81311555.93970537</v>
+        <v>1048919071.622199</v>
       </c>
       <c r="O50">
-        <v>587983121.5545678</v>
+        <v>7584982268.053925</v>
       </c>
       <c r="P50">
-        <v>890419702.3596313</v>
+        <v>11486414160.43924</v>
       </c>
       <c r="Q50">
-        <v>704679458.8838298</v>
+        <v>9090365019.601404</v>
       </c>
     </row>
     <row r="51">
@@ -12094,52 +12094,52 @@
         </is>
       </c>
       <c r="B51">
-        <v>91142905.83311483</v>
+        <v>1175743485.247181</v>
       </c>
       <c r="C51">
-        <v>1659178.24056388</v>
+        <v>21403399.30327405</v>
       </c>
       <c r="D51">
-        <v>135469732.2818689</v>
+        <v>1747559546.436109</v>
       </c>
       <c r="E51">
-        <v>5934509.49773185</v>
+        <v>76555172.52074087</v>
       </c>
       <c r="F51">
-        <v>60582080.95712794</v>
+        <v>781508844.3469505</v>
       </c>
       <c r="G51">
-        <v>203645500.9772926</v>
+        <v>2627026962.607075</v>
       </c>
       <c r="H51">
-        <v>170445107.531981</v>
+        <v>2198741887.162555</v>
       </c>
       <c r="I51">
-        <v>48078900.2179137</v>
+        <v>620217812.8110868</v>
       </c>
       <c r="J51">
-        <v>16722576.85564077</v>
+        <v>215721241.4377659</v>
       </c>
       <c r="K51">
-        <v>14473281.54721438</v>
+        <v>186705331.9590655</v>
       </c>
       <c r="L51">
-        <v>8148715.78863203</v>
+        <v>105118433.6733532</v>
       </c>
       <c r="M51">
-        <v>249410933.094195</v>
+        <v>3217401036.915116</v>
       </c>
       <c r="N51">
-        <v>81923746.02846102</v>
+        <v>1056816323.767147</v>
       </c>
       <c r="O51">
-        <v>589203261.0640379</v>
+        <v>7600722067.726089</v>
       </c>
       <c r="P51">
-        <v>883991667.8744454</v>
+        <v>11403492515.58035</v>
       </c>
       <c r="Q51">
-        <v>702776300.2242374</v>
+        <v>9065814272.892664</v>
       </c>
     </row>
     <row r="52">
@@ -12149,52 +12149,52 @@
         </is>
       </c>
       <c r="B52">
-        <v>90067055.03625967</v>
+        <v>1161865009.96775</v>
       </c>
       <c r="C52">
-        <v>1446959.05206259</v>
+        <v>18665771.77160741</v>
       </c>
       <c r="D52">
-        <v>136852902.4913732</v>
+        <v>1765402442.138714</v>
       </c>
       <c r="E52">
-        <v>5757945.63857217</v>
+        <v>74277498.737581</v>
       </c>
       <c r="F52">
-        <v>61904281.79411806</v>
+        <v>798565235.144123</v>
       </c>
       <c r="G52">
-        <v>205962088.976126</v>
+        <v>2656910947.792025</v>
       </c>
       <c r="H52">
-        <v>175792293.807584</v>
+        <v>2267720590.117834</v>
       </c>
       <c r="I52">
-        <v>50153612.74064702</v>
+        <v>646981604.3543465</v>
       </c>
       <c r="J52">
-        <v>16301575.22069297</v>
+        <v>210290320.3469393</v>
       </c>
       <c r="K52">
-        <v>13913689.67233853</v>
+        <v>179486596.773167</v>
       </c>
       <c r="L52">
-        <v>8303873.35282829</v>
+        <v>107119966.2514849</v>
       </c>
       <c r="M52">
-        <v>248821345.073581</v>
+        <v>3209795351.449195</v>
       </c>
       <c r="N52">
-        <v>83958168.29215103</v>
+        <v>1083060370.968748</v>
       </c>
       <c r="O52">
-        <v>597244558.1598228</v>
+        <v>7704454800.261715</v>
       </c>
       <c r="P52">
-        <v>893273702.1722085</v>
+        <v>11523230758.02149</v>
       </c>
       <c r="Q52">
-        <v>710944605.4909694</v>
+        <v>9171185410.833506</v>
       </c>
     </row>
     <row r="53">
@@ -12204,52 +12204,52 @@
         </is>
       </c>
       <c r="B53">
-        <v>89545485.64662015</v>
+        <v>1155136764.8414</v>
       </c>
       <c r="C53">
-        <v>1433761.68329197</v>
+        <v>18495525.71446642</v>
       </c>
       <c r="D53">
-        <v>140046494.3858328</v>
+        <v>1806599777.577244</v>
       </c>
       <c r="E53">
-        <v>5750695.30987495</v>
+        <v>74183969.49738686</v>
       </c>
       <c r="F53">
-        <v>61989119.40326769</v>
+        <v>799659640.3021532</v>
       </c>
       <c r="G53">
-        <v>209220070.7822675</v>
+        <v>2698938913.09125</v>
       </c>
       <c r="H53">
-        <v>178892393.9561905</v>
+        <v>2307711882.034858</v>
       </c>
       <c r="I53">
-        <v>52735402.32220194</v>
+        <v>680286689.956405</v>
       </c>
       <c r="J53">
-        <v>16486667.91601975</v>
+        <v>212678016.1166548</v>
       </c>
       <c r="K53">
-        <v>13162875.64112071</v>
+        <v>169801095.7704571</v>
       </c>
       <c r="L53">
-        <v>8643358.144868171</v>
+        <v>111499320.0687994</v>
       </c>
       <c r="M53">
-        <v>250041431.3837397</v>
+        <v>3225534464.850243</v>
       </c>
       <c r="N53">
-        <v>84654684.99089414</v>
+        <v>1092045436.382535</v>
       </c>
       <c r="O53">
-        <v>604616814.3550349</v>
+        <v>7799556905.179951</v>
       </c>
       <c r="P53">
-        <v>903382370.7839227</v>
+        <v>11653632583.1126</v>
       </c>
       <c r="Q53">
-        <v>720538842.0015402</v>
+        <v>9294951061.819868</v>
       </c>
     </row>
     <row r="54">
@@ -12259,52 +12259,52 @@
         </is>
       </c>
       <c r="B54">
-        <v>89016402.76416537</v>
+        <v>1148311595.657733</v>
       </c>
       <c r="C54">
-        <v>1223474.69848089</v>
+        <v>15782823.61040348</v>
       </c>
       <c r="D54">
-        <v>141580501.4137744</v>
+        <v>1826388468.23769</v>
       </c>
       <c r="E54">
-        <v>5806274.18716969</v>
+        <v>74900937.014489</v>
       </c>
       <c r="F54">
-        <v>60766308.18048114</v>
+        <v>783885375.5282068</v>
       </c>
       <c r="G54">
-        <v>209376558.4799061</v>
+        <v>2700957604.39079</v>
       </c>
       <c r="H54">
-        <v>180343713.1645305</v>
+        <v>2326433899.822443</v>
       </c>
       <c r="I54">
-        <v>54412304.53604599</v>
+        <v>701918728.5149933</v>
       </c>
       <c r="J54">
-        <v>16089772.11005716</v>
+        <v>207558060.2197374</v>
       </c>
       <c r="K54">
-        <v>13558602.23756825</v>
+        <v>174905968.8646304</v>
       </c>
       <c r="L54">
-        <v>8430691.65868159</v>
+        <v>108755922.3969925</v>
       </c>
       <c r="M54">
-        <v>251787235.371408</v>
+        <v>3248055336.291163</v>
       </c>
       <c r="N54">
-        <v>87200755.68586349</v>
+        <v>1124889748.347639</v>
       </c>
       <c r="O54">
-        <v>611823074.764155</v>
+        <v>7892517664.4576</v>
       </c>
       <c r="P54">
-        <v>910216036.0082265</v>
+        <v>11741786864.50612</v>
       </c>
       <c r="Q54">
-        <v>725568185.8995161</v>
+        <v>9359829598.103758</v>
       </c>
     </row>
     <row r="55">
@@ -12314,52 +12314,52 @@
         </is>
       </c>
       <c r="B55">
-        <v>89835430.07681568</v>
+        <v>1158877047.990922</v>
       </c>
       <c r="C55">
-        <v>1010311.70708011</v>
+        <v>13033021.02133342</v>
       </c>
       <c r="D55">
-        <v>142577271.4657385</v>
+        <v>1839246801.908027</v>
       </c>
       <c r="E55">
-        <v>5454418.9891126</v>
+        <v>70362004.95955254</v>
       </c>
       <c r="F55">
-        <v>60363578.50741995</v>
+        <v>778690162.7457174</v>
       </c>
       <c r="G55">
-        <v>209405580.6693512</v>
+        <v>2701331990.63463</v>
       </c>
       <c r="H55">
-        <v>181372289.8358208</v>
+        <v>2339702538.882089</v>
       </c>
       <c r="I55">
-        <v>55227790.05758968</v>
+        <v>712438491.7429069</v>
       </c>
       <c r="J55">
-        <v>15842418.1612474</v>
+        <v>204367194.2800914</v>
       </c>
       <c r="K55">
-        <v>14684188.47144348</v>
+        <v>189426031.2816209</v>
       </c>
       <c r="L55">
-        <v>8094039.48977271</v>
+        <v>104413109.418068</v>
       </c>
       <c r="M55">
-        <v>256882254.2118583</v>
+        <v>3313781079.332972</v>
       </c>
       <c r="N55">
-        <v>89119909.2411176</v>
+        <v>1149646829.210417</v>
       </c>
       <c r="O55">
-        <v>621222889.46885</v>
+        <v>8013775274.148166</v>
       </c>
       <c r="P55">
-        <v>920463900.2150168</v>
+        <v>11873984312.77372</v>
       </c>
       <c r="Q55">
-        <v>733414521.407311</v>
+        <v>9461047326.154312</v>
       </c>
     </row>
     <row r="56">
@@ -12369,52 +12369,52 @@
         </is>
       </c>
       <c r="B56">
-        <v>89488631.70902786</v>
+        <v>1154403349.046459</v>
       </c>
       <c r="C56">
-        <v>961124.44983533</v>
+        <v>12398505.40287576</v>
       </c>
       <c r="D56">
-        <v>144050023.0377032</v>
+        <v>1858245297.186371</v>
       </c>
       <c r="E56">
-        <v>5235577.19217297</v>
+        <v>67538945.77903131</v>
       </c>
       <c r="F56">
-        <v>60056138.42349985</v>
+        <v>774724185.6631482</v>
       </c>
       <c r="G56">
-        <v>210302863.1032113</v>
+        <v>2712906934.031425</v>
       </c>
       <c r="H56">
-        <v>179620286.1782488</v>
+        <v>2317101691.69941</v>
       </c>
       <c r="I56">
-        <v>57493965.54716993</v>
+        <v>741672155.5584922</v>
       </c>
       <c r="J56">
-        <v>15770729.38246432</v>
+        <v>203442409.0337897</v>
       </c>
       <c r="K56">
-        <v>15956191.46991158</v>
+        <v>205834869.9618594</v>
       </c>
       <c r="L56">
-        <v>7626958.7049732</v>
+        <v>98387767.29415429</v>
       </c>
       <c r="M56">
-        <v>257178740.2812075</v>
+        <v>3317605749.627577</v>
       </c>
       <c r="N56">
-        <v>89508211.73355839</v>
+        <v>1154655931.362903</v>
       </c>
       <c r="O56">
-        <v>623155083.2975338</v>
+        <v>8038700574.538186</v>
       </c>
       <c r="P56">
-        <v>922946578.1097729</v>
+        <v>11906010857.61607</v>
       </c>
       <c r="Q56">
-        <v>736322775.9622136</v>
+        <v>9498563809.912556</v>
       </c>
     </row>
   </sheetData>

--- a/Dados/table_PROD_RS_1_aux.xlsx
+++ b/Dados/table_PROD_RS_1_aux.xlsx
@@ -6598,7 +6598,7 @@
         <v>99360772.54939012</v>
       </c>
       <c r="F5">
-        <v>842111128.761479</v>
+        <v>842111128.7614791</v>
       </c>
       <c r="G5">
         <v>3032567313.513539</v>
@@ -6619,7 +6619,7 @@
         <v>76577088.19425139</v>
       </c>
       <c r="M5">
-        <v>2785418846.685489</v>
+        <v>2785418846.68549</v>
       </c>
       <c r="N5">
         <v>1045556110.093815</v>
@@ -6653,7 +6653,7 @@
         <v>99131011.66766337</v>
       </c>
       <c r="F6">
-        <v>868843654.9654176</v>
+        <v>868843654.9654177</v>
       </c>
       <c r="G6">
         <v>3061977205.093699</v>
@@ -6686,7 +6686,7 @@
         <v>11853674875.59094</v>
       </c>
       <c r="Q6">
-        <v>9003521289.134356</v>
+        <v>9003521289.134357</v>
       </c>
     </row>
     <row r="7">
@@ -6699,7 +6699,7 @@
         <v>1658932688.062088</v>
       </c>
       <c r="C7">
-        <v>37848816.61730761</v>
+        <v>37848816.61730762</v>
       </c>
       <c r="D7">
         <v>2057246226.913576</v>
@@ -6729,16 +6729,16 @@
         <v>95852797.3759474</v>
       </c>
       <c r="M7">
-        <v>2711886648.947676</v>
+        <v>2711886648.947677</v>
       </c>
       <c r="N7">
         <v>1108046732.626275</v>
       </c>
       <c r="O7">
-        <v>7167357462.36818</v>
+        <v>7167357462.368181</v>
       </c>
       <c r="P7">
-        <v>11886633411.75453</v>
+        <v>11886633411.75454</v>
       </c>
       <c r="Q7">
         <v>9023801193.690222</v>
@@ -6766,13 +6766,13 @@
         <v>882669911.4834847</v>
       </c>
       <c r="G8">
-        <v>3083753165.325918</v>
+        <v>3083753165.325917</v>
       </c>
       <c r="H8">
-        <v>2305385437.71089</v>
+        <v>2305385437.710889</v>
       </c>
       <c r="I8">
-        <v>693797918.4158005</v>
+        <v>693797918.4158003</v>
       </c>
       <c r="J8">
         <v>131057745.2198845</v>
@@ -6796,7 +6796,7 @@
         <v>11982547319.77362</v>
       </c>
       <c r="Q8">
-        <v>9108035224.72278</v>
+        <v>9108035224.722778</v>
       </c>
     </row>
     <row r="9">
@@ -6830,7 +6830,7 @@
         <v>683914093.1382109</v>
       </c>
       <c r="J9">
-        <v>130070473.6883858</v>
+        <v>130070473.6883857</v>
       </c>
       <c r="K9">
         <v>166812913.6431664</v>
@@ -6876,7 +6876,7 @@
         <v>890167338.5229517</v>
       </c>
       <c r="G10">
-        <v>3082137114.066375</v>
+        <v>3082137114.066376</v>
       </c>
       <c r="H10">
         <v>2400917541.761965</v>
@@ -6900,7 +6900,7 @@
         <v>1122633976.508075</v>
       </c>
       <c r="O10">
-        <v>7418735302.317218</v>
+        <v>7418735302.317219</v>
       </c>
       <c r="P10">
         <v>12077428421.97582</v>
@@ -6925,10 +6925,10 @@
         <v>2042217370.837914</v>
       </c>
       <c r="E11">
-        <v>92059645.28986047</v>
+        <v>92059645.28986046</v>
       </c>
       <c r="F11">
-        <v>885312401.5859705</v>
+        <v>885312401.5859704</v>
       </c>
       <c r="G11">
         <v>3051249375.821754</v>
@@ -7071,7 +7071,7 @@
         <v>11954134244.79719</v>
       </c>
       <c r="Q13">
-        <v>9290500916.646912</v>
+        <v>9290500916.646914</v>
       </c>
     </row>
     <row r="14">
@@ -7093,13 +7093,13 @@
         <v>92278858.73779356</v>
       </c>
       <c r="F14">
-        <v>861416909.681933</v>
+        <v>861416909.6819332</v>
       </c>
       <c r="G14">
         <v>2969298785.395252</v>
       </c>
       <c r="H14">
-        <v>2326441547.8376</v>
+        <v>2326441547.837601</v>
       </c>
       <c r="I14">
         <v>611208786.1218305</v>
@@ -7111,7 +7111,7 @@
         <v>158533964.1658722</v>
       </c>
       <c r="L14">
-        <v>83066741.57560527</v>
+        <v>83066741.57560529</v>
       </c>
       <c r="M14">
         <v>3062810538.785179</v>
@@ -7120,13 +7120,13 @@
         <v>1112666911.926231</v>
       </c>
       <c r="O14">
-        <v>7497802065.283683</v>
+        <v>7497802065.283682</v>
       </c>
       <c r="P14">
         <v>11954682926.16833</v>
       </c>
       <c r="Q14">
-        <v>9271367197.177095</v>
+        <v>9271367197.177097</v>
       </c>
     </row>
     <row r="15">
@@ -7145,7 +7145,7 @@
         <v>1947442205.245013</v>
       </c>
       <c r="E15">
-        <v>99520228.34862396</v>
+        <v>99520228.34862395</v>
       </c>
       <c r="F15">
         <v>851415083.5379437</v>
@@ -7163,13 +7163,13 @@
         <v>152216174.5319983</v>
       </c>
       <c r="K15">
-        <v>160782142.7109168</v>
+        <v>160782142.7109169</v>
       </c>
       <c r="L15">
         <v>86634971.79304528</v>
       </c>
       <c r="M15">
-        <v>3048760366.50465</v>
+        <v>3048760366.504649</v>
       </c>
       <c r="N15">
         <v>1111458967.748359</v>
@@ -7178,7 +7178,7 @@
         <v>7510182421.89635</v>
       </c>
       <c r="P15">
-        <v>11922041419.20381</v>
+        <v>11922041419.2038</v>
       </c>
       <c r="Q15">
         <v>9244309039.838089</v>
@@ -7206,13 +7206,13 @@
         <v>837072001.1616951</v>
       </c>
       <c r="G16">
-        <v>2906961896.946962</v>
+        <v>2906961896.946961</v>
       </c>
       <c r="H16">
         <v>2340188568.563882</v>
       </c>
       <c r="I16">
-        <v>625572148.1784012</v>
+        <v>625572148.1784014</v>
       </c>
       <c r="J16">
         <v>156919299.4431634</v>
@@ -7221,7 +7221,7 @@
         <v>156371730.5189398</v>
       </c>
       <c r="L16">
-        <v>83035461.88091721</v>
+        <v>83035461.88091719</v>
       </c>
       <c r="M16">
         <v>3016342471.562</v>
@@ -7236,7 +7236,7 @@
         <v>11863989492.6813</v>
       </c>
       <c r="Q16">
-        <v>9202356115.21335</v>
+        <v>9202356115.213348</v>
       </c>
     </row>
     <row r="17">
@@ -7258,7 +7258,7 @@
         <v>113529398.3849992</v>
       </c>
       <c r="F17">
-        <v>825784554.478267</v>
+        <v>825784554.4782671</v>
       </c>
       <c r="G17">
         <v>2901340246.125573</v>
@@ -7285,7 +7285,7 @@
         <v>1123691472.280933</v>
       </c>
       <c r="O17">
-        <v>7494503640.933693</v>
+        <v>7494503640.933694</v>
       </c>
       <c r="P17">
         <v>11850992798.72868</v>
@@ -7322,7 +7322,7 @@
         <v>2316883878.936318</v>
       </c>
       <c r="I18">
-        <v>655940716.4900165</v>
+        <v>655940716.4900163</v>
       </c>
       <c r="J18">
         <v>153506178.5510876</v>
@@ -7340,13 +7340,13 @@
         <v>1123489018.94451</v>
       </c>
       <c r="O18">
-        <v>7451071344.772676</v>
+        <v>7451071344.772675</v>
       </c>
       <c r="P18">
         <v>11812554031.16871</v>
       </c>
       <c r="Q18">
-        <v>9152604192.515982</v>
+        <v>9152604192.515984</v>
       </c>
     </row>
     <row r="19">
@@ -7368,7 +7368,7 @@
         <v>113799785.1335913</v>
       </c>
       <c r="F19">
-        <v>858653827.5255642</v>
+        <v>858653827.5255641</v>
       </c>
       <c r="G19">
         <v>2899140528.279636</v>
@@ -7386,7 +7386,7 @@
         <v>157817280.3007053</v>
       </c>
       <c r="L19">
-        <v>73300273.35245231</v>
+        <v>73300273.35245229</v>
       </c>
       <c r="M19">
         <v>2951376495.717516</v>
@@ -7423,7 +7423,7 @@
         <v>109331219.6575412</v>
       </c>
       <c r="F20">
-        <v>875016417.6609222</v>
+        <v>875016417.6609221</v>
       </c>
       <c r="G20">
         <v>2883524092.725325</v>
@@ -7432,7 +7432,7 @@
         <v>2266029430.099063</v>
       </c>
       <c r="I20">
-        <v>643942634.940055</v>
+        <v>643942634.9400551</v>
       </c>
       <c r="J20">
         <v>139475392.5130858</v>
@@ -7441,7 +7441,7 @@
         <v>166014858.8879741</v>
       </c>
       <c r="L20">
-        <v>74653217.93761085</v>
+        <v>74653217.93761086</v>
       </c>
       <c r="M20">
         <v>2972587045.065854</v>
@@ -7450,7 +7450,7 @@
         <v>1155537196.834804</v>
       </c>
       <c r="O20">
-        <v>7418239776.278446</v>
+        <v>7418239776.278447</v>
       </c>
       <c r="P20">
         <v>11778704910.73469</v>
@@ -7469,10 +7469,10 @@
         <v>1493622097.608162</v>
       </c>
       <c r="C21">
-        <v>33113164.38484176</v>
+        <v>33113164.38484175</v>
       </c>
       <c r="D21">
-        <v>1840665176.608772</v>
+        <v>1840665176.608773</v>
       </c>
       <c r="E21">
         <v>107288656.6366937</v>
@@ -7505,10 +7505,10 @@
         <v>1140830346.135111</v>
       </c>
       <c r="O21">
-        <v>7369066459.213658</v>
+        <v>7369066459.213657</v>
       </c>
       <c r="P21">
-        <v>11718119242.73445</v>
+        <v>11718119242.73444</v>
       </c>
       <c r="Q21">
         <v>9003079493.951563</v>
@@ -7533,7 +7533,7 @@
         <v>104614754.0117106</v>
       </c>
       <c r="F22">
-        <v>854372721.4779269</v>
+        <v>854372721.4779267</v>
       </c>
       <c r="G22">
         <v>2805224534.697367</v>
@@ -7548,13 +7548,13 @@
         <v>133708997.5449358</v>
       </c>
       <c r="K22">
-        <v>172950568.7366012</v>
+        <v>172950568.7366013</v>
       </c>
       <c r="L22">
         <v>82619085.98825663</v>
       </c>
       <c r="M22">
-        <v>3010836982.251305</v>
+        <v>3010836982.251306</v>
       </c>
       <c r="N22">
         <v>1132533638.900146</v>
@@ -7566,7 +7566,7 @@
         <v>11657134997.75057</v>
       </c>
       <c r="Q22">
-        <v>8965901076.506212</v>
+        <v>8965901076.506214</v>
       </c>
     </row>
     <row r="23">
@@ -7576,7 +7576,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>1475092057.818109</v>
+        <v>1475092057.81811</v>
       </c>
       <c r="C23">
         <v>30160914.59884974</v>
@@ -7606,10 +7606,10 @@
         <v>167534592.9290599</v>
       </c>
       <c r="L23">
-        <v>90466985.54097606</v>
+        <v>90466985.54097608</v>
       </c>
       <c r="M23">
-        <v>3034347224.711196</v>
+        <v>3034347224.711197</v>
       </c>
       <c r="N23">
         <v>1123577852.555613</v>
@@ -7621,7 +7621,7 @@
         <v>11648456237.02843</v>
       </c>
       <c r="Q23">
-        <v>8959319341.113731</v>
+        <v>8959319341.113733</v>
       </c>
     </row>
     <row r="24">
@@ -7698,7 +7698,7 @@
         <v>121735140.6015855</v>
       </c>
       <c r="F25">
-        <v>783374433.7984706</v>
+        <v>783374433.7984705</v>
       </c>
       <c r="G25">
         <v>2702375961.318317</v>
@@ -7716,7 +7716,7 @@
         <v>159336832.1575324</v>
       </c>
       <c r="L25">
-        <v>90722502.20396827</v>
+        <v>90722502.20396829</v>
       </c>
       <c r="M25">
         <v>3048000861.556219</v>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>1425398642.636166</v>
+        <v>1425398642.636167</v>
       </c>
       <c r="C26">
         <v>30383105.5700039</v>
@@ -7753,10 +7753,10 @@
         <v>124853598.3177445</v>
       </c>
       <c r="F26">
-        <v>794731938.9193097</v>
+        <v>794731938.9193096</v>
       </c>
       <c r="G26">
-        <v>2708541372.181555</v>
+        <v>2708541372.181556</v>
       </c>
       <c r="H26">
         <v>2255958231.129111</v>
@@ -7780,7 +7780,7 @@
         <v>1125607120.336928</v>
       </c>
       <c r="O26">
-        <v>7440912488.169258</v>
+        <v>7440912488.169259</v>
       </c>
       <c r="P26">
         <v>11574852502.98698</v>
@@ -7799,7 +7799,7 @@
         <v>1401291200.258347</v>
       </c>
       <c r="C27">
-        <v>30056508.4945992</v>
+        <v>30056508.49459921</v>
       </c>
       <c r="D27">
         <v>1773594294.685737</v>
@@ -7817,7 +7817,7 @@
         <v>2232378969.806181</v>
       </c>
       <c r="I27">
-        <v>647302620.6592041</v>
+        <v>647302620.6592042</v>
       </c>
       <c r="J27">
         <v>138729373.8088899</v>
@@ -7866,7 +7866,7 @@
         <v>824553093.7196828</v>
       </c>
       <c r="G28">
-        <v>2750420536.737604</v>
+        <v>2750420536.737603</v>
       </c>
       <c r="H28">
         <v>2213506335.361175</v>
@@ -7881,7 +7881,7 @@
         <v>147742357.2500233</v>
       </c>
       <c r="L28">
-        <v>83237556.67551699</v>
+        <v>83237556.67551698</v>
       </c>
       <c r="M28">
         <v>2996616472.142084</v>
@@ -7896,7 +7896,7 @@
         <v>11490477486.04233</v>
       </c>
       <c r="Q28">
-        <v>8896471580.83363</v>
+        <v>8896471580.833632</v>
       </c>
     </row>
     <row r="29">
@@ -7927,7 +7927,7 @@
         <v>2206559713.800075</v>
       </c>
       <c r="I29">
-        <v>637205426.4579076</v>
+        <v>637205426.4579077</v>
       </c>
       <c r="J29">
         <v>150463665.3407424</v>
@@ -7979,10 +7979,10 @@
         <v>2735799412.814496</v>
       </c>
       <c r="H30">
-        <v>2203754774.064193</v>
+        <v>2203754774.064194</v>
       </c>
       <c r="I30">
-        <v>631837249.5808512</v>
+        <v>631837249.5808513</v>
       </c>
       <c r="J30">
         <v>162263647.5794727</v>
@@ -8000,7 +8000,7 @@
         <v>1148531378.339578</v>
       </c>
       <c r="O30">
-        <v>7462636802.017945</v>
+        <v>7462636802.017946</v>
       </c>
       <c r="P30">
         <v>11585769110.69029</v>
@@ -8019,7 +8019,7 @@
         <v>1407255678.011788</v>
       </c>
       <c r="C31">
-        <v>19001299.24188246</v>
+        <v>19001299.24188245</v>
       </c>
       <c r="D31">
         <v>1756067648.175431</v>
@@ -8055,10 +8055,10 @@
         <v>1165599539.696611</v>
       </c>
       <c r="O31">
-        <v>7562402718.930623</v>
+        <v>7562402718.930624</v>
       </c>
       <c r="P31">
-        <v>11687535637.18364</v>
+        <v>11687535637.18363</v>
       </c>
       <c r="Q31">
         <v>9027654795.782614</v>
@@ -8101,13 +8101,13 @@
         <v>136707353.0454389</v>
       </c>
       <c r="L32">
-        <v>83508592.73825446</v>
+        <v>83508592.73825447</v>
       </c>
       <c r="M32">
         <v>3137071937.178809</v>
       </c>
       <c r="N32">
-        <v>1177226451.548046</v>
+        <v>1177226451.548047</v>
       </c>
       <c r="O32">
         <v>7639917983.240028</v>
@@ -8132,7 +8132,7 @@
         <v>24390351.95840202</v>
       </c>
       <c r="D33">
-        <v>1772337957.271766</v>
+        <v>1772337957.271767</v>
       </c>
       <c r="E33">
         <v>99212934.07965195</v>
@@ -8156,7 +8156,7 @@
         <v>132897974.4236218</v>
       </c>
       <c r="L33">
-        <v>83102246.06125215</v>
+        <v>83102246.06125216</v>
       </c>
       <c r="M33">
         <v>3145519131.992598</v>
@@ -8193,7 +8193,7 @@
         <v>88347839.947199</v>
       </c>
       <c r="F34">
-        <v>815896463.1607894</v>
+        <v>815896463.1607895</v>
       </c>
       <c r="G34">
         <v>2697723211.549889</v>
@@ -8211,7 +8211,7 @@
         <v>127611516.1774373</v>
       </c>
       <c r="L34">
-        <v>78407558.82428822</v>
+        <v>78407558.8242882</v>
       </c>
       <c r="M34">
         <v>3128387583.157789</v>
@@ -8226,7 +8226,7 @@
         <v>11767391005.21087</v>
       </c>
       <c r="Q34">
-        <v>9129856847.45056</v>
+        <v>9129856847.450558</v>
       </c>
     </row>
     <row r="35">
@@ -8272,7 +8272,7 @@
         <v>3064690015.358222</v>
       </c>
       <c r="N35">
-        <v>1190336533.564002</v>
+        <v>1190336533.564003</v>
       </c>
       <c r="O35">
         <v>7529385972.885364</v>
@@ -8300,7 +8300,7 @@
         <v>1670371028.546649</v>
       </c>
       <c r="E36">
-        <v>85481072.7152645</v>
+        <v>85481072.71526448</v>
       </c>
       <c r="F36">
         <v>751181425.1338376</v>
@@ -8312,7 +8312,7 @@
         <v>2098406334.988716</v>
       </c>
       <c r="I36">
-        <v>671691201.2828456</v>
+        <v>671691201.2828457</v>
       </c>
       <c r="J36">
         <v>184251792.7267878</v>
@@ -8324,7 +8324,7 @@
         <v>69049163.36114307</v>
       </c>
       <c r="M36">
-        <v>2971378165.692813</v>
+        <v>2971378165.692814</v>
       </c>
       <c r="N36">
         <v>1162931309.45031</v>
@@ -8336,7 +8336,7 @@
         <v>11191102650.76443</v>
       </c>
       <c r="Q36">
-        <v>8581538522.991062</v>
+        <v>8581538522.99106</v>
       </c>
     </row>
     <row r="37">
@@ -8382,16 +8382,16 @@
         <v>2875455624.628149</v>
       </c>
       <c r="N37">
-        <v>1149688739.882843</v>
+        <v>1149688739.882844</v>
       </c>
       <c r="O37">
-        <v>7107408973.544337</v>
+        <v>7107408973.544338</v>
       </c>
       <c r="P37">
         <v>10950520634.92537</v>
       </c>
       <c r="Q37">
-        <v>8312268942.459921</v>
+        <v>8312268942.45992</v>
       </c>
     </row>
     <row r="38">
@@ -8446,7 +8446,7 @@
         <v>10813622866.27892</v>
       </c>
       <c r="Q38">
-        <v>8173635221.503926</v>
+        <v>8173635221.503925</v>
       </c>
     </row>
     <row r="39">
@@ -8495,13 +8495,13 @@
         <v>1123440423.948768</v>
       </c>
       <c r="O39">
-        <v>7096725904.368171</v>
+        <v>7096725904.368172</v>
       </c>
       <c r="P39">
-        <v>10955002883.5172</v>
+        <v>10955002883.51721</v>
       </c>
       <c r="Q39">
-        <v>8260895444.502716</v>
+        <v>8260895444.502717</v>
       </c>
     </row>
     <row r="40">
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="B40">
-        <v>1553725722.401619</v>
+        <v>1553725722.401618</v>
       </c>
       <c r="C40">
         <v>22575434.36800833</v>
@@ -8526,7 +8526,7 @@
         <v>695212507.9848387</v>
       </c>
       <c r="G40">
-        <v>2361397622.331707</v>
+        <v>2361397622.331706</v>
       </c>
       <c r="H40">
         <v>2191152134.276417</v>
@@ -8541,7 +8541,7 @@
         <v>208692211.9085523</v>
       </c>
       <c r="L40">
-        <v>55978755.04993405</v>
+        <v>55978755.04993406</v>
       </c>
       <c r="M40">
         <v>2906012404.135952</v>
@@ -8596,7 +8596,7 @@
         <v>199925376.1998916</v>
       </c>
       <c r="L41">
-        <v>63100086.2098577</v>
+        <v>63100086.20985771</v>
       </c>
       <c r="M41">
         <v>2968134286.36657</v>
@@ -8605,7 +8605,7 @@
         <v>1158643864.774287</v>
       </c>
       <c r="O41">
-        <v>7380445335.537069</v>
+        <v>7380445335.53707</v>
       </c>
       <c r="P41">
         <v>11367605160.57302</v>
@@ -8630,10 +8630,10 @@
         <v>1643255318.154449</v>
       </c>
       <c r="E42">
-        <v>92826509.76540585</v>
+        <v>92826509.76540586</v>
       </c>
       <c r="F42">
-        <v>749238022.1843729</v>
+        <v>749238022.1843728</v>
       </c>
       <c r="G42">
         <v>2512861523.872002</v>
@@ -8660,7 +8660,7 @@
         <v>1163215500.455252</v>
       </c>
       <c r="O42">
-        <v>7482870803.925387</v>
+        <v>7482870803.925388</v>
       </c>
       <c r="P42">
         <v>11569123833.02765</v>
@@ -8679,7 +8679,7 @@
         <v>1538555615.321137</v>
       </c>
       <c r="C43">
-        <v>27102429.39729235</v>
+        <v>27102429.39729236</v>
       </c>
       <c r="D43">
         <v>1698081240.510358</v>
@@ -8697,7 +8697,7 @@
         <v>2264879513.622609</v>
       </c>
       <c r="I43">
-        <v>625037300.9394944</v>
+        <v>625037300.9394945</v>
       </c>
       <c r="J43">
         <v>196689981.2365513</v>
@@ -8715,13 +8715,13 @@
         <v>1168053028.142322</v>
       </c>
       <c r="O43">
-        <v>7627726758.072421</v>
+        <v>7627726758.07242</v>
       </c>
       <c r="P43">
         <v>11738857982.68494</v>
       </c>
       <c r="Q43">
-        <v>8937545120.21945</v>
+        <v>8937545120.219452</v>
       </c>
     </row>
     <row r="44">
@@ -8743,7 +8743,7 @@
         <v>88462284.83223167</v>
       </c>
       <c r="F44">
-        <v>779827171.0526906</v>
+        <v>779827171.0526907</v>
       </c>
       <c r="G44">
         <v>2673296416.894528</v>
@@ -8819,19 +8819,19 @@
         <v>114836582.9537242</v>
       </c>
       <c r="M45">
-        <v>3220065878.917754</v>
+        <v>3220065878.917755</v>
       </c>
       <c r="N45">
         <v>1167962565.694499</v>
       </c>
       <c r="O45">
-        <v>7839944448.308271</v>
+        <v>7839944448.30827</v>
       </c>
       <c r="P45">
         <v>12087784441.77275</v>
       </c>
       <c r="Q45">
-        <v>9310508630.962744</v>
+        <v>9310508630.962746</v>
       </c>
     </row>
     <row r="46">
@@ -8844,16 +8844,16 @@
         <v>1466507306.800771</v>
       </c>
       <c r="C46">
-        <v>20704975.7680623</v>
+        <v>20704975.76806231</v>
       </c>
       <c r="D46">
-        <v>1904784755.475993</v>
+        <v>1904784755.475992</v>
       </c>
       <c r="E46">
-        <v>81293279.11672963</v>
+        <v>81293279.11672965</v>
       </c>
       <c r="F46">
-        <v>821217312.7647098</v>
+        <v>821217312.7647097</v>
       </c>
       <c r="G46">
         <v>2828000323.125494</v>
@@ -8868,7 +8868,7 @@
         <v>205951983.1080327</v>
       </c>
       <c r="K46">
-        <v>189316876.74664</v>
+        <v>189316876.7466401</v>
       </c>
       <c r="L46">
         <v>108331168.6018779</v>
@@ -8935,7 +8935,7 @@
         <v>1149796323.203795</v>
       </c>
       <c r="O47">
-        <v>7880437688.101175</v>
+        <v>7880437688.101174</v>
       </c>
       <c r="P47">
         <v>12218400356.14344</v>
@@ -8954,16 +8954,16 @@
         <v>1412687700.868596</v>
       </c>
       <c r="C48">
-        <v>21923968.36301083</v>
+        <v>21923968.36301084</v>
       </c>
       <c r="D48">
         <v>1910328138.010891</v>
       </c>
       <c r="E48">
-        <v>80878462.56122838</v>
+        <v>80878462.56122839</v>
       </c>
       <c r="F48">
-        <v>853796820.4995731</v>
+        <v>853796820.4995732</v>
       </c>
       <c r="G48">
         <v>2866927389.434704</v>
@@ -8990,7 +8990,7 @@
         <v>1139404705.815642</v>
       </c>
       <c r="O48">
-        <v>7874699278.9684</v>
+        <v>7874699278.968401</v>
       </c>
       <c r="P48">
         <v>12154314369.2717</v>
@@ -9012,7 +9012,7 @@
         <v>23732968.26127441</v>
       </c>
       <c r="D49">
-        <v>1890854111.892396</v>
+        <v>1890854111.892395</v>
       </c>
       <c r="E49">
         <v>82132974.02358925</v>
@@ -9045,7 +9045,7 @@
         <v>1133712059.451271</v>
       </c>
       <c r="O49">
-        <v>7902032222.398874</v>
+        <v>7902032222.398873</v>
       </c>
       <c r="P49">
         <v>12129590003.30516</v>
@@ -9064,16 +9064,16 @@
         <v>1318341904.3321</v>
       </c>
       <c r="C50">
-        <v>23306102.81297825</v>
+        <v>23306102.81297824</v>
       </c>
       <c r="D50">
-        <v>1871897286.039242</v>
+        <v>1871897286.039241</v>
       </c>
       <c r="E50">
-        <v>81202257.64913015</v>
+        <v>81202257.64913017</v>
       </c>
       <c r="F50">
-        <v>862232743.2547419</v>
+        <v>862232743.2547418</v>
       </c>
       <c r="G50">
         <v>2838638389.756092</v>
@@ -9106,7 +9106,7 @@
         <v>12128349611.10027</v>
       </c>
       <c r="Q50">
-        <v>9568026080.149105</v>
+        <v>9568026080.149107</v>
       </c>
     </row>
     <row r="51">
@@ -9125,7 +9125,7 @@
         <v>1873541195.875222</v>
       </c>
       <c r="E51">
-        <v>80728220.58874328</v>
+        <v>80728220.58874327</v>
       </c>
       <c r="F51">
         <v>847321605.490865</v>
@@ -9155,7 +9155,7 @@
         <v>1146663029.059399</v>
       </c>
       <c r="O51">
-        <v>8021157061.938584</v>
+        <v>8021157061.938585</v>
       </c>
       <c r="P51">
         <v>12111459432.95164</v>
@@ -9183,16 +9183,16 @@
         <v>78129876.13160437</v>
       </c>
       <c r="F52">
-        <v>855287904.3632486</v>
+        <v>855287904.3632485</v>
       </c>
       <c r="G52">
-        <v>2839445898.591901</v>
+        <v>2839445898.591902</v>
       </c>
       <c r="H52">
         <v>2351639088.977147</v>
       </c>
       <c r="I52">
-        <v>674130127.829845</v>
+        <v>674130127.8298448</v>
       </c>
       <c r="J52">
         <v>217811321.9870729</v>
@@ -9204,19 +9204,19 @@
         <v>111888249.445068</v>
       </c>
       <c r="M52">
-        <v>3399057541.987335</v>
+        <v>3399057541.987334</v>
       </c>
       <c r="N52">
         <v>1170068195.997775</v>
       </c>
       <c r="O52">
-        <v>8110960972.462741</v>
+        <v>8110960972.462742</v>
       </c>
       <c r="P52">
         <v>12194707962.47702</v>
       </c>
       <c r="Q52">
-        <v>9668450425.611799</v>
+        <v>9668450425.611797</v>
       </c>
     </row>
     <row r="53">
@@ -9226,7 +9226,7 @@
         </is>
       </c>
       <c r="B53">
-        <v>1228166417.509794</v>
+        <v>1228166417.509795</v>
       </c>
       <c r="C53">
         <v>19383940.86119448</v>
@@ -9247,7 +9247,7 @@
         <v>2386734864.354422</v>
       </c>
       <c r="I53">
-        <v>710801397.1656162</v>
+        <v>710801397.1656163</v>
       </c>
       <c r="J53">
         <v>219322344.9994514</v>
@@ -9265,7 +9265,7 @@
         <v>1173742825.006025</v>
       </c>
       <c r="O53">
-        <v>8188545050.395305</v>
+        <v>8188545050.395304</v>
       </c>
       <c r="P53">
         <v>12284220121.67467</v>
@@ -9299,7 +9299,7 @@
         <v>2858954657.445683</v>
       </c>
       <c r="H54">
-        <v>2403254766.248175</v>
+        <v>2403254766.248176</v>
       </c>
       <c r="I54">
         <v>740829610.9991121</v>
@@ -9308,7 +9308,7 @@
         <v>215440195.5901141</v>
       </c>
       <c r="K54">
-        <v>183432042.5858553</v>
+        <v>183432042.5858552</v>
       </c>
       <c r="L54">
         <v>111876217.45872</v>
@@ -9320,7 +9320,7 @@
         <v>1195207463.645716</v>
       </c>
       <c r="O54">
-        <v>8265460123.126508</v>
+        <v>8265460123.126509</v>
       </c>
       <c r="P54">
         <v>12338885083.00449</v>
@@ -9345,7 +9345,7 @@
         <v>1929070651.05566</v>
       </c>
       <c r="E55">
-        <v>72490210.15356022</v>
+        <v>72490210.15356021</v>
       </c>
       <c r="F55">
         <v>821371507.6067193</v>
@@ -9357,7 +9357,7 @@
         <v>2411673207.033216</v>
       </c>
       <c r="I55">
-        <v>748596406.7815045</v>
+        <v>748596406.7815044</v>
       </c>
       <c r="J55">
         <v>213224026.3549303</v>
@@ -9375,7 +9375,7 @@
         <v>1217671149.673286</v>
       </c>
       <c r="O55">
-        <v>8347432822.219435</v>
+        <v>8347432822.219434</v>
       </c>
       <c r="P55">
         <v>12389824025.02605</v>
@@ -9409,7 +9409,7 @@
         <v>2841749986.28512</v>
       </c>
       <c r="H56">
-        <v>2391885379.313776</v>
+        <v>2391885379.313775</v>
       </c>
       <c r="I56">
         <v>774862177.3974456</v>
@@ -9436,7 +9436,7 @@
         <v>12401192752.65973</v>
       </c>
       <c r="Q56">
-        <v>9882280052.593939</v>
+        <v>9882280052.593941</v>
       </c>
     </row>
   </sheetData>
@@ -9573,7 +9573,7 @@
         <v>1937149029.261456</v>
       </c>
       <c r="E5">
-        <v>94909020.64065097</v>
+        <v>94909020.64065099</v>
       </c>
       <c r="F5">
         <v>789020440.4237388</v>
@@ -9658,13 +9658,13 @@
         <v>986556124.321003</v>
       </c>
       <c r="O6">
-        <v>6730454992.580909</v>
+        <v>6730454992.58091</v>
       </c>
       <c r="P6">
         <v>11176086144.75254</v>
       </c>
       <c r="Q6">
-        <v>8524060017.359204</v>
+        <v>8524060017.359203</v>
       </c>
     </row>
     <row r="7">
@@ -9677,7 +9677,7 @@
         <v>1562471341.719969</v>
       </c>
       <c r="C7">
-        <v>35136749.41034343</v>
+        <v>35136749.41034342</v>
       </c>
       <c r="D7">
         <v>1937489722.691234</v>
@@ -9692,7 +9692,7 @@
         <v>2868410953.169657</v>
       </c>
       <c r="H7">
-        <v>2177042556.614185</v>
+        <v>2177042556.614184</v>
       </c>
       <c r="I7">
         <v>653041105.0977619</v>
@@ -9707,7 +9707,7 @@
         <v>90203210.06318516</v>
       </c>
       <c r="M7">
-        <v>2572765562.761545</v>
+        <v>2572765562.761546</v>
       </c>
       <c r="N7">
         <v>1024428413.868392</v>
@@ -9716,7 +9716,7 @@
         <v>6804061794.360339</v>
       </c>
       <c r="P7">
-        <v>11234944089.24996</v>
+        <v>11234944089.24997</v>
       </c>
       <c r="Q7">
         <v>8557841123.598419</v>
@@ -9732,7 +9732,7 @@
         <v>1542060333.82329</v>
       </c>
       <c r="C8">
-        <v>33880716.81737347</v>
+        <v>33880716.81737346</v>
       </c>
       <c r="D8">
         <v>1936237836.574864</v>
@@ -9747,13 +9747,13 @@
         <v>2887691961.943667</v>
       </c>
       <c r="H8">
-        <v>2216022005.585667</v>
+        <v>2216022005.585666</v>
       </c>
       <c r="I8">
-        <v>661748720.2090988</v>
+        <v>661748720.2090987</v>
       </c>
       <c r="J8">
-        <v>124178498.5440719</v>
+        <v>124178498.544072</v>
       </c>
       <c r="K8">
         <v>160851505.2798958</v>
@@ -9768,7 +9768,7 @@
         <v>1044337517.81712</v>
       </c>
       <c r="O8">
-        <v>6898148044.517373</v>
+        <v>6898148044.517372</v>
       </c>
       <c r="P8">
         <v>11327900340.28433</v>
@@ -9796,7 +9796,7 @@
         <v>98610594.35067379</v>
       </c>
       <c r="F9">
-        <v>828626635.0314194</v>
+        <v>828626635.0314193</v>
       </c>
       <c r="G9">
         <v>2898005127.850576</v>
@@ -9805,7 +9805,7 @@
         <v>2273952729.754072</v>
       </c>
       <c r="I9">
-        <v>655062973.2302107</v>
+        <v>655062973.2302105</v>
       </c>
       <c r="J9">
         <v>124305246.2428731</v>
@@ -9829,7 +9829,7 @@
         <v>11451366830.31851</v>
       </c>
       <c r="Q9">
-        <v>8756014455.843273</v>
+        <v>8756014455.843275</v>
       </c>
     </row>
     <row r="10">
@@ -9869,10 +9869,10 @@
         <v>157144246.5357549</v>
       </c>
       <c r="L10">
-        <v>96894481.8296804</v>
+        <v>96894481.82968041</v>
       </c>
       <c r="M10">
-        <v>2709098919.281715</v>
+        <v>2709098919.281714</v>
       </c>
       <c r="N10">
         <v>1050762561.941942</v>
@@ -9894,7 +9894,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>1461091762.775192</v>
+        <v>1461091762.775191</v>
       </c>
       <c r="C11">
         <v>28174025.13551896</v>
@@ -9906,7 +9906,7 @@
         <v>87938836.50767793</v>
       </c>
       <c r="F11">
-        <v>831808086.6734463</v>
+        <v>831808086.6734462</v>
       </c>
       <c r="G11">
         <v>2867598428.45173</v>
@@ -9924,7 +9924,7 @@
         <v>150714324.7161883</v>
       </c>
       <c r="L11">
-        <v>89793574.24766831</v>
+        <v>89793574.24766833</v>
       </c>
       <c r="M11">
         <v>2802463029.533333</v>
@@ -9967,7 +9967,7 @@
         <v>2837934212.37792</v>
       </c>
       <c r="H12">
-        <v>2303248996.212588</v>
+        <v>2303248996.212587</v>
       </c>
       <c r="I12">
         <v>608438306.2271649</v>
@@ -9985,7 +9985,7 @@
         <v>2849577184.427641</v>
       </c>
       <c r="N12">
-        <v>1018535079.523347</v>
+        <v>1018535079.523346</v>
       </c>
       <c r="O12">
         <v>7146820816.750468</v>
@@ -10034,16 +10034,16 @@
         <v>148696124.9611558</v>
       </c>
       <c r="L13">
-        <v>82676424.75307852</v>
+        <v>82676424.75307854</v>
       </c>
       <c r="M13">
-        <v>2885956520.555508</v>
+        <v>2885956520.555509</v>
       </c>
       <c r="N13">
         <v>1016968142.956372</v>
       </c>
       <c r="O13">
-        <v>7127177602.491365</v>
+        <v>7127177602.491366</v>
       </c>
       <c r="P13">
         <v>11337627434.08062</v>
@@ -10092,7 +10092,7 @@
         <v>82366703.87759489</v>
       </c>
       <c r="M14">
-        <v>2927149642.981146</v>
+        <v>2927149642.981147</v>
       </c>
       <c r="N14">
         <v>1026875681.378475</v>
@@ -10135,7 +10135,7 @@
         <v>2256877086.283231</v>
       </c>
       <c r="I15">
-        <v>598187621.5374997</v>
+        <v>598187621.5374998</v>
       </c>
       <c r="J15">
         <v>147684113.2860059</v>
@@ -10144,7 +10144,7 @@
         <v>153973309.090525</v>
       </c>
       <c r="L15">
-        <v>86006854.19499983</v>
+        <v>86006854.19499984</v>
       </c>
       <c r="M15">
         <v>2916295792.50747</v>
@@ -10190,13 +10190,13 @@
         <v>2263924308.494076</v>
       </c>
       <c r="I16">
-        <v>599208712.2659117</v>
+        <v>599208712.2659116</v>
       </c>
       <c r="J16">
         <v>150847514.9142585</v>
       </c>
       <c r="K16">
-        <v>148739505.0354246</v>
+        <v>148739505.0354245</v>
       </c>
       <c r="L16">
         <v>81248028.34950697</v>
@@ -10227,7 +10227,7 @@
         <v>1370521772.961607</v>
       </c>
       <c r="C17">
-        <v>37732874.53948223</v>
+        <v>37732874.53948224</v>
       </c>
       <c r="D17">
         <v>1809673160.009313</v>
@@ -10242,25 +10242,25 @@
         <v>2721271188.907864</v>
       </c>
       <c r="H17">
-        <v>2266165255.646842</v>
+        <v>2266165255.646843</v>
       </c>
       <c r="I17">
         <v>608214790.6601781</v>
       </c>
       <c r="J17">
-        <v>157633015.9798804</v>
+        <v>157633015.9798803</v>
       </c>
       <c r="K17">
-        <v>148935378.9127745</v>
+        <v>148935378.9127746</v>
       </c>
       <c r="L17">
-        <v>76087421.95076819</v>
+        <v>76087421.95076817</v>
       </c>
       <c r="M17">
         <v>2864268865.310942</v>
       </c>
       <c r="N17">
-        <v>1043662184.979834</v>
+        <v>1043662184.979833</v>
       </c>
       <c r="O17">
         <v>7164966913.441221</v>
@@ -10346,10 +10346,10 @@
         <v>109206102.4187586</v>
       </c>
       <c r="F19">
-        <v>802023033.5053588</v>
+        <v>802023033.5053587</v>
       </c>
       <c r="G19">
-        <v>2734996447.064914</v>
+        <v>2734996447.064915</v>
       </c>
       <c r="H19">
         <v>2194898850.812572</v>
@@ -10367,19 +10367,19 @@
         <v>68102617.19538192</v>
       </c>
       <c r="M19">
-        <v>2832522620.419976</v>
+        <v>2832522620.419975</v>
       </c>
       <c r="N19">
         <v>1067016969.223425</v>
       </c>
       <c r="O19">
-        <v>7073154334.484014</v>
+        <v>7073154334.484013</v>
       </c>
       <c r="P19">
         <v>11206040377.62258</v>
       </c>
       <c r="Q19">
-        <v>8673031195.130121</v>
+        <v>8673031195.130119</v>
       </c>
     </row>
     <row r="20">
@@ -10401,7 +10401,7 @@
         <v>105405893.5143872</v>
       </c>
       <c r="F20">
-        <v>822076141.1914791</v>
+        <v>822076141.191479</v>
       </c>
       <c r="G20">
         <v>2728428757.806439</v>
@@ -10416,7 +10416,7 @@
         <v>134888383.9512558</v>
       </c>
       <c r="K20">
-        <v>154481858.0085402</v>
+        <v>154481858.0085403</v>
       </c>
       <c r="L20">
         <v>70402559.01149797</v>
@@ -10434,7 +10434,7 @@
         <v>11221604962.34947</v>
       </c>
       <c r="Q20">
-        <v>8652014246.294201</v>
+        <v>8652014246.294203</v>
       </c>
     </row>
     <row r="21">
@@ -10444,13 +10444,13 @@
         </is>
       </c>
       <c r="B21">
-        <v>1439152757.010034</v>
+        <v>1439152757.010035</v>
       </c>
       <c r="C21">
         <v>30939885.97937073</v>
       </c>
       <c r="D21">
-        <v>1747469443.364244</v>
+        <v>1747469443.364243</v>
       </c>
       <c r="E21">
         <v>102796343.2045579</v>
@@ -10471,7 +10471,7 @@
         <v>123172415.1818584</v>
       </c>
       <c r="K21">
-        <v>159710808.2849971</v>
+        <v>159710808.284997</v>
       </c>
       <c r="L21">
         <v>77078122.9135906</v>
@@ -10489,7 +10489,7 @@
         <v>11153415052.39113</v>
       </c>
       <c r="Q21">
-        <v>8575151030.994443</v>
+        <v>8575151030.994442</v>
       </c>
     </row>
     <row r="22">
@@ -10514,7 +10514,7 @@
         <v>802493932.0873369</v>
       </c>
       <c r="G22">
-        <v>2659845172.129354</v>
+        <v>2659845172.129353</v>
       </c>
       <c r="H22">
         <v>2146507958.12969</v>
@@ -10544,7 +10544,7 @@
         <v>11105701249.90813</v>
       </c>
       <c r="Q22">
-        <v>8553352811.47715</v>
+        <v>8553352811.477151</v>
       </c>
     </row>
     <row r="23">
@@ -10572,10 +10572,10 @@
         <v>2592068390.139036</v>
       </c>
       <c r="H23">
-        <v>2159230319.355775</v>
+        <v>2159230319.355776</v>
       </c>
       <c r="I23">
-        <v>589961058.4902734</v>
+        <v>589961058.4902732</v>
       </c>
       <c r="J23">
         <v>126708963.5613839</v>
@@ -10593,7 +10593,7 @@
         <v>1037364611.149186</v>
       </c>
       <c r="O23">
-        <v>7040327488.539773</v>
+        <v>7040327488.539772</v>
       </c>
       <c r="P23">
         <v>11039910684.34896</v>
@@ -10612,7 +10612,7 @@
         <v>1405642502.257177</v>
       </c>
       <c r="C24">
-        <v>24655957.8105862</v>
+        <v>24655957.81058619</v>
       </c>
       <c r="D24">
         <v>1689311871.339432</v>
@@ -10654,7 +10654,7 @@
         <v>11022408999.81225</v>
       </c>
       <c r="Q24">
-        <v>8504450171.012513</v>
+        <v>8504450171.012512</v>
       </c>
     </row>
     <row r="25">
@@ -10685,7 +10685,7 @@
         <v>2162924722.189374</v>
       </c>
       <c r="I25">
-        <v>617016211.7860646</v>
+        <v>617016211.7860647</v>
       </c>
       <c r="J25">
         <v>128426467.7443375</v>
@@ -10703,7 +10703,7 @@
         <v>1035188988.875927</v>
       </c>
       <c r="O25">
-        <v>7078951265.906757</v>
+        <v>7078951265.906758</v>
       </c>
       <c r="P25">
         <v>10999906034.47343</v>
@@ -10722,7 +10722,7 @@
         <v>1353522549.906337</v>
       </c>
       <c r="C26">
-        <v>29339726.24456175</v>
+        <v>29339726.24456174</v>
       </c>
       <c r="D26">
         <v>1650586146.218303</v>
@@ -10743,7 +10743,7 @@
         <v>622266095.43365</v>
       </c>
       <c r="J26">
-        <v>128351611.2128967</v>
+        <v>128351611.2128968</v>
       </c>
       <c r="K26">
         <v>142849173.8748506</v>
@@ -10777,7 +10777,7 @@
         <v>1338719710.753291</v>
       </c>
       <c r="C27">
-        <v>28949295.96114744</v>
+        <v>28949295.96114743</v>
       </c>
       <c r="D27">
         <v>1674093952.308203</v>
@@ -10792,7 +10792,7 @@
         <v>2576644814.683671</v>
       </c>
       <c r="H27">
-        <v>2149456462.767514</v>
+        <v>2149456462.767515</v>
       </c>
       <c r="I27">
         <v>616057427.4021981</v>
@@ -10859,7 +10859,7 @@
         <v>138658292.1357452</v>
       </c>
       <c r="L28">
-        <v>76243334.37692191</v>
+        <v>76243334.37692189</v>
       </c>
       <c r="M28">
         <v>2866888594.708129</v>
@@ -10890,7 +10890,7 @@
         <v>22075698.79194208</v>
       </c>
       <c r="D29">
-        <v>1679129084.779475</v>
+        <v>1679129084.779476</v>
       </c>
       <c r="E29">
         <v>118948352.0595987</v>
@@ -10914,10 +10914,10 @@
         <v>133196663.6420356</v>
       </c>
       <c r="L29">
-        <v>80923096.01680647</v>
+        <v>80923096.01680645</v>
       </c>
       <c r="M29">
-        <v>2900752441.138544</v>
+        <v>2900752441.138545</v>
       </c>
       <c r="N29">
         <v>1055545778.382182</v>
@@ -10929,7 +10929,7 @@
         <v>10945686515.81198</v>
       </c>
       <c r="Q29">
-        <v>8500084164.240288</v>
+        <v>8500084164.240287</v>
       </c>
     </row>
     <row r="30">
@@ -10957,7 +10957,7 @@
         <v>2583103821.50093</v>
       </c>
       <c r="H30">
-        <v>2109979969.808817</v>
+        <v>2109979969.808816</v>
       </c>
       <c r="I30">
         <v>607830809.3470219</v>
@@ -11027,13 +11027,13 @@
         <v>83603949.26037699</v>
       </c>
       <c r="M31">
-        <v>2985793003.480009</v>
+        <v>2985793003.480008</v>
       </c>
       <c r="N31">
-        <v>1081486765.287845</v>
+        <v>1081486765.287844</v>
       </c>
       <c r="O31">
-        <v>7198974271.103934</v>
+        <v>7198974271.103933</v>
       </c>
       <c r="P31">
         <v>11105725633.00116</v>
@@ -11061,7 +11061,7 @@
         <v>108034847.8534234</v>
       </c>
       <c r="F32">
-        <v>763767134.1155298</v>
+        <v>763767134.1155299</v>
       </c>
       <c r="G32">
         <v>2562411921.57837</v>
@@ -11088,7 +11088,7 @@
         <v>1100286682.362217</v>
       </c>
       <c r="O32">
-        <v>7303399136.988545</v>
+        <v>7303399136.988546</v>
       </c>
       <c r="P32">
         <v>11208833374.32189</v>
@@ -11131,10 +11131,10 @@
         <v>178395443.8116641</v>
       </c>
       <c r="K33">
-        <v>127066864.2094099</v>
+        <v>127066864.20941</v>
       </c>
       <c r="L33">
-        <v>80149072.5011079</v>
+        <v>80149072.50110789</v>
       </c>
       <c r="M33">
         <v>3011847320.186256</v>
@@ -11149,7 +11149,7 @@
         <v>11262971476.8176</v>
       </c>
       <c r="Q33">
-        <v>8762815624.413473</v>
+        <v>8762815624.413471</v>
       </c>
     </row>
     <row r="34">
@@ -11162,25 +11162,25 @@
         <v>1289992654.990526</v>
       </c>
       <c r="C34">
-        <v>23441672.39486201</v>
+        <v>23441672.394862</v>
       </c>
       <c r="D34">
         <v>1665557899.767694</v>
       </c>
       <c r="E34">
-        <v>84881371.7644165</v>
+        <v>84881371.76441649</v>
       </c>
       <c r="F34">
-        <v>750071043.5420797</v>
+        <v>750071043.5420796</v>
       </c>
       <c r="G34">
-        <v>2523951987.469051</v>
+        <v>2523951987.469052</v>
       </c>
       <c r="H34">
         <v>2167727548.220243</v>
       </c>
       <c r="I34">
-        <v>688021431.4341673</v>
+        <v>688021431.4341671</v>
       </c>
       <c r="J34">
         <v>177650614.9544928</v>
@@ -11189,7 +11189,7 @@
         <v>120419044.8867294</v>
       </c>
       <c r="L34">
-        <v>72926104.8621598</v>
+        <v>72926104.86215979</v>
       </c>
       <c r="M34">
         <v>2945551566.469209</v>
@@ -11204,7 +11204,7 @@
         <v>11085327624.43173</v>
       </c>
       <c r="Q34">
-        <v>8623322193.433893</v>
+        <v>8623322193.433891</v>
       </c>
     </row>
     <row r="35">
@@ -11226,7 +11226,7 @@
         <v>81196056.3538467</v>
       </c>
       <c r="F35">
-        <v>688286589.1409719</v>
+        <v>688286589.1409718</v>
       </c>
       <c r="G35">
         <v>2351545839.486589</v>
@@ -11259,7 +11259,7 @@
         <v>10435354103.11479</v>
       </c>
       <c r="Q35">
-        <v>8045684860.351694</v>
+        <v>8045684860.351692</v>
       </c>
     </row>
     <row r="36">
@@ -11281,7 +11281,7 @@
         <v>78385905.17275414</v>
       </c>
       <c r="F36">
-        <v>648403755.5883492</v>
+        <v>648403755.5883491</v>
       </c>
       <c r="G36">
         <v>2237051126.748913</v>
@@ -11293,7 +11293,7 @@
         <v>602321587.1584252</v>
       </c>
       <c r="J36">
-        <v>171790812.1831079</v>
+        <v>171790812.1831078</v>
       </c>
       <c r="K36">
         <v>121536729.4896697</v>
@@ -11305,13 +11305,13 @@
         <v>2591483156.727175</v>
       </c>
       <c r="N36">
-        <v>997858053.8679069</v>
+        <v>997858053.867907</v>
       </c>
       <c r="O36">
         <v>6449276427.897529</v>
       </c>
       <c r="P36">
-        <v>9985566236.000418</v>
+        <v>9985566236.000416</v>
       </c>
       <c r="Q36">
         <v>7626647573.790332</v>
@@ -11327,7 +11327,7 @@
         <v>1359507140.351265</v>
       </c>
       <c r="C37">
-        <v>13476508.35338262</v>
+        <v>13476508.35338261</v>
       </c>
       <c r="D37">
         <v>1412680876.001791</v>
@@ -11336,7 +11336,7 @@
         <v>84666498.19325231</v>
       </c>
       <c r="F37">
-        <v>613810627.9379523</v>
+        <v>613810627.9379524</v>
       </c>
       <c r="G37">
         <v>2124634510.486378</v>
@@ -11348,7 +11348,7 @@
         <v>567009163.1355623</v>
       </c>
       <c r="J37">
-        <v>175383498.2871279</v>
+        <v>175383498.287128</v>
       </c>
       <c r="K37">
         <v>141379655.4529789</v>
@@ -11382,7 +11382,7 @@
         <v>1400755696.042918</v>
       </c>
       <c r="C38">
-        <v>14143592.43467718</v>
+        <v>14143592.43467717</v>
       </c>
       <c r="D38">
         <v>1394574199.838001</v>
@@ -11391,7 +11391,7 @@
         <v>89738910.64810051</v>
       </c>
       <c r="F38">
-        <v>584486287.5805593</v>
+        <v>584486287.5805591</v>
       </c>
       <c r="G38">
         <v>2082942990.501337</v>
@@ -11415,7 +11415,7 @@
         <v>2487602320.422307</v>
       </c>
       <c r="N38">
-        <v>983260473.4898823</v>
+        <v>983260473.4898822</v>
       </c>
       <c r="O38">
         <v>6270904884.713104</v>
@@ -11424,7 +11424,7 @@
         <v>9754603571.25736</v>
       </c>
       <c r="Q38">
-        <v>7320189098.550233</v>
+        <v>7320189098.550232</v>
       </c>
     </row>
     <row r="39">
@@ -11440,7 +11440,7 @@
         <v>17046954.19338853</v>
       </c>
       <c r="D39">
-        <v>1448255476.776696</v>
+        <v>1448255476.776697</v>
       </c>
       <c r="E39">
         <v>92635455.58151492</v>
@@ -11458,7 +11458,7 @@
         <v>537646067.9572381</v>
       </c>
       <c r="J39">
-        <v>198000547.230348</v>
+        <v>198000547.2303479</v>
       </c>
       <c r="K39">
         <v>197668530.501948</v>
@@ -11470,7 +11470,7 @@
         <v>2621041437.967065</v>
       </c>
       <c r="N39">
-        <v>1032341725.795266</v>
+        <v>1032341725.795265</v>
       </c>
       <c r="O39">
         <v>6639105577.82825</v>
@@ -11510,7 +11510,7 @@
         <v>2114794696.769099</v>
       </c>
       <c r="I40">
-        <v>550953499.7421014</v>
+        <v>550953499.7421013</v>
       </c>
       <c r="J40">
         <v>205002655.5827617</v>
@@ -11519,13 +11519,13 @@
         <v>200781665.5879009</v>
       </c>
       <c r="L40">
-        <v>54181365.03208194</v>
+        <v>54181365.03208193</v>
       </c>
       <c r="M40">
         <v>2742761571.324274</v>
       </c>
       <c r="N40">
-        <v>1074592947.695</v>
+        <v>1074592947.694999</v>
       </c>
       <c r="O40">
         <v>6943068401.733218</v>
@@ -11534,7 +11534,7 @@
         <v>10687976721.32083</v>
       </c>
       <c r="Q40">
-        <v>8046545568.30024</v>
+        <v>8046545568.300239</v>
       </c>
     </row>
     <row r="41">
@@ -11550,7 +11550,7 @@
         <v>25747883.80786069</v>
       </c>
       <c r="D41">
-        <v>1524973795.767022</v>
+        <v>1524973795.767023</v>
       </c>
       <c r="E41">
         <v>87703387.61685225</v>
@@ -11583,13 +11583,13 @@
         <v>1100498360.147457</v>
       </c>
       <c r="O41">
-        <v>7079696127.319751</v>
+        <v>7079696127.31975</v>
       </c>
       <c r="P41">
         <v>10903849183.65663</v>
       </c>
       <c r="Q41">
-        <v>8229858787.13086</v>
+        <v>8229858787.130859</v>
       </c>
     </row>
     <row r="42">
@@ -11614,13 +11614,13 @@
         <v>700968491.2891454</v>
       </c>
       <c r="G42">
-        <v>2384141411.275413</v>
+        <v>2384141411.275414</v>
       </c>
       <c r="H42">
         <v>2178805687.429097</v>
       </c>
       <c r="I42">
-        <v>564757489.7101849</v>
+        <v>564757489.7101851</v>
       </c>
       <c r="J42">
         <v>197074675.888285</v>
@@ -11644,7 +11644,7 @@
         <v>11084960845.21968</v>
       </c>
       <c r="Q42">
-        <v>8386142309.350394</v>
+        <v>8386142309.350395</v>
       </c>
     </row>
     <row r="43">
@@ -11672,7 +11672,7 @@
         <v>2453090248.859408</v>
       </c>
       <c r="H43">
-        <v>2191814029.530694</v>
+        <v>2191814029.530693</v>
       </c>
       <c r="I43">
         <v>593718122.4619706</v>
@@ -11687,19 +11687,19 @@
         <v>91586122.61933595</v>
       </c>
       <c r="M43">
-        <v>2983846628.941672</v>
+        <v>2983846628.941671</v>
       </c>
       <c r="N43">
         <v>1105982171.538902</v>
       </c>
       <c r="O43">
-        <v>7324813541.221863</v>
+        <v>7324813541.221864</v>
       </c>
       <c r="P43">
         <v>11252766027.79964</v>
       </c>
       <c r="Q43">
-        <v>8580335495.923032</v>
+        <v>8580335495.923033</v>
       </c>
     </row>
     <row r="44">
@@ -11745,7 +11745,7 @@
         <v>3064315095.374269</v>
       </c>
       <c r="N44">
-        <v>1096543284.776806</v>
+        <v>1096543284.776805</v>
       </c>
       <c r="O44">
         <v>7423183038.258906</v>
@@ -11797,7 +11797,7 @@
         <v>110501946.6265305</v>
       </c>
       <c r="M45">
-        <v>3089824732.201755</v>
+        <v>3089824732.201756</v>
       </c>
       <c r="N45">
         <v>1094747753.095286</v>
@@ -11809,7 +11809,7 @@
         <v>11538137020.43752</v>
       </c>
       <c r="Q45">
-        <v>8901876983.026093</v>
+        <v>8901876983.026091</v>
       </c>
     </row>
     <row r="46">
@@ -11858,7 +11858,7 @@
         <v>1087980769.140754</v>
       </c>
       <c r="O46">
-        <v>7550454649.471056</v>
+        <v>7550454649.471055</v>
       </c>
       <c r="P46">
         <v>11641164318.3082</v>
@@ -11904,7 +11904,7 @@
         <v>189654288.2029102</v>
       </c>
       <c r="L47">
-        <v>98935699.57990567</v>
+        <v>98935699.57990569</v>
       </c>
       <c r="M47">
         <v>3157790995.399621</v>
@@ -11913,13 +11913,13 @@
         <v>1076340629.704695</v>
       </c>
       <c r="O47">
-        <v>7552029053.349873</v>
+        <v>7552029053.349874</v>
       </c>
       <c r="P47">
-        <v>11692532555.4338</v>
+        <v>11692532555.43381</v>
       </c>
       <c r="Q47">
-        <v>9114019374.892778</v>
+        <v>9114019374.892776</v>
       </c>
     </row>
     <row r="48">
@@ -11950,7 +11950,7 @@
         <v>2177908277.440259</v>
       </c>
       <c r="I48">
-        <v>602461810.2569444</v>
+        <v>602461810.2569443</v>
       </c>
       <c r="J48">
         <v>214405328.3657275</v>
@@ -11962,7 +11962,7 @@
         <v>96647759.94339338</v>
       </c>
       <c r="M48">
-        <v>3185103809.990922</v>
+        <v>3185103809.990923</v>
       </c>
       <c r="N48">
         <v>1064186294.874278</v>
@@ -11987,7 +11987,7 @@
         <v>1305895806.658115</v>
       </c>
       <c r="C49">
-        <v>23521622.26511129</v>
+        <v>23521622.2651113</v>
       </c>
       <c r="D49">
         <v>1784921624.77703</v>
@@ -12051,13 +12051,13 @@
         <v>77297588.68247698</v>
       </c>
       <c r="F50">
-        <v>806497984.6370118</v>
+        <v>806497984.6370116</v>
       </c>
       <c r="G50">
-        <v>2655744937.037489</v>
+        <v>2655744937.03749</v>
       </c>
       <c r="H50">
-        <v>2185108623.204825</v>
+        <v>2185108623.204826</v>
       </c>
       <c r="I50">
         <v>601753300.5976237</v>
@@ -12084,7 +12084,7 @@
         <v>11486414160.43924</v>
       </c>
       <c r="Q50">
-        <v>9090365019.601404</v>
+        <v>9090365019.601406</v>
       </c>
     </row>
     <row r="51">
@@ -12100,19 +12100,19 @@
         <v>21403399.30327405</v>
       </c>
       <c r="D51">
-        <v>1747559546.436109</v>
+        <v>1747559546.43611</v>
       </c>
       <c r="E51">
         <v>76555172.52074087</v>
       </c>
       <c r="F51">
-        <v>781508844.3469505</v>
+        <v>781508844.3469504</v>
       </c>
       <c r="G51">
         <v>2627026962.607075</v>
       </c>
       <c r="H51">
-        <v>2198741887.162555</v>
+        <v>2198741887.162556</v>
       </c>
       <c r="I51">
         <v>620217812.8110868</v>
@@ -12164,13 +12164,13 @@
         <v>798565235.144123</v>
       </c>
       <c r="G52">
-        <v>2656910947.792025</v>
+        <v>2656910947.792026</v>
       </c>
       <c r="H52">
         <v>2267720590.117834</v>
       </c>
       <c r="I52">
-        <v>646981604.3543465</v>
+        <v>646981604.3543466</v>
       </c>
       <c r="J52">
         <v>210290320.3469393</v>
@@ -12188,7 +12188,7 @@
         <v>1083060370.968748</v>
       </c>
       <c r="O52">
-        <v>7704454800.261715</v>
+        <v>7704454800.261714</v>
       </c>
       <c r="P52">
         <v>11523230758.02149</v>
@@ -12271,10 +12271,10 @@
         <v>74900937.014489</v>
       </c>
       <c r="F54">
-        <v>783885375.5282068</v>
+        <v>783885375.5282067</v>
       </c>
       <c r="G54">
-        <v>2700957604.39079</v>
+        <v>2700957604.390789</v>
       </c>
       <c r="H54">
         <v>2326433899.822443</v>
@@ -12298,7 +12298,7 @@
         <v>1124889748.347639</v>
       </c>
       <c r="O54">
-        <v>7892517664.4576</v>
+        <v>7892517664.457601</v>
       </c>
       <c r="P54">
         <v>11741786864.50612</v>
@@ -12329,7 +12329,7 @@
         <v>778690162.7457174</v>
       </c>
       <c r="G55">
-        <v>2701331990.63463</v>
+        <v>2701331990.634631</v>
       </c>
       <c r="H55">
         <v>2339702538.882089</v>
@@ -12338,7 +12338,7 @@
         <v>712438491.7429069</v>
       </c>
       <c r="J55">
-        <v>204367194.2800914</v>
+        <v>204367194.2800915</v>
       </c>
       <c r="K55">
         <v>189426031.2816209</v>
@@ -12359,7 +12359,7 @@
         <v>11873984312.77372</v>
       </c>
       <c r="Q55">
-        <v>9461047326.154312</v>
+        <v>9461047326.15431</v>
       </c>
     </row>
     <row r="56">
@@ -12381,7 +12381,7 @@
         <v>67538945.77903131</v>
       </c>
       <c r="F56">
-        <v>774724185.6631482</v>
+        <v>774724185.663148</v>
       </c>
       <c r="G56">
         <v>2712906934.031425</v>
@@ -12393,7 +12393,7 @@
         <v>741672155.5584922</v>
       </c>
       <c r="J56">
-        <v>203442409.0337897</v>
+        <v>203442409.0337898</v>
       </c>
       <c r="K56">
         <v>205834869.9618594</v>
@@ -12408,7 +12408,7 @@
         <v>1154655931.362903</v>
       </c>
       <c r="O56">
-        <v>8038700574.538186</v>
+        <v>8038700574.538187</v>
       </c>
       <c r="P56">
         <v>11906010857.61607</v>
